--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="1825">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433881759644</t>
+    <t xml:space="preserve">3.4243381023407</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">3.46986722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47331643104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34707713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981520652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637146949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324896812439</t>
+    <t xml:space="preserve">3.47331619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812517166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34707760810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981472969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28637170791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324944496155</t>
   </si>
   <si>
     <t xml:space="preserve">3.03803110122681</t>
@@ -80,70 +80,70 @@
     <t xml:space="preserve">3.13874697685242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14288592338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16496062278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736748695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564490318298</t>
+    <t xml:space="preserve">3.1428861618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425543785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1649603843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.137366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564514160156</t>
   </si>
   <si>
     <t xml:space="preserve">3.19945216178894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30430746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20911002159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20772981643677</t>
+    <t xml:space="preserve">3.30430698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20910954475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20773005485535</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631920814514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06700420379639</t>
+    <t xml:space="preserve">3.06700396537781</t>
   </si>
   <si>
     <t xml:space="preserve">3.00077986717224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9980206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114291191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151640892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046908378601</t>
+    <t xml:space="preserve">3.0021595954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802088737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837300300598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322854042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115312576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151688575745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046932220459</t>
   </si>
   <si>
     <t xml:space="preserve">3.14150619506836</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">3.11805152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531321525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18703508377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321784973145</t>
+    <t xml:space="preserve">3.23808264732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323851585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18703484535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321761131287</t>
   </si>
   <si>
     <t xml:space="preserve">3.18013715744019</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">3.19255352020264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18427538871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636054039001</t>
+    <t xml:space="preserve">3.18427634239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636125564575</t>
   </si>
   <si>
     <t xml:space="preserve">3.20635032653809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19807291030884</t>
+    <t xml:space="preserve">3.19807267189026</t>
   </si>
   <si>
     <t xml:space="preserve">3.10563468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906845092773</t>
+    <t xml:space="preserve">3.04906821250916</t>
   </si>
   <si>
     <t xml:space="preserve">3.0545871257782</t>
@@ -200,85 +200,85 @@
     <t xml:space="preserve">3.03941059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00491881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05182766914368</t>
+    <t xml:space="preserve">3.0049192905426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0518274307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.98422384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05044746398926</t>
+    <t xml:space="preserve">3.05044794082642</t>
   </si>
   <si>
     <t xml:space="preserve">3.05320739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01595664024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147507667542</t>
+    <t xml:space="preserve">3.01595640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147483825684</t>
   </si>
   <si>
     <t xml:space="preserve">3.00629854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00767850875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0256142616272</t>
+    <t xml:space="preserve">3.00767803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561402320862</t>
   </si>
   <si>
     <t xml:space="preserve">3.09873676300049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08769869804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978432655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0559663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838393211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02975296974182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01871562004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766805648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249152183533</t>
+    <t xml:space="preserve">3.08769917488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05596661567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838345527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319742202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0297532081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01871585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766781806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249104499817</t>
   </si>
   <si>
     <t xml:space="preserve">2.94421362876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93869495391846</t>
+    <t xml:space="preserve">2.93869471549988</t>
   </si>
   <si>
     <t xml:space="preserve">2.93593573570251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02235865592957</t>
+    <t xml:space="preserve">3.02235889434814</t>
   </si>
   <si>
     <t xml:space="preserve">3.02659225463867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837183952332</t>
+    <t xml:space="preserve">2.99837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98426198959351</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.99131679534912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97861814498901</t>
+    <t xml:space="preserve">2.97861838340759</t>
   </si>
   <si>
     <t xml:space="preserve">3.06892204284668</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">3.01389312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0209481716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00683808326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929114341736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03505802154541</t>
+    <t xml:space="preserve">3.02094793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00683832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671528816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03505778312683</t>
   </si>
   <si>
     <t xml:space="preserve">2.99978303909302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96450853347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714959144592</t>
+    <t xml:space="preserve">2.9645082950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714911460876</t>
   </si>
   <si>
     <t xml:space="preserve">2.80083227157593</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">2.87843704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9320547580719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702631950378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089010238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61034750938416</t>
+    <t xml:space="preserve">2.93205499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702608108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9108898639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72181630134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61034774780273</t>
   </si>
   <si>
     <t xml:space="preserve">2.67525315284729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899437904358</t>
+    <t xml:space="preserve">2.718994140625</t>
   </si>
   <si>
     <t xml:space="preserve">2.79659938812256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79518795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162830352783</t>
+    <t xml:space="preserve">2.79518842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162782669067</t>
   </si>
   <si>
     <t xml:space="preserve">2.83610725402832</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">2.87279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94475412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97438502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00542759895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02518081665039</t>
+    <t xml:space="preserve">2.94475388526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97438549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00542736053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02518105506897</t>
   </si>
   <si>
     <t xml:space="preserve">3.0421130657196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07597732543945</t>
+    <t xml:space="preserve">3.07597684860229</t>
   </si>
   <si>
     <t xml:space="preserve">3.03364706039429</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">3.07033324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05481243133545</t>
+    <t xml:space="preserve">3.05481219291687</t>
   </si>
   <si>
     <t xml:space="preserve">3.03788018226624</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">3.05199003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17333602905273</t>
+    <t xml:space="preserve">3.17333579063416</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204762458801</t>
@@ -407,151 +407,151 @@
     <t xml:space="preserve">3.15499305725098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14088273048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14793801307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10842990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149813652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241720199585</t>
+    <t xml:space="preserve">3.14088320732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843014717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149789810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241696357727</t>
   </si>
   <si>
     <t xml:space="preserve">3.13947200775146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15075993537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419678688049</t>
+    <t xml:space="preserve">3.15076017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419702529907</t>
   </si>
   <si>
     <t xml:space="preserve">3.08444333076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02800273895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01248168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02377009391785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07174396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045603752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09008717536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732284545898</t>
+    <t xml:space="preserve">3.02800321578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01248216629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02376985549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07174372673035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732260704041</t>
   </si>
   <si>
     <t xml:space="preserve">3.21002173423767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18462419509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21284413337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707677841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27774953842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351689338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130990028381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861124992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873404502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18180203437805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15358209609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217065811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16628050804138</t>
+    <t xml:space="preserve">3.1846239566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2128438949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707653999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27775001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22131013870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861077308655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18180179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1535816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217089653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16628098487854</t>
   </si>
   <si>
     <t xml:space="preserve">3.1253616809845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11125206947327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08726477622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09714198112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11548519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867573738098</t>
+    <t xml:space="preserve">3.11125183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08726501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0971417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11548495292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08867597579956</t>
   </si>
   <si>
     <t xml:space="preserve">3.07738780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06186699867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696087837219</t>
+    <t xml:space="preserve">3.06186652183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696159362793</t>
   </si>
   <si>
     <t xml:space="preserve">2.92923307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95321989059448</t>
+    <t xml:space="preserve">2.95322012901306</t>
   </si>
   <si>
     <t xml:space="preserve">2.95180892944336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93911004066467</t>
+    <t xml:space="preserve">2.93910980224609</t>
   </si>
   <si>
     <t xml:space="preserve">2.92076730728149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95886397361755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92782235145569</t>
+    <t xml:space="preserve">2.95886373519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92782211303711</t>
   </si>
   <si>
     <t xml:space="preserve">2.98002910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04493498802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622267723083</t>
+    <t xml:space="preserve">3.04493474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622315406799</t>
   </si>
   <si>
     <t xml:space="preserve">3.0195369720459</t>
@@ -560,121 +560,121 @@
     <t xml:space="preserve">2.97720694541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99555039405823</t>
+    <t xml:space="preserve">2.99554991722107</t>
   </si>
   <si>
     <t xml:space="preserve">3.0407018661499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01812624931335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96309661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92641115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849511146545</t>
+    <t xml:space="preserve">3.01812601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9630970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92641091346741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849534988403</t>
   </si>
   <si>
     <t xml:space="preserve">2.87138247489929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8572723865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86856007575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604228973389</t>
+    <t xml:space="preserve">2.85727214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86856031417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604205131531</t>
   </si>
   <si>
     <t xml:space="preserve">2.88690328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89819145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303902626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034013748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84457349777222</t>
+    <t xml:space="preserve">2.89819073677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303950309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034061431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457325935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.85021710395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78390026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377722740173</t>
+    <t xml:space="preserve">2.78390049934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377746582031</t>
   </si>
   <si>
     <t xml:space="preserve">2.82340836524963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75568056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132440567017</t>
+    <t xml:space="preserve">2.75568008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132464408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.80929827690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89254689216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89395833015442</t>
+    <t xml:space="preserve">2.8925473690033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893958568573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89960241317749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86009430885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665698051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831400871277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91230058670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94052147865295</t>
+    <t xml:space="preserve">2.86009383201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665745735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91230082511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9405210018158</t>
   </si>
   <si>
     <t xml:space="preserve">3.09431982040405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08020997047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303141593933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560822486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585381507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523840904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511632919312</t>
+    <t xml:space="preserve">3.08021020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10560774803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585429191589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511609077454</t>
   </si>
   <si>
     <t xml:space="preserve">3.13806104660034</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">3.17051386833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20437741279602</t>
+    <t xml:space="preserve">3.20437788963318</t>
   </si>
   <si>
     <t xml:space="preserve">3.19591188430786</t>
@@ -695,37 +695,37 @@
     <t xml:space="preserve">3.12253999710083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278606414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290909767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06751084327698</t>
+    <t xml:space="preserve">3.09573101997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06751108169556</t>
   </si>
   <si>
     <t xml:space="preserve">3.11830687522888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17897987365723</t>
+    <t xml:space="preserve">3.17897963523865</t>
   </si>
   <si>
     <t xml:space="preserve">3.1366503238678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07456612586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10701870918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2452974319458</t>
+    <t xml:space="preserve">3.07456564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1070191860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855341911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529695510864</t>
   </si>
   <si>
     <t xml:space="preserve">3.26646184921265</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">3.25376296043396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25094056129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891514778137</t>
+    <t xml:space="preserve">3.25094032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891467094421</t>
   </si>
   <si>
     <t xml:space="preserve">3.31443572044373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38357472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228655815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37652015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4456582069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41461682319641</t>
+    <t xml:space="preserve">3.38357448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3722870349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651944160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44565868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41461706161499</t>
   </si>
   <si>
     <t xml:space="preserve">3.44283676147461</t>
@@ -764,31 +764,31 @@
     <t xml:space="preserve">3.40756154060364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4005069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657727241516</t>
+    <t xml:space="preserve">3.40050673484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657751083374</t>
   </si>
   <si>
     <t xml:space="preserve">3.51338672637939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47105646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160666465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47811150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798799514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633144378662</t>
+    <t xml:space="preserve">3.47105598449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47811126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633192062378</t>
   </si>
   <si>
     <t xml:space="preserve">3.49222159385681</t>
@@ -800,118 +800,118 @@
     <t xml:space="preserve">3.53455185890198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52749633789062</t>
+    <t xml:space="preserve">3.5274965763092</t>
   </si>
   <si>
     <t xml:space="preserve">3.54866170883179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51056480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099173545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568379402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5839364528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209903717041</t>
+    <t xml:space="preserve">3.51056504249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099102020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568427085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209808349609</t>
   </si>
   <si>
     <t xml:space="preserve">3.55924415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62273812294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66154193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6650698184967</t>
+    <t xml:space="preserve">3.62273931503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.650958776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506910324097</t>
   </si>
   <si>
     <t xml:space="preserve">3.61921167373657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804677963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7375226020813</t>
+    <t xml:space="preserve">3.63332152366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804606437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73752212524414</t>
   </si>
   <si>
     <t xml:space="preserve">3.6866717338562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72299385070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71936130523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195948600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285593032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85012149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88644218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101698875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648871421814</t>
+    <t xml:space="preserve">3.72299432754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71936106681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124653816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195996284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285616874695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85012054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8864426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101746559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648823738098</t>
   </si>
   <si>
     <t xml:space="preserve">3.82469487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8392231464386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451209068298</t>
+    <t xml:space="preserve">3.83922386169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451113700867</t>
   </si>
   <si>
     <t xml:space="preserve">3.90097093582153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94455766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9263961315155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913199424744</t>
+    <t xml:space="preserve">3.94455742835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9263973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913223266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.81016659736633</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">3.61330151557922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62201905250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313129425049</t>
+    <t xml:space="preserve">3.62201881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313153266907</t>
   </si>
   <si>
     <t xml:space="preserve">3.59150862693787</t>
@@ -938,58 +938,58 @@
     <t xml:space="preserve">3.62492418289185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67214369773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030356407166</t>
+    <t xml:space="preserve">3.67214298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030380249023</t>
   </si>
   <si>
     <t xml:space="preserve">3.63218879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65035009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572947502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662615776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191343307495</t>
+    <t xml:space="preserve">3.65035033226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71572875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7266263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191319465637</t>
   </si>
   <si>
     <t xml:space="preserve">3.96635103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93366074562073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352354049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04989051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07894802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182132720947</t>
+    <t xml:space="preserve">3.93366050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9590859413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998333930969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182204246521</t>
   </si>
   <si>
     <t xml:space="preserve">3.91549968719482</t>
@@ -998,70 +998,70 @@
     <t xml:space="preserve">4.00993728637695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177575111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04262685775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10437393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271824836731</t>
+    <t xml:space="preserve">3.99540734291077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446508407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04262638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10437345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271872520447</t>
   </si>
   <si>
     <t xml:space="preserve">3.86464929580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89733862876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9881443977356</t>
+    <t xml:space="preserve">3.89733910560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98814344406128</t>
   </si>
   <si>
     <t xml:space="preserve">3.95545411109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93002843856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01720094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88280940055847</t>
+    <t xml:space="preserve">3.93002867698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01720142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88281059265137</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06805229187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14796018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625940322876</t>
+    <t xml:space="preserve">4.0680513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14795970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0462589263916</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11527061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1080060005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12253427505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18065023422241</t>
+    <t xml:space="preserve">4.11527013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10800552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12253522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18064975738525</t>
   </si>
   <si>
     <t xml:space="preserve">4.15885639190674</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">4.18791437149048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1661205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338562011719</t>
+    <t xml:space="preserve">4.16612148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338514328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14069557189941</t>
+    <t xml:space="preserve">4.14069604873657</t>
   </si>
   <si>
     <t xml:space="preserve">4.12979888916016</t>
@@ -1088,130 +1088,130 @@
     <t xml:space="preserve">4.24602890014648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22060441970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26055765151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2169713973999</t>
+    <t xml:space="preserve">4.22060298919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26055812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21697092056274</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26419019699097</t>
+    <t xml:space="preserve">4.26418972015381</t>
   </si>
   <si>
     <t xml:space="preserve">4.27508735656738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24239778518677</t>
+    <t xml:space="preserve">4.24239683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17701768875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08984518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30777597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42763805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51481056213379</t>
+    <t xml:space="preserve">4.08984470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30777549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29688024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4276385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51481151580811</t>
   </si>
   <si>
     <t xml:space="preserve">4.5402364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60198402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929397583008</t>
+    <t xml:space="preserve">4.60198354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59835243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72184562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929349899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.56202983856201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62014532089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59471940994263</t>
+    <t xml:space="preserve">4.62014484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59471988677979</t>
   </si>
   <si>
     <t xml:space="preserve">4.60924768447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4893856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844310760498</t>
+    <t xml:space="preserve">4.48938608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669603347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844358444214</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207565307617</t>
+    <t xml:space="preserve">4.52207469940186</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49301767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50391530990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46032857894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306444168091</t>
+    <t xml:space="preserve">4.49301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50391435623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49665021896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46032810211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306396484375</t>
   </si>
   <si>
     <t xml:space="preserve">4.4675931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47848892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750204086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53660440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315654754639</t>
+    <t xml:space="preserve">4.4784893989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5366039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315559387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.39131641387939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42037487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29324722290039</t>
+    <t xml:space="preserve">4.42037439346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29324817657471</t>
   </si>
   <si>
     <t xml:space="preserve">4.40947771072388</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">4.51117897033691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42400646209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140851974487</t>
+    <t xml:space="preserve">4.42400693893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140804290771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">4.20607566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12616729736328</t>
+    <t xml:space="preserve">4.12616634368896</t>
   </si>
   <si>
     <t xml:space="preserve">4.23150062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14432764053345</t>
+    <t xml:space="preserve">4.14432811737061</t>
   </si>
   <si>
     <t xml:space="preserve">3.97361469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94092583656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9772469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258104324341</t>
+    <t xml:space="preserve">3.94092559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724652290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">4.169753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44579935073853</t>
+    <t xml:space="preserve">4.44579982757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.40584564208984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4167423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108781814575</t>
+    <t xml:space="preserve">4.41674089431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108734130859</t>
   </si>
   <si>
     <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55113315582275</t>
+    <t xml:space="preserve">4.55113363265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.5765585899353</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53297185897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67825984954834</t>
+    <t xml:space="preserve">4.52570724487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53297233581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67825937271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.6492018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67099523544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64557027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283489227295</t>
+    <t xml:space="preserve">4.67099475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64556980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283393859863</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816774368286</t>
@@ -1310,79 +1310,79 @@
     <t xml:space="preserve">4.75090360641479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76180028915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72547817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68552446365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911024093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65646696090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84534072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8199143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83807611465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88166236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8489727973938</t>
+    <t xml:space="preserve">4.76179933547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68552398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65646600723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84534025192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81991529464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8380765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88166284561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">4.91798448562622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89255905151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95430564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94704151153564</t>
+    <t xml:space="preserve">4.89255857467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95430612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9470419883728</t>
   </si>
   <si>
     <t xml:space="preserve">4.93977737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93251276016235</t>
+    <t xml:space="preserve">4.9325122833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.99062776565552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94340896606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7330756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888193130493</t>
+    <t xml:space="preserve">4.94340944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713266372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73307657241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888145446777</t>
   </si>
   <si>
     <t xml:space="preserve">4.86018848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82654094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75176858901978</t>
+    <t xml:space="preserve">4.82654142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
     <t xml:space="preserve">4.6508264541626</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">4.49380540847778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62091732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699670791626</t>
+    <t xml:space="preserve">4.62091779708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699718475342</t>
   </si>
   <si>
     <t xml:space="preserve">4.63587236404419</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">4.7218599319458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70690536499023</t>
+    <t xml:space="preserve">4.70690584182739</t>
   </si>
   <si>
     <t xml:space="preserve">4.57979297637939</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">4.75924587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83027935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93496036529541</t>
+    <t xml:space="preserve">4.83027982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496084213257</t>
   </si>
   <si>
     <t xml:space="preserve">4.85644960403442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81532526016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94243812561035</t>
+    <t xml:space="preserve">4.8153247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94243764877319</t>
   </si>
   <si>
     <t xml:space="preserve">4.91252899169922</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">4.91626739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90505170822144</t>
+    <t xml:space="preserve">4.90505123138428</t>
   </si>
   <si>
     <t xml:space="preserve">4.88262033462524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93869972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486902236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01721000671387</t>
+    <t xml:space="preserve">4.93869924545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216409683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01721048355103</t>
   </si>
   <si>
     <t xml:space="preserve">5.13684511184692</t>
@@ -1460,40 +1460,40 @@
     <t xml:space="preserve">5.05833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98356199264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89757490158081</t>
+    <t xml:space="preserve">4.98356246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89757537841797</t>
   </si>
   <si>
     <t xml:space="preserve">5.12936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24900388717651</t>
+    <t xml:space="preserve">5.24900341033936</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31629800796509</t>
+    <t xml:space="preserve">5.3162989616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34246921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09945917129517</t>
+    <t xml:space="preserve">5.34246873855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09945964813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.0134711265564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17796993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2004017829895</t>
+    <t xml:space="preserve">5.17797040939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20040225982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.23404884338379</t>
@@ -1505,73 +1505,73 @@
     <t xml:space="preserve">5.20787858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21535634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666290283203</t>
+    <t xml:space="preserve">5.21535587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666242599487</t>
   </si>
   <si>
     <t xml:space="preserve">5.11815214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04337978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11067533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17049312591553</t>
+    <t xml:space="preserve">5.04338026046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99851751327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11067485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17049169540405</t>
   </si>
   <si>
     <t xml:space="preserve">5.047119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982358932495</t>
+    <t xml:space="preserve">5.11441373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982406616211</t>
   </si>
   <si>
     <t xml:space="preserve">4.95739221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0396409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05459594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18544673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0957202911377</t>
+    <t xml:space="preserve">5.03964138031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05459642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076620101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18544721603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09572076797485</t>
   </si>
   <si>
     <t xml:space="preserve">5.2116174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88635778427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672315597534</t>
+    <t xml:space="preserve">4.88635873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.920006275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77420091629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672267913818</t>
   </si>
   <si>
     <t xml:space="preserve">4.68073558807373</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">4.67325782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68447399139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839460372925</t>
+    <t xml:space="preserve">4.68447351455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.5685772895813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58727073669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69568967819214</t>
+    <t xml:space="preserve">4.58727025985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6956901550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.56110000610352</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79289388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766576766968</t>
+    <t xml:space="preserve">4.79289245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766529083252</t>
   </si>
   <si>
     <t xml:space="preserve">4.78915500640869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78167772293091</t>
+    <t xml:space="preserve">4.78167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">4.7779393196106</t>
@@ -1637,34 +1637,34 @@
     <t xml:space="preserve">4.87140417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83775663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68821239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71812105178833</t>
+    <t xml:space="preserve">4.83775568008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68821287155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74055290222168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60222482681274</t>
+    <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52371406555176</t>
+    <t xml:space="preserve">4.5237135887146</t>
   </si>
   <si>
     <t xml:space="preserve">4.51997518539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48632717132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903257369995</t>
+    <t xml:space="preserve">4.486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903305053711</t>
   </si>
   <si>
     <t xml:space="preserve">4.46015787124634</t>
@@ -1673,58 +1673,58 @@
     <t xml:space="preserve">4.64334917068481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66204214096069</t>
+    <t xml:space="preserve">4.66204261779785</t>
   </si>
   <si>
     <t xml:space="preserve">4.65456485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76298475265503</t>
+    <t xml:space="preserve">4.76298427581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.73681449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86392688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730182647705</t>
+    <t xml:space="preserve">4.86392736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730087280273</t>
   </si>
   <si>
     <t xml:space="preserve">5.14806127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927743911743</t>
+    <t xml:space="preserve">5.15927696228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.21909475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22657251358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18918561935425</t>
+    <t xml:space="preserve">5.22657155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">5.15179920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20414066314697</t>
+    <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
     <t xml:space="preserve">5.37237739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16675472259521</t>
+    <t xml:space="preserve">5.16675424575806</t>
   </si>
   <si>
     <t xml:space="preserve">5.34620714187622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09019088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87335062026978</t>
+    <t xml:space="preserve">6.09019041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87335109710693</t>
   </si>
   <si>
     <t xml:space="preserve">5.79484033584595</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">5.76119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353330612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79110193252563</t>
+    <t xml:space="preserve">5.81353282928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79110145568848</t>
   </si>
   <si>
     <t xml:space="preserve">5.80231714248657</t>
@@ -1751,52 +1751,52 @@
     <t xml:space="preserve">5.87708950042725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92195272445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167917251587</t>
+    <t xml:space="preserve">5.92195320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924875259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167964935303</t>
   </si>
   <si>
     <t xml:space="preserve">6.02663373947144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96307706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00794076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9256911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93316841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699863433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94064521789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07897472381592</t>
+    <t xml:space="preserve">5.96307754516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0079402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92569160461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93316793441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699815750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94064569473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07897424697876</t>
   </si>
   <si>
     <t xml:space="preserve">5.9369068145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95933866500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89952087402344</t>
+    <t xml:space="preserve">5.95933818817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8995213508606</t>
   </si>
   <si>
     <t xml:space="preserve">5.89578247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8808274269104</t>
+    <t xml:space="preserve">5.88082838058472</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812297821045</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">5.95560073852539</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97429323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91362047195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.840660572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75234079360962</t>
+    <t xml:space="preserve">5.97429275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9136209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84066104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7523398399353</t>
   </si>
   <si>
     <t xml:space="preserve">5.694739818573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71778011322021</t>
+    <t xml:space="preserve">5.71778059005737</t>
   </si>
   <si>
     <t xml:space="preserve">5.68322038650513</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">5.66402006149292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66786050796509</t>
+    <t xml:space="preserve">5.66786003112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.7830605506897</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002025604248</t>
+    <t xml:space="preserve">5.76002073287964</t>
   </si>
   <si>
     <t xml:space="preserve">5.87522077560425</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">5.69858026504517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64481973648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60642051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77538061141968</t>
+    <t xml:space="preserve">5.64482021331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60641956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77538013458252</t>
   </si>
   <si>
     <t xml:space="preserve">5.72162008285522</t>
@@ -1871,40 +1871,40 @@
     <t xml:space="preserve">5.81762027740479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78690004348755</t>
+    <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970106124878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0557017326355</t>
+    <t xml:space="preserve">6.05570125579834</t>
   </si>
   <si>
     <t xml:space="preserve">6.28226280212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17474174499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09026193618774</t>
+    <t xml:space="preserve">6.17474222183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09026145935059</t>
   </si>
   <si>
     <t xml:space="preserve">6.12866163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22850179672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19394159317017</t>
+    <t xml:space="preserve">6.22850227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19394207000732</t>
   </si>
   <si>
     <t xml:space="preserve">6.06722164154053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10178184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25154256820679</t>
+    <t xml:space="preserve">6.10178136825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25154304504395</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090177536011</t>
@@ -1919,37 +1919,37 @@
     <t xml:space="preserve">6.39746284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43586349487305</t>
+    <t xml:space="preserve">6.43586254119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.4627423286438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38210296630859</t>
+    <t xml:space="preserve">6.38210248947144</t>
   </si>
   <si>
     <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44738292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52802276611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58946323394775</t>
+    <t xml:space="preserve">6.44738388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5280237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410383224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58946371078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.62018299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64322280883789</t>
+    <t xml:space="preserve">6.64322376251221</t>
   </si>
   <si>
     <t xml:space="preserve">6.62786388397217</t>
@@ -1958,22 +1958,22 @@
     <t xml:space="preserve">6.66626358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80450439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138513565063</t>
+    <t xml:space="preserve">6.80450391769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138465881348</t>
   </si>
   <si>
     <t xml:space="preserve">6.83522367477417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78914403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76610374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114490509033</t>
+    <t xml:space="preserve">6.78914451599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76610422134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114395141602</t>
   </si>
   <si>
     <t xml:space="preserve">6.98882532119751</t>
@@ -1982,85 +1982,85 @@
     <t xml:space="preserve">6.88514518737793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68930435180664</t>
+    <t xml:space="preserve">6.68930339813232</t>
   </si>
   <si>
     <t xml:space="preserve">6.63554382324219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61634302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642534255981</t>
+    <t xml:space="preserve">6.61634349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338312149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298448562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642629623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.0080246925354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99266481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786485671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714557647705</t>
+    <t xml:space="preserve">6.9926643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10402584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0617847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330465316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714605331421</t>
   </si>
   <si>
     <t xml:space="preserve">7.00034475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96578407287598</t>
+    <t xml:space="preserve">6.96578454971313</t>
   </si>
   <si>
     <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02722454071045</t>
+    <t xml:space="preserve">7.02722501754761</t>
   </si>
   <si>
     <t xml:space="preserve">7.01186561584473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94274473190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04258489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7507438659668</t>
+    <t xml:space="preserve">6.94274520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0425853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074434280396</t>
   </si>
   <si>
     <t xml:space="preserve">6.93506479263306</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">6.90434408187866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02338600158691</t>
+    <t xml:space="preserve">7.02338552474976</t>
   </si>
   <si>
     <t xml:space="preserve">6.97346496582031</t>
@@ -2078,34 +2078,34 @@
     <t xml:space="preserve">7.15778493881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602479934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16930627822876</t>
+    <t xml:space="preserve">7.16546487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2960262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16930532455444</t>
   </si>
   <si>
     <t xml:space="preserve">7.3113865852356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27682685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19234609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010452270508</t>
+    <t xml:space="preserve">7.27682638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850612640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706565856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698574066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19234561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010595321655</t>
   </si>
   <si>
     <t xml:space="preserve">7.26914644241333</t>
@@ -2114,103 +2114,103 @@
     <t xml:space="preserve">7.34210586547852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43426561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2806658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11938524246216</t>
+    <t xml:space="preserve">7.43426609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730590820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658567428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938571929932</t>
   </si>
   <si>
     <t xml:space="preserve">7.2230658531189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11554622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06562471389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08866405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98498487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7737832069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066347122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92738485336304</t>
+    <t xml:space="preserve">7.11554527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06562423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08866500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9849853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77378416061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066299438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88898420333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92738580703735</t>
   </si>
   <si>
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202402114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290409088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8621039390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84674406051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0809850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03106498718262</t>
+    <t xml:space="preserve">6.912024974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290456771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210489273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08098459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03106451034546</t>
   </si>
   <si>
     <t xml:space="preserve">7.05794429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75842380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218385696411</t>
+    <t xml:space="preserve">6.75842428207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218338012695</t>
   </si>
   <si>
     <t xml:space="preserve">6.81602430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87746429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306344985962</t>
+    <t xml:space="preserve">6.87746477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306440353394</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72002363204956</t>
+    <t xml:space="preserve">6.7200231552124</t>
   </si>
   <si>
     <t xml:space="preserve">6.89282417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79682350158691</t>
+    <t xml:space="preserve">6.79682445526123</t>
   </si>
   <si>
     <t xml:space="preserve">6.70466327667236</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">6.67778348922729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314624786377</t>
+    <t xml:space="preserve">6.7853045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2077054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314529418945</t>
   </si>
   <si>
     <t xml:space="preserve">7.22690486907959</t>
@@ -2246,28 +2246,28 @@
     <t xml:space="preserve">7.20002555847168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11170673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2576265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6646671295166</t>
+    <t xml:space="preserve">7.1117057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826684951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466665267944</t>
   </si>
   <si>
     <t xml:space="preserve">7.83362770080566</t>
@@ -2279,34 +2279,34 @@
     <t xml:space="preserve">8.00258827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17922878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434745788574</t>
+    <t xml:space="preserve">8.17922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434698104858</t>
   </si>
   <si>
     <t xml:space="preserve">7.77218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73378801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186658859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858749389648</t>
+    <t xml:space="preserve">7.73378658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482648849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858654022217</t>
   </si>
   <si>
     <t xml:space="preserve">7.68002796173096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3689866065979</t>
+    <t xml:space="preserve">7.36898708343506</t>
   </si>
   <si>
     <t xml:space="preserve">6.91970539093018</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27458190917969</t>
+    <t xml:space="preserve">6.274582862854</t>
   </si>
   <si>
     <t xml:space="preserve">5.77154016494751</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">6.26690196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33602285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922445297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938669204712</t>
+    <t xml:space="preserve">6.33602333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1539454460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938716888428</t>
   </si>
   <si>
     <t xml:space="preserve">7.78754806518555</t>
@@ -2345,19 +2345,19 @@
     <t xml:space="preserve">8.2717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88021850585938</t>
+    <t xml:space="preserve">7.88021755218506</t>
   </si>
   <si>
     <t xml:space="preserve">7.57023000717163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64364767074585</t>
+    <t xml:space="preserve">7.64364814758301</t>
   </si>
   <si>
     <t xml:space="preserve">8.13718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35335731506348</t>
+    <t xml:space="preserve">8.35335540771484</t>
   </si>
   <si>
     <t xml:space="preserve">8.72860527038574</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">9.03043460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95701789855957</t>
+    <t xml:space="preserve">8.95701694488525</t>
   </si>
   <si>
     <t xml:space="preserve">8.70413208007812</t>
@@ -2378,58 +2378,58 @@
     <t xml:space="preserve">7.99442481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8312726020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969720840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81903600692749</t>
+    <t xml:space="preserve">7.83127117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969625473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81903648376465</t>
   </si>
   <si>
     <t xml:space="preserve">7.79864168167114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87613868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68035650253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5090479850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70482921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377511978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653253555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9454779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85574388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010829925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85739850997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78709697723389</t>
+    <t xml:space="preserve">7.87613821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679845809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035697937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50904846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496816635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70482969284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94547843933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8557448387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146295547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85739803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78709506988525</t>
   </si>
   <si>
     <t xml:space="preserve">7.75814723968506</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">7.600998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58032274246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5182900428772</t>
+    <t xml:space="preserve">7.580322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51829051971436</t>
   </si>
   <si>
     <t xml:space="preserve">7.73333501815796</t>
@@ -2459,175 +2459,175 @@
     <t xml:space="preserve">7.5555100440979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53483152389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45212316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4934778213501</t>
+    <t xml:space="preserve">7.53483247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212268829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49347686767578</t>
   </si>
   <si>
     <t xml:space="preserve">7.63408327102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249681472778</t>
+    <t xml:space="preserve">7.40249729156494</t>
   </si>
   <si>
     <t xml:space="preserve">7.40663242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36941337585449</t>
+    <t xml:space="preserve">7.36941242218018</t>
   </si>
   <si>
     <t xml:space="preserve">7.58445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48520565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656030654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7540111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919988632202</t>
+    <t xml:space="preserve">7.48520612716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235353469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656173706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401258468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919893264771</t>
   </si>
   <si>
     <t xml:space="preserve">7.37354850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44385147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460115432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73746824264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69198083877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77468919754028</t>
+    <t xml:space="preserve">7.44385290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768411636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73746967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69198036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77468872070312</t>
   </si>
   <si>
     <t xml:space="preserve">7.72506332397461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68784427642822</t>
+    <t xml:space="preserve">7.6878457069397</t>
   </si>
   <si>
     <t xml:space="preserve">7.67543792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62167692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438623428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71265697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62581300735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242612838745</t>
+    <t xml:space="preserve">7.6216778755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71265745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242517471313</t>
   </si>
   <si>
     <t xml:space="preserve">7.42317485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33632898330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3652777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08406448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02203273773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95586538314819</t>
+    <t xml:space="preserve">7.33632946014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36527729034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25775527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08406543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02203321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067855834961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09647178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07165908813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534940719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17091083526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03443956375122</t>
+    <t xml:space="preserve">7.06752347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09647226333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07165861129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534845352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17091035842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.98894929885864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93932390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05511713027954</t>
+    <t xml:space="preserve">6.93932437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05511665344238</t>
   </si>
   <si>
     <t xml:space="preserve">6.91864633560181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90624046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9517297744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89796924591064</t>
+    <t xml:space="preserve">6.90623998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95173025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89796876907349</t>
   </si>
   <si>
     <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93105268478394</t>
+    <t xml:space="preserve">6.93105316162109</t>
   </si>
   <si>
     <t xml:space="preserve">6.82353067398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75322723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78217554092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.947594165802</t>
+    <t xml:space="preserve">6.75322771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78217506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324554443359</t>
@@ -2636,25 +2636,25 @@
     <t xml:space="preserve">7.43558073043823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35700798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48934125900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59272909164429</t>
+    <t xml:space="preserve">7.35700702667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48934173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59272861480713</t>
   </si>
   <si>
     <t xml:space="preserve">7.80777311325073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60927057266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71679210662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092819213867</t>
+    <t xml:space="preserve">7.60926961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71679162979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092866897583</t>
   </si>
   <si>
     <t xml:space="preserve">7.84085702896118</t>
@@ -2666,70 +2666,70 @@
     <t xml:space="preserve">7.82845115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8367223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912824630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67957305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61754179000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60513496398926</t>
+    <t xml:space="preserve">7.83672094345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912729263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67957401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61754131317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60513401031494</t>
   </si>
   <si>
     <t xml:space="preserve">7.59686470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54723834991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55137348175049</t>
+    <t xml:space="preserve">7.57205104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54723882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55137300491333</t>
   </si>
   <si>
     <t xml:space="preserve">8.03522396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20064353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15515327453613</t>
+    <t xml:space="preserve">8.20064258575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15515232086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.47772026062012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14688205718994</t>
+    <t xml:space="preserve">8.14688301086426</t>
   </si>
   <si>
     <t xml:space="preserve">8.31230068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56042861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40328121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41155242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28748893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33711433410645</t>
+    <t xml:space="preserve">8.56042957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40328025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41155338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33711338043213</t>
   </si>
   <si>
     <t xml:space="preserve">8.6100549697876</t>
@@ -2738,19 +2738,19 @@
     <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55215835571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25026988983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59351253509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92434978485107</t>
+    <t xml:space="preserve">8.55215930938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25026893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59351444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88299560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92435073852539</t>
   </si>
   <si>
     <t xml:space="preserve">8.99051856994629</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">8.8002872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81682777404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73411846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35365581512451</t>
+    <t xml:space="preserve">8.81682872772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73412036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">8.18823719024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13860988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24199867248535</t>
+    <t xml:space="preserve">8.13861083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32057285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545623779297</t>
+    <t xml:space="preserve">8.22545528411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.27921772003174</t>
@@ -2801,40 +2801,40 @@
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9566502571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86980533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85326242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875411987305</t>
+    <t xml:space="preserve">7.95664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86980485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875364303589</t>
   </si>
   <si>
     <t xml:space="preserve">7.74574089050293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66303205490112</t>
+    <t xml:space="preserve">7.66303157806396</t>
   </si>
   <si>
     <t xml:space="preserve">7.65476083755493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5141544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4479866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219289779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35287094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46866369247437</t>
+    <t xml:space="preserve">7.51415395736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44798707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219385147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35287189483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46866416931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43971633911133</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">7.43144416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82017946243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38182020187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20399475097656</t>
+    <t xml:space="preserve">7.50588417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82017993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76228284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38181972503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2039942741394</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338739395142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02616834640503</t>
+    <t xml:space="preserve">7.02616882324219</t>
   </si>
   <si>
     <t xml:space="preserve">7.09233617782593</t>
@@ -2873,34 +2873,34 @@
     <t xml:space="preserve">7.28670406341553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12955617904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518877029419</t>
+    <t xml:space="preserve">7.12955474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518781661987</t>
   </si>
   <si>
     <t xml:space="preserve">7.04271078109741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16263914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2991099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5389666557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70025014877319</t>
+    <t xml:space="preserve">7.16263961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29910945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70025205612183</t>
   </si>
   <si>
     <t xml:space="preserve">7.80281066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03108882904053</t>
+    <t xml:space="preserve">8.03108787536621</t>
   </si>
   <si>
     <t xml:space="preserve">7.88386535644531</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">8.01123905181885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81935358047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79454040527344</t>
+    <t xml:space="preserve">7.8193531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77138137817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453992843628</t>
   </si>
   <si>
     <t xml:space="preserve">7.70190525054932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273603439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619455337524</t>
+    <t xml:space="preserve">7.86732482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619407653809</t>
   </si>
   <si>
     <t xml:space="preserve">7.69694185256958</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635124206543</t>
+    <t xml:space="preserve">7.97319316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635219573975</t>
   </si>
   <si>
     <t xml:space="preserve">8.01785564422607</t>
@@ -2951,88 +2951,88 @@
     <t xml:space="preserve">7.99965953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02281665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05094051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003366470337</t>
+    <t xml:space="preserve">8.02281761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05093955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003461837769</t>
   </si>
   <si>
     <t xml:space="preserve">7.8805570602417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86897754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82431602478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371608734131</t>
+    <t xml:space="preserve">7.86897802352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8243145942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371513366699</t>
   </si>
   <si>
     <t xml:space="preserve">8.01289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81604433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63904571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66055011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73498916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79480361938477</t>
+    <t xml:space="preserve">7.84416627883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81604385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63904523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66054964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73498964309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79480504989624</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967666625977</t>
+    <t xml:space="preserve">7.78967714309692</t>
   </si>
   <si>
     <t xml:space="preserve">7.80847549438477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85291051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8238582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404190063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89221811294556</t>
+    <t xml:space="preserve">7.85291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82385683059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404237747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89221715927124</t>
   </si>
   <si>
     <t xml:space="preserve">7.94007015228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98963117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09388160705566</t>
+    <t xml:space="preserve">7.98963165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09388065338135</t>
   </si>
   <si>
     <t xml:space="preserve">8.18445873260498</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">8.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39808464050293</t>
+    <t xml:space="preserve">8.39808654785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.38099479675293</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">8.46302795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21180152893066</t>
+    <t xml:space="preserve">8.44252014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2118034362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.36390495300293</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">8.31947135925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2442741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1912956237793</t>
+    <t xml:space="preserve">8.24427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19129467010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.12806224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09900760650635</t>
+    <t xml:space="preserve">8.09900856018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
@@ -3098,19 +3098,19 @@
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877704620361</t>
+    <t xml:space="preserve">8.35877895355225</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45619201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44081020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986389160156</t>
+    <t xml:space="preserve">8.45619106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44081115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46986293792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.40663051605225</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644687652588</t>
+    <t xml:space="preserve">8.46644592285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">8.32630729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24256610870361</t>
+    <t xml:space="preserve">8.24256420135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">8.21863842010498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17420387268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28187370300293</t>
+    <t xml:space="preserve">8.17420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28187274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
@@ -3158,34 +3158,34 @@
     <t xml:space="preserve">8.35365104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45277404785156</t>
+    <t xml:space="preserve">8.45277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42030239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50233459472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896343231201</t>
+    <t xml:space="preserve">8.50404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42030334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50233554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6006031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6347827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6262378692627</t>
+    <t xml:space="preserve">8.60060214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63478374481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62623882293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.61769390106201</t>
@@ -3203,10 +3203,10 @@
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051128387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5382251739502</t>
+    <t xml:space="preserve">8.63051223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822326660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143329620361</t>
+    <t xml:space="preserve">8.33143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.36561393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23401927947998</t>
+    <t xml:space="preserve">8.2340202331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.31434440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40492153167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30579948425293</t>
+    <t xml:space="preserve">8.40492248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30579853057861</t>
   </si>
   <si>
     <t xml:space="preserve">8.49720859527588</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459831237793</t>
+    <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.2323112487793</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">8.20838451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17933082580566</t>
+    <t xml:space="preserve">8.1793327331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08875370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475812911987</t>
+    <t xml:space="preserve">8.07166385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08875465393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475860595703</t>
   </si>
   <si>
     <t xml:space="preserve">8.23914813995361</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">8.31776237487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">8.2545280456543</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">8.26478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25111103057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31605243682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21692943572998</t>
+    <t xml:space="preserve">8.36048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2511100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31605434417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2169303894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">8.43055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32972621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45106410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44935512542725</t>
+    <t xml:space="preserve">8.32972526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45106601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56642246246338</t>
+    <t xml:space="preserve">8.5664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.50575351715088</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47670078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02358436584473</t>
+    <t xml:space="preserve">8.47669982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02358531951904</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
@@ -3362,40 +3362,40 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704639434814</t>
+    <t xml:space="preserve">8.82704734802246</t>
   </si>
   <si>
     <t xml:space="preserve">8.71168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65614604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72023391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72450733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63905620574951</t>
+    <t xml:space="preserve">8.65614700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72023487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72450637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6390552520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.6091480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69460010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75441455841064</t>
+    <t xml:space="preserve">8.69459915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75441551208496</t>
   </si>
   <si>
     <t xml:space="preserve">8.77150535583496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88686180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88259029388428</t>
+    <t xml:space="preserve">8.88686275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88259124755859</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531490325928</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">8.92104244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98940467834473</t>
+    <t xml:space="preserve">8.98940372467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612533569336</t>
+    <t xml:space="preserve">9.12612438201904</t>
   </si>
   <si>
     <t xml:space="preserve">9.20303058624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212928771973</t>
+    <t xml:space="preserve">9.03212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98513126373291</t>
@@ -3440,67 +3440,67 @@
     <t xml:space="preserve">8.28870868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26136493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15882301330566</t>
+    <t xml:space="preserve">8.26136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1588249206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20667552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35706901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454923629761</t>
+    <t xml:space="preserve">8.2066764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35706806182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78455066680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.81873083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8136043548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81018590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12635231018066</t>
+    <t xml:space="preserve">7.81360292434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8101863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12635326385498</t>
   </si>
   <si>
     <t xml:space="preserve">7.8802547454834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71106290817261</t>
+    <t xml:space="preserve">7.71106195449829</t>
   </si>
   <si>
     <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61364889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54699611663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45129299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58459568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953851699829</t>
+    <t xml:space="preserve">7.61364841461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54699754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45129346847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58459711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953756332397</t>
   </si>
   <si>
     <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58288669586182</t>
+    <t xml:space="preserve">7.58288621902466</t>
   </si>
   <si>
     <t xml:space="preserve">7.48376417160034</t>
@@ -3509,19 +3509,19 @@
     <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556676864624</t>
+    <t xml:space="preserve">7.69055557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556629180908</t>
   </si>
   <si>
     <t xml:space="preserve">7.5657958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60510396957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78625965118408</t>
+    <t xml:space="preserve">7.6051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78625917434692</t>
   </si>
   <si>
     <t xml:space="preserve">7.56237888336182</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">7.77087736129761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62561225891113</t>
+    <t xml:space="preserve">7.62561178207397</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
@@ -3545,55 +3545,55 @@
     <t xml:space="preserve">7.9178524017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07508277893066</t>
+    <t xml:space="preserve">7.95545244216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07508182525635</t>
   </si>
   <si>
     <t xml:space="preserve">8.14173316955566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20325756072998</t>
+    <t xml:space="preserve">8.2032585144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.2288932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50062656402588</t>
+    <t xml:space="preserve">8.48182582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50062561035156</t>
   </si>
   <si>
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5433521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5578784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68178176879883</t>
+    <t xml:space="preserve">8.54335117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55787754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68178081512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.68605422973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73732471466064</t>
+    <t xml:space="preserve">8.73732376098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93813419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404537200928</t>
+    <t xml:space="preserve">8.97658538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93813323974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404441833496</t>
   </si>
   <si>
     <t xml:space="preserve">8.89113521575928</t>
@@ -3602,19 +3602,19 @@
     <t xml:space="preserve">8.95095157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91677093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90395355224609</t>
+    <t xml:space="preserve">8.91676998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90395259857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.81422996520996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61342144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67323589324951</t>
+    <t xml:space="preserve">8.6134204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6732349395752</t>
   </si>
   <si>
     <t xml:space="preserve">8.69887256622314</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">8.70314502716064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74159622192383</t>
+    <t xml:space="preserve">8.74159717559814</t>
   </si>
   <si>
     <t xml:space="preserve">8.46131896972656</t>
@@ -3635,19 +3635,19 @@
     <t xml:space="preserve">8.5621509552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92368698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16629981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26775550842285</t>
+    <t xml:space="preserve">8.92368793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26775455474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600032806396</t>
+    <t xml:space="preserve">9.20599937438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.14424324035645</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">8.98985385894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7498893737793</t>
+    <t xml:space="preserve">8.74989032745361</t>
   </si>
   <si>
     <t xml:space="preserve">8.43229007720947</t>
@@ -3677,25 +3677,25 @@
     <t xml:space="preserve">8.23820114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23996543884277</t>
+    <t xml:space="preserve">8.23996448516846</t>
   </si>
   <si>
     <t xml:space="preserve">8.25760936737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21702766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31583595275879</t>
+    <t xml:space="preserve">8.21702671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31583499908447</t>
   </si>
   <si>
     <t xml:space="preserve">8.4234676361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73224449157715</t>
+    <t xml:space="preserve">8.79929447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73224544525146</t>
   </si>
   <si>
     <t xml:space="preserve">8.58932590484619</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">8.54344940185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77988624572754</t>
+    <t xml:space="preserve">8.77988529205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.71636581420898</t>
@@ -3719,40 +3719,40 @@
     <t xml:space="preserve">8.82223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80458641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77635669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91486549377441</t>
+    <t xml:space="preserve">8.80458736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7763557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91486644744873</t>
   </si>
   <si>
     <t xml:space="preserve">8.93692207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84428691864014</t>
+    <t xml:space="preserve">8.84428787231445</t>
   </si>
   <si>
     <t xml:space="preserve">8.85311031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81517505645752</t>
+    <t xml:space="preserve">8.8151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57168102264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78694343566895</t>
+    <t xml:space="preserve">8.57168006896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78694438934326</t>
   </si>
   <si>
     <t xml:space="preserve">8.75341892242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03396606445312</t>
+    <t xml:space="preserve">9.03396701812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.91045570373535</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5575647354126</t>
+    <t xml:space="preserve">8.55756568908691</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">8.6157922744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77106380462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74459648132324</t>
+    <t xml:space="preserve">8.77106475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74459552764893</t>
   </si>
   <si>
     <t xml:space="preserve">8.90163230895996</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">8.84869861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8354663848877</t>
+    <t xml:space="preserve">8.83546543121338</t>
   </si>
   <si>
     <t xml:space="preserve">8.68460559844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56638813018799</t>
+    <t xml:space="preserve">8.56638717651367</t>
   </si>
   <si>
     <t xml:space="preserve">8.63167285919189</t>
@@ -3803,34 +3803,34 @@
     <t xml:space="preserve">8.37935638427734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3493595123291</t>
+    <t xml:space="preserve">8.34936046600342</t>
   </si>
   <si>
     <t xml:space="preserve">8.29995536804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693868637085</t>
+    <t xml:space="preserve">8.16938781738281</t>
   </si>
   <si>
     <t xml:space="preserve">8.10763072967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25584506988525</t>
+    <t xml:space="preserve">8.25584411621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53639221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39700126647949</t>
+    <t xml:space="preserve">8.53639125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39700031280518</t>
   </si>
   <si>
     <t xml:space="preserve">8.32818698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70754337310791</t>
+    <t xml:space="preserve">8.70754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">8.45699214935303</t>
@@ -3842,28 +3842,28 @@
     <t xml:space="preserve">8.08292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22585010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0035285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412445068359</t>
+    <t xml:space="preserve">8.22584915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00352954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412397384644</t>
   </si>
   <si>
     <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92589426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90472030639648</t>
+    <t xml:space="preserve">7.92589378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90471982955933</t>
   </si>
   <si>
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91354274749756</t>
+    <t xml:space="preserve">7.9135422706604</t>
   </si>
   <si>
     <t xml:space="preserve">7.94706773757935</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">8.15703678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04411220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78473806381226</t>
+    <t xml:space="preserve">8.04411125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78473854064941</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.39479494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40538167953491</t>
+    <t xml:space="preserve">7.40538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">7.51124858856201</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">7.43890619277954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52359914779663</t>
+    <t xml:space="preserve">7.52359962463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.3101019859314</t>
@@ -3917,25 +3917,25 @@
     <t xml:space="preserve">7.73709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75297689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8747239112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88001871109009</t>
+    <t xml:space="preserve">7.75297832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87472438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88001775741577</t>
   </si>
   <si>
     <t xml:space="preserve">7.85355138778687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94353818893433</t>
+    <t xml:space="preserve">7.94353771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08822250366211</t>
+    <t xml:space="preserve">8.08822345733643</t>
   </si>
   <si>
     <t xml:space="preserve">8.14291954040527</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">8.38817882537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76047706604004</t>
+    <t xml:space="preserve">8.76047611236572</t>
   </si>
   <si>
     <t xml:space="preserve">8.69872093200684</t>
@@ -3956,40 +3956,40 @@
     <t xml:space="preserve">8.4005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33524513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48698806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46934413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4816951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49404621124268</t>
+    <t xml:space="preserve">8.33524608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48698711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4693431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48169422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49404525756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.40935134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28054809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53109836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47640037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46757793426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42699718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37053489685059</t>
+    <t xml:space="preserve">8.28054714202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53109931945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47640132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46757888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.36347579956055</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">8.53286361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55580043792725</t>
+    <t xml:space="preserve">8.55580139160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.4305248260498</t>
@@ -4013,10 +4013,10 @@
     <t xml:space="preserve">8.16232967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37582778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35112476348877</t>
+    <t xml:space="preserve">8.37582874298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35112571716309</t>
   </si>
   <si>
     <t xml:space="preserve">8.29642772674561</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">8.29819202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41640853881836</t>
+    <t xml:space="preserve">8.41641044616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4075870513916</t>
+    <t xml:space="preserve">8.40758800506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4046,19 +4046,19 @@
     <t xml:space="preserve">8.55227184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64402389526367</t>
+    <t xml:space="preserve">8.64402294158936</t>
   </si>
   <si>
     <t xml:space="preserve">8.67049026489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61226367950439</t>
+    <t xml:space="preserve">8.61226272583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.7887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82046890258789</t>
+    <t xml:space="preserve">8.82046794891357</t>
   </si>
   <si>
     <t xml:space="preserve">8.73400974273682</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456600189209</t>
+    <t xml:space="preserve">8.95456504821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
@@ -4079,19 +4079,19 @@
     <t xml:space="preserve">8.8619327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8928108215332</t>
+    <t xml:space="preserve">8.89280986785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.11336612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89722156524658</t>
+    <t xml:space="preserve">8.89722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867725372314</t>
+    <t xml:space="preserve">8.99867630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4109,22 +4109,22 @@
     <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15306568145752</t>
+    <t xml:space="preserve">9.15306663513184</t>
   </si>
   <si>
     <t xml:space="preserve">9.14865493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13101100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13983249664307</t>
+    <t xml:space="preserve">9.13101005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13983154296875</t>
   </si>
   <si>
     <t xml:space="preserve">9.08248805999756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04278755187988</t>
+    <t xml:space="preserve">9.0427885055542</t>
   </si>
   <si>
     <t xml:space="preserve">9.93383407592773</t>
@@ -4142,19 +4142,19 @@
     <t xml:space="preserve">10.1720342636108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0264663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78385543823242</t>
+    <t xml:space="preserve">10.0264673233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78385639190674</t>
   </si>
   <si>
     <t xml:space="preserve">10.0705785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87207794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706630706787</t>
+    <t xml:space="preserve">9.87207698822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706726074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.77944469451904</t>
@@ -4166,16 +4166,16 @@
     <t xml:space="preserve">9.99117755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5116901397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778570175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6131458282471</t>
+    <t xml:space="preserve">10.5116891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3440675735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778560638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6131448745728</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.6925458908081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7278337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8425235748291</t>
+    <t xml:space="preserve">10.7278347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8425226211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.0013236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9219236373901</t>
+    <t xml:space="preserve">10.9219245910645</t>
   </si>
   <si>
     <t xml:space="preserve">10.9175128936768</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">10.789589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160581588745</t>
+    <t xml:space="preserve">10.8160572052002</t>
   </si>
   <si>
     <t xml:space="preserve">10.868989944458</t>
@@ -4238,37 +4238,37 @@
     <t xml:space="preserve">11.0454359054565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1248350143433</t>
+    <t xml:space="preserve">11.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0983686447144</t>
+    <t xml:space="preserve">11.09836769104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8645782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6396131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8274984359741</t>
+    <t xml:space="preserve">10.6969566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660795211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.639612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4852228164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6352005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8274974822998</t>
   </si>
   <si>
     <t xml:space="preserve">10.7820806503296</t>
@@ -4280,22 +4280,22 @@
     <t xml:space="preserve">10.6276607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6594543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6639947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684545516968</t>
+    <t xml:space="preserve">10.6594533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6639957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684555053711</t>
   </si>
   <si>
     <t xml:space="preserve">10.8093309402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7593727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.732120513916</t>
+    <t xml:space="preserve">10.7593717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7321214675903</t>
   </si>
   <si>
     <t xml:space="preserve">10.7366628646851</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">10.5913276672363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5686187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6231203079224</t>
+    <t xml:space="preserve">10.5686197280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.623119354248</t>
   </si>
   <si>
     <t xml:space="preserve">10.8138723373413</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">10.5822439193726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775382995605</t>
+    <t xml:space="preserve">10.7775392532349</t>
   </si>
   <si>
     <t xml:space="preserve">10.8774576187134</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">10.6776208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5958690643311</t>
+    <t xml:space="preserve">10.5958700180054</t>
   </si>
   <si>
     <t xml:space="preserve">10.5640773773193</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">10.9910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9773750305176</t>
+    <t xml:space="preserve">10.9773759841919</t>
   </si>
   <si>
     <t xml:space="preserve">10.8729152679443</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">10.5277433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5549945831299</t>
+    <t xml:space="preserve">10.5549936294556</t>
   </si>
   <si>
     <t xml:space="preserve">10.3687829971313</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">10.3778667449951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3824090957642</t>
+    <t xml:space="preserve">10.3824081420898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597808837891</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">10.2416143417358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598634719849</t>
+    <t xml:space="preserve">10.1598625183105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1462373733521</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">10.0826539993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236110687256</t>
+    <t xml:space="preserve">10.0236101150513</t>
   </si>
   <si>
     <t xml:space="preserve">10.1916551589966</t>
@@ -4448,16 +4448,16 @@
     <t xml:space="preserve">10.1416959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1099033355713</t>
+    <t xml:space="preserve">10.1099042892456</t>
   </si>
   <si>
     <t xml:space="preserve">10.3642406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4187412261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414501190186</t>
+    <t xml:space="preserve">10.4187421798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414510726929</t>
   </si>
   <si>
     <t xml:space="preserve">10.4459924697876</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">10.3551568984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4278249740601</t>
+    <t xml:space="preserve">10.4278240203857</t>
   </si>
   <si>
     <t xml:space="preserve">10.5413684844971</t>
@@ -4481,16 +4481,16 @@
     <t xml:space="preserve">10.7275800704956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912469863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4505348205566</t>
+    <t xml:space="preserve">10.6912460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4505338668823</t>
   </si>
   <si>
     <t xml:space="preserve">10.4596176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3006572723389</t>
+    <t xml:space="preserve">10.3006563186646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1734886169434</t>
@@ -4499,25 +4499,25 @@
     <t xml:space="preserve">10.059944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2325315475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0917367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89190101623535</t>
+    <t xml:space="preserve">10.2325305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0917358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89190006256104</t>
   </si>
   <si>
     <t xml:space="preserve">9.62847995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48768615722656</t>
+    <t xml:space="preserve">9.48768520355225</t>
   </si>
   <si>
     <t xml:space="preserve">9.5648946762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62393856048584</t>
+    <t xml:space="preserve">9.62393760681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.79652404785156</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">9.65573024749756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75564861297607</t>
+    <t xml:space="preserve">9.75564765930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.64210510253906</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">9.71023082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72385692596436</t>
+    <t xml:space="preserve">9.72385597229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.59668731689453</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">9.65118885040283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68752288818359</t>
+    <t xml:space="preserve">9.68752193450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.67389678955078</t>
@@ -4598,16 +4598,16 @@
     <t xml:space="preserve">9.9009838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7738151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83285713195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8146915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7465648651123</t>
+    <t xml:space="preserve">9.77381610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83285808563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81469058990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74656391143799</t>
   </si>
   <si>
     <t xml:space="preserve">9.80106544494629</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">10.2961149215698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3460750579834</t>
+    <t xml:space="preserve">10.3460741043091</t>
   </si>
   <si>
     <t xml:space="preserve">10.3279066085815</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">10.4868679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3506155014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051170349121</t>
+    <t xml:space="preserve">10.3960332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3506164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051160812378</t>
   </si>
   <si>
     <t xml:space="preserve">10.2279891967773</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">10.2734069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4550752639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4323663711548</t>
+    <t xml:space="preserve">10.4550762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4323673248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.4005746841431</t>
@@ -4670,10 +4670,10 @@
     <t xml:space="preserve">10.3324489593506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3188228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0690288543701</t>
+    <t xml:space="preserve">10.3188238143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">10.0190687179565</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">10.0463199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009031295776</t>
+    <t xml:space="preserve">10.0009021759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.1280708312988</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">10.2143630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1189870834351</t>
+    <t xml:space="preserve">10.1189880371094</t>
   </si>
   <si>
     <t xml:space="preserve">9.94185924530029</t>
@@ -4706,28 +4706,28 @@
     <t xml:space="preserve">9.75110626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80560684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66027164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73748111724854</t>
+    <t xml:space="preserve">9.80560779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6602725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73748207092285</t>
   </si>
   <si>
     <t xml:space="preserve">9.74202346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78289890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70114803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46043491363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2969331741333</t>
+    <t xml:space="preserve">9.78289985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70114707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46043586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29693222045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.51493740081787</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">9.49676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41047668457031</t>
+    <t xml:space="preserve">9.410475730896</t>
   </si>
   <si>
     <t xml:space="preserve">9.35143375396729</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">9.57397937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63302040100098</t>
+    <t xml:space="preserve">9.63302135467529</t>
   </si>
   <si>
     <t xml:space="preserve">9.34689235687256</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">9.20155715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06530475616455</t>
+    <t xml:space="preserve">9.06530380249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.03805446624756</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">8.85184288024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90634346008301</t>
+    <t xml:space="preserve">8.90634441375732</t>
   </si>
   <si>
     <t xml:space="preserve">8.95176029205322</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">9.21972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3650598526001</t>
+    <t xml:space="preserve">9.36505889892578</t>
   </si>
   <si>
     <t xml:space="preserve">9.29239082336426</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">9.31964206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4377269744873</t>
+    <t xml:space="preserve">9.43772792816162</t>
   </si>
   <si>
     <t xml:space="preserve">9.40139293670654</t>
@@ -5484,6 +5484,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.84000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8149995803833</t>
   </si>
 </sst>
 </file>
@@ -70458,7 +70461,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6493981481</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>664548</v>
@@ -70479,6 +70482,32 @@
         <v>1823</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493171296</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>972515</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>9.86499977111816</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>9.79500007629395</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>9.85000038146973</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>9.8149995803833</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="1827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1828">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433834075928</t>
+    <t xml:space="preserve">3.42433881759644</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296906471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45607113838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986746788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331619262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812421798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845685958862</t>
+    <t xml:space="preserve">3.46296882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45607089996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986699104309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812469482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845662117004</t>
   </si>
   <si>
     <t xml:space="preserve">3.34707713127136</t>
@@ -71,49 +71,49 @@
     <t xml:space="preserve">3.28637146949768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21324872970581</t>
+    <t xml:space="preserve">3.21324920654297</t>
   </si>
   <si>
     <t xml:space="preserve">3.03803062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13874697685242</t>
+    <t xml:space="preserve">3.13874650001526</t>
   </si>
   <si>
     <t xml:space="preserve">3.14288592338562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16496014595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.137366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564538002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1994526386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430698394775</t>
+    <t xml:space="preserve">3.10425496101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16495990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736701011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430722236633</t>
   </si>
   <si>
     <t xml:space="preserve">3.27119517326355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20911049842834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20773005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631873130798</t>
+    <t xml:space="preserve">3.24222159385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20911002159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2077305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631944656372</t>
   </si>
   <si>
     <t xml:space="preserve">3.06700372695923</t>
@@ -122,76 +122,76 @@
     <t xml:space="preserve">3.00078010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00215935707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837324142456</t>
+    <t xml:space="preserve">3.00215983390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802041053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837347984314</t>
   </si>
   <si>
     <t xml:space="preserve">3.07114291191101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115312576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046884536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14150619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12494969367981</t>
+    <t xml:space="preserve">3.13322806358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1111536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151617050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046836853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14150595664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12494993209839</t>
   </si>
   <si>
     <t xml:space="preserve">3.11805152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323780059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18703532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013691902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255375862122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427610397339</t>
+    <t xml:space="preserve">3.23808264732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323899269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531321525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18703484535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321808815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013739585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20635080337524</t>
+    <t xml:space="preserve">3.20635056495667</t>
   </si>
   <si>
     <t xml:space="preserve">3.19807243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10563445091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906845092773</t>
+    <t xml:space="preserve">3.10563468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906868934631</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
@@ -200,76 +200,76 @@
     <t xml:space="preserve">3.03941082954407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00491881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05182790756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422431945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.050448179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595640182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457667350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147459983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767827033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08769917488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05596661567688</t>
+    <t xml:space="preserve">3.00491905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05182766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422408103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05044770240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147531509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629878044128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767874717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873652458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0876989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978456497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0559663772583</t>
   </si>
   <si>
     <t xml:space="preserve">3.06838345527649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01319742202759</t>
+    <t xml:space="preserve">3.01319718360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.02975296974182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01871538162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766781806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249152183533</t>
+    <t xml:space="preserve">3.01871609687805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766805648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249128341675</t>
   </si>
   <si>
     <t xml:space="preserve">2.94421362876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93869471549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593597412109</t>
+    <t xml:space="preserve">2.93869519233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593573570251</t>
   </si>
   <si>
     <t xml:space="preserve">3.02235889434814</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">2.99837183952332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98426246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97861838340759</t>
+    <t xml:space="preserve">2.98426222801208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99131655693054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97861862182617</t>
   </si>
   <si>
     <t xml:space="preserve">3.06892228126526</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">3.01389312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02094769477844</t>
+    <t xml:space="preserve">3.0209481716156</t>
   </si>
   <si>
     <t xml:space="preserve">3.00683808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03929138183594</t>
+    <t xml:space="preserve">3.03929114341736</t>
   </si>
   <si>
     <t xml:space="preserve">3.01671481132507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03505802154541</t>
+    <t xml:space="preserve">3.03505825996399</t>
   </si>
   <si>
     <t xml:space="preserve">2.99978303909302</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">2.86714935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80083227157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843728065491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702608108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72181630134583</t>
+    <t xml:space="preserve">2.80083274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843680381775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9108898639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72181606292725</t>
   </si>
   <si>
     <t xml:space="preserve">2.61034727096558</t>
@@ -347,46 +347,46 @@
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899437904358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79659914970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79518842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162806510925</t>
+    <t xml:space="preserve">2.718994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79659938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79518818855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162830352783</t>
   </si>
   <si>
     <t xml:space="preserve">2.83610725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87279343605042</t>
+    <t xml:space="preserve">2.87279272079468</t>
   </si>
   <si>
     <t xml:space="preserve">2.94475412368774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97438526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00542688369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02518129348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364658355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07033276557922</t>
+    <t xml:space="preserve">2.97438502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00542736053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02518081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0421130657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597708702087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364729881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0703330039978</t>
   </si>
   <si>
     <t xml:space="preserve">3.05481219291687</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">3.03788018226624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0519905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333626747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204810142517</t>
+    <t xml:space="preserve">3.05199003219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204762458801</t>
   </si>
   <si>
     <t xml:space="preserve">3.15499305725098</t>
@@ -410,148 +410,148 @@
     <t xml:space="preserve">3.14088296890259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1479377746582</t>
+    <t xml:space="preserve">3.14793801307678</t>
   </si>
   <si>
     <t xml:space="preserve">3.1084303855896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09149789810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241720199585</t>
+    <t xml:space="preserve">3.09149813652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241696357727</t>
   </si>
   <si>
     <t xml:space="preserve">3.13947200775146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15076017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419726371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02800250053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01248240470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02376985549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0717442035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045579910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0900866985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732308387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21002197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1846239566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2128438949585</t>
+    <t xml:space="preserve">3.15076041221619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419678688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444333076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02800297737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0124819278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02377033233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07174396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008741378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732260704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21002173423767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18462443351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21284365653992</t>
   </si>
   <si>
     <t xml:space="preserve">3.21707701683044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27774977684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351641654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873356819153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18180179595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15358185768127</t>
+    <t xml:space="preserve">3.27774953842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351689338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22131013870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861101150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18180227279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1535816192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.15217113494873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16628074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12536215782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125206947327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08726477622986</t>
+    <t xml:space="preserve">3.16628122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12536191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08726525306702</t>
   </si>
   <si>
     <t xml:space="preserve">3.09714198112488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548471450806</t>
+    <t xml:space="preserve">3.11548495292664</t>
   </si>
   <si>
     <t xml:space="preserve">3.08867573738098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.077388048172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06186676025391</t>
+    <t xml:space="preserve">3.07738780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06186699867249</t>
   </si>
   <si>
     <t xml:space="preserve">2.99696135520935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92923331260681</t>
+    <t xml:space="preserve">2.92923307418823</t>
   </si>
   <si>
     <t xml:space="preserve">2.95322012901306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95180916786194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93911051750183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92076706886292</t>
+    <t xml:space="preserve">2.95180940628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93911004066467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92076683044434</t>
   </si>
   <si>
     <t xml:space="preserve">2.95886397361755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92782211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622267723083</t>
+    <t xml:space="preserve">2.92782258987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002886772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.0195369720459</t>
@@ -563,142 +563,142 @@
     <t xml:space="preserve">2.99555015563965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0407018661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0181257724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96309661865234</t>
+    <t xml:space="preserve">3.04070210456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01812624931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96309685707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.92641091346741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98849487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138223648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8572723865509</t>
+    <t xml:space="preserve">2.98849511146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85727214813232</t>
   </si>
   <si>
     <t xml:space="preserve">2.86856031417847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92358922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604181289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88690328598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89819121360779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303950309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034013748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84457325935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85021710395813</t>
+    <t xml:space="preserve">2.92358899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604205131531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8869035243988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89819097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85021734237671</t>
   </si>
   <si>
     <t xml:space="preserve">2.78390026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79377722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82340812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568008422852</t>
+    <t xml:space="preserve">2.79377746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82340788841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568056106567</t>
   </si>
   <si>
     <t xml:space="preserve">2.76132440567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80929851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254713058472</t>
+    <t xml:space="preserve">2.80929827690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89254689216614</t>
   </si>
   <si>
     <t xml:space="preserve">2.89395833015442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89960241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009430885315</t>
+    <t xml:space="preserve">2.89960193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009407043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.90665698051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88831400871277</t>
+    <t xml:space="preserve">2.88831424713135</t>
   </si>
   <si>
     <t xml:space="preserve">2.9123010635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94052076339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08020997047424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560822486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585405349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523888587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511632919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13806080818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063714027405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051339149475</t>
+    <t xml:space="preserve">2.94052124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09432005882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08020973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303189277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1056079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585381507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511609077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051386833191</t>
   </si>
   <si>
     <t xml:space="preserve">3.2043776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19591164588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573125839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278534889221</t>
+    <t xml:space="preserve">3.19591188430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253975868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278582572937</t>
   </si>
   <si>
     <t xml:space="preserve">3.09290909767151</t>
@@ -707,49 +707,49 @@
     <t xml:space="preserve">3.06751108169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11830711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17897987365723</t>
+    <t xml:space="preserve">3.11830735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17897963523865</t>
   </si>
   <si>
     <t xml:space="preserve">3.13664984703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07456588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10701870918274</t>
+    <t xml:space="preserve">3.07456612586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10701894760132</t>
   </si>
   <si>
     <t xml:space="preserve">3.09855318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24529623985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26646208763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25376296043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891514778137</t>
+    <t xml:space="preserve">3.24529671669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26646184921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2537624835968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094103813171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891443252563</t>
   </si>
   <si>
     <t xml:space="preserve">3.3144359588623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38357496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3722870349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651991844177</t>
+    <t xml:space="preserve">3.38357472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37228679656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651920318604</t>
   </si>
   <si>
     <t xml:space="preserve">3.4456582069397</t>
@@ -758,67 +758,67 @@
     <t xml:space="preserve">3.41461682319641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44283676147461</t>
+    <t xml:space="preserve">3.44283723831177</t>
   </si>
   <si>
     <t xml:space="preserve">3.40756154060364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40050673484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105717658997</t>
+    <t xml:space="preserve">3.40050649642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657774925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338696479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105693817139</t>
   </si>
   <si>
     <t xml:space="preserve">3.54160666465759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47811150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798823356628</t>
+    <t xml:space="preserve">3.47811126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798847198486</t>
   </si>
   <si>
     <t xml:space="preserve">3.52185297012329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50633120536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277203559875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5274965763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099221229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568379402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5839364528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209856033325</t>
+    <t xml:space="preserve">3.50633096694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222159385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56277227401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5345516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056408882141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099102020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209903717041</t>
   </si>
   <si>
     <t xml:space="preserve">3.55924415588379</t>
@@ -827,70 +827,70 @@
     <t xml:space="preserve">3.62273955345154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.650958776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66154146194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506910324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6333212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804677963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73752307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6866717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299385070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71936178207397</t>
+    <t xml:space="preserve">3.65095901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506934165955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73752284049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71936130523682</t>
   </si>
   <si>
     <t xml:space="preserve">3.7048327922821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66124653816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195972442627</t>
+    <t xml:space="preserve">3.66124677658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195924758911</t>
   </si>
   <si>
     <t xml:space="preserve">3.82832765579224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81379914283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285593032837</t>
+    <t xml:space="preserve">3.81379866600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285616874695</t>
   </si>
   <si>
     <t xml:space="preserve">3.85012102127075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88644242286682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648871421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469487190247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922386169434</t>
+    <t xml:space="preserve">3.88644313812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8464879989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469534873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922362327576</t>
   </si>
   <si>
     <t xml:space="preserve">3.9845118522644</t>
@@ -899,58 +899,58 @@
     <t xml:space="preserve">3.90097141265869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94455718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639660835266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823578834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913199424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8101658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68303966522217</t>
+    <t xml:space="preserve">3.94455695152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087954521179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9263961315155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823531150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016564369202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304014205933</t>
   </si>
   <si>
     <t xml:space="preserve">3.6576144695282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61330223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201905250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313129425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150862693787</t>
+    <t xml:space="preserve">3.61330151557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313177108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150838851929</t>
   </si>
   <si>
     <t xml:space="preserve">3.624924659729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67214322090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030427932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035057067871</t>
+    <t xml:space="preserve">3.67214274406433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073658943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218927383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035033226013</t>
   </si>
   <si>
     <t xml:space="preserve">3.71572947502136</t>
@@ -962,91 +962,91 @@
     <t xml:space="preserve">3.87191343307495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9663507938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908617973328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998238563538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356935501099</t>
+    <t xml:space="preserve">3.96635103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356887817383</t>
   </si>
   <si>
     <t xml:space="preserve">4.05352354049683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989099502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0789475440979</t>
+    <t xml:space="preserve">4.04989147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894802093506</t>
   </si>
   <si>
     <t xml:space="preserve">4.00267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95182228088379</t>
+    <t xml:space="preserve">3.95182204246521</t>
   </si>
   <si>
     <t xml:space="preserve">3.9154999256134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446556091309</t>
+    <t xml:space="preserve">4.00993680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177575111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446603775024</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10437393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271848678589</t>
+    <t xml:space="preserve">4.10437440872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271872520447</t>
   </si>
   <si>
     <t xml:space="preserve">3.86464953422546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89733862876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9881432056427</t>
+    <t xml:space="preserve">3.8973376750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98814344406128</t>
   </si>
   <si>
     <t xml:space="preserve">3.95545411109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93002891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01720142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88281011581421</t>
+    <t xml:space="preserve">3.93002843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01720094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88280987739563</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06805181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14795970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625844955444</t>
+    <t xml:space="preserve">4.06805229187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14796018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04625797271729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078767776489</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">4.11527061462402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1080060005188</t>
+    <t xml:space="preserve">4.10800552368164</t>
   </si>
   <si>
     <t xml:space="preserve">4.12253475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1806492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885591506958</t>
+    <t xml:space="preserve">4.18064975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885639190674</t>
   </si>
   <si>
     <t xml:space="preserve">4.18791389465332</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">4.17338514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09710884094238</t>
+    <t xml:space="preserve">4.09710931777954</t>
   </si>
   <si>
     <t xml:space="preserve">4.14069557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.129798412323</t>
+    <t xml:space="preserve">4.12979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">4.24602937698364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22060346603394</t>
+    <t xml:space="preserve">4.22060394287109</t>
   </si>
   <si>
     <t xml:space="preserve">4.26055765151978</t>
@@ -1097,25 +1097,25 @@
     <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25329351425171</t>
+    <t xml:space="preserve">4.25329399108887</t>
   </si>
   <si>
     <t xml:space="preserve">4.26419019699097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27508687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08984518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30777645111084</t>
+    <t xml:space="preserve">4.27508735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17701721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08984422683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30777597427368</t>
   </si>
   <si>
     <t xml:space="preserve">4.29688024520874</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">4.4276385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51481151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5402364730835</t>
+    <t xml:space="preserve">4.51481103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54023599624634</t>
   </si>
   <si>
     <t xml:space="preserve">4.60198354721069</t>
@@ -1136,43 +1136,43 @@
     <t xml:space="preserve">4.5983510017395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72184562683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929302215576</t>
+    <t xml:space="preserve">4.72184610366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929349899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.56202983856201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62014436721802</t>
+    <t xml:space="preserve">4.62014532089233</t>
   </si>
   <si>
     <t xml:space="preserve">4.59471940994263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6092472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48938608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669651031494</t>
+    <t xml:space="preserve">4.60924768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4893856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669603347778</t>
   </si>
   <si>
     <t xml:space="preserve">4.51844263076782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52207612991333</t>
+    <t xml:space="preserve">4.33683347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52207517623901</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49301815032959</t>
+    <t xml:space="preserve">4.49301767349243</t>
   </si>
   <si>
     <t xml:space="preserve">4.50391435623169</t>
@@ -1181,40 +1181,40 @@
     <t xml:space="preserve">4.49665021896362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46032810211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306348800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46759223937988</t>
+    <t xml:space="preserve">4.46032857894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46759271621704</t>
   </si>
   <si>
     <t xml:space="preserve">4.47848892211914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750108718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037439346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29324722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40947818756104</t>
+    <t xml:space="preserve">4.54750156402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53660440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39131641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29324674606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40947771072388</t>
   </si>
   <si>
     <t xml:space="preserve">4.51117849349976</t>
@@ -1223,85 +1223,85 @@
     <t xml:space="preserve">4.42400693893433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140851974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28235054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2060751914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12616634368896</t>
+    <t xml:space="preserve">4.31140899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28235101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20607471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12616682052612</t>
   </si>
   <si>
     <t xml:space="preserve">4.23150014877319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14432764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361516952515</t>
+    <t xml:space="preserve">4.14432716369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361493110657</t>
   </si>
   <si>
     <t xml:space="preserve">3.94092512130737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9772469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258104324341</t>
+    <t xml:space="preserve">3.97724723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16975259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44579887390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41674137115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108686447144</t>
+    <t xml:space="preserve">4.169753074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44579982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40584468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41674184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108734130859</t>
   </si>
   <si>
     <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55113315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52933979034424</t>
+    <t xml:space="preserve">4.5511326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5765585899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
     <t xml:space="preserve">4.52570772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53297138214111</t>
+    <t xml:space="preserve">4.53297233581543</t>
   </si>
   <si>
     <t xml:space="preserve">4.67825984954834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6492018699646</t>
+    <t xml:space="preserve">4.64920282363892</t>
   </si>
   <si>
     <t xml:space="preserve">4.67099523544312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64557075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283441543579</t>
+    <t xml:space="preserve">4.64557027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283393859863</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816822052002</t>
@@ -1313,22 +1313,22 @@
     <t xml:space="preserve">4.76180028915405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7254786491394</t>
+    <t xml:space="preserve">4.72547817230225</t>
   </si>
   <si>
     <t xml:space="preserve">4.68552398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72911071777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65646648406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84534025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81265068054199</t>
+    <t xml:space="preserve">4.72910976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65646600723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84534120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81265115737915</t>
   </si>
   <si>
     <t xml:space="preserve">4.81991529464722</t>
@@ -1337,76 +1337,76 @@
     <t xml:space="preserve">4.83807611465454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166189193726</t>
+    <t xml:space="preserve">4.8816614151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.84897232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91798400878906</t>
+    <t xml:space="preserve">4.9179835319519</t>
   </si>
   <si>
     <t xml:space="preserve">4.89255905151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95430564880371</t>
+    <t xml:space="preserve">4.95430612564087</t>
   </si>
   <si>
     <t xml:space="preserve">4.94704103469849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93977737426758</t>
+    <t xml:space="preserve">4.93977689743042</t>
   </si>
   <si>
     <t xml:space="preserve">4.93251323699951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99062871932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7330756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86018848419189</t>
+    <t xml:space="preserve">4.99062776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73307609558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888193130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86018800735474</t>
   </si>
   <si>
     <t xml:space="preserve">4.82654142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75176858901978</t>
+    <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
     <t xml:space="preserve">4.65082597732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49380445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62091779708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699670791626</t>
+    <t xml:space="preserve">4.49380493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62091732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699718475342</t>
   </si>
   <si>
     <t xml:space="preserve">4.63587188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74803066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7218599319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690584182739</t>
+    <t xml:space="preserve">4.7480297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72186088562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690488815308</t>
   </si>
   <si>
     <t xml:space="preserve">4.57979297637939</t>
@@ -1418,100 +1418,100 @@
     <t xml:space="preserve">4.83027935028076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93496084213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8153247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94243812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91252946853638</t>
+    <t xml:space="preserve">4.93495988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85645055770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81532526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94243764877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.8489727973938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91626787185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90505170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88262033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93869876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216409683228</t>
+    <t xml:space="preserve">4.91626739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90505218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88261985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93869972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96486902236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216505050659</t>
   </si>
   <si>
     <t xml:space="preserve">5.01721000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13684558868408</t>
+    <t xml:space="preserve">5.13684511184692</t>
   </si>
   <si>
     <t xml:space="preserve">5.05833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98356246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89757442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1293683052063</t>
+    <t xml:space="preserve">4.98356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89757490158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12936878204346</t>
   </si>
   <si>
     <t xml:space="preserve">5.24900388717651</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37985467910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3162989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41350221633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34246826171875</t>
+    <t xml:space="preserve">5.37985515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31629848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41350173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34246873855591</t>
   </si>
   <si>
     <t xml:space="preserve">5.09945869445801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0134711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17797040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20040130615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274133682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283315658569</t>
+    <t xml:space="preserve">5.01347160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17796993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274229049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283363342285</t>
   </si>
   <si>
     <t xml:space="preserve">5.19666337966919</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">5.11815214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04338026046753</t>
+    <t xml:space="preserve">5.04337978363037</t>
   </si>
   <si>
     <t xml:space="preserve">4.99851703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11067533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17049264907837</t>
+    <t xml:space="preserve">5.1106743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17049312591553</t>
   </si>
   <si>
     <t xml:space="preserve">5.04711866378784</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">5.11441421508789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06581163406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982358932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95739221572876</t>
+    <t xml:space="preserve">5.06581211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982454299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95739269256592</t>
   </si>
   <si>
     <t xml:space="preserve">5.0396409034729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05459642410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076620101929</t>
+    <t xml:space="preserve">5.05459594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076667785645</t>
   </si>
   <si>
     <t xml:space="preserve">5.18544626235962</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">5.09572076797485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2116174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88635873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000675201416</t>
+    <t xml:space="preserve">5.21161699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8863582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92000579833984</t>
   </si>
   <si>
     <t xml:space="preserve">4.77420091629028</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68073558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66951942443848</t>
+    <t xml:space="preserve">4.68073606491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66951990127563</t>
   </si>
   <si>
     <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67325830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68447399139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839460372925</t>
+    <t xml:space="preserve">4.67325782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68447351455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.56857681274414</t>
@@ -1604,25 +1604,25 @@
     <t xml:space="preserve">4.69568967819214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56109952926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4078164100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61344003677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84523344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79289388656616</t>
+    <t xml:space="preserve">4.5610990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40781784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848642349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550842285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84523439407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.792893409729</t>
   </si>
   <si>
     <t xml:space="preserve">4.86766576766968</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">4.78915500640869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78167772293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7779393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140369415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83775615692139</t>
+    <t xml:space="preserve">4.78167819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77793884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140417098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83775663375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821287155151</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74055337905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60222482681274</t>
+    <t xml:space="preserve">4.74055290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988384246826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5237135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48632764816284</t>
+    <t xml:space="preserve">4.52371454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48632717132568</t>
   </si>
   <si>
     <t xml:space="preserve">4.41903305053711</t>
@@ -1673,31 +1673,31 @@
     <t xml:space="preserve">4.46015787124634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64334869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456533432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73681354522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86392736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806127548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927648544312</t>
+    <t xml:space="preserve">4.64334917068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298475265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73681402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86392688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927696228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.21909427642822</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">5.22657155990601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18918657302856</t>
+    <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">5.15179967880249</t>
@@ -1718,28 +1718,28 @@
     <t xml:space="preserve">5.37237739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16675329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620714187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09019088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87335109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79483985900879</t>
+    <t xml:space="preserve">5.1667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620761871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09018993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87335062026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79483938217163</t>
   </si>
   <si>
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79110050201416</t>
+    <t xml:space="preserve">5.81353330612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79110097885132</t>
   </si>
   <si>
     <t xml:space="preserve">5.80231761932373</t>
@@ -1751,49 +1751,49 @@
     <t xml:space="preserve">5.82474851608276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87708854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924827575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02663373947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96307706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00794124603271</t>
+    <t xml:space="preserve">5.87708950042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195272445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924779891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02663421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9630765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0079402923584</t>
   </si>
   <si>
     <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93316841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699815750122</t>
+    <t xml:space="preserve">5.93316888809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699863433838</t>
   </si>
   <si>
     <t xml:space="preserve">5.94064569473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0789737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9369068145752</t>
+    <t xml:space="preserve">6.07897472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93690729141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.95933866500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89952087402344</t>
+    <t xml:space="preserve">5.8995213508606</t>
   </si>
   <si>
     <t xml:space="preserve">5.89578247070312</t>
@@ -1802,34 +1802,34 @@
     <t xml:space="preserve">5.88082790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94812250137329</t>
+    <t xml:space="preserve">5.94812297821045</t>
   </si>
   <si>
     <t xml:space="preserve">5.95560026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97429370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9136209487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84066104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75234031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69474029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778059005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68321990966797</t>
+    <t xml:space="preserve">5.97429323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91362047195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.840660572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7523398399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.694739818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68322038650513</t>
   </si>
   <si>
     <t xml:space="preserve">5.66402006149292</t>
@@ -1838,13 +1838,13 @@
     <t xml:space="preserve">5.66785955429077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78306007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70626020431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76002025604248</t>
+    <t xml:space="preserve">5.78306102752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70626068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76002073287964</t>
   </si>
   <si>
     <t xml:space="preserve">5.87522077560425</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">5.74850082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69857978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64482021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77538013458252</t>
+    <t xml:space="preserve">5.69858026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64481973648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60642051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77538061141968</t>
   </si>
   <si>
     <t xml:space="preserve">5.72162008285522</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95970106124878</t>
+    <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
     <t xml:space="preserve">6.0557017326355</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">6.17474174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09026145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850179672241</t>
+    <t xml:space="preserve">6.09026193618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12866115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850227355957</t>
   </si>
   <si>
     <t xml:space="preserve">6.19394207000732</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">6.10178184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25154256820679</t>
+    <t xml:space="preserve">6.25154209136963</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090177536011</t>
@@ -1916,34 +1916,34 @@
     <t xml:space="preserve">6.1670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29378223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746284484863</t>
+    <t xml:space="preserve">6.29378175735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746236801147</t>
   </si>
   <si>
     <t xml:space="preserve">6.43586254119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210344314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35522222518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44738292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52802324295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954315185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410383224487</t>
+    <t xml:space="preserve">6.46274280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35522317886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44738340377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52802276611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410287857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.58946371078491</t>
@@ -1952,22 +1952,22 @@
     <t xml:space="preserve">6.62018299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64322376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786436080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626358032227</t>
+    <t xml:space="preserve">6.64322328567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786388397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626310348511</t>
   </si>
   <si>
     <t xml:space="preserve">6.80450391769409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83138418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522367477417</t>
+    <t xml:space="preserve">6.83138465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522415161133</t>
   </si>
   <si>
     <t xml:space="preserve">6.78914403915405</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">6.76610469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98114490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882532119751</t>
+    <t xml:space="preserve">6.98114585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">6.88514423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68930387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554382324219</t>
+    <t xml:space="preserve">6.68930435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554430007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.61634254455566</t>
@@ -1997,82 +1997,82 @@
     <t xml:space="preserve">6.54338359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79298400878906</t>
+    <t xml:space="preserve">6.79298448562622</t>
   </si>
   <si>
     <t xml:space="preserve">7.14626502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01570510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946468353271</t>
+    <t xml:space="preserve">7.01570606231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946563720703</t>
   </si>
   <si>
     <t xml:space="preserve">7.04642486572266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0080246925354</t>
+    <t xml:space="preserve">7.00802421569824</t>
   </si>
   <si>
     <t xml:space="preserve">6.9926643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330465316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714605331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034475326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96578550338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426416397095</t>
+    <t xml:space="preserve">7.1040244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0617847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330560684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96578502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
     <t xml:space="preserve">7.02722501754761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274520874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0425853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634494781494</t>
+    <t xml:space="preserve">7.01186513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04258441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634399414062</t>
   </si>
   <si>
     <t xml:space="preserve">6.7507438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9350643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90434503555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0233850479126</t>
+    <t xml:space="preserve">6.93506479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02338552474976</t>
   </si>
   <si>
     <t xml:space="preserve">6.97346496582031</t>
@@ -2081,37 +2081,37 @@
     <t xml:space="preserve">7.15778541564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602479934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16930532455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138706207275</t>
+    <t xml:space="preserve">7.16546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138610839844</t>
   </si>
   <si>
     <t xml:space="preserve">7.27682590484619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18850517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698526382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19234561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010643005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914596557617</t>
+    <t xml:space="preserve">7.18850469589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706565856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1923451423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010452270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914644241333</t>
   </si>
   <si>
     <t xml:space="preserve">7.34210681915283</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">7.43426656723022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066492080688</t>
+    <t xml:space="preserve">7.45730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978532791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658662796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2806658744812</t>
   </si>
   <si>
     <t xml:space="preserve">7.11938619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22306442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11554431915283</t>
+    <t xml:space="preserve">7.2230658531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11554574966431</t>
   </si>
   <si>
     <t xml:space="preserve">7.06562519073486</t>
@@ -2153,25 +2153,25 @@
     <t xml:space="preserve">6.77378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762365341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88898468017578</t>
+    <t xml:space="preserve">6.80066442489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88898420333862</t>
   </si>
   <si>
     <t xml:space="preserve">6.9273853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90818500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.912024974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290313720703</t>
+    <t xml:space="preserve">6.90818452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91202449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290361404419</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210441589355</t>
@@ -2183,118 +2183,118 @@
     <t xml:space="preserve">7.08098554611206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03106451034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05794525146484</t>
+    <t xml:space="preserve">7.03106546401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05794429779053</t>
   </si>
   <si>
     <t xml:space="preserve">6.75842475891113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81218385696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87746429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306440353394</t>
+    <t xml:space="preserve">6.81218433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87746477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306392669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72002363204956</t>
+    <t xml:space="preserve">6.7200231552124</t>
   </si>
   <si>
     <t xml:space="preserve">6.89282464981079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79682445526123</t>
+    <t xml:space="preserve">6.79682397842407</t>
   </si>
   <si>
     <t xml:space="preserve">6.70466327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67778301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78530359268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386552810669</t>
+    <t xml:space="preserve">6.67778396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7853045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73538446426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386505126953</t>
   </si>
   <si>
     <t xml:space="preserve">7.05410480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20770597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314481735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002603530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11170530319214</t>
+    <t xml:space="preserve">7.20770645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314577102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002412796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1117057800293</t>
   </si>
   <si>
     <t xml:space="preserve">7.25762605667114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29986524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826589584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098699569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17922878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378705978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186706542969</t>
+    <t xml:space="preserve">7.29986476898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282657623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098556518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362913131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434698104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186658859253</t>
   </si>
   <si>
     <t xml:space="preserve">7.36130619049072</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">7.56482696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898565292358</t>
+    <t xml:space="preserve">7.61858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898612976074</t>
   </si>
   <si>
     <t xml:space="preserve">6.91970491409302</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">5.77154016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26690196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33602285385132</t>
+    <t xml:space="preserve">6.26690244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33602237701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.15394449234009</t>
@@ -2336,25 +2336,25 @@
     <t xml:space="preserve">7.21922540664673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5801854133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754758834839</t>
+    <t xml:space="preserve">7.58018636703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938859939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754806518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.2717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88021850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57022953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364814758301</t>
+    <t xml:space="preserve">7.88021755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364719390869</t>
   </si>
   <si>
     <t xml:space="preserve">8.13718128204346</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">8.95701789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70413208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75307750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99442434310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127164840698</t>
+    <t xml:space="preserve">8.70413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99442338943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8312726020813</t>
   </si>
   <si>
     <t xml:space="preserve">7.74969530105591</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">7.79864263534546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87613821029663</t>
+    <t xml:space="preserve">7.87613725662231</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6803560256958</t>
+    <t xml:space="preserve">7.68035745620728</t>
   </si>
   <si>
     <t xml:space="preserve">7.50904750823975</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">7.50496912002563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70482921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377416610718</t>
+    <t xml:space="preserve">7.70482969284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377511978149</t>
   </si>
   <si>
     <t xml:space="preserve">7.89653301239014</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">7.94010829925537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98146295547485</t>
+    <t xml:space="preserve">7.98146200180054</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739803314209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78709554672241</t>
+    <t xml:space="preserve">7.78709602355957</t>
   </si>
   <si>
     <t xml:space="preserve">7.75814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69611549377441</t>
+    <t xml:space="preserve">7.69611644744873</t>
   </si>
   <si>
     <t xml:space="preserve">7.54310274124146</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">7.60099983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58032178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51829051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73333501815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65062522888184</t>
+    <t xml:space="preserve">7.580322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5182900428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7333345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65062570571899</t>
   </si>
   <si>
     <t xml:space="preserve">7.55550956726074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53483200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45212316513062</t>
+    <t xml:space="preserve">7.53483247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212268829346</t>
   </si>
   <si>
     <t xml:space="preserve">7.4934778213501</t>
@@ -2474,46 +2474,46 @@
     <t xml:space="preserve">7.63408327102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663194656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58445835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235401153564</t>
+    <t xml:space="preserve">7.40249729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941289901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58445739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520612716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6423544883728</t>
   </si>
   <si>
     <t xml:space="preserve">7.52656126022339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75401258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354803085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768459320068</t>
+    <t xml:space="preserve">7.75401163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768411636353</t>
   </si>
   <si>
     <t xml:space="preserve">7.73746919631958</t>
@@ -2525,16 +2525,16 @@
     <t xml:space="preserve">7.77468872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72506332397461</t>
+    <t xml:space="preserve">7.72506427764893</t>
   </si>
   <si>
     <t xml:space="preserve">7.68784427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67543792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62167739868164</t>
+    <t xml:space="preserve">7.67543840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62167692184448</t>
   </si>
   <si>
     <t xml:space="preserve">7.70438575744629</t>
@@ -2543,37 +2543,37 @@
     <t xml:space="preserve">7.71265697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581300735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4231743812561</t>
+    <t xml:space="preserve">7.62581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42317485809326</t>
   </si>
   <si>
     <t xml:space="preserve">7.33632946014404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36527633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25775480270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08406543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02203321456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95586585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98067808151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06752300262451</t>
+    <t xml:space="preserve">7.36527681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25775527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08406496047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02203273773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95586538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98067760467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06752395629883</t>
   </si>
   <si>
     <t xml:space="preserve">7.09647226333618</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">7.07165908813477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24534845352173</t>
+    <t xml:space="preserve">7.24534893035889</t>
   </si>
   <si>
     <t xml:space="preserve">7.17091035842896</t>
@@ -2591,70 +2591,70 @@
     <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98894929885864</t>
+    <t xml:space="preserve">6.9889497756958</t>
   </si>
   <si>
     <t xml:space="preserve">6.93932437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05511665344238</t>
+    <t xml:space="preserve">7.05511713027954</t>
   </si>
   <si>
     <t xml:space="preserve">6.91864633560181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90623998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95173025131226</t>
+    <t xml:space="preserve">6.90624046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9517297744751</t>
   </si>
   <si>
     <t xml:space="preserve">6.89796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98481369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93105268478394</t>
+    <t xml:space="preserve">6.98481321334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93105316162109</t>
   </si>
   <si>
     <t xml:space="preserve">6.82353067398071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75322818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78217554092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413707733154</t>
+    <t xml:space="preserve">6.75322771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78217506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413660049438</t>
   </si>
   <si>
     <t xml:space="preserve">6.947594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30324459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43558120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700654983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48934125900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59272909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80777359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60927057266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71679353713989</t>
+    <t xml:space="preserve">7.30324506759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43557977676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700702667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48934173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59272861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80777263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6092700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71679306030273</t>
   </si>
   <si>
     <t xml:space="preserve">7.72092771530151</t>
@@ -2663,22 +2663,22 @@
     <t xml:space="preserve">7.84085607528687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81190824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845067977905</t>
+    <t xml:space="preserve">7.81190919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82844972610474</t>
   </si>
   <si>
     <t xml:space="preserve">7.83672189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912729263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716766357422</t>
+    <t xml:space="preserve">7.96078443527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912824630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716718673706</t>
   </si>
   <si>
     <t xml:space="preserve">7.67957353591919</t>
@@ -2690,25 +2690,25 @@
     <t xml:space="preserve">7.60513401031494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59686422348022</t>
+    <t xml:space="preserve">7.59686470031738</t>
   </si>
   <si>
     <t xml:space="preserve">7.57205104827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54723834991455</t>
+    <t xml:space="preserve">7.54723882675171</t>
   </si>
   <si>
     <t xml:space="preserve">7.55137348175049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03522396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20064258575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15515232086182</t>
+    <t xml:space="preserve">8.03522491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20064353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15515327453613</t>
   </si>
   <si>
     <t xml:space="preserve">8.47772026062012</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230163574219</t>
+    <t xml:space="preserve">8.31230068206787</t>
   </si>
   <si>
     <t xml:space="preserve">8.56042957305908</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">8.41155242919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28748798370361</t>
+    <t xml:space="preserve">8.28748893737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.33711338043213</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">8.68449306488037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55215930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25026893615723</t>
+    <t xml:space="preserve">8.55215835571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25026988983154</t>
   </si>
   <si>
     <t xml:space="preserve">8.59351348876953</t>
@@ -2762,19 +2762,19 @@
     <t xml:space="preserve">8.80028629302979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81682777404785</t>
+    <t xml:space="preserve">8.81682872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365581512451</t>
+    <t xml:space="preserve">8.35365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21304988861084</t>
+    <t xml:space="preserve">8.21304893493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.18823719024658</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">8.32057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24199771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.304030418396</t>
+    <t xml:space="preserve">8.24199867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30402946472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.22545623779297</t>
@@ -2798,46 +2798,46 @@
     <t xml:space="preserve">8.27921676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25853824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23786354064941</t>
+    <t xml:space="preserve">8.2585391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.9566502571106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86980628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85326290130615</t>
+    <t xml:space="preserve">7.86980533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85326337814331</t>
   </si>
   <si>
     <t xml:space="preserve">7.89875364303589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74574136734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303110122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44798755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219385147095</t>
+    <t xml:space="preserve">7.74574089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303300857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415395736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219337463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866464614868</t>
+    <t xml:space="preserve">7.46866416931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43971681594849</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">7.43144464492798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50588369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8201789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76228332519531</t>
+    <t xml:space="preserve">7.50588417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82017993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.762282371521</t>
   </si>
   <si>
     <t xml:space="preserve">7.38181972503662</t>
@@ -2861,46 +2861,46 @@
     <t xml:space="preserve">7.2039942741394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338739395142</t>
+    <t xml:space="preserve">7.06338787078857</t>
   </si>
   <si>
     <t xml:space="preserve">7.02616882324219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12541961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12955474853516</t>
+    <t xml:space="preserve">7.09233665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12542009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12955570220947</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518877029419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29910945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53896713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70025205612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80281019210815</t>
+    <t xml:space="preserve">7.04271078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16264009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29910898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896808624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70025062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.802809715271</t>
   </si>
   <si>
     <t xml:space="preserve">8.03108882904053</t>
@@ -2912,28 +2912,28 @@
     <t xml:space="preserve">8.01123905181885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81935214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190525054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86732530593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69694232940674</t>
+    <t xml:space="preserve">7.8193531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77138042449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7945384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190477371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8673243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69694328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.05590152740479</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">7.97319173812866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99635124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01785469055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05259227752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99965906143188</t>
+    <t xml:space="preserve">7.99635028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01785564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05259323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9996600151062</t>
   </si>
   <si>
     <t xml:space="preserve">8.02281856536865</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">8.05093860626221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003461837769</t>
+    <t xml:space="preserve">7.93845462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003271102905</t>
   </si>
   <si>
     <t xml:space="preserve">7.88055753707886</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82431554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371656417847</t>
+    <t xml:space="preserve">7.8243145942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371561050415</t>
   </si>
   <si>
     <t xml:space="preserve">8.01289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84416484832764</t>
+    <t xml:space="preserve">7.84416675567627</t>
   </si>
   <si>
     <t xml:space="preserve">7.81604433059692</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">7.66055107116699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73499011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79480457305908</t>
+    <t xml:space="preserve">7.73498821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79480361938477</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">7.78967714309692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80847549438477</t>
+    <t xml:space="preserve">7.80847644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.85291051864624</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">7.82385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77258729934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960735321045</t>
+    <t xml:space="preserve">7.77258634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960830688477</t>
   </si>
   <si>
     <t xml:space="preserve">7.76404237747192</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">7.8922176361084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94006967544556</t>
+    <t xml:space="preserve">7.94007015228271</t>
   </si>
   <si>
     <t xml:space="preserve">7.98963117599487</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09388160705566</t>
+    <t xml:space="preserve">8.09388065338135</t>
   </si>
   <si>
     <t xml:space="preserve">8.18445873260498</t>
@@ -3050,34 +3050,34 @@
     <t xml:space="preserve">8.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39808559417725</t>
+    <t xml:space="preserve">8.39808464050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.38099384307861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46302700042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44252014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21180248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36390495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31947040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2442741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1912956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12806224822998</t>
+    <t xml:space="preserve">8.46302795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2118034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36390590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31947135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24427509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19129657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12806129455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09900760650635</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11951732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22718524932861</t>
+    <t xml:space="preserve">8.11951637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2271842956543</t>
   </si>
   <si>
     <t xml:space="preserve">8.36903190612793</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">8.2904167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877895355225</t>
+    <t xml:space="preserve">8.35877799987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">8.40663146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37244987487793</t>
+    <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.46644592285156</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5749683380127</t>
+    <t xml:space="preserve">8.57496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">8.32630729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15027904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21864032745361</t>
+    <t xml:space="preserve">8.24256610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15027809143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2186393737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.17420482635498</t>
@@ -3161,16 +3161,16 @@
     <t xml:space="preserve">8.35365104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45277404785156</t>
+    <t xml:space="preserve">8.45277309417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42030334472656</t>
+    <t xml:space="preserve">8.50404453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42030239105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.50233554840088</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">8.66896438598633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60060214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63478374481201</t>
+    <t xml:space="preserve">8.64760208129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6006031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63478469848633</t>
   </si>
   <si>
     <t xml:space="preserve">8.62623882293701</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051128387451</t>
+    <t xml:space="preserve">8.63051223754883</t>
   </si>
   <si>
     <t xml:space="preserve">8.53822422027588</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">8.2340202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31434345245361</t>
+    <t xml:space="preserve">8.3143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40492248535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30579853057861</t>
+    <t xml:space="preserve">8.30579948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.49720859527588</t>
@@ -3254,25 +3254,25 @@
     <t xml:space="preserve">8.34681415557861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459831237793</t>
+    <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.2323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21522045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17933082580566</t>
+    <t xml:space="preserve">8.2152214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17933177947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166290283203</t>
+    <t xml:space="preserve">8.07166481018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.08875370025635</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">8.23914813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33485126495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40150260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17762279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2647819519043</t>
+    <t xml:space="preserve">8.33485221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40150356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31776142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2545280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26478290557861</t>
   </si>
   <si>
     <t xml:space="preserve">8.36048793792725</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">8.2511100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16565990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31605339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21693134307861</t>
+    <t xml:space="preserve">8.16565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31605243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2169303894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">8.45106506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44935607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53480625152588</t>
+    <t xml:space="preserve">8.44935512542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5348072052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.5664234161377</t>
@@ -3344,22 +3344,22 @@
     <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47669982910156</t>
+    <t xml:space="preserve">8.47669887542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.02358436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08767223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86977195739746</t>
+    <t xml:space="preserve">9.08767127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86977291107178</t>
   </si>
   <si>
     <t xml:space="preserve">8.80141162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78005027770996</t>
+    <t xml:space="preserve">8.78004932403564</t>
   </si>
   <si>
     <t xml:space="preserve">8.66041946411133</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">8.71168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65614604949951</t>
+    <t xml:space="preserve">8.65614700317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.72023391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72450733184814</t>
+    <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
     <t xml:space="preserve">8.6390552520752</t>
@@ -3392,22 +3392,22 @@
     <t xml:space="preserve">8.75441551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77150535583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88686275482178</t>
+    <t xml:space="preserve">8.77150440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88686370849609</t>
   </si>
   <si>
     <t xml:space="preserve">8.88259124755859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92531490325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94667911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95522403717041</t>
+    <t xml:space="preserve">8.92531585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94667816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95522308349609</t>
   </si>
   <si>
     <t xml:space="preserve">8.98085880279541</t>
@@ -3416,16 +3416,16 @@
     <t xml:space="preserve">8.92104244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98940372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06630897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12612438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20303058624268</t>
+    <t xml:space="preserve">8.98940467834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06630802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20302963256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.03212833404541</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">8.98513126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70741653442383</t>
+    <t xml:space="preserve">8.70741558074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.5877857208252</t>
@@ -3443,13 +3443,13 @@
     <t xml:space="preserve">8.28870868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26136493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15882396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08020877838135</t>
+    <t xml:space="preserve">8.2613639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15882301330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08021068572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.20667552947998</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">8.35706806182861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78454971313477</t>
+    <t xml:space="preserve">7.78455066680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.81873083114624</t>
@@ -3473,19 +3473,19 @@
     <t xml:space="preserve">8.15540504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12635231018066</t>
+    <t xml:space="preserve">8.12635135650635</t>
   </si>
   <si>
     <t xml:space="preserve">7.88025522232056</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71106243133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60168647766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61364841461182</t>
+    <t xml:space="preserve">7.71106338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60168552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61364889144897</t>
   </si>
   <si>
     <t xml:space="preserve">7.54699754714966</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">7.45129299163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58459663391113</t>
+    <t xml:space="preserve">7.58459568023682</t>
   </si>
   <si>
     <t xml:space="preserve">7.64953756332397</t>
@@ -3503,34 +3503,34 @@
     <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5828857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48376369476318</t>
+    <t xml:space="preserve">7.58288717269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48376417160034</t>
   </si>
   <si>
     <t xml:space="preserve">7.41369390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055509567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556676864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579637527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78625917434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56237936019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72302579879761</t>
+    <t xml:space="preserve">7.69055557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5657958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78626012802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56237888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72302675247192</t>
   </si>
   <si>
     <t xml:space="preserve">7.66491889953613</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">7.77087783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62561178207397</t>
+    <t xml:space="preserve">7.62561225891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">7.91785335540771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95545196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07508277893066</t>
+    <t xml:space="preserve">7.95545101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07508182525635</t>
   </si>
   <si>
     <t xml:space="preserve">8.14173316955566</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">8.68605422973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73732471466064</t>
+    <t xml:space="preserve">8.73732376098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93813419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404537200928</t>
+    <t xml:space="preserve">8.97658538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93813323974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404632568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.89113521575928</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">8.95095157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91677093505859</t>
+    <t xml:space="preserve">8.91677188873291</t>
   </si>
   <si>
     <t xml:space="preserve">8.90395355224609</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">8.67323589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69887256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70314407348633</t>
+    <t xml:space="preserve">8.69887161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70314311981201</t>
   </si>
   <si>
     <t xml:space="preserve">8.74159717559814</t>
@@ -3644,31 +3644,31 @@
     <t xml:space="preserve">9.16629981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26775550842285</t>
+    <t xml:space="preserve">9.26775455474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20599937438965</t>
+    <t xml:space="preserve">9.20600032806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.14424324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18835544586182</t>
+    <t xml:space="preserve">9.1883544921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.1927661895752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98985481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74989032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228912353516</t>
+    <t xml:space="preserve">8.98985385894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7498893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43229007720947</t>
   </si>
   <si>
     <t xml:space="preserve">8.15350723266602</t>
@@ -3680,19 +3680,19 @@
     <t xml:space="preserve">8.23820114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23996448516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25760936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21702766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31583595275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4234676361084</t>
+    <t xml:space="preserve">8.23996543884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25760841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21702671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42346668243408</t>
   </si>
   <si>
     <t xml:space="preserve">8.79929447174072</t>
@@ -3701,19 +3701,19 @@
     <t xml:space="preserve">8.73224544525146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58932495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57520961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54344940185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77988529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71636581420898</t>
+    <t xml:space="preserve">8.58932590484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57521057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54345035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77988624572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71636486053467</t>
   </si>
   <si>
     <t xml:space="preserve">8.86634349822998</t>
@@ -3722,22 +3722,22 @@
     <t xml:space="preserve">8.82223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80458736419678</t>
+    <t xml:space="preserve">8.80458831787109</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91486549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93692111968994</t>
+    <t xml:space="preserve">8.91486644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93692207336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.84428787231445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85311031341553</t>
+    <t xml:space="preserve">8.85310935974121</t>
   </si>
   <si>
     <t xml:space="preserve">8.8151741027832</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">8.57168006896973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78694438934326</t>
+    <t xml:space="preserve">8.78694343566895</t>
   </si>
   <si>
     <t xml:space="preserve">8.75341892242432</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">9.03396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91045475006104</t>
+    <t xml:space="preserve">8.91045570373535</t>
   </si>
   <si>
     <t xml:space="preserve">8.97662162780762</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">8.62814235687256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58756160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6157922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77106380462646</t>
+    <t xml:space="preserve">8.58756065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61579132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77106475830078</t>
   </si>
   <si>
     <t xml:space="preserve">8.74459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90163230895996</t>
+    <t xml:space="preserve">8.90163326263428</t>
   </si>
   <si>
     <t xml:space="preserve">8.84869861602783</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">8.8354663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68460655212402</t>
+    <t xml:space="preserve">8.68460464477539</t>
   </si>
   <si>
     <t xml:space="preserve">8.56638813018799</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">8.63167285919189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37935638427734</t>
+    <t xml:space="preserve">8.37935543060303</t>
   </si>
   <si>
     <t xml:space="preserve">8.34936046600342</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">8.29995632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693868637085</t>
+    <t xml:space="preserve">8.16938781738281</t>
   </si>
   <si>
     <t xml:space="preserve">8.10763168334961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25584506988525</t>
+    <t xml:space="preserve">8.25584411621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
@@ -3830,13 +3830,13 @@
     <t xml:space="preserve">8.39700031280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32818794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70754241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45699214935303</t>
+    <t xml:space="preserve">8.32818698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45699310302734</t>
   </si>
   <si>
     <t xml:space="preserve">8.39347171783447</t>
@@ -3848,19 +3848,19 @@
     <t xml:space="preserve">8.22584915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0035285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9082498550415</t>
+    <t xml:space="preserve">8.00352954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412397384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
     <t xml:space="preserve">7.92589378356934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90471982955933</t>
+    <t xml:space="preserve">7.90472078323364</t>
   </si>
   <si>
     <t xml:space="preserve">7.80061817169189</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">7.9135422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94706726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15703678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04411220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78473901748657</t>
+    <t xml:space="preserve">7.94706678390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15703582763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04411125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7847375869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">7.64534664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52007150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39479541778564</t>
+    <t xml:space="preserve">7.52007102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39479494094849</t>
   </si>
   <si>
     <t xml:space="preserve">7.40538215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51124811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64711141586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43890619277954</t>
+    <t xml:space="preserve">7.51124858856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64711093902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4389066696167</t>
   </si>
   <si>
     <t xml:space="preserve">7.52359962463379</t>
@@ -3911,28 +3911,28 @@
     <t xml:space="preserve">7.3101019859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50948429107666</t>
+    <t xml:space="preserve">7.5094838142395</t>
   </si>
   <si>
     <t xml:space="preserve">7.73180437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73709774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75297832489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87472343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88001823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85355091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94353723526001</t>
+    <t xml:space="preserve">7.7370982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75297737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87472438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88001775741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85355138778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94353771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
@@ -3941,19 +3941,19 @@
     <t xml:space="preserve">8.08822250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14291954040527</t>
+    <t xml:space="preserve">8.14292049407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.38817882537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76047706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69871997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50286769866943</t>
+    <t xml:space="preserve">8.76047611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69872093200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50286674499512</t>
   </si>
   <si>
     <t xml:space="preserve">8.40053081512451</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">8.4693431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48169326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49404621124268</t>
+    <t xml:space="preserve">8.48169422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49404525756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.40935230255127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28054714202881</t>
+    <t xml:space="preserve">8.28054618835449</t>
   </si>
   <si>
     <t xml:space="preserve">8.53109931945801</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">8.46757888793945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42699527740479</t>
+    <t xml:space="preserve">8.4269962310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.37053394317627</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">8.36347579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53286266326904</t>
+    <t xml:space="preserve">8.53286361694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.55580139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43052577972412</t>
+    <t xml:space="preserve">8.4305248260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.2152624130249</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">8.16232967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37582778930664</t>
+    <t xml:space="preserve">8.37582874298096</t>
   </si>
   <si>
     <t xml:space="preserve">8.35112476348877</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">8.30524921417236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37406349182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4075870513916</t>
+    <t xml:space="preserve">8.37406253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40758800506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">8.55227184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64402294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67049026489258</t>
+    <t xml:space="preserve">8.64402389526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67048931121826</t>
   </si>
   <si>
     <t xml:space="preserve">8.61226367950439</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867725372314</t>
+    <t xml:space="preserve">8.99867630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4106,19 +4106,19 @@
     <t xml:space="preserve">9.26334381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2809886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22805595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15306568145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14865398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13101100921631</t>
+    <t xml:space="preserve">9.28098964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22805500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15306663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14865493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13101005554199</t>
   </si>
   <si>
     <t xml:space="preserve">9.13983249664307</t>
@@ -4133,19 +4133,19 @@
     <t xml:space="preserve">9.93383407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0485219955444</t>
+    <t xml:space="preserve">10.0485239028931</t>
   </si>
   <si>
     <t xml:space="preserve">9.74415588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1411561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1720333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0264663696289</t>
+    <t xml:space="preserve">10.1411552429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1720342636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0264673233032</t>
   </si>
   <si>
     <t xml:space="preserve">9.78385543823242</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">9.94706726074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77944469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1191005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99117851257324</t>
+    <t xml:space="preserve">9.77944564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99117755889893</t>
   </si>
   <si>
     <t xml:space="preserve">10.5116891860962</t>
@@ -4175,10 +4175,10 @@
     <t xml:space="preserve">10.3440675735474</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5778560638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6131458282471</t>
+    <t xml:space="preserve">10.5778570175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6131448745728</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">10.7057790756226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6925458908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7278347015381</t>
+    <t xml:space="preserve">10.6925449371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7278337478638</t>
   </si>
   <si>
     <t xml:space="preserve">10.8425235748291</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">11.0013236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9219245910645</t>
+    <t xml:space="preserve">10.9219236373901</t>
   </si>
   <si>
     <t xml:space="preserve">10.9175128936768</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">10.8778123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8601684570312</t>
+    <t xml:space="preserve">10.8601675033569</t>
   </si>
   <si>
     <t xml:space="preserve">10.789589881897</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">10.868989944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9395685195923</t>
+    <t xml:space="preserve">10.939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">10.8248796463013</t>
@@ -4232,16 +4232,16 @@
     <t xml:space="preserve">10.9439792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.018967628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116027832031</t>
+    <t xml:space="preserve">11.0189685821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0454359054565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1248350143433</t>
+    <t xml:space="preserve">11.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
@@ -4250,7 +4250,7 @@
     <t xml:space="preserve">11.09836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8645792007446</t>
+    <t xml:space="preserve">10.8645782470703</t>
   </si>
   <si>
     <t xml:space="preserve">10.6969566345215</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">10.4852237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8274974822998</t>
+    <t xml:space="preserve">10.6352005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8274984359741</t>
   </si>
   <si>
     <t xml:space="preserve">10.7820806503296</t>
@@ -4283,22 +4283,22 @@
     <t xml:space="preserve">10.6276607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6594533920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6639957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684555053711</t>
+    <t xml:space="preserve">10.6594543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6639947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684545516968</t>
   </si>
   <si>
     <t xml:space="preserve">10.8093309402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7593717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7321214675903</t>
+    <t xml:space="preserve">10.7593727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.732120513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7366628646851</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">10.5913276672363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5686197280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.623119354248</t>
+    <t xml:space="preserve">10.5686187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6231203079224</t>
   </si>
   <si>
     <t xml:space="preserve">10.8138723373413</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">10.5822439193726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775392532349</t>
+    <t xml:space="preserve">10.7775382995605</t>
   </si>
   <si>
     <t xml:space="preserve">10.8774576187134</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">10.6776208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5958700180054</t>
+    <t xml:space="preserve">10.5958690643311</t>
   </si>
   <si>
     <t xml:space="preserve">10.5640773773193</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">10.9910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9773759841919</t>
+    <t xml:space="preserve">10.9773750305176</t>
   </si>
   <si>
     <t xml:space="preserve">10.8729152679443</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">10.5277433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5549936294556</t>
+    <t xml:space="preserve">10.5549945831299</t>
   </si>
   <si>
     <t xml:space="preserve">10.3687829971313</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">10.3778667449951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3824081420898</t>
+    <t xml:space="preserve">10.3824090957642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597808837891</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">10.2416143417358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598625183105</t>
+    <t xml:space="preserve">10.1598634719849</t>
   </si>
   <si>
     <t xml:space="preserve">10.1462373733521</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">10.0826539993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236101150513</t>
+    <t xml:space="preserve">10.0236110687256</t>
   </si>
   <si>
     <t xml:space="preserve">10.1916551589966</t>
@@ -4451,16 +4451,16 @@
     <t xml:space="preserve">10.1416959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1099042892456</t>
+    <t xml:space="preserve">10.1099033355713</t>
   </si>
   <si>
     <t xml:space="preserve">10.3642406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4187421798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414510726929</t>
+    <t xml:space="preserve">10.4187412261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414501190186</t>
   </si>
   <si>
     <t xml:space="preserve">10.4459924697876</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">10.3551568984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4278240203857</t>
+    <t xml:space="preserve">10.4278249740601</t>
   </si>
   <si>
     <t xml:space="preserve">10.5413684844971</t>
@@ -4484,16 +4484,16 @@
     <t xml:space="preserve">10.7275800704956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4505338668823</t>
+    <t xml:space="preserve">10.6912469863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4505348205566</t>
   </si>
   <si>
     <t xml:space="preserve">10.4596176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3006563186646</t>
+    <t xml:space="preserve">10.3006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">10.1734886169434</t>
@@ -4502,25 +4502,25 @@
     <t xml:space="preserve">10.059944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0917358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89190006256104</t>
+    <t xml:space="preserve">10.2325315475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0917367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89190101623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.62847995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48768520355225</t>
+    <t xml:space="preserve">9.48768615722656</t>
   </si>
   <si>
     <t xml:space="preserve">9.5648946762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62393760681152</t>
+    <t xml:space="preserve">9.62393856048584</t>
   </si>
   <si>
     <t xml:space="preserve">9.79652404785156</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">9.65573024749756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75564765930176</t>
+    <t xml:space="preserve">9.75564861297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.64210510253906</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">9.71023082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72385597229004</t>
+    <t xml:space="preserve">9.72385692596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.59668731689453</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">9.65118885040283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68752193450928</t>
+    <t xml:space="preserve">9.68752288818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.67389678955078</t>
@@ -4601,16 +4601,16 @@
     <t xml:space="preserve">9.9009838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83285808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81469058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74656391143799</t>
+    <t xml:space="preserve">9.7738151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83285713195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7465648651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.80106544494629</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">10.2961149215698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3460741043091</t>
+    <t xml:space="preserve">10.3460750579834</t>
   </si>
   <si>
     <t xml:space="preserve">10.3279066085815</t>
@@ -4637,13 +4637,13 @@
     <t xml:space="preserve">10.4868679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3960332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3506164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051160812378</t>
+    <t xml:space="preserve">10.396032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3506155014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051170349121</t>
   </si>
   <si>
     <t xml:space="preserve">10.2279891967773</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">10.2734069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4550762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4323673248291</t>
+    <t xml:space="preserve">10.4550752639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4323663711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.4005746841431</t>
@@ -4673,10 +4673,10 @@
     <t xml:space="preserve">10.3324489593506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3188238143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0690279006958</t>
+    <t xml:space="preserve">10.3188228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0690288543701</t>
   </si>
   <si>
     <t xml:space="preserve">10.0190687179565</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">10.0463199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009021759033</t>
+    <t xml:space="preserve">10.0009031295776</t>
   </si>
   <si>
     <t xml:space="preserve">10.1280708312988</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">10.2143630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1189880371094</t>
+    <t xml:space="preserve">10.1189870834351</t>
   </si>
   <si>
     <t xml:space="preserve">9.94185924530029</t>
@@ -4709,28 +4709,28 @@
     <t xml:space="preserve">9.75110626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80560779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6602725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73748207092285</t>
+    <t xml:space="preserve">9.80560684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66027164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73748111724854</t>
   </si>
   <si>
     <t xml:space="preserve">9.74202346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78289985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70114707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46043586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29693222045898</t>
+    <t xml:space="preserve">9.78289890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70114803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46043491363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2969331741333</t>
   </si>
   <si>
     <t xml:space="preserve">9.51493740081787</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">9.49676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.410475730896</t>
+    <t xml:space="preserve">9.41047668457031</t>
   </si>
   <si>
     <t xml:space="preserve">9.35143375396729</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">9.57397937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63302135467529</t>
+    <t xml:space="preserve">9.63302040100098</t>
   </si>
   <si>
     <t xml:space="preserve">9.34689235687256</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">9.20155715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06530380249023</t>
+    <t xml:space="preserve">9.06530475616455</t>
   </si>
   <si>
     <t xml:space="preserve">9.03805446624756</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">8.85184288024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90634441375732</t>
+    <t xml:space="preserve">8.90634346008301</t>
   </si>
   <si>
     <t xml:space="preserve">8.95176029205322</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">9.21972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36505889892578</t>
+    <t xml:space="preserve">9.3650598526001</t>
   </si>
   <si>
     <t xml:space="preserve">9.29239082336426</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">9.31964206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43772792816162</t>
+    <t xml:space="preserve">9.4377269744873</t>
   </si>
   <si>
     <t xml:space="preserve">9.40139293670654</t>
@@ -5493,6 +5493,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.77999973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67500019073486</t>
   </si>
 </sst>
 </file>
@@ -70519,7 +70522,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6525462963</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1461173</v>
@@ -70540,6 +70543,32 @@
         <v>1826</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6510648148</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>1619406</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>9.82499980926514</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>9.63000011444092</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>9.77499961853027</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>9.67500019073486</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1827</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1829">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">3.46296906471252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45607137680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986818313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331595420837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845662117004</t>
+    <t xml:space="preserve">3.45607018470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986746788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331643104553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812421798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845614433289</t>
   </si>
   <si>
     <t xml:space="preserve">3.3470766544342</t>
@@ -71,46 +71,46 @@
     <t xml:space="preserve">3.28637170791626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21324896812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03803110122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13874697685242</t>
+    <t xml:space="preserve">3.21324872970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03803086280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.138747215271</t>
   </si>
   <si>
     <t xml:space="preserve">3.14288568496704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1649603843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736748695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119517326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20910954475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20773029327393</t>
+    <t xml:space="preserve">3.10425543785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16495990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736653327942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20911026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2077305316925</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631944656372</t>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">3.00215983390808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9980206489563</t>
+    <t xml:space="preserve">2.99802088737488</t>
   </si>
   <si>
     <t xml:space="preserve">3.02837300300598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07114315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1111536026001</t>
+    <t xml:space="preserve">3.07114338874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115336418152</t>
   </si>
   <si>
     <t xml:space="preserve">3.18151640892029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13046836853027</t>
+    <t xml:space="preserve">3.13046860694885</t>
   </si>
   <si>
     <t xml:space="preserve">3.14150595664978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12495040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11805200576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1732382774353</t>
+    <t xml:space="preserve">3.12494969367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11805176734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808240890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323875427246</t>
   </si>
   <si>
     <t xml:space="preserve">3.19531321525574</t>
@@ -167,67 +167,67 @@
     <t xml:space="preserve">3.18703532218933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013691902161</t>
+    <t xml:space="preserve">3.0932183265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013668060303</t>
   </si>
   <si>
     <t xml:space="preserve">3.19255352020264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18427562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636054039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20635056495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10563445091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906868934631</t>
+    <t xml:space="preserve">3.18427634239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20635080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1980721950531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10563468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906845092773</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03941082954407</t>
+    <t xml:space="preserve">3.03941059112549</t>
   </si>
   <si>
     <t xml:space="preserve">3.00491881370544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05182814598083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422455787659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05044770240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320715904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595664024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147531509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767803192139</t>
+    <t xml:space="preserve">3.0518274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422408103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.050448179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147507667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629830360413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767850875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.02561402320862</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">3.09873652458191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08769869804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0559663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838393211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319742202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0297532081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01871562004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766781806946</t>
+    <t xml:space="preserve">3.0876989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978432655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05596661567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838345527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319718360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02975296974182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01871585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766805648804</t>
   </si>
   <si>
     <t xml:space="preserve">2.95249152183533</t>
@@ -266,31 +266,31 @@
     <t xml:space="preserve">2.9442138671875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0223593711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02659177780151</t>
+    <t xml:space="preserve">2.93869543075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593525886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235913276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02659225463867</t>
   </si>
   <si>
     <t xml:space="preserve">2.99837207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98426151275635</t>
+    <t xml:space="preserve">2.98426198959351</t>
   </si>
   <si>
     <t xml:space="preserve">2.99131679534912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97861838340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06892156600952</t>
+    <t xml:space="preserve">2.97861814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06892228126526</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610035896301</t>
@@ -299,37 +299,37 @@
     <t xml:space="preserve">3.01389312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0209481716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00683784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03505778312683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96450853347778</t>
+    <t xml:space="preserve">3.02094793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00683808326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929090499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671528816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03505802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99978256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9645082950592</t>
   </si>
   <si>
     <t xml:space="preserve">2.86714935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80083250999451</t>
+    <t xml:space="preserve">2.80083203315735</t>
   </si>
   <si>
     <t xml:space="preserve">2.87843728065491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93205547332764</t>
+    <t xml:space="preserve">2.93205523490906</t>
   </si>
   <si>
     <t xml:space="preserve">2.87702608108521</t>
@@ -338,40 +338,40 @@
     <t xml:space="preserve">2.91089010238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61034727096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67525362968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.718994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79659938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79518866539001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162830352783</t>
+    <t xml:space="preserve">2.72181630134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61034750938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67525339126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71899437904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79659914970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79518818855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162806510925</t>
   </si>
   <si>
     <t xml:space="preserve">2.83610725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87279343605042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94475388526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97438502311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00542712211609</t>
+    <t xml:space="preserve">2.87279319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94475412368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97438526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00542759895325</t>
   </si>
   <si>
     <t xml:space="preserve">3.02518105506897</t>
@@ -380,16 +380,16 @@
     <t xml:space="preserve">3.04211282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07597684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0703330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05481219291687</t>
+    <t xml:space="preserve">3.07597732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364682197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07033324241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05481195449829</t>
   </si>
   <si>
     <t xml:space="preserve">3.03788018226624</t>
@@ -401,37 +401,37 @@
     <t xml:space="preserve">3.17333579063416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16204786300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1549928188324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14088296890259</t>
+    <t xml:space="preserve">3.16204762458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15499305725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14088344573975</t>
   </si>
   <si>
     <t xml:space="preserve">3.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1084303855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149813652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947200775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15075969696045</t>
+    <t xml:space="preserve">3.10842990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149789810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947224617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15075993537903</t>
   </si>
   <si>
     <t xml:space="preserve">3.10419702529907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08444333076477</t>
+    <t xml:space="preserve">3.08444356918335</t>
   </si>
   <si>
     <t xml:space="preserve">3.02800297737122</t>
@@ -440,49 +440,49 @@
     <t xml:space="preserve">3.01248216629028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02376961708069</t>
+    <t xml:space="preserve">3.02376985549927</t>
   </si>
   <si>
     <t xml:space="preserve">3.0717442035675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604555606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646898269653</t>
+    <t xml:space="preserve">3.06045579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646874427795</t>
   </si>
   <si>
     <t xml:space="preserve">3.09008693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19732308387756</t>
+    <t xml:space="preserve">3.19732260704041</t>
   </si>
   <si>
     <t xml:space="preserve">3.21002221107483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18462371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2128438949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707653999329</t>
+    <t xml:space="preserve">3.18462347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21284365653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707677841187</t>
   </si>
   <si>
     <t xml:space="preserve">3.27774977684021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27351665496826</t>
+    <t xml:space="preserve">3.27351689338684</t>
   </si>
   <si>
     <t xml:space="preserve">3.22131013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20861101150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873404502869</t>
+    <t xml:space="preserve">3.20861029624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873380661011</t>
   </si>
   <si>
     <t xml:space="preserve">3.18180203437805</t>
@@ -494,70 +494,70 @@
     <t xml:space="preserve">3.15217089653015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16628074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1253616809845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125159263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08726501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09714198112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11548495292664</t>
+    <t xml:space="preserve">3.16628122329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12536191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08726525306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0971417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11548447608948</t>
   </si>
   <si>
     <t xml:space="preserve">3.08867597579956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.077388048172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06186723709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92923307418823</t>
+    <t xml:space="preserve">3.07738733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06186676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696135520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92923283576965</t>
   </si>
   <si>
     <t xml:space="preserve">2.95322012901306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95180916786194</t>
+    <t xml:space="preserve">2.95180940628052</t>
   </si>
   <si>
     <t xml:space="preserve">2.93911004066467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92076730728149</t>
+    <t xml:space="preserve">2.92076706886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.95886397361755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92782211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002910614014</t>
+    <t xml:space="preserve">2.92782235145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002934455872</t>
   </si>
   <si>
     <t xml:space="preserve">3.04493522644043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05622315406799</t>
+    <t xml:space="preserve">3.05622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.01953721046448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97720718383789</t>
+    <t xml:space="preserve">2.97720694541931</t>
   </si>
   <si>
     <t xml:space="preserve">2.99554991722107</t>
@@ -569,37 +569,37 @@
     <t xml:space="preserve">3.0181257724762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9630970954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92641115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849534988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138247489929</t>
+    <t xml:space="preserve">2.96309685707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92641091346741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849511146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138223648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.8572723865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86855983734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604205131531</t>
+    <t xml:space="preserve">2.86856007575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604181289673</t>
   </si>
   <si>
     <t xml:space="preserve">2.88690328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89819097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303950309753</t>
+    <t xml:space="preserve">2.89819121360779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303926467896</t>
   </si>
   <si>
     <t xml:space="preserve">2.84034037590027</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">2.84457325935364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85021686553955</t>
+    <t xml:space="preserve">2.85021710395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.78390049934387</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">2.79377722740173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82340788841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568056106567</t>
+    <t xml:space="preserve">2.82340836524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568032264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.76132440567017</t>
@@ -632,34 +632,34 @@
     <t xml:space="preserve">2.80929827690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89254713058472</t>
+    <t xml:space="preserve">2.8925473690033</t>
   </si>
   <si>
     <t xml:space="preserve">2.89395833015442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89960217475891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665745735168</t>
+    <t xml:space="preserve">2.89960265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009383201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665698051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.88831400871277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9123010635376</t>
+    <t xml:space="preserve">2.91230082511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.94052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09432005882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08020997047424</t>
+    <t xml:space="preserve">3.09431982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08020973205566</t>
   </si>
   <si>
     <t xml:space="preserve">3.08303189277649</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">3.10560822486877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08585381507874</t>
+    <t xml:space="preserve">3.08585405349731</t>
   </si>
   <si>
     <t xml:space="preserve">3.13523888587952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14511585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13806080818176</t>
+    <t xml:space="preserve">3.14511632919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13806056976318</t>
   </si>
   <si>
     <t xml:space="preserve">3.16063690185547</t>
@@ -686,49 +686,49 @@
     <t xml:space="preserve">3.17051362991333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20437788963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591212272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253999710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573101997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278606414795</t>
+    <t xml:space="preserve">3.20437812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1959114074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12254023551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278582572937</t>
   </si>
   <si>
     <t xml:space="preserve">3.09290885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751108169556</t>
+    <t xml:space="preserve">3.06751132011414</t>
   </si>
   <si>
     <t xml:space="preserve">3.11830687522888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17898011207581</t>
+    <t xml:space="preserve">3.17897987365723</t>
   </si>
   <si>
     <t xml:space="preserve">3.13664984703064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07456541061401</t>
+    <t xml:space="preserve">3.07456564903259</t>
   </si>
   <si>
     <t xml:space="preserve">3.10701894760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.098552942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529623985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26646208763123</t>
+    <t xml:space="preserve">3.09855318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529695510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26646161079407</t>
   </si>
   <si>
     <t xml:space="preserve">3.25376272201538</t>
@@ -737,94 +737,94 @@
     <t xml:space="preserve">3.25094056129456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29891467094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31443572044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228679656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651920318604</t>
+    <t xml:space="preserve">3.29891490936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31443619728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37228655815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651968002319</t>
   </si>
   <si>
     <t xml:space="preserve">3.4456582069397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41461706161499</t>
+    <t xml:space="preserve">3.41461658477783</t>
   </si>
   <si>
     <t xml:space="preserve">3.44283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40756177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40050673484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657774925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338648796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105669975281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47811055183411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798847198486</t>
+    <t xml:space="preserve">3.4075620174408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4005069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4865779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160666465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.478111743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798823356628</t>
   </si>
   <si>
     <t xml:space="preserve">3.52185273170471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50633144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222159385681</t>
+    <t xml:space="preserve">3.5063316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222135543823</t>
   </si>
   <si>
     <t xml:space="preserve">3.56277132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53455185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5274965763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866218566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056456565857</t>
+    <t xml:space="preserve">3.53455114364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866147041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056408882141</t>
   </si>
   <si>
     <t xml:space="preserve">3.59099149703979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61568355560303</t>
+    <t xml:space="preserve">3.61568331718445</t>
   </si>
   <si>
     <t xml:space="preserve">3.58393621444702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50209856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924439430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273955345154</t>
+    <t xml:space="preserve">3.50209879875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62273931503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.65095901489258</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">3.66154170036316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66506910324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921167373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804677963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7375226020813</t>
+    <t xml:space="preserve">3.66506886482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332152366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73752284049988</t>
   </si>
   <si>
     <t xml:space="preserve">3.6866717338562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72299385070801</t>
+    <t xml:space="preserve">3.72299361228943</t>
   </si>
   <si>
     <t xml:space="preserve">3.71936130523682</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.70483326911926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66124701499939</t>
+    <t xml:space="preserve">3.66124653816223</t>
   </si>
   <si>
     <t xml:space="preserve">3.83195948600769</t>
@@ -869,58 +869,58 @@
     <t xml:space="preserve">3.82832717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81379890441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285569190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85012054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88644194602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648776054382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8246955871582</t>
+    <t xml:space="preserve">3.81379818916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285616874695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85012030601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88644218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469487190247</t>
   </si>
   <si>
     <t xml:space="preserve">3.83922386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98451113700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455718994141</t>
+    <t xml:space="preserve">3.9845118522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097069740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455814361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.98087906837463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92639708518982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823531150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913199424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016659736633</t>
+    <t xml:space="preserve">3.92639636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913247108459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016683578491</t>
   </si>
   <si>
     <t xml:space="preserve">3.68303990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65761423110962</t>
+    <t xml:space="preserve">3.65761470794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.6133017539978</t>
@@ -932,70 +932,70 @@
     <t xml:space="preserve">3.60313200950623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59150815010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.624924659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214369773865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030404090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218927383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662568092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96635031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366050720215</t>
+    <t xml:space="preserve">3.59150838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492442131042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214322090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307361125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030451774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218951225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035033226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7157289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662615776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191367149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96635055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366098403931</t>
   </si>
   <si>
     <t xml:space="preserve">3.95908617973328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96998357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356935501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352306365967</t>
+    <t xml:space="preserve">3.96998286247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352258682251</t>
   </si>
   <si>
     <t xml:space="preserve">4.04989147186279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07894802093506</t>
+    <t xml:space="preserve">4.07894849777222</t>
   </si>
   <si>
     <t xml:space="preserve">4.00267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95182132720947</t>
+    <t xml:space="preserve">3.95182156562805</t>
   </si>
   <si>
     <t xml:space="preserve">3.91549968719482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00993680953979</t>
+    <t xml:space="preserve">4.00993633270264</t>
   </si>
   <si>
     <t xml:space="preserve">3.9954080581665</t>
@@ -1004,28 +1004,28 @@
     <t xml:space="preserve">3.99177575111389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02446508407593</t>
+    <t xml:space="preserve">4.0244665145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10437440872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271872520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89733862876892</t>
+    <t xml:space="preserve">4.10437393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464953422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8973388671875</t>
   </si>
   <si>
     <t xml:space="preserve">3.9881432056427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9554545879364</t>
+    <t xml:space="preserve">3.95545434951782</t>
   </si>
   <si>
     <t xml:space="preserve">3.93002867698669</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">4.01720142364502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88281011581421</t>
+    <t xml:space="preserve">3.88280987739563</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531642913818</t>
@@ -1043,58 +1043,58 @@
     <t xml:space="preserve">4.06805181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1479606628418</t>
+    <t xml:space="preserve">4.14796018600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.04625940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06078815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11526966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10800647735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12253427505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18065023422241</t>
+    <t xml:space="preserve">4.06078767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11527013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1080060005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12253475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18064975738525</t>
   </si>
   <si>
     <t xml:space="preserve">4.15885639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18791437149048</t>
+    <t xml:space="preserve">4.18791389465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.16612100601196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17338562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0971097946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14069557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.129798412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24602937698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22060251235962</t>
+    <t xml:space="preserve">4.17338514328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09710931777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14069509506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24602890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22060346603394</t>
   </si>
   <si>
     <t xml:space="preserve">4.26055717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2169713973999</t>
+    <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">4.26418972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239730834961</t>
+    <t xml:space="preserve">4.27508687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17701768875122</t>
@@ -1115,22 +1115,22 @@
     <t xml:space="preserve">4.08984470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30777645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4276385307312</t>
+    <t xml:space="preserve">4.30777597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29687929153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42763805389404</t>
   </si>
   <si>
     <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54023694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60198402404785</t>
+    <t xml:space="preserve">4.5402364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60198307037354</t>
   </si>
   <si>
     <t xml:space="preserve">4.59835147857666</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">4.72184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56929397583008</t>
+    <t xml:space="preserve">4.56929349899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.56202936172485</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">4.62014484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59471940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60924768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48938608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669603347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844310760498</t>
+    <t xml:space="preserve">4.59471893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60924673080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4893856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844358444214</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683395385742</t>
@@ -1172,46 +1172,46 @@
     <t xml:space="preserve">4.48575401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49301815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50391435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46032810211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306396484375</t>
+    <t xml:space="preserve">4.49301862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50391387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49665021896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46032857894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306444168091</t>
   </si>
   <si>
     <t xml:space="preserve">4.46759223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47848892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750108718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315559387207</t>
+    <t xml:space="preserve">4.4784893989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750156402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53660440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853521347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315607070923</t>
   </si>
   <si>
     <t xml:space="preserve">4.39131689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42037439346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29324722290039</t>
+    <t xml:space="preserve">4.42037487030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29324769973755</t>
   </si>
   <si>
     <t xml:space="preserve">4.40947771072388</t>
@@ -1223,31 +1223,31 @@
     <t xml:space="preserve">4.42400646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28235101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20607471466064</t>
+    <t xml:space="preserve">4.31140851974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28235149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20607566833496</t>
   </si>
   <si>
     <t xml:space="preserve">4.12616682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23149967193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432764053345</t>
+    <t xml:space="preserve">4.23150062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432811737061</t>
   </si>
   <si>
     <t xml:space="preserve">3.97361469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94092535972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97724676132202</t>
+    <t xml:space="preserve">3.94092583656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724723815918</t>
   </si>
   <si>
     <t xml:space="preserve">4.08258008956909</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">4.44579982757568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40584516525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4167423248291</t>
+    <t xml:space="preserve">4.40584564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41674184799194</t>
   </si>
   <si>
     <t xml:space="preserve">4.59108734130859</t>
@@ -1274,52 +1274,52 @@
     <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55113363265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655811309814</t>
+    <t xml:space="preserve">4.55113315582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57655954360962</t>
   </si>
   <si>
     <t xml:space="preserve">4.52933979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570819854736</t>
+    <t xml:space="preserve">4.52570772171021</t>
   </si>
   <si>
     <t xml:space="preserve">4.53297185897827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67825984954834</t>
+    <t xml:space="preserve">4.67825937271118</t>
   </si>
   <si>
     <t xml:space="preserve">4.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67099523544312</t>
+    <t xml:space="preserve">4.6709942817688</t>
   </si>
   <si>
     <t xml:space="preserve">4.64557027816772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65283393859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75816774368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75090360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76179981231689</t>
+    <t xml:space="preserve">4.65283489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75816822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75090312957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76180028915405</t>
   </si>
   <si>
     <t xml:space="preserve">4.7254786491394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68552350997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7291111946106</t>
+    <t xml:space="preserve">4.68552398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911024093628</t>
   </si>
   <si>
     <t xml:space="preserve">4.65646648406982</t>
@@ -1328,85 +1328,85 @@
     <t xml:space="preserve">4.84533977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81265020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81991577148438</t>
+    <t xml:space="preserve">4.81265068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81991529464722</t>
   </si>
   <si>
     <t xml:space="preserve">4.83807563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166189193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8489727973938</t>
+    <t xml:space="preserve">4.88166236877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">4.91798448562622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89255857467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95430612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94704151153564</t>
+    <t xml:space="preserve">4.89255952835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94704103469849</t>
   </si>
   <si>
     <t xml:space="preserve">4.93977785110474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9325122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99062824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713409423828</t>
+    <t xml:space="preserve">4.93251276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99062776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713361740112</t>
   </si>
   <si>
     <t xml:space="preserve">4.7330756187439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87888240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86018848419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82654047012329</t>
+    <t xml:space="preserve">4.87888145446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86018896102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82654094696045</t>
   </si>
   <si>
     <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65082597732544</t>
+    <t xml:space="preserve">4.65082693099976</t>
   </si>
   <si>
     <t xml:space="preserve">4.49380540847778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62091779708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699718475342</t>
+    <t xml:space="preserve">4.62091732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699670791626</t>
   </si>
   <si>
     <t xml:space="preserve">4.63587188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7480297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72186040878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690584182739</t>
+    <t xml:space="preserve">4.74803066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72185945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690536499023</t>
   </si>
   <si>
     <t xml:space="preserve">4.57979297637939</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">4.75924587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83028030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93495988845825</t>
+    <t xml:space="preserve">4.83027935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496036529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.85644960403442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8153247833252</t>
+    <t xml:space="preserve">4.81532526016235</t>
   </si>
   <si>
     <t xml:space="preserve">4.94243764877319</t>
@@ -1433,49 +1433,49 @@
     <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91626739501953</t>
+    <t xml:space="preserve">4.91626644134521</t>
   </si>
   <si>
     <t xml:space="preserve">4.90505123138428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88262033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93869924545288</t>
+    <t xml:space="preserve">4.88261985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93869876861572</t>
   </si>
   <si>
     <t xml:space="preserve">4.96486902236938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03216457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01721000671387</t>
+    <t xml:space="preserve">5.03216505050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01720952987671</t>
   </si>
   <si>
     <t xml:space="preserve">5.13684511184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0583348274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98356199264526</t>
+    <t xml:space="preserve">5.05833435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98356246948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.89757490158081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12936878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24900388717651</t>
+    <t xml:space="preserve">5.12936782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24900341033936</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3162989616394</t>
+    <t xml:space="preserve">5.31629943847656</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350221633911</t>
@@ -1490,16 +1490,16 @@
     <t xml:space="preserve">5.01347160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17797040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20040225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274181365967</t>
+    <t xml:space="preserve">5.17796993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20040082931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274276733398</t>
   </si>
   <si>
     <t xml:space="preserve">5.20787906646729</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">5.21535587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22283315658569</t>
+    <t xml:space="preserve">5.22283363342285</t>
   </si>
   <si>
     <t xml:space="preserve">5.19666290283203</t>
@@ -1517,37 +1517,37 @@
     <t xml:space="preserve">5.11815214157104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04337978363037</t>
+    <t xml:space="preserve">5.04338026046753</t>
   </si>
   <si>
     <t xml:space="preserve">4.99851703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11067581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17049217224121</t>
+    <t xml:space="preserve">5.11067533493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17049264907837</t>
   </si>
   <si>
     <t xml:space="preserve">5.04711866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441326141357</t>
+    <t xml:space="preserve">5.11441373825073</t>
   </si>
   <si>
     <t xml:space="preserve">5.06581163406372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97982406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95739269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0396409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05459547042847</t>
+    <t xml:space="preserve">4.97982358932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95739221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03964138031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05459642410278</t>
   </si>
   <si>
     <t xml:space="preserve">5.08076667785645</t>
@@ -1556,55 +1556,55 @@
     <t xml:space="preserve">5.18544721603394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09572124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21161794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8863582611084</t>
+    <t xml:space="preserve">5.09572076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2116174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88635873794556</t>
   </si>
   <si>
     <t xml:space="preserve">4.920006275177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77420091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672220230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073606491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71064472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67325830459595</t>
+    <t xml:space="preserve">4.77420043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66951942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71064519882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67325782775879</t>
   </si>
   <si>
     <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62839460372925</t>
+    <t xml:space="preserve">4.62839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">4.5685772895813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58727073669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69568967819214</t>
+    <t xml:space="preserve">4.58727025985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568920135498</t>
   </si>
   <si>
     <t xml:space="preserve">4.56109952926636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40781688690186</t>
+    <t xml:space="preserve">4.40781736373901</t>
   </si>
   <si>
     <t xml:space="preserve">4.61344051361084</t>
@@ -1619,112 +1619,112 @@
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.792893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167867660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77793884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140369415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83775568008423</t>
+    <t xml:space="preserve">4.79289388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766576766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915548324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7779393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83775663375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74055290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60222482681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54988384246826</t>
+    <t xml:space="preserve">4.71812105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74055242538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6022253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54988431930542</t>
   </si>
   <si>
     <t xml:space="preserve">4.52371406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51997566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46015787124634</t>
+    <t xml:space="preserve">4.51997470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48632764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903257369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46015739440918</t>
   </si>
   <si>
     <t xml:space="preserve">4.64334917068481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66204261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456533432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298475265503</t>
+    <t xml:space="preserve">4.66204214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298427581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.73681449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86392641067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806079864502</t>
+    <t xml:space="preserve">4.86392736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806127548218</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21909427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22657203674316</t>
+    <t xml:space="preserve">5.21909475326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22657155990601</t>
   </si>
   <si>
     <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15179967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20414066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37237739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620761871338</t>
+    <t xml:space="preserve">5.15179920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20414018630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37237691879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16675472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620714187622</t>
   </si>
   <si>
     <t xml:space="preserve">6.09018993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87335062026978</t>
+    <t xml:space="preserve">5.87335109710693</t>
   </si>
   <si>
     <t xml:space="preserve">5.79483938217163</t>
@@ -1733,58 +1733,58 @@
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79110145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75745391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87708950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195272445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924779891968</t>
+    <t xml:space="preserve">5.81353378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79110193252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75745439529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87708902359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924732208252</t>
   </si>
   <si>
     <t xml:space="preserve">6.01167917251587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02663469314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9630765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00794076919556</t>
+    <t xml:space="preserve">6.02663421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96307706832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0079402923584</t>
   </si>
   <si>
     <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93316841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699911117554</t>
+    <t xml:space="preserve">5.93316888809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699768066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.94064569473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0789737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93690729141235</t>
+    <t xml:space="preserve">6.07897424697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9369068145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.95933818817139</t>
@@ -1793,22 +1793,22 @@
     <t xml:space="preserve">5.89952087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89578199386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88082790374756</t>
+    <t xml:space="preserve">5.89578247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8808274269104</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812297821045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95560073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97429275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114152908325</t>
+    <t xml:space="preserve">5.95560026168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97429323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114200592041</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
@@ -1817,16 +1817,16 @@
     <t xml:space="preserve">5.840660572052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75234031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69473934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68322038650513</t>
+    <t xml:space="preserve">5.75234079360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69474029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778059005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68321990966797</t>
   </si>
   <si>
     <t xml:space="preserve">5.66402006149292</t>
@@ -1835,40 +1835,40 @@
     <t xml:space="preserve">5.66786003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78306102752686</t>
+    <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
     <t xml:space="preserve">5.70625972747803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002073287964</t>
+    <t xml:space="preserve">5.76002025604248</t>
   </si>
   <si>
     <t xml:space="preserve">5.87522077560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82146120071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74850082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69858121871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64481973648071</t>
+    <t xml:space="preserve">5.82146072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74850034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69858026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64482021331787</t>
   </si>
   <si>
     <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77538061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72162055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81762075424194</t>
+    <t xml:space="preserve">5.77537965774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72162008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81762027740479</t>
   </si>
   <si>
     <t xml:space="preserve">5.78690099716187</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">6.0557017326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28226184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474174499512</t>
+    <t xml:space="preserve">6.28226232528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474126815796</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">6.22850179672241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19394111633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06722211837769</t>
+    <t xml:space="preserve">6.19394159317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06722164154053</t>
   </si>
   <si>
     <t xml:space="preserve">6.10178184509277</t>
@@ -1910,253 +1910,253 @@
     <t xml:space="preserve">6.17090177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16706228256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29378175735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746332168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43586301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46274280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210248947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35522270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44738388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52802276611328</t>
+    <t xml:space="preserve">6.16706132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29378223419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43586254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4627423286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35522222518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44738292694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5280237197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.53954362869263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57410287857056</t>
+    <t xml:space="preserve">6.57410335540771</t>
   </si>
   <si>
     <t xml:space="preserve">6.58946323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62018299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322328567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786388397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626405715942</t>
+    <t xml:space="preserve">6.62018442153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626310348511</t>
   </si>
   <si>
     <t xml:space="preserve">6.80450391769409</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83138513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522367477417</t>
+    <t xml:space="preserve">6.83138418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522462844849</t>
   </si>
   <si>
     <t xml:space="preserve">6.78914403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76610422134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114538192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554430007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338359832764</t>
+    <t xml:space="preserve">6.76610565185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634397506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338407516479</t>
   </si>
   <si>
     <t xml:space="preserve">6.79298400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14626550674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642534255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0080246925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99266386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0617847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714509963989</t>
+    <t xml:space="preserve">7.14626598358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026578903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99266481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10402488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06178426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330560684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714557647705</t>
   </si>
   <si>
     <t xml:space="preserve">7.00034427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96578502655029</t>
+    <t xml:space="preserve">6.96578407287598</t>
   </si>
   <si>
     <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02722406387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186609268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274425506592</t>
+    <t xml:space="preserve">7.02722454071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274473190308</t>
   </si>
   <si>
     <t xml:space="preserve">7.04258441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09634447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7507438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506526947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9043436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02338552474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15778589248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16546535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850421905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706565856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698526382446</t>
+    <t xml:space="preserve">7.09634590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074338912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93506383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0233850479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346448898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15778541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602670669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16930532455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850469589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706518173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698574066162</t>
   </si>
   <si>
     <t xml:space="preserve">7.19234561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15010595321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210681915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43426752090454</t>
+    <t xml:space="preserve">7.15010643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210634231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43426656723022</t>
   </si>
   <si>
     <t xml:space="preserve">7.45730590820312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34978580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11938619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22306537628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11554622650146</t>
+    <t xml:space="preserve">7.34978628158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658710479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066492080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2230658531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11554574966431</t>
   </si>
   <si>
     <t xml:space="preserve">7.06562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08866405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9849853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77378416061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88898468017578</t>
+    <t xml:space="preserve">7.08866548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98498487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77378368377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88898515701294</t>
   </si>
   <si>
     <t xml:space="preserve">6.9273853302002</t>
@@ -2165,40 +2165,40 @@
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290409088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86210441589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8467435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08098554611206</t>
+    <t xml:space="preserve">6.91202545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290456771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210489273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674453735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08098459243774</t>
   </si>
   <si>
     <t xml:space="preserve">7.03106451034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05794477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87746524810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306392669678</t>
+    <t xml:space="preserve">7.05794525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842428207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218385696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87746429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306344985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
@@ -2207,52 +2207,52 @@
     <t xml:space="preserve">6.72002363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89282417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466375350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778444290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234273910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770645141602</t>
+    <t xml:space="preserve">6.89282464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682397842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78530502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7353835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2077054977417</t>
   </si>
   <si>
     <t xml:space="preserve">7.17314624786377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22690582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1117057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25762605667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986524581909</t>
+    <t xml:space="preserve">7.22690486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002603530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11170482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986619949341</t>
   </si>
   <si>
     <t xml:space="preserve">7.33826589584351</t>
@@ -2261,40 +2261,40 @@
     <t xml:space="preserve">7.37282657623291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58786773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17922973632812</t>
+    <t xml:space="preserve">7.58786678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466665267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362722396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17922878265381</t>
   </si>
   <si>
     <t xml:space="preserve">7.8643479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77218818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186563491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130571365356</t>
+    <t xml:space="preserve">7.77218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130619049072</t>
   </si>
   <si>
     <t xml:space="preserve">7.56482696533203</t>
@@ -2303,52 +2303,52 @@
     <t xml:space="preserve">7.61858654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68002700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898565292358</t>
+    <t xml:space="preserve">7.6800274848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898756027222</t>
   </si>
   <si>
     <t xml:space="preserve">6.91970491409302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89442110061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27458190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77154111862183</t>
+    <t xml:space="preserve">5.8944206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27458238601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77154064178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.26690196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33602237701416</t>
+    <t xml:space="preserve">6.33602285385132</t>
   </si>
   <si>
     <t xml:space="preserve">7.15394496917725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21922636032104</t>
+    <t xml:space="preserve">7.21922588348389</t>
   </si>
   <si>
     <t xml:space="preserve">7.58018684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59938812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2717809677124</t>
+    <t xml:space="preserve">7.59938764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27178192138672</t>
   </si>
   <si>
     <t xml:space="preserve">7.8802170753479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57022857666016</t>
+    <t xml:space="preserve">7.57023000717163</t>
   </si>
   <si>
     <t xml:space="preserve">7.64364862442017</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">8.35335731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72860431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03043556213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95701694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70413303375244</t>
+    <t xml:space="preserve">8.72860622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03043365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95701789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70413208007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.75307750701904</t>
@@ -2378,25 +2378,25 @@
     <t xml:space="preserve">7.99442338943481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8312726020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969625473022</t>
+    <t xml:space="preserve">7.83127212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969577789307</t>
   </si>
   <si>
     <t xml:space="preserve">7.81903553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79864263534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613821029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6803560256958</t>
+    <t xml:space="preserve">7.79864168167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
     <t xml:space="preserve">7.5090479850769</t>
@@ -2405,31 +2405,31 @@
     <t xml:space="preserve">7.50496959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70483016967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377607345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94547700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85574388504028</t>
+    <t xml:space="preserve">7.70482873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653253555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94547748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8557448387146</t>
   </si>
   <si>
     <t xml:space="preserve">7.94010877609253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98146295547485</t>
+    <t xml:space="preserve">7.9814624786377</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78709506988525</t>
+    <t xml:space="preserve">7.78709554672241</t>
   </si>
   <si>
     <t xml:space="preserve">7.75814771652222</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">7.58032178878784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51828956604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73333549499512</t>
+    <t xml:space="preserve">7.5182900428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73333501815796</t>
   </si>
   <si>
     <t xml:space="preserve">7.65062475204468</t>
@@ -2459,43 +2459,43 @@
     <t xml:space="preserve">7.55551052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53483200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45212268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49347734451294</t>
+    <t xml:space="preserve">7.53483247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49347686767578</t>
   </si>
   <si>
     <t xml:space="preserve">7.63408279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663194656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941289901733</t>
+    <t xml:space="preserve">7.40249586105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941337585449</t>
   </si>
   <si>
     <t xml:space="preserve">7.58445739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48520708084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235401153564</t>
+    <t xml:space="preserve">7.48520660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6423544883728</t>
   </si>
   <si>
     <t xml:space="preserve">7.52656221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75401210784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919988632202</t>
+    <t xml:space="preserve">7.75401306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919893264771</t>
   </si>
   <si>
     <t xml:space="preserve">7.37354898452759</t>
@@ -2504,19 +2504,19 @@
     <t xml:space="preserve">7.44385242462158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34460020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009141921997</t>
+    <t xml:space="preserve">7.34459972381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009094238281</t>
   </si>
   <si>
     <t xml:space="preserve">7.37768459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73746967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69197988510132</t>
+    <t xml:space="preserve">7.73746919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69198036193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.77468967437744</t>
@@ -2525,25 +2525,25 @@
     <t xml:space="preserve">7.72506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68784475326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6216778755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438671112061</t>
+    <t xml:space="preserve">7.68784427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67543745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62167739868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438623428345</t>
   </si>
   <si>
     <t xml:space="preserve">7.71265745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242517471313</t>
+    <t xml:space="preserve">7.62581205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242565155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.42317390441895</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">7.33632898330688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36527729034424</t>
+    <t xml:space="preserve">7.3652777671814</t>
   </si>
   <si>
     <t xml:space="preserve">7.25775480270386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08406496047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02203321456909</t>
+    <t xml:space="preserve">7.08406543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02203273773193</t>
   </si>
   <si>
     <t xml:space="preserve">6.95586538314819</t>
@@ -2576,31 +2576,31 @@
     <t xml:space="preserve">7.09647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07165908813477</t>
+    <t xml:space="preserve">7.07165956497192</t>
   </si>
   <si>
     <t xml:space="preserve">7.24534845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17091035842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03443956375122</t>
+    <t xml:space="preserve">7.17091083526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.98894929885864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93932437896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05511713027954</t>
+    <t xml:space="preserve">6.93932390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0551176071167</t>
   </si>
   <si>
     <t xml:space="preserve">6.91864633560181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90624046325684</t>
+    <t xml:space="preserve">6.90624094009399</t>
   </si>
   <si>
     <t xml:space="preserve">6.95173072814941</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">6.89796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98481416702271</t>
+    <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.93105268478394</t>
@@ -2621,49 +2621,49 @@
     <t xml:space="preserve">6.75322771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78217554092407</t>
+    <t xml:space="preserve">6.78217601776123</t>
   </si>
   <si>
     <t xml:space="preserve">6.96413660049438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.947594165802</t>
+    <t xml:space="preserve">6.94759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324506759644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43558025360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700654983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.489342212677</t>
+    <t xml:space="preserve">7.43558073043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700702667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48934173583984</t>
   </si>
   <si>
     <t xml:space="preserve">7.59272956848145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80777215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60927104949951</t>
+    <t xml:space="preserve">7.80777263641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
     <t xml:space="preserve">7.71679210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72092771530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085702896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190919876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845067977905</t>
+    <t xml:space="preserve">7.72092819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82845115661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.8367223739624</t>
@@ -2672,10 +2672,10 @@
     <t xml:space="preserve">7.96078443527222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84912633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716814041138</t>
+    <t xml:space="preserve">7.84912729263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716766357422</t>
   </si>
   <si>
     <t xml:space="preserve">7.67957353591919</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">7.60513401031494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59686422348022</t>
+    <t xml:space="preserve">7.59686517715454</t>
   </si>
   <si>
     <t xml:space="preserve">7.57205104827881</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.20064258575439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15515232086182</t>
+    <t xml:space="preserve">8.15515327453613</t>
   </si>
   <si>
     <t xml:space="preserve">8.4777193069458</t>
@@ -2720,40 +2720,40 @@
     <t xml:space="preserve">8.5604305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40328121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4115514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28748893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33711433410645</t>
+    <t xml:space="preserve">8.40328216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41155242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33711338043213</t>
   </si>
   <si>
     <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68449401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55215930938721</t>
+    <t xml:space="preserve">8.68449306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55215835571289</t>
   </si>
   <si>
     <t xml:space="preserve">8.25026893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59351348876953</t>
+    <t xml:space="preserve">8.59351253509521</t>
   </si>
   <si>
     <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92435073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99051856994629</t>
+    <t xml:space="preserve">8.92435169219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99051761627197</t>
   </si>
   <si>
     <t xml:space="preserve">8.8002872467041</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365676879883</t>
+    <t xml:space="preserve">8.35365581512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">8.18823623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13861179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24199771881104</t>
+    <t xml:space="preserve">8.13861083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32057285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24199867248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
@@ -2801,49 +2801,49 @@
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95665073394775</t>
+    <t xml:space="preserve">7.95664978027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.86980581283569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85326242446899</t>
+    <t xml:space="preserve">7.85326337814331</t>
   </si>
   <si>
     <t xml:space="preserve">7.89875316619873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74574136734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303157806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415395736694</t>
+    <t xml:space="preserve">7.74574184417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65475988388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415491104126</t>
   </si>
   <si>
     <t xml:space="preserve">7.44798707962036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33219480514526</t>
+    <t xml:space="preserve">7.33219337463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43144416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50588417053223</t>
+    <t xml:space="preserve">7.46866369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43144512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50588321685791</t>
   </si>
   <si>
     <t xml:space="preserve">7.82017946243286</t>
@@ -2861,34 +2861,34 @@
     <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02616834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12542009353638</t>
+    <t xml:space="preserve">7.02616882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09233570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12542057037354</t>
   </si>
   <si>
     <t xml:space="preserve">7.28670454025269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12955570220947</t>
+    <t xml:space="preserve">7.12955617904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271078109741</t>
+    <t xml:space="preserve">7.04271125793457</t>
   </si>
   <si>
     <t xml:space="preserve">7.16263914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29910945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053575515747</t>
+    <t xml:space="preserve">7.2991099357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053623199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.53896713256836</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">7.70025110244751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80281066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03108882904053</t>
+    <t xml:space="preserve">7.80281019210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03108787536621</t>
   </si>
   <si>
     <t xml:space="preserve">7.88386631011963</t>
@@ -2915,28 +2915,28 @@
     <t xml:space="preserve">7.77138090133667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79453992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190525054932</t>
+    <t xml:space="preserve">7.79453945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190572738647</t>
   </si>
   <si>
     <t xml:space="preserve">7.86732339859009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81273603439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6969428062439</t>
+    <t xml:space="preserve">7.81273460388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69694328308105</t>
   </si>
   <si>
     <t xml:space="preserve">8.05590057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319269180298</t>
+    <t xml:space="preserve">7.97319221496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.99635076522827</t>
@@ -2948,91 +2948,91 @@
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9996600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02281856536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05093860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003366470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88055801391602</t>
+    <t xml:space="preserve">7.99965953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02281761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05093955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845415115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003414154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055753707886</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82431507110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0128927230835</t>
+    <t xml:space="preserve">7.8243145942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01289176940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.84416532516479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81604480743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63904523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66055107116699</t>
+    <t xml:space="preserve">7.81604337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63904619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66055011749268</t>
   </si>
   <si>
     <t xml:space="preserve">7.73498868942261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79480504989624</t>
+    <t xml:space="preserve">7.79480361938477</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967714309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847549438477</t>
+    <t xml:space="preserve">7.78967761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847597122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82385683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258777618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960735321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404237747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89221715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94007015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98963165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09388065338135</t>
+    <t xml:space="preserve">7.82385873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404285430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89221811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94006967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98963117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09388160705566</t>
   </si>
   <si>
     <t xml:space="preserve">8.18445873260498</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">8.24940204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28699970245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41517543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39808654785156</t>
+    <t xml:space="preserve">8.28700065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41517448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39808559417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.38099479675293</t>
@@ -3056,25 +3056,25 @@
     <t xml:space="preserve">8.46302795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44252014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2118034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36390495300293</t>
+    <t xml:space="preserve">8.44251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21180248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36390590667725</t>
   </si>
   <si>
     <t xml:space="preserve">8.31947135925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24427318572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19129467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12806224822998</t>
+    <t xml:space="preserve">8.2442741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1912956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12806129455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09900856018066</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11951637268066</t>
+    <t xml:space="preserve">8.11951541900635</t>
   </si>
   <si>
     <t xml:space="preserve">8.2271842956543</t>
@@ -3098,19 +3098,19 @@
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877895355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48011779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45619106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44081115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986293792725</t>
+    <t xml:space="preserve">8.35877704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48011875152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45619201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44081020355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46986389160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.40663051605225</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644592285156</t>
+    <t xml:space="preserve">8.46644687652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25965595245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32630729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24256420135498</t>
+    <t xml:space="preserve">8.25965690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32630634307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24256610870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">8.17420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28187274932861</t>
+    <t xml:space="preserve">8.28187370300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
@@ -3158,37 +3158,37 @@
     <t xml:space="preserve">8.35365104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45277500152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46473693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42030334472656</t>
+    <t xml:space="preserve">8.45277309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46473789215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50404453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42030239105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.50233554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66896438598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60060214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63478374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62623882293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61769390106201</t>
+    <t xml:space="preserve">8.66896343231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6476001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6006031036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6347827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6262378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6176929473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.5416431427002</t>
@@ -3203,10 +3203,10 @@
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822326660156</t>
+    <t xml:space="preserve">8.63051128387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822422027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">8.42372035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49208068847656</t>
+    <t xml:space="preserve">8.49208164215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.54506015777588</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143424987793</t>
+    <t xml:space="preserve">8.33143329620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.36561393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2340202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31434440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40492248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30579853057861</t>
+    <t xml:space="preserve">8.23401927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31434345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40492153167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30579948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.49720859527588</t>
@@ -3254,43 +3254,43 @@
     <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2323112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2152214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1793327331543</t>
+    <t xml:space="preserve">8.23231029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21522045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17933082580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166385650635</t>
+    <t xml:space="preserve">8.07166481018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.08875465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99475860595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23914813995361</t>
+    <t xml:space="preserve">7.99475812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.33485126495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40150260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2545280456543</t>
+    <t xml:space="preserve">8.40150356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31776142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452899932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">8.26478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31605434417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2169303894043</t>
+    <t xml:space="preserve">8.36048698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25111103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31605243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21692943572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
@@ -3323,28 +3323,28 @@
     <t xml:space="preserve">8.32972526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45106601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44935607910156</t>
+    <t xml:space="preserve">8.45106410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44935512542725</t>
   </si>
   <si>
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50575351715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49891757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47669982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02358531951904</t>
+    <t xml:space="preserve">8.56642246246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50575256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4989185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47670078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02358341217041</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
@@ -3362,16 +3362,16 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704734802246</t>
+    <t xml:space="preserve">8.82704639434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.71168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65614700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72023487091064</t>
+    <t xml:space="preserve">8.65614604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72023391723633</t>
   </si>
   <si>
     <t xml:space="preserve">8.72450637817383</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">8.6390552520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6091480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69459915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75441551208496</t>
+    <t xml:space="preserve">8.60914707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69460010528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75441455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.77150535583496</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">8.88686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88259124755859</t>
+    <t xml:space="preserve">8.88259029388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531490325928</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">8.92104244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98940372467041</t>
+    <t xml:space="preserve">8.98940467834473</t>
   </si>
   <si>
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20303058624268</t>
+    <t xml:space="preserve">9.12612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20302963256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.03212833404541</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">8.98513126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70741653442383</t>
+    <t xml:space="preserve">8.70741558074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.5877857208252</t>
@@ -3440,37 +3440,37 @@
     <t xml:space="preserve">8.28870868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1588249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08020973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2066764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35706806182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78455066680908</t>
+    <t xml:space="preserve">8.26136493682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15882396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08021068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20667552947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35706901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454971313477</t>
   </si>
   <si>
     <t xml:space="preserve">7.81873083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81360292434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8101863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12635326385498</t>
+    <t xml:space="preserve">7.81360387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81018590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540504455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12635231018066</t>
   </si>
   <si>
     <t xml:space="preserve">7.8802547454834</t>
@@ -3482,25 +3482,25 @@
     <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61364841461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54699754714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45129346847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58459711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953756332397</t>
+    <t xml:space="preserve">7.61364889144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54699659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45129299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58459615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953804016113</t>
   </si>
   <si>
     <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58288621902466</t>
+    <t xml:space="preserve">7.58288717269897</t>
   </si>
   <si>
     <t xml:space="preserve">7.48376417160034</t>
@@ -3509,46 +3509,46 @@
     <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055557250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556629180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5657958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6051025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78625917434692</t>
+    <t xml:space="preserve">7.69055461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579637527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510396957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78625965118408</t>
   </si>
   <si>
     <t xml:space="preserve">7.56237888336182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72302532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66491937637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77087736129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62561178207397</t>
+    <t xml:space="preserve">7.72302579879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66491985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77087688446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62561225891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9178524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95545244216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07508182525635</t>
+    <t xml:space="preserve">7.91785287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95545101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07508277893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.14173316955566</t>
@@ -3557,43 +3557,43 @@
     <t xml:space="preserve">8.2032585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2288932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48182582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50062561035156</t>
+    <t xml:space="preserve">8.22889232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48182773590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50062656402588</t>
   </si>
   <si>
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54335117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55787754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68178081512451</t>
+    <t xml:space="preserve">8.5433521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5578784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68178176879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.68605422973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73732376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82277488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97658538818359</t>
+    <t xml:space="preserve">8.73732471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82277393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97658634185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.93813323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404441833496</t>
+    <t xml:space="preserve">8.87404537200928</t>
   </si>
   <si>
     <t xml:space="preserve">8.89113521575928</t>
@@ -3602,28 +3602,28 @@
     <t xml:space="preserve">8.95095157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91676998138428</t>
+    <t xml:space="preserve">8.91677093505859</t>
   </si>
   <si>
     <t xml:space="preserve">8.90395259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81422996520996</t>
+    <t xml:space="preserve">8.81422901153564</t>
   </si>
   <si>
     <t xml:space="preserve">8.6134204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6732349395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69887256622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70314502716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74159717559814</t>
+    <t xml:space="preserve">8.67323589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69887161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70314407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74159622192383</t>
   </si>
   <si>
     <t xml:space="preserve">8.46131896972656</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">8.92368793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16630077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26775455474854</t>
+    <t xml:space="preserve">9.16629981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26775550842285</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20599937438965</t>
+    <t xml:space="preserve">9.20600032806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.14424324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18835544586182</t>
+    <t xml:space="preserve">9.1883544921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.1927661895752</t>
@@ -3677,13 +3677,13 @@
     <t xml:space="preserve">8.23820114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23996448516846</t>
+    <t xml:space="preserve">8.23996543884277</t>
   </si>
   <si>
     <t xml:space="preserve">8.25760936737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21702671051025</t>
+    <t xml:space="preserve">8.21702766418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.31583499908447</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">8.58932590484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57520961761475</t>
+    <t xml:space="preserve">8.57521057128906</t>
   </si>
   <si>
     <t xml:space="preserve">8.54344940185547</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">8.71636581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86634349822998</t>
+    <t xml:space="preserve">8.86634254455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.82223224639893</t>
@@ -3722,22 +3722,22 @@
     <t xml:space="preserve">8.80458736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7763557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91486644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93692207336426</t>
+    <t xml:space="preserve">8.77635669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91486549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93692111968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.84428787231445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8151741027832</t>
+    <t xml:space="preserve">8.85310935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517505645752</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">8.78694438934326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75341892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03396701812744</t>
+    <t xml:space="preserve">8.75341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03396606445312</t>
   </si>
   <si>
     <t xml:space="preserve">8.91045570373535</t>
@@ -3764,22 +3764,22 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55756568908691</t>
+    <t xml:space="preserve">8.5575647354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58756065368652</t>
+    <t xml:space="preserve">8.58756160736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.6157922744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77106475830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74459552764893</t>
+    <t xml:space="preserve">8.77106380462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74459648132324</t>
   </si>
   <si>
     <t xml:space="preserve">8.90163230895996</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">8.84869861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83546543121338</t>
+    <t xml:space="preserve">8.8354663848877</t>
   </si>
   <si>
     <t xml:space="preserve">8.68460559844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56638717651367</t>
+    <t xml:space="preserve">8.56638813018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.63167285919189</t>
@@ -3806,16 +3806,16 @@
     <t xml:space="preserve">8.34936046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29995536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16938781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10763072967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25584411621094</t>
+    <t xml:space="preserve">8.29995632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10763168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25584506988525</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">8.32818698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70754241943359</t>
+    <t xml:space="preserve">8.70754337310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.45699214935303</t>
@@ -3839,22 +3839,22 @@
     <t xml:space="preserve">8.39347171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08292865753174</t>
+    <t xml:space="preserve">8.08292961120605</t>
   </si>
   <si>
     <t xml:space="preserve">8.22584915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00352954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412397384644</t>
+    <t xml:space="preserve">8.0035285949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412540435791</t>
   </si>
   <si>
     <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92589378356934</t>
+    <t xml:space="preserve">7.92589426040649</t>
   </si>
   <si>
     <t xml:space="preserve">7.90471982955933</t>
@@ -3863,40 +3863,40 @@
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9135422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94706773757935</t>
+    <t xml:space="preserve">7.91354322433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94706726074219</t>
   </si>
   <si>
     <t xml:space="preserve">8.15703678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04411125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78473854064941</t>
+    <t xml:space="preserve">8.04411220550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78473806381226</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64534711837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39479494094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40538215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51124858856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64711093902588</t>
+    <t xml:space="preserve">7.64534759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39479541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40538167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51124811172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64711141586304</t>
   </si>
   <si>
     <t xml:space="preserve">7.43890619277954</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">7.3101019859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50948429107666</t>
+    <t xml:space="preserve">7.50948476791382</t>
   </si>
   <si>
     <t xml:space="preserve">7.73180437088013</t>
@@ -3917,46 +3917,46 @@
     <t xml:space="preserve">7.73709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75297832489014</t>
+    <t xml:space="preserve">7.75297737121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.87472438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88001775741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85355138778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94353771209717</t>
+    <t xml:space="preserve">7.88001823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85355091094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94353818893433</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08822345733643</t>
+    <t xml:space="preserve">8.08822250366211</t>
   </si>
   <si>
     <t xml:space="preserve">8.14291954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38817882537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76047611236572</t>
+    <t xml:space="preserve">8.3881778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76047706604004</t>
   </si>
   <si>
     <t xml:space="preserve">8.69872093200684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50286674499512</t>
+    <t xml:space="preserve">8.50286769866943</t>
   </si>
   <si>
     <t xml:space="preserve">8.4005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33524608612061</t>
+    <t xml:space="preserve">8.33524513244629</t>
   </si>
   <si>
     <t xml:space="preserve">8.48698711395264</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">8.48169422149658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49404525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40935134887695</t>
+    <t xml:space="preserve">8.49404621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40935230255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.28054714202881</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">8.47640132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46757888793945</t>
+    <t xml:space="preserve">8.46757793426514</t>
   </si>
   <si>
     <t xml:space="preserve">8.4269962310791</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">8.37053394317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36347579956055</t>
+    <t xml:space="preserve">8.36347675323486</t>
   </si>
   <si>
     <t xml:space="preserve">8.53286361694336</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">8.2152624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26466655731201</t>
+    <t xml:space="preserve">8.26466751098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.16232967376709</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">8.37582874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35112571716309</t>
+    <t xml:space="preserve">8.35112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.29642772674561</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">8.22937870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29819202423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41641044616699</t>
+    <t xml:space="preserve">8.29819107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41640853881836</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40758800506592</t>
+    <t xml:space="preserve">8.4075870513916</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4046,13 +4046,13 @@
     <t xml:space="preserve">8.55227184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64402294158936</t>
+    <t xml:space="preserve">8.64402389526367</t>
   </si>
   <si>
     <t xml:space="preserve">8.67049026489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61226272583008</t>
+    <t xml:space="preserve">8.61226367950439</t>
   </si>
   <si>
     <t xml:space="preserve">8.7887077331543</t>
@@ -4067,31 +4067,31 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456504821777</t>
+    <t xml:space="preserve">8.95456600189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91927719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8619327545166</t>
+    <t xml:space="preserve">8.91927623748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">8.89280986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11336612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89722061157227</t>
+    <t xml:space="preserve">9.11336517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89722156524658</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867630004883</t>
+    <t xml:space="preserve">8.99867725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">9.21041011810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26334381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2809886932373</t>
+    <t xml:space="preserve">9.26334476470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28098964691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15306663513184</t>
+    <t xml:space="preserve">9.15306568145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.14865493774414</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">9.13101005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13983154296875</t>
+    <t xml:space="preserve">9.13983249664307</t>
   </si>
   <si>
     <t xml:space="preserve">9.08248805999756</t>
@@ -4130,31 +4130,31 @@
     <t xml:space="preserve">9.93383407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0485229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74415493011475</t>
+    <t xml:space="preserve">10.0485219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74415588378906</t>
   </si>
   <si>
     <t xml:space="preserve">10.1411561965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1720342636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0264673233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78385639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0705785751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87207698822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706726074219</t>
+    <t xml:space="preserve">10.1720333099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0264663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78385543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.07057762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87207794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706630706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.77944469451904</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">10.5778560638428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6131448745728</t>
+    <t xml:space="preserve">10.6131458282471</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4190,7 +4190,7 @@
     <t xml:space="preserve">10.7278347015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8425226211548</t>
+    <t xml:space="preserve">10.8425235748291</t>
   </si>
   <si>
     <t xml:space="preserve">11.0013236999512</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">10.8601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.789589881897</t>
+    <t xml:space="preserve">10.7895889282227</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160572052002</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">10.868989944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.939567565918</t>
+    <t xml:space="preserve">10.9395685195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.8248796463013</t>
@@ -4229,43 +4229,43 @@
     <t xml:space="preserve">10.9439792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0189685821533</t>
+    <t xml:space="preserve">11.018967628479</t>
   </si>
   <si>
     <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0454359054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1248340606689</t>
+    <t xml:space="preserve">11.0454349517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1248350143433</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.09836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8645782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6969566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660795211792</t>
+    <t xml:space="preserve">11.0983686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8645792007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528453826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660785675049</t>
   </si>
   <si>
     <t xml:space="preserve">10.639612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4852228164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6352005004883</t>
+    <t xml:space="preserve">10.4852237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6352014541626</t>
   </si>
   <si>
     <t xml:space="preserve">10.8274974822998</t>
@@ -5496,6 +5496,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.6899995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78499984741211</t>
   </si>
 </sst>
 </file>
@@ -70574,7 +70577,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6496296296</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>1481615</v>
@@ -70595,6 +70598,32 @@
         <v>1827</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494328704</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>1096723</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>9.79500007629395</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>9.63000011444092</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>9.78499984741211</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1828</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1830">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,70 +44,70 @@
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296906471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45607018470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986746788025</t>
+    <t xml:space="preserve">3.46296882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4560706615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986794471741</t>
   </si>
   <si>
     <t xml:space="preserve">3.47331643104553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39812421798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845614433289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3470766544342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981496810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637170791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324872970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03803086280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.138747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288568496704</t>
+    <t xml:space="preserve">3.3981249332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34707713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981472969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28637146949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324849128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03803062438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13874697685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14288592338562</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425543785095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16495990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736653327942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945216178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222230911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20911026000977</t>
+    <t xml:space="preserve">3.16496086120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564538002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945192337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119517326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222254753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20910954475403</t>
   </si>
   <si>
     <t xml:space="preserve">3.2077305316925</t>
@@ -116,67 +116,67 @@
     <t xml:space="preserve">3.08631944656372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06700396537781</t>
+    <t xml:space="preserve">3.06700420379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.00078010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00215983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802088737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837300300598</t>
+    <t xml:space="preserve">3.00215935707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9980206489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837347984314</t>
   </si>
   <si>
     <t xml:space="preserve">3.07114338874817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13322830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151640892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046860694885</t>
+    <t xml:space="preserve">3.13322806358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1111536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046884536743</t>
   </si>
   <si>
     <t xml:space="preserve">3.14150595664978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12494969367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11805176734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531321525574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18703532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0932183265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427634239197</t>
+    <t xml:space="preserve">3.12494993209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11805129051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323851585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321808815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255375862122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427586555481</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636077880859</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">3.20635080337524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1980721950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10563468933105</t>
+    <t xml:space="preserve">3.19807314872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10563445091248</t>
   </si>
   <si>
     <t xml:space="preserve">3.04906845092773</t>
@@ -203,52 +203,52 @@
     <t xml:space="preserve">3.00491881370544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0518274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422408103943</t>
+    <t xml:space="preserve">3.05182766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422384262085</t>
   </si>
   <si>
     <t xml:space="preserve">3.050448179245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05320739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457643508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147507667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629830360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767850875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561402320862</t>
+    <t xml:space="preserve">3.05320763587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457619667053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767827033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0256142616272</t>
   </si>
   <si>
     <t xml:space="preserve">3.09873652458191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0876989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978432655334</t>
+    <t xml:space="preserve">3.08769917488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978384971619</t>
   </si>
   <si>
     <t xml:space="preserve">3.05596661567688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06838345527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319718360901</t>
+    <t xml:space="preserve">3.06838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.02975296974182</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">3.01871585845947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96766805648804</t>
+    <t xml:space="preserve">2.96766781806946</t>
   </si>
   <si>
     <t xml:space="preserve">2.95249152183533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9442138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869543075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593525886536</t>
+    <t xml:space="preserve">2.94421362876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869495391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593549728394</t>
   </si>
   <si>
     <t xml:space="preserve">3.02235913276672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02659225463867</t>
+    <t xml:space="preserve">3.02659153938293</t>
   </si>
   <si>
     <t xml:space="preserve">2.99837207794189</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">2.98426198959351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97861814498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06892228126526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06610035896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01389312744141</t>
+    <t xml:space="preserve">2.99131727218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97861838340759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06892204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01389265060425</t>
   </si>
   <si>
     <t xml:space="preserve">3.02094793319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00683808326721</t>
+    <t xml:space="preserve">3.00683784484863</t>
   </si>
   <si>
     <t xml:space="preserve">3.03929090499878</t>
@@ -314,31 +314,31 @@
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9645082950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083203315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843728065491</t>
+    <t xml:space="preserve">2.9997832775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714911460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083250999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843680381775</t>
   </si>
   <si>
     <t xml:space="preserve">2.93205523490906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87702608108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089010238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72181630134583</t>
+    <t xml:space="preserve">2.87702631950378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9108898639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
     <t xml:space="preserve">2.61034750938416</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899437904358</t>
+    <t xml:space="preserve">2.71899461746216</t>
   </si>
   <si>
     <t xml:space="preserve">2.79659914970398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79518818855286</t>
+    <t xml:space="preserve">2.79518842697144</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162806510925</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">3.00542759895325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02518105506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211282730103</t>
+    <t xml:space="preserve">3.02518129348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211330413818</t>
   </si>
   <si>
     <t xml:space="preserve">3.07597732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03364682197571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07033324241638</t>
+    <t xml:space="preserve">3.03364706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0703330039978</t>
   </si>
   <si>
     <t xml:space="preserve">3.05481195449829</t>
@@ -395,64 +395,64 @@
     <t xml:space="preserve">3.03788018226624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05199027061462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333579063416</t>
+    <t xml:space="preserve">3.0519905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333626747131</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204762458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15499305725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14088344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10842990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149789810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947224617004</t>
+    <t xml:space="preserve">3.15499329566956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14088296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10842967033386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947200775146</t>
   </si>
   <si>
     <t xml:space="preserve">3.15075993537903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10419702529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444356918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02800297737122</t>
+    <t xml:space="preserve">3.10419750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02800273895264</t>
   </si>
   <si>
     <t xml:space="preserve">3.01248216629028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02376985549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0717442035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045579910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646874427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09008693695068</t>
+    <t xml:space="preserve">3.02377009391785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07174396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045603752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646922111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008717536926</t>
   </si>
   <si>
     <t xml:space="preserve">3.19732260704041</t>
@@ -461,46 +461,46 @@
     <t xml:space="preserve">3.21002221107483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18462347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21284365653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707677841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27774977684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351689338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22131013870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861029624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873380661011</t>
+    <t xml:space="preserve">3.1846239566803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2128438949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707701683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27774930000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861077308655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873404502869</t>
   </si>
   <si>
     <t xml:space="preserve">3.18180203437805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15358185768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217089653015</t>
+    <t xml:space="preserve">3.1535816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217065811157</t>
   </si>
   <si>
     <t xml:space="preserve">3.16628122329712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12536191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125183105469</t>
+    <t xml:space="preserve">3.12536144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125206947327</t>
   </si>
   <si>
     <t xml:space="preserve">3.08726525306702</t>
@@ -509,97 +509,97 @@
     <t xml:space="preserve">3.0971417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548447608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867597579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07738733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06186676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696135520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92923283576965</t>
+    <t xml:space="preserve">3.11548495292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07738780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06186699867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696087837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92923331260681</t>
   </si>
   <si>
     <t xml:space="preserve">2.95322012901306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95180940628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93911004066467</t>
+    <t xml:space="preserve">2.95180916786194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93910956382751</t>
   </si>
   <si>
     <t xml:space="preserve">2.92076706886292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95886397361755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92782235145569</t>
+    <t xml:space="preserve">2.9588634967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92782187461853</t>
   </si>
   <si>
     <t xml:space="preserve">2.98002934455872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01953721046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720694541931</t>
+    <t xml:space="preserve">3.04493474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622315406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720670700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.99554991722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04070234298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0181257724762</t>
+    <t xml:space="preserve">3.04070162773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">2.96309685707092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92641091346741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849511146545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138223648071</t>
+    <t xml:space="preserve">2.92641115188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849534988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138199806213</t>
   </si>
   <si>
     <t xml:space="preserve">2.8572723865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86856007575989</t>
+    <t xml:space="preserve">2.86856031417847</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95604181289673</t>
+    <t xml:space="preserve">2.95604252815247</t>
   </si>
   <si>
     <t xml:space="preserve">2.88690328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89819121360779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303926467896</t>
+    <t xml:space="preserve">2.89819097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303950309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.84034037590027</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">2.82199740409851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84457325935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85021710395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78390049934387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377722740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82340836524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568032264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132440567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80929827690125</t>
+    <t xml:space="preserve">2.84457349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85021734237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78390026092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82340812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568056106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132464408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80929851531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.8925473690033</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">2.89395833015442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89960265159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009383201599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665698051453</t>
+    <t xml:space="preserve">2.89960217475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009430885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665721893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.88831400871277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91230082511902</t>
+    <t xml:space="preserve">2.91230130195618</t>
   </si>
   <si>
     <t xml:space="preserve">2.94052124023438</t>
@@ -659,49 +659,49 @@
     <t xml:space="preserve">3.09431982040405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08020973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303189277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560822486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585405349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523888587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511632919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13806056976318</t>
+    <t xml:space="preserve">3.0802104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10560774803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585429191589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1352391242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511609077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13806080818176</t>
   </si>
   <si>
     <t xml:space="preserve">3.16063690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17051362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20437812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1959114074707</t>
+    <t xml:space="preserve">3.17051386833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2043776512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591188430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.12254023551941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278582572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290885925293</t>
+    <t xml:space="preserve">3.09573125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290909767151</t>
   </si>
   <si>
     <t xml:space="preserve">3.06751132011414</t>
@@ -710,73 +710,73 @@
     <t xml:space="preserve">3.11830687522888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13664984703064</t>
+    <t xml:space="preserve">3.17898035049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13665008544922</t>
   </si>
   <si>
     <t xml:space="preserve">3.07456564903259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10701894760132</t>
+    <t xml:space="preserve">3.10701870918274</t>
   </si>
   <si>
     <t xml:space="preserve">3.09855318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24529695510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26646161079407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25376272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094056129456</t>
+    <t xml:space="preserve">3.24529671669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2664623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25376319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094032287598</t>
   </si>
   <si>
     <t xml:space="preserve">3.29891490936279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31443619728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228655815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651968002319</t>
+    <t xml:space="preserve">3.3144359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357424736023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3722870349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651944160461</t>
   </si>
   <si>
     <t xml:space="preserve">3.4456582069397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41461658477783</t>
+    <t xml:space="preserve">3.41461682319641</t>
   </si>
   <si>
     <t xml:space="preserve">3.44283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4075620174408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4005069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160666465759</t>
+    <t xml:space="preserve">3.40756177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40050673484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657774925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338696479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105622291565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160642623901</t>
   </si>
   <si>
     <t xml:space="preserve">3.478111743927</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">3.48798823356628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52185273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5063316822052</t>
+    <t xml:space="preserve">3.52185249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633120536804</t>
   </si>
   <si>
     <t xml:space="preserve">3.49222135543823</t>
@@ -797,37 +797,37 @@
     <t xml:space="preserve">3.56277132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53455114364624</t>
+    <t xml:space="preserve">3.53455138206482</t>
   </si>
   <si>
     <t xml:space="preserve">3.52749633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54866147041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056408882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099149703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568331718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393621444702</t>
+    <t xml:space="preserve">3.54866218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056432723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099102020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568379402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5839364528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209879875183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55924415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273931503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095901489258</t>
+    <t xml:space="preserve">3.55924344062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62273907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.650958776474</t>
   </si>
   <si>
     <t xml:space="preserve">3.66154170036316</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.66506886482239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61921191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332152366638</t>
+    <t xml:space="preserve">3.61921167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332104682922</t>
   </si>
   <si>
     <t xml:space="preserve">3.59804630279541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73752284049988</t>
+    <t xml:space="preserve">3.7375226020813</t>
   </si>
   <si>
     <t xml:space="preserve">3.6866717338562</t>
@@ -854,82 +854,82 @@
     <t xml:space="preserve">3.72299361228943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71936130523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483326911926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124653816223</t>
+    <t xml:space="preserve">3.7193615436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7048327922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124725341797</t>
   </si>
   <si>
     <t xml:space="preserve">3.83195948600769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82832717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379818916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285616874695</t>
+    <t xml:space="preserve">3.82832765579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285569190979</t>
   </si>
   <si>
     <t xml:space="preserve">3.85012030601501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88644218444824</t>
+    <t xml:space="preserve">3.8864426612854</t>
   </si>
   <si>
     <t xml:space="preserve">3.86101698875427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84648847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469487190247</t>
+    <t xml:space="preserve">3.84648895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469534873962</t>
   </si>
   <si>
     <t xml:space="preserve">3.83922386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9845118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097069740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087906837463</t>
+    <t xml:space="preserve">3.98451232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097117424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087954521179</t>
   </si>
   <si>
     <t xml:space="preserve">3.92639636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90823554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913247108459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016683578491</t>
+    <t xml:space="preserve">3.90823602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913199424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016659736633</t>
   </si>
   <si>
     <t xml:space="preserve">3.68303990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65761470794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6133017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313200950623</t>
+    <t xml:space="preserve">3.6576144695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330127716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201905250549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313177108765</t>
   </si>
   <si>
     <t xml:space="preserve">3.59150838851929</t>
@@ -938,31 +938,31 @@
     <t xml:space="preserve">3.62492442131042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67214322090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6307361125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030451774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218951225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035033226013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7157289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662615776062</t>
+    <t xml:space="preserve">3.67214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030404090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218903541565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65034985542297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71572947502136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7266263961792</t>
   </si>
   <si>
     <t xml:space="preserve">3.87191367149353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96635055541992</t>
+    <t xml:space="preserve">3.96635007858276</t>
   </si>
   <si>
     <t xml:space="preserve">3.93366098403931</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">3.96998286247253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04989147186279</t>
+    <t xml:space="preserve">4.01356935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04989051818848</t>
   </si>
   <si>
     <t xml:space="preserve">4.07894849777222</t>
@@ -992,61 +992,61 @@
     <t xml:space="preserve">3.95182156562805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91549968719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00993633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177575111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0244665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04262685775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10437393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271848678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464953422546</t>
+    <t xml:space="preserve">3.91549921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00993776321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04262638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10437345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464881896973</t>
   </si>
   <si>
     <t xml:space="preserve">3.8973388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9881432056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545434951782</t>
+    <t xml:space="preserve">3.98814415931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545482635498</t>
   </si>
   <si>
     <t xml:space="preserve">3.93002867698669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01720142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88280987739563</t>
+    <t xml:space="preserve">4.01720094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88281035423279</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06805181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14796018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625940322876</t>
+    <t xml:space="preserve">4.0680513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14796113967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04625844955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078767776489</t>
@@ -1061,28 +1061,28 @@
     <t xml:space="preserve">4.12253475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18064975738525</t>
+    <t xml:space="preserve">4.1806492805481</t>
   </si>
   <si>
     <t xml:space="preserve">4.15885639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18791389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16612100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338514328003</t>
+    <t xml:space="preserve">4.18791437149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16612148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338466644287</t>
   </si>
   <si>
     <t xml:space="preserve">4.09710931777954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14069509506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979936599731</t>
+    <t xml:space="preserve">4.14069557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">4.24602890014648</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">4.26055717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21697187423706</t>
+    <t xml:space="preserve">4.2169713973999</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26418972015381</t>
+    <t xml:space="preserve">4.26419067382812</t>
   </si>
   <si>
     <t xml:space="preserve">4.27508687973022</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">4.17701768875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08984470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30777597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687929153442</t>
+    <t xml:space="preserve">4.08984518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30777645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29687976837158</t>
   </si>
   <si>
     <t xml:space="preserve">4.42763805389404</t>
@@ -1130,49 +1130,49 @@
     <t xml:space="preserve">4.5402364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60198307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59835147857666</t>
+    <t xml:space="preserve">4.60198354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59835195541382</t>
   </si>
   <si>
     <t xml:space="preserve">4.72184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56929349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56202936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62014484405518</t>
+    <t xml:space="preserve">4.56929397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56202983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62014436721802</t>
   </si>
   <si>
     <t xml:space="preserve">4.59471893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60924673080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4893856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844358444214</t>
+    <t xml:space="preserve">4.60924816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48938608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669603347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844310760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207517623901</t>
+    <t xml:space="preserve">4.52207565307617</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49301862716675</t>
+    <t xml:space="preserve">4.49301815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.50391387939453</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">4.46032857894897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45306444168091</t>
+    <t xml:space="preserve">4.45306348800659</t>
   </si>
   <si>
     <t xml:space="preserve">4.46759223937988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4784893989563</t>
+    <t xml:space="preserve">4.47848987579346</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750156402588</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">4.43853521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37315607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39131689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037487030029</t>
+    <t xml:space="preserve">4.37315559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39131641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.29324769973755</t>
@@ -1223,31 +1223,31 @@
     <t xml:space="preserve">4.42400646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140851974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28235149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20607566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12616682052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23150062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432811737061</t>
+    <t xml:space="preserve">4.31140804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28235101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2060751914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12616634368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23150014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432716369629</t>
   </si>
   <si>
     <t xml:space="preserve">3.97361469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94092583656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97724723815918</t>
+    <t xml:space="preserve">3.94092440605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9772469997406</t>
   </si>
   <si>
     <t xml:space="preserve">4.08258008956909</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">4.169753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44579982757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41674184799194</t>
+    <t xml:space="preserve">4.44579887390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.405846118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4167423248291</t>
   </si>
   <si>
     <t xml:space="preserve">4.59108734130859</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55113315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655954360962</t>
+    <t xml:space="preserve">4.5511326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57655811309814</t>
   </si>
   <si>
     <t xml:space="preserve">4.52933979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570772171021</t>
+    <t xml:space="preserve">4.52570724487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.53297185897827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67825937271118</t>
+    <t xml:space="preserve">4.67825984954834</t>
   </si>
   <si>
     <t xml:space="preserve">4.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6709942817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64557027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75816822052002</t>
+    <t xml:space="preserve">4.67099475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64556980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283393859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
     <t xml:space="preserve">4.75090312957764</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">4.76180028915405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7254786491394</t>
+    <t xml:space="preserve">4.72547817230225</t>
   </si>
   <si>
     <t xml:space="preserve">4.68552398681641</t>
@@ -1322,40 +1322,40 @@
     <t xml:space="preserve">4.72911024093628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65646648406982</t>
+    <t xml:space="preserve">4.65646696090698</t>
   </si>
   <si>
     <t xml:space="preserve">4.84533977508545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81991529464722</t>
+    <t xml:space="preserve">4.81265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81991481781006</t>
   </si>
   <si>
     <t xml:space="preserve">4.83807563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84897232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91798448562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89255952835083</t>
+    <t xml:space="preserve">4.88166189193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8489727973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89255905151367</t>
   </si>
   <si>
     <t xml:space="preserve">4.95430564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94704103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977785110474</t>
+    <t xml:space="preserve">4.9470419883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977832794189</t>
   </si>
   <si>
     <t xml:space="preserve">4.93251276016235</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">4.99062776565552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94340896606445</t>
+    <t xml:space="preserve">4.94340944290161</t>
   </si>
   <si>
     <t xml:space="preserve">4.86713361740112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7330756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86018896102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82654094696045</t>
+    <t xml:space="preserve">4.73307609558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888193130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86018848419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82654142379761</t>
   </si>
   <si>
     <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65082693099976</t>
+    <t xml:space="preserve">4.6508264541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.49380540847778</t>
@@ -1403,40 +1403,40 @@
     <t xml:space="preserve">4.74803066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72185945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979297637939</t>
+    <t xml:space="preserve">4.72186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979249954224</t>
   </si>
   <si>
     <t xml:space="preserve">4.75924587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83027935028076</t>
+    <t xml:space="preserve">4.83027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">4.93496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85644960403442</t>
+    <t xml:space="preserve">4.85645008087158</t>
   </si>
   <si>
     <t xml:space="preserve">4.81532526016235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94243764877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91252899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91626644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90505123138428</t>
+    <t xml:space="preserve">4.94243812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91252946853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91626691818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90505170822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.88261985778809</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">4.93869876861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96486902236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216505050659</t>
+    <t xml:space="preserve">4.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216457366943</t>
   </si>
   <si>
     <t xml:space="preserve">5.01720952987671</t>
@@ -1457,58 +1457,58 @@
     <t xml:space="preserve">5.13684511184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05833435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98356246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89757490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12936782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24900341033936</t>
+    <t xml:space="preserve">5.0583348274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89757442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12936735153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2490029335022</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31629943847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41350221633911</t>
+    <t xml:space="preserve">5.31629848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41350173950195</t>
   </si>
   <si>
     <t xml:space="preserve">5.34246873855591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09945917129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01347160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17796993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20040082931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404884338379</t>
+    <t xml:space="preserve">5.09945964813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0134711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17797040939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20040130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404932022095</t>
   </si>
   <si>
     <t xml:space="preserve">5.25274276733398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20787906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283363342285</t>
+    <t xml:space="preserve">5.20787858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283267974854</t>
   </si>
   <si>
     <t xml:space="preserve">5.19666290283203</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">5.06581163406372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97982358932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95739221572876</t>
+    <t xml:space="preserve">4.97982406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95739269256592</t>
   </si>
   <si>
     <t xml:space="preserve">5.03964138031006</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">5.05459642410278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08076667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18544721603394</t>
+    <t xml:space="preserve">5.08076620101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18544673919678</t>
   </si>
   <si>
     <t xml:space="preserve">5.09572076797485</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">4.88635873794556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.920006275177</t>
+    <t xml:space="preserve">4.92000579833984</t>
   </si>
   <si>
     <t xml:space="preserve">4.77420043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672315597534</t>
+    <t xml:space="preserve">4.7667236328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.68073558807373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66951942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71064519882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67325782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68447399139404</t>
+    <t xml:space="preserve">4.66951990127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67325830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68447351455688</t>
   </si>
   <si>
     <t xml:space="preserve">4.62839508056641</t>
@@ -1598,22 +1598,22 @@
     <t xml:space="preserve">4.58727025985718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56109952926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40781736373901</t>
+    <t xml:space="preserve">4.6956901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
     <t xml:space="preserve">4.61344051361084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59848594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550746917725</t>
+    <t xml:space="preserve">4.59848546981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550699234009</t>
   </si>
   <si>
     <t xml:space="preserve">4.84523391723633</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">4.86766576766968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78915548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7779393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140464782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83775663375854</t>
+    <t xml:space="preserve">4.78915452957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167772293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77793884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140369415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8377571105957</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821287155151</t>
@@ -1646,28 +1646,28 @@
     <t xml:space="preserve">4.71812105178833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74055242538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6022253036499</t>
+    <t xml:space="preserve">4.74055290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60222482681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52371406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997470855713</t>
+    <t xml:space="preserve">4.5237135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997518539429</t>
   </si>
   <si>
     <t xml:space="preserve">4.48632764816284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41903257369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46015739440918</t>
+    <t xml:space="preserve">4.41903305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46015787124634</t>
   </si>
   <si>
     <t xml:space="preserve">4.64334917068481</t>
@@ -1682,19 +1682,19 @@
     <t xml:space="preserve">4.76298427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73681449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86392736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806127548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927696228027</t>
+    <t xml:space="preserve">4.73681402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86392688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730039596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927743911743</t>
   </si>
   <si>
     <t xml:space="preserve">5.21909475326538</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15179920196533</t>
+    <t xml:space="preserve">5.15180015563965</t>
   </si>
   <si>
     <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37237691879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16675472259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620714187622</t>
+    <t xml:space="preserve">5.37237739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16675424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620761871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.09018993377686</t>
@@ -1727,55 +1727,55 @@
     <t xml:space="preserve">5.87335109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79483938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7611927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81353378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79110193252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231714248657</t>
+    <t xml:space="preserve">5.79484033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81353425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79110097885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231761932373</t>
   </si>
   <si>
     <t xml:space="preserve">5.75745439529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82474899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87708902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167917251587</t>
+    <t xml:space="preserve">5.82474851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87708950042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195224761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167964935303</t>
   </si>
   <si>
     <t xml:space="preserve">6.02663421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96307706832886</t>
+    <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
     <t xml:space="preserve">6.0079402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92569160461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93316888809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699768066406</t>
+    <t xml:space="preserve">5.92569208145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699863433838</t>
   </si>
   <si>
     <t xml:space="preserve">5.94064569473267</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">5.89578247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8808274269104</t>
+    <t xml:space="preserve">5.88082790374756</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812297821045</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">5.95560026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97429323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114200592041</t>
+    <t xml:space="preserve">5.97429275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114105224609</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">5.840660572052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75234079360962</t>
+    <t xml:space="preserve">5.75234031677246</t>
   </si>
   <si>
     <t xml:space="preserve">5.69474029541016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71778059005737</t>
+    <t xml:space="preserve">5.71778011322021</t>
   </si>
   <si>
     <t xml:space="preserve">5.68321990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66402006149292</t>
+    <t xml:space="preserve">5.66401958465576</t>
   </si>
   <si>
     <t xml:space="preserve">5.66786003112793</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70625972747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76002025604248</t>
+    <t xml:space="preserve">5.70626020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76002073287964</t>
   </si>
   <si>
     <t xml:space="preserve">5.87522077560425</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">5.74850034713745</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69858026504517</t>
+    <t xml:space="preserve">5.69858074188232</t>
   </si>
   <si>
     <t xml:space="preserve">5.64482021331787</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77537965774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72162008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81762027740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78690099716187</t>
+    <t xml:space="preserve">5.77538061141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72162055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81762075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970153808594</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">6.0557017326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28226232528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474126815796</t>
+    <t xml:space="preserve">6.28226280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474222183228</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">6.12866163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22850179672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19394159317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06722164154053</t>
+    <t xml:space="preserve">6.22850227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19394111633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06722211837769</t>
   </si>
   <si>
     <t xml:space="preserve">6.10178184509277</t>
@@ -1916,100 +1916,100 @@
     <t xml:space="preserve">6.29378223419189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39746189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43586254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4627423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210296630859</t>
+    <t xml:space="preserve">6.39746284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43586301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46274280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210344314575</t>
   </si>
   <si>
     <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44738292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5280237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954362869263</t>
+    <t xml:space="preserve">6.44738340377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52802324295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954410552979</t>
   </si>
   <si>
     <t xml:space="preserve">6.57410335540771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58946323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018442153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322376251221</t>
+    <t xml:space="preserve">6.5894627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322328567505</t>
   </si>
   <si>
     <t xml:space="preserve">6.62786340713501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66626310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80450391769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522462844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78914403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76610565185547</t>
+    <t xml:space="preserve">6.66626358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80450439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78914356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76610422134399</t>
   </si>
   <si>
     <t xml:space="preserve">6.98114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98882579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930387496948</t>
+    <t xml:space="preserve">6.98882627487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6893048286438</t>
   </si>
   <si>
     <t xml:space="preserve">6.63554382324219</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61634397506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570558547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642486572266</t>
+    <t xml:space="preserve">6.61634254455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298448562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642629623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.00802421569824</t>
@@ -2018,58 +2018,58 @@
     <t xml:space="preserve">6.99266481399536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10402488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786485671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178426742554</t>
+    <t xml:space="preserve">7.10402536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082666397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06178569793701</t>
   </si>
   <si>
     <t xml:space="preserve">7.07330560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07714557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034427642822</t>
+    <t xml:space="preserve">7.07714509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034379959106</t>
   </si>
   <si>
     <t xml:space="preserve">6.96578407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95426464080811</t>
+    <t xml:space="preserve">6.95426559448242</t>
   </si>
   <si>
     <t xml:space="preserve">7.02722454071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274473190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634590148926</t>
+    <t xml:space="preserve">7.01186418533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0425853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634494781494</t>
   </si>
   <si>
     <t xml:space="preserve">6.75074338912964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93506383895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90434455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0233850479126</t>
+    <t xml:space="preserve">6.93506479263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434312820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02338552474976</t>
   </si>
   <si>
     <t xml:space="preserve">6.97346448898315</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">7.15778541564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602670669556</t>
+    <t xml:space="preserve">7.16546630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602575302124</t>
   </si>
   <si>
     <t xml:space="preserve">7.16930532455444</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">7.27682685852051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18850469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698574066162</t>
+    <t xml:space="preserve">7.18850517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706470489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1769847869873</t>
   </si>
   <si>
     <t xml:space="preserve">7.19234561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15010643005371</t>
+    <t xml:space="preserve">7.15010595321655</t>
   </si>
   <si>
     <t xml:space="preserve">7.26914644241333</t>
@@ -2114,22 +2114,22 @@
     <t xml:space="preserve">7.34210634231567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43426656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730590820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978628158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11938571929932</t>
+    <t xml:space="preserve">7.43426609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.119384765625</t>
   </si>
   <si>
     <t xml:space="preserve">7.2230658531189</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">7.06562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08866548538208</t>
+    <t xml:space="preserve">7.08866453170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.98498487472534</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">6.77378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066394805908</t>
+    <t xml:space="preserve">6.80066442489624</t>
   </si>
   <si>
     <t xml:space="preserve">6.77762365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88898515701294</t>
+    <t xml:space="preserve">6.88898468017578</t>
   </si>
   <si>
     <t xml:space="preserve">6.9273853302002</t>
@@ -2165,40 +2165,40 @@
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202545166016</t>
+    <t xml:space="preserve">6.912024974823</t>
   </si>
   <si>
     <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84674453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08098459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03106451034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05794525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842428207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218385696411</t>
+    <t xml:space="preserve">6.86210441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674406051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0809850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03106498718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05794429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842475891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218433380127</t>
   </si>
   <si>
     <t xml:space="preserve">6.81602430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87746429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306344985962</t>
+    <t xml:space="preserve">6.87746381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306392669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
@@ -2207,49 +2207,49 @@
     <t xml:space="preserve">6.72002363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89282464981079</t>
+    <t xml:space="preserve">6.89282512664795</t>
   </si>
   <si>
     <t xml:space="preserve">6.79682397842407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70466423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78530502319336</t>
+    <t xml:space="preserve">6.70466375350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78530406951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.71234321594238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7353835105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410623550415</t>
+    <t xml:space="preserve">6.73538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410480499268</t>
   </si>
   <si>
     <t xml:space="preserve">7.2077054977417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17314624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002603530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11170482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25762510299683</t>
+    <t xml:space="preserve">7.17314529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002508163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11170625686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762605667114</t>
   </si>
   <si>
     <t xml:space="preserve">7.29986619949341</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">7.33826589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37282657623291</t>
+    <t xml:space="preserve">7.37282609939575</t>
   </si>
   <si>
     <t xml:space="preserve">7.58786678314209</t>
@@ -2267,10 +2267,10 @@
     <t xml:space="preserve">7.56098651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66466665267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362722396851</t>
+    <t xml:space="preserve">7.66466617584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362817764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.96418809890747</t>
@@ -2285,49 +2285,49 @@
     <t xml:space="preserve">7.8643479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378801345825</t>
+    <t xml:space="preserve">7.77218627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378753662109</t>
   </si>
   <si>
     <t xml:space="preserve">7.49186706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36130619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6800274848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898756027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8944206237793</t>
+    <t xml:space="preserve">7.36130666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970443725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
     <t xml:space="preserve">6.27458238601685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77154064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26690196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33602285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394496917725</t>
+    <t xml:space="preserve">5.77153968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26690244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33602237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1539454460144</t>
   </si>
   <si>
     <t xml:space="preserve">7.21922588348389</t>
@@ -2336,34 +2336,34 @@
     <t xml:space="preserve">7.58018684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59938764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27178192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8802170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57023000717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364862442017</t>
+    <t xml:space="preserve">7.59938716888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88021659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364671707153</t>
   </si>
   <si>
     <t xml:space="preserve">8.13718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35335731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72860622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03043365478516</t>
+    <t xml:space="preserve">8.35335636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72860527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03043556213379</t>
   </si>
   <si>
     <t xml:space="preserve">8.95701789855957</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">7.99442338943481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83127212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969577789307</t>
+    <t xml:space="preserve">7.83127307891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969673156738</t>
   </si>
   <si>
     <t xml:space="preserve">7.81903553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79864168167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679988861084</t>
+    <t xml:space="preserve">7.79864263534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679893493652</t>
   </si>
   <si>
     <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5090479850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496959686279</t>
+    <t xml:space="preserve">7.50904846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496912002563</t>
   </si>
   <si>
     <t xml:space="preserve">7.70482873916626</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">7.89653253555298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94547748565674</t>
+    <t xml:space="preserve">7.94547843933105</t>
   </si>
   <si>
     <t xml:space="preserve">7.8557448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94010877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9814624786377</t>
+    <t xml:space="preserve">7.94010972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146343231201</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739898681641</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">7.78709554672241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75814771652222</t>
+    <t xml:space="preserve">7.7581467628479</t>
   </si>
   <si>
     <t xml:space="preserve">7.69611549377441</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">7.54310274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60099935531616</t>
+    <t xml:space="preserve">7.600998878479</t>
   </si>
   <si>
     <t xml:space="preserve">7.58032178878784</t>
@@ -2450,28 +2450,28 @@
     <t xml:space="preserve">7.5182900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73333501815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65062475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55551052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53483247756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45212316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49347686767578</t>
+    <t xml:space="preserve">7.73333597183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65062570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55550956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53483152389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4521222114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4934778213501</t>
   </si>
   <si>
     <t xml:space="preserve">7.63408279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249586105347</t>
+    <t xml:space="preserve">7.40249681472778</t>
   </si>
   <si>
     <t xml:space="preserve">7.40663146972656</t>
@@ -2480,40 +2480,40 @@
     <t xml:space="preserve">7.36941337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58445739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6423544883728</t>
+    <t xml:space="preserve">7.58445835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520708084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235401153564</t>
   </si>
   <si>
     <t xml:space="preserve">7.52656221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75401306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385242462158</t>
+    <t xml:space="preserve">7.75401210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354803085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385147094727</t>
   </si>
   <si>
     <t xml:space="preserve">7.34459972381592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39009094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73746919631958</t>
+    <t xml:space="preserve">7.39009046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7374701499939</t>
   </si>
   <si>
     <t xml:space="preserve">7.69198036193848</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">7.52242565155029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42317390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33632898330688</t>
+    <t xml:space="preserve">7.42317485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3363299369812</t>
   </si>
   <si>
     <t xml:space="preserve">7.3652777671814</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">7.25775480270386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08406543731689</t>
+    <t xml:space="preserve">7.08406448364258</t>
   </si>
   <si>
     <t xml:space="preserve">7.02203273773193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95586538314819</t>
+    <t xml:space="preserve">6.95586633682251</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
@@ -2573,49 +2573,49 @@
     <t xml:space="preserve">7.06752347946167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09647178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07165956497192</t>
+    <t xml:space="preserve">7.09647130966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07166004180908</t>
   </si>
   <si>
     <t xml:space="preserve">7.24534845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17091083526611</t>
+    <t xml:space="preserve">7.17091035842896</t>
   </si>
   <si>
     <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98894929885864</t>
+    <t xml:space="preserve">6.98894882202148</t>
   </si>
   <si>
     <t xml:space="preserve">6.93932390213013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864633560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90624094009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95173072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98481369018555</t>
+    <t xml:space="preserve">7.05511665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90623998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95173025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8979697227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98481416702271</t>
   </si>
   <si>
     <t xml:space="preserve">6.93105268478394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82353115081787</t>
+    <t xml:space="preserve">6.82353067398071</t>
   </si>
   <si>
     <t xml:space="preserve">6.75322771072388</t>
@@ -2624,25 +2624,25 @@
     <t xml:space="preserve">6.78217601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96413660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759464263916</t>
+    <t xml:space="preserve">6.96413612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324506759644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43558073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700702667236</t>
+    <t xml:space="preserve">7.43557977676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700750350952</t>
   </si>
   <si>
     <t xml:space="preserve">7.48934173583984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59272956848145</t>
+    <t xml:space="preserve">7.59272861480713</t>
   </si>
   <si>
     <t xml:space="preserve">7.80777263641357</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">7.72092819213867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84085750579834</t>
+    <t xml:space="preserve">7.84085655212402</t>
   </si>
   <si>
     <t xml:space="preserve">7.81190776824951</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">7.8367223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912729263306</t>
+    <t xml:space="preserve">7.96078538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912824630737</t>
   </si>
   <si>
     <t xml:space="preserve">7.66716766357422</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">7.61754179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60513401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59686517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57205104827881</t>
+    <t xml:space="preserve">7.60513496398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59686422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57205152511597</t>
   </si>
   <si>
     <t xml:space="preserve">7.54723787307739</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">8.03522396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20064258575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15515327453613</t>
+    <t xml:space="preserve">8.20064353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15515232086182</t>
   </si>
   <si>
     <t xml:space="preserve">8.4777193069458</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5604305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40328216552734</t>
+    <t xml:space="preserve">8.31229972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56042957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40328121185303</t>
   </si>
   <si>
     <t xml:space="preserve">8.41155242919922</t>
@@ -2732,10 +2732,10 @@
     <t xml:space="preserve">8.33711338043213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6100549697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68449306488037</t>
+    <t xml:space="preserve">8.61005592346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.55215835571289</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">8.99051761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8002872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81682872772217</t>
+    <t xml:space="preserve">8.80028629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81682968139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.7341194152832</t>
@@ -2774,28 +2774,28 @@
     <t xml:space="preserve">8.21304988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18823623657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13861083984375</t>
+    <t xml:space="preserve">8.18823719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13860988616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.32057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24199867248535</t>
+    <t xml:space="preserve">8.24199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27921676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2585391998291</t>
+    <t xml:space="preserve">8.22545528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27921772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25854015350342</t>
   </si>
   <si>
     <t xml:space="preserve">8.2378625869751</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">7.86980581283569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85326337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875316619873</t>
+    <t xml:space="preserve">7.85326242446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875411987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.74574184417725</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">7.66303253173828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65475988388062</t>
+    <t xml:space="preserve">7.65476083755493</t>
   </si>
   <si>
     <t xml:space="preserve">7.51415491104126</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43144512176514</t>
+    <t xml:space="preserve">7.46866416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43144416809082</t>
   </si>
   <si>
     <t xml:space="preserve">7.50588321685791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82017946243286</t>
+    <t xml:space="preserve">7.82018041610718</t>
   </si>
   <si>
     <t xml:space="preserve">7.76228284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38181924819946</t>
+    <t xml:space="preserve">7.38182020187378</t>
   </si>
   <si>
     <t xml:space="preserve">7.2039942741394</t>
@@ -2861,34 +2861,34 @@
     <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02616882324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09233570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12542057037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670454025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12955617904663</t>
+    <t xml:space="preserve">7.02616834640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09233617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12541961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12955522537231</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263914108276</t>
+    <t xml:space="preserve">7.04271173477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16263961791992</t>
   </si>
   <si>
     <t xml:space="preserve">7.2991099357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22053623199463</t>
+    <t xml:space="preserve">7.22053575515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.53896713256836</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">7.80281019210815</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03108787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88386631011963</t>
+    <t xml:space="preserve">8.03108882904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88386535644531</t>
   </si>
   <si>
     <t xml:space="preserve">8.01123809814453</t>
@@ -2912,28 +2912,28 @@
     <t xml:space="preserve">7.81935214996338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77138090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453945159912</t>
+    <t xml:space="preserve">7.77137994766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79454040527344</t>
   </si>
   <si>
     <t xml:space="preserve">7.70190572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86732339859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69694328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05590057373047</t>
+    <t xml:space="preserve">7.8673243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619407653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6969428062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
     <t xml:space="preserve">7.97319221496582</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">7.99635076522827</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01785564422607</t>
+    <t xml:space="preserve">8.01785469055176</t>
   </si>
   <si>
     <t xml:space="preserve">8.05259323120117</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">7.99965953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02281761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05093955993652</t>
+    <t xml:space="preserve">8.02281665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05093860626221</t>
   </si>
   <si>
     <t xml:space="preserve">7.93845415115356</t>
@@ -2963,37 +2963,37 @@
     <t xml:space="preserve">7.95003414154053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88055753707886</t>
+    <t xml:space="preserve">7.88055658340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8243145942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01289176940918</t>
+    <t xml:space="preserve">7.82431554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0128927230835</t>
   </si>
   <si>
     <t xml:space="preserve">7.84416532516479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81604337692261</t>
+    <t xml:space="preserve">7.81604433059692</t>
   </si>
   <si>
     <t xml:space="preserve">7.63904619216919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66055011749268</t>
+    <t xml:space="preserve">7.66055107116699</t>
   </si>
   <si>
     <t xml:space="preserve">7.73498868942261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79480361938477</t>
+    <t xml:space="preserve">7.79480409622192</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
@@ -3026,46 +3026,46 @@
     <t xml:space="preserve">7.94006967544556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98963117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046459197998</t>
+    <t xml:space="preserve">7.98963212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09388160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18445873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24940204620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28700065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41517448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39808559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099479675293</t>
+    <t xml:space="preserve">8.1844596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2494010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28699970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41517543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39808654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099575042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.46302795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44251918792725</t>
+    <t xml:space="preserve">8.44252014160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.21180248260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36390590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31947135925293</t>
+    <t xml:space="preserve">8.36390495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31947040557861</t>
   </si>
   <si>
     <t xml:space="preserve">8.2442741394043</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">8.48011875152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45619201660156</t>
+    <t xml:space="preserve">8.45619297027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.44081020355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46986389160156</t>
+    <t xml:space="preserve">8.46986293792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.40663051605225</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644687652588</t>
+    <t xml:space="preserve">8.46644592285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5749683380127</t>
+    <t xml:space="preserve">8.57496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
@@ -3137,31 +3137,31 @@
     <t xml:space="preserve">8.32630634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24256610870361</t>
+    <t xml:space="preserve">8.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28187370300293</t>
+    <t xml:space="preserve">8.2186393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1742057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28187274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365104675293</t>
+    <t xml:space="preserve">8.35365200042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.45277309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46473789215088</t>
+    <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.50404453277588</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">8.50233554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66896343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6476001739502</t>
+    <t xml:space="preserve">8.66896438598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.6006031036377</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">8.6347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6262378692627</t>
+    <t xml:space="preserve">8.62623882293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.6176929473877</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">8.6219654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69032764434814</t>
+    <t xml:space="preserve">8.69032669067383</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">8.63051128387451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53822422027588</t>
+    <t xml:space="preserve">8.53822326660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">8.33143329620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36561393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23401927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31434345245361</t>
+    <t xml:space="preserve">8.36561489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2340202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40492153167725</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">8.47840881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34681510925293</t>
+    <t xml:space="preserve">8.34681415557861</t>
   </si>
   <si>
     <t xml:space="preserve">8.32459735870361</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">8.23231029510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21522045135498</t>
+    <t xml:space="preserve">8.2152214050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.2083854675293</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">8.08875465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99475812911987</t>
+    <t xml:space="preserve">7.99475908279419</t>
   </si>
   <si>
     <t xml:space="preserve">8.2391471862793</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">8.40150356292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31776142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">8.3177604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2545280456543</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26478290557861</t>
+    <t xml:space="preserve">8.2647819519043</t>
   </si>
   <si>
     <t xml:space="preserve">8.36048698425293</t>
@@ -3311,19 +3311,19 @@
     <t xml:space="preserve">8.31605243682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21692943572998</t>
+    <t xml:space="preserve">8.2169303894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055629730225</t>
+    <t xml:space="preserve">8.43055725097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.32972526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45106410980225</t>
+    <t xml:space="preserve">8.45106506347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.44935512542725</t>
@@ -3332,13 +3332,13 @@
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56642246246338</t>
+    <t xml:space="preserve">8.5664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.50575256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4989185333252</t>
+    <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.47670078277588</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704639434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65614604949951</t>
+    <t xml:space="preserve">8.82704734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65614700317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.72023391723633</t>
@@ -3377,34 +3377,34 @@
     <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60914707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69460010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75441455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77150535583496</t>
+    <t xml:space="preserve">8.63905620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6091480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69459915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75441360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77150440216064</t>
   </si>
   <si>
     <t xml:space="preserve">8.88686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88259029388428</t>
+    <t xml:space="preserve">8.88259124755859</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531490325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94667911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95522308349609</t>
+    <t xml:space="preserve">8.94667816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95522212982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.98085880279541</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612533569336</t>
+    <t xml:space="preserve">9.12612438201904</t>
   </si>
   <si>
     <t xml:space="preserve">9.20302963256836</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">8.08021068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20667552947998</t>
+    <t xml:space="preserve">8.2066764831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.35706901550293</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">7.78454971313477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81873083114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81360387802124</t>
+    <t xml:space="preserve">7.81872987747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81360292434692</t>
   </si>
   <si>
     <t xml:space="preserve">7.81018590927124</t>
@@ -3494,10 +3494,10 @@
     <t xml:space="preserve">7.58459615707397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64953804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434129714966</t>
+    <t xml:space="preserve">7.64953708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434225082397</t>
   </si>
   <si>
     <t xml:space="preserve">7.58288717269897</t>
@@ -3515,10 +3515,10 @@
     <t xml:space="preserve">7.82556676864624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579637527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510396957397</t>
+    <t xml:space="preserve">7.56579685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510301589966</t>
   </si>
   <si>
     <t xml:space="preserve">7.78625965118408</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">7.72302579879761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66491985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77087688446045</t>
+    <t xml:space="preserve">7.66491889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77087783813477</t>
   </si>
   <si>
     <t xml:space="preserve">7.62561225891113</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">7.95545101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07508277893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14173316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2032585144043</t>
+    <t xml:space="preserve">8.07508182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14173412322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20325946807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.22889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182773590088</t>
+    <t xml:space="preserve">8.48182678222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.50062656402588</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5433521270752</t>
+    <t xml:space="preserve">8.54335117340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.5578784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68178176879883</t>
+    <t xml:space="preserve">8.68178081512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.68605422973633</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">8.73732471466064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82277393341064</t>
+    <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
     <t xml:space="preserve">8.97658634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93813323974609</t>
+    <t xml:space="preserve">8.93813228607178</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404537200928</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">8.89113521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95095157623291</t>
+    <t xml:space="preserve">8.95095062255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.91677093505859</t>
@@ -5499,6 +5499,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.78499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77000045776367</t>
   </si>
 </sst>
 </file>
@@ -70603,7 +70606,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494328704</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>1096723</v>
@@ -70624,6 +70627,32 @@
         <v>1828</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6495833333</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>536454</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>9.85499954223633</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>9.79500007629395</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1829</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433834075928</t>
+    <t xml:space="preserve">3.42433905601501</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4560706615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986794471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331643104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3981249332428</t>
+    <t xml:space="preserve">3.46296906471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45607089996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812421798706</t>
   </si>
   <si>
     <t xml:space="preserve">3.34845685958862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34707713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981472969055</t>
+    <t xml:space="preserve">3.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981496810913</t>
   </si>
   <si>
     <t xml:space="preserve">3.28637146949768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21324849128723</t>
+    <t xml:space="preserve">3.21324920654297</t>
   </si>
   <si>
     <t xml:space="preserve">3.03803062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13874697685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288592338562</t>
+    <t xml:space="preserve">3.138747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14288568496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425543785095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16496086120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564538002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945192337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430722236633</t>
+    <t xml:space="preserve">3.1649603843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.137366771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430674552917</t>
   </si>
   <si>
     <t xml:space="preserve">3.27119517326355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222254753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20910954475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2077305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631944656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06700420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00078010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00215935707092</t>
+    <t xml:space="preserve">3.24222207069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20911002159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631920814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06700396537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0007803440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0021595954895</t>
   </si>
   <si>
     <t xml:space="preserve">2.9980206489563</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">3.02837347984314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07114338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1111536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151664733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046884536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14150595664978</t>
+    <t xml:space="preserve">3.07114315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115336418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151640892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046860694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14150643348694</t>
   </si>
   <si>
     <t xml:space="preserve">3.12494993209839</t>
@@ -155,43 +155,43 @@
     <t xml:space="preserve">3.11805129051208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323851585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321808815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013715744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255375862122</t>
+    <t xml:space="preserve">3.23808336257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1732382774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531321525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18703508377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0932183265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255352020264</t>
   </si>
   <si>
     <t xml:space="preserve">3.18427586555481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24636077880859</t>
+    <t xml:space="preserve">3.24636101722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.20635080337524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19807314872742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10563445091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906845092773</t>
+    <t xml:space="preserve">3.19807243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10563492774963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906821250916</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">3.00491881370544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05182766914368</t>
+    <t xml:space="preserve">3.0518274307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.98422384262085</t>
@@ -212,34 +212,34 @@
     <t xml:space="preserve">3.050448179245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05320763587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595592498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767827033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0256142616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873652458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08769917488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978384971619</t>
+    <t xml:space="preserve">3.05320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629878044128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767850875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873676300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0876989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978408813477</t>
   </si>
   <si>
     <t xml:space="preserve">3.05596661567688</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">3.06838369369507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01319694519043</t>
+    <t xml:space="preserve">3.01319718360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.02975296974182</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">2.95249152183533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94421362876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02235913276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02659153938293</t>
+    <t xml:space="preserve">2.94421315193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869519233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593525886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235889434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02659201622009</t>
   </si>
   <si>
     <t xml:space="preserve">2.99837207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98426198959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99131727218628</t>
+    <t xml:space="preserve">2.98426246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99131679534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.97861838340759</t>
@@ -296,40 +296,40 @@
     <t xml:space="preserve">3.06610012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01389265060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02094793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00683784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929090499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671528816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03505802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9997832775116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96450805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714911460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083250999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843680381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205523490906</t>
+    <t xml:space="preserve">3.01389288902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0209481716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00683808326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03505825996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99978303909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9645082950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083227157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843728065491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205547332764</t>
   </si>
   <si>
     <t xml:space="preserve">2.87702631950378</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.9108898639679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7218165397644</t>
+    <t xml:space="preserve">2.72181630134583</t>
   </si>
   <si>
     <t xml:space="preserve">2.61034750938416</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79659914970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79518842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162806510925</t>
+    <t xml:space="preserve">2.718994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7965989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79518818855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162830352783</t>
   </si>
   <si>
     <t xml:space="preserve">2.83610725402832</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">2.87279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94475412368774</t>
+    <t xml:space="preserve">2.94475388526917</t>
   </si>
   <si>
     <t xml:space="preserve">2.97438526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00542759895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02518129348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211330413818</t>
+    <t xml:space="preserve">3.00542712211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02518153190613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211258888245</t>
   </si>
   <si>
     <t xml:space="preserve">3.07597732543945</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">3.03364706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0703330039978</t>
+    <t xml:space="preserve">3.07033276557922</t>
   </si>
   <si>
     <t xml:space="preserve">3.05481195449829</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">3.03788018226624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0519905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333626747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204762458801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15499329566956</t>
+    <t xml:space="preserve">3.05199003219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204810142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15499305725098</t>
   </si>
   <si>
     <t xml:space="preserve">3.14088296890259</t>
@@ -413,73 +413,73 @@
     <t xml:space="preserve">3.14793801307678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10842967033386</t>
+    <t xml:space="preserve">3.10842990875244</t>
   </si>
   <si>
     <t xml:space="preserve">3.09149837493896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13241696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947200775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15075993537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444261550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02800273895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01248216629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02377009391785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07174396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045603752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09008717536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732260704041</t>
+    <t xml:space="preserve">3.13241767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947176933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15076041221619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419726371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444333076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02800321578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01248168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02376985549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0717442035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646874427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0900866985321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732284545898</t>
   </si>
   <si>
     <t xml:space="preserve">3.21002221107483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1846239566803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2128438949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707701683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27774930000305</t>
+    <t xml:space="preserve">3.18462371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21284437179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707653999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27774953842163</t>
   </si>
   <si>
     <t xml:space="preserve">3.27351665496826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861077308655</t>
+    <t xml:space="preserve">3.22130990028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861053466797</t>
   </si>
   <si>
     <t xml:space="preserve">3.19873404502869</t>
@@ -488,97 +488,97 @@
     <t xml:space="preserve">3.18180203437805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1535816192627</t>
+    <t xml:space="preserve">3.15358138084412</t>
   </si>
   <si>
     <t xml:space="preserve">3.15217065811157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16628122329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12536144256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125206947327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08726525306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0971417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11548495292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0886754989624</t>
+    <t xml:space="preserve">3.16628098487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12536191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125159263611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08726501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09714198112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11548471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08867597579956</t>
   </si>
   <si>
     <t xml:space="preserve">3.07738780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06186699867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696087837219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92923331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95322012901306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180916786194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93910956382751</t>
+    <t xml:space="preserve">3.06186723709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696111679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92923259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95322036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180869102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93910980224609</t>
   </si>
   <si>
     <t xml:space="preserve">2.92076706886292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9588634967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92782187461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002934455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622315406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01953744888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99554991722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04070162773132</t>
+    <t xml:space="preserve">2.95886373519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92782211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01953721046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720718383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99555039405823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04070258140564</t>
   </si>
   <si>
     <t xml:space="preserve">3.01812601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96309685707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92641115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849534988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138199806213</t>
+    <t xml:space="preserve">2.9630970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92641091346741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138247489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.8572723865509</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">2.92358899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95604252815247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88690328598022</t>
+    <t xml:space="preserve">2.95604228973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88690304756165</t>
   </si>
   <si>
     <t xml:space="preserve">2.89819097518921</t>
@@ -602,31 +602,31 @@
     <t xml:space="preserve">2.85303950309753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034037590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199740409851</t>
+    <t xml:space="preserve">2.84034061431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199716567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.84457349777222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85021734237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78390026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82340812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132464408875</t>
+    <t xml:space="preserve">2.85021710395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78390002250671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82340788841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75567984580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132440567017</t>
   </si>
   <si>
     <t xml:space="preserve">2.80929851531982</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">2.8925473690033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89395833015442</t>
+    <t xml:space="preserve">2.893958568573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89960217475891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86009430885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831400871277</t>
+    <t xml:space="preserve">2.86009407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831377029419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91230130195618</t>
@@ -656,37 +656,37 @@
     <t xml:space="preserve">2.94052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09431982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0802104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303165435791</t>
+    <t xml:space="preserve">3.09432029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08021068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303141593933</t>
   </si>
   <si>
     <t xml:space="preserve">3.10560774803162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08585429191589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1352391242981</t>
+    <t xml:space="preserve">3.08585405349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523864746094</t>
   </si>
   <si>
     <t xml:space="preserve">3.14511609077454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13806080818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063690185547</t>
+    <t xml:space="preserve">3.13806104660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063666343689</t>
   </si>
   <si>
     <t xml:space="preserve">3.17051386833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2043776512146</t>
+    <t xml:space="preserve">3.20437788963318</t>
   </si>
   <si>
     <t xml:space="preserve">3.19591188430786</t>
@@ -695,64 +695,64 @@
     <t xml:space="preserve">3.12254023551941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09573125839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290909767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06751132011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830687522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17898035049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13665008544922</t>
+    <t xml:space="preserve">3.0957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278606414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06751108169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1183066368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17897963523865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13664984703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.07456564903259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10701870918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529671669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2664623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25376319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891490936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3144359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357424736023</t>
+    <t xml:space="preserve">3.1070191860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.098552942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26646208763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25376296043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094056129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31443572044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357472419739</t>
   </si>
   <si>
     <t xml:space="preserve">3.3722870349884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37651944160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4456582069397</t>
+    <t xml:space="preserve">3.37651920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44565892219543</t>
   </si>
   <si>
     <t xml:space="preserve">3.41461682319641</t>
@@ -761,130 +761,130 @@
     <t xml:space="preserve">3.44283676147461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40756177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40050673484802</t>
+    <t xml:space="preserve">3.4075620174408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40050649642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.48657774925232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51338696479797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105622291565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160642623901</t>
+    <t xml:space="preserve">3.51338624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160690307617</t>
   </si>
   <si>
     <t xml:space="preserve">3.478111743927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48798823356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633120536804</t>
+    <t xml:space="preserve">3.48798799514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185297012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633144378662</t>
   </si>
   <si>
     <t xml:space="preserve">3.49222135543823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56277132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455138206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52749633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866218566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099102020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568379402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5839364528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209879875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924344062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273907661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.650958776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66154170036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506886482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921167373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332104682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7375226020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6866717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299361228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7193615436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7048327922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195948600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832765579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285569190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85012030601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8864426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101698875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648895263672</t>
+    <t xml:space="preserve">3.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53455209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5274965763092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866170883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056408882141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099149703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568403244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6227388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65095901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.661541223526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506862640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332176208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804701805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73752331733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68667149543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299385070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71936178207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483350753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124629974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195924758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832789421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379866600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85012102127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88644242286682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648823738098</t>
   </si>
   <si>
     <t xml:space="preserve">3.82469534873962</t>
@@ -893,28 +893,28 @@
     <t xml:space="preserve">3.83922386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98451232910156</t>
+    <t xml:space="preserve">3.98451161384583</t>
   </si>
   <si>
     <t xml:space="preserve">3.90097117424011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94455718994141</t>
+    <t xml:space="preserve">3.94455742835999</t>
   </si>
   <si>
     <t xml:space="preserve">3.98087954521179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92639636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913199424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016659736633</t>
+    <t xml:space="preserve">3.9263961315155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823578834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8101658821106</t>
   </si>
   <si>
     <t xml:space="preserve">3.68303990364075</t>
@@ -923,55 +923,55 @@
     <t xml:space="preserve">3.6576144695282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61330127716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201905250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313177108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492442131042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214345932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030404090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218903541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65034985542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572947502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7266263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191367149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96635007858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908617973328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998286247253</t>
+    <t xml:space="preserve">3.61330246925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313153266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150791168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.624924659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214322090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073682785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218927383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71572923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662544250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96635031700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908665657043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998262405396</t>
   </si>
   <si>
     <t xml:space="preserve">4.01356935501099</t>
@@ -980,31 +980,31 @@
     <t xml:space="preserve">4.05352306365967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989051818848</t>
+    <t xml:space="preserve">4.04989147186279</t>
   </si>
   <si>
     <t xml:space="preserve">4.07894849777222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182156562805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91549921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00993776321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446556091309</t>
+    <t xml:space="preserve">4.00267219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182228088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9154999256134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00993633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9954080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177575111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446603775024</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262638092041</t>
@@ -1013,40 +1013,40 @@
     <t xml:space="preserve">4.10437345504761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96271872520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8973388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98814415931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002867698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01720094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88281035423279</t>
+    <t xml:space="preserve">3.96271777153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464953422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89733862876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9881432056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9554545879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01720237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88280916213989</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0680513381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14796113967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625844955444</t>
+    <t xml:space="preserve">4.06805229187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14796018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0462589263916</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078767776489</t>
@@ -1055,31 +1055,31 @@
     <t xml:space="preserve">4.11527013778687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1080060005188</t>
+    <t xml:space="preserve">4.10800647735596</t>
   </si>
   <si>
     <t xml:space="preserve">4.12253475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1806492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18791437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16612148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338466644287</t>
+    <t xml:space="preserve">4.18065023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18791389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16612100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338609695435</t>
   </si>
   <si>
     <t xml:space="preserve">4.09710931777954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14069557189941</t>
+    <t xml:space="preserve">4.14069509506226</t>
   </si>
   <si>
     <t xml:space="preserve">4.12979888916016</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">4.22060346603394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26055717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2169713973999</t>
+    <t xml:space="preserve">4.26055812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">4.26419067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27508687973022</t>
+    <t xml:space="preserve">4.27508640289307</t>
   </si>
   <si>
     <t xml:space="preserve">4.24239683151245</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">4.17701768875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08984518051147</t>
+    <t xml:space="preserve">4.08984470367432</t>
   </si>
   <si>
     <t xml:space="preserve">4.30777645111084</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">4.29687976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42763805389404</t>
+    <t xml:space="preserve">4.4276385307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.51481103897095</t>
@@ -1142,70 +1142,70 @@
     <t xml:space="preserve">4.56929397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56202983856201</t>
+    <t xml:space="preserve">4.56202936172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.62014436721802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59471893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60924816131592</t>
+    <t xml:space="preserve">4.59471940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60924768447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.48938608169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45669603347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844310760498</t>
+    <t xml:space="preserve">4.45669651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844358444214</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207565307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575401306152</t>
+    <t xml:space="preserve">4.52207517623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575353622437</t>
   </si>
   <si>
     <t xml:space="preserve">4.49301815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50391387939453</t>
+    <t xml:space="preserve">4.50391435623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.49665021896362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46032857894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306348800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46759223937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47848987579346</t>
+    <t xml:space="preserve">4.46032810211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46759271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47848844528198</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750156402588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53660440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39131641387939</t>
+    <t xml:space="preserve">4.53660345077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315607070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39131736755371</t>
   </si>
   <si>
     <t xml:space="preserve">4.42037439346313</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">4.40947771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51117897033691</t>
+    <t xml:space="preserve">4.51117849349976</t>
   </si>
   <si>
     <t xml:space="preserve">4.42400646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140804290771</t>
+    <t xml:space="preserve">4.31140899658203</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
@@ -1235,52 +1235,52 @@
     <t xml:space="preserve">4.12616634368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23150014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432716369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94092440605164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9772469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258008956909</t>
+    <t xml:space="preserve">4.23150062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94092535972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.169753074646</t>
+    <t xml:space="preserve">4.16975259780884</t>
   </si>
   <si>
     <t xml:space="preserve">4.44579887390137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.405846118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4167423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288022994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5511326789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52933979034424</t>
+    <t xml:space="preserve">4.40584468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41674184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61288070678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55113363265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5765585899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
     <t xml:space="preserve">4.52570724487305</t>
@@ -1292,25 +1292,25 @@
     <t xml:space="preserve">4.67825984954834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64920234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67099475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64556980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283393859863</t>
+    <t xml:space="preserve">4.64920282363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67099523544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64557027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75090312957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76180028915405</t>
+    <t xml:space="preserve">4.75090360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76179981231689</t>
   </si>
   <si>
     <t xml:space="preserve">4.72547817230225</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">4.68552398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72911024093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65646696090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84533977508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81265115737915</t>
+    <t xml:space="preserve">4.72911071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65646648406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84534025192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81265068054199</t>
   </si>
   <si>
     <t xml:space="preserve">4.81991481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83807563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88166189193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8489727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91798496246338</t>
+    <t xml:space="preserve">4.83807611465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88166236877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798448562622</t>
   </si>
   <si>
     <t xml:space="preserve">4.89255905151367</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">4.95430564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9470419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977832794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93251276016235</t>
+    <t xml:space="preserve">4.94704103469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977689743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93251323699951</t>
   </si>
   <si>
     <t xml:space="preserve">4.99062776565552</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">4.94340944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86713361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73307609558105</t>
+    <t xml:space="preserve">4.86713314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7330756187439</t>
   </si>
   <si>
     <t xml:space="preserve">4.87888193130493</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">4.86018848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82654142379761</t>
+    <t xml:space="preserve">4.82654094696045</t>
   </si>
   <si>
     <t xml:space="preserve">4.75176906585693</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">4.6508264541626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49380540847778</t>
+    <t xml:space="preserve">4.49380493164062</t>
   </si>
   <si>
     <t xml:space="preserve">4.62091732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67699670791626</t>
+    <t xml:space="preserve">4.67699718475342</t>
   </si>
   <si>
     <t xml:space="preserve">4.63587188720703</t>
@@ -1403,43 +1403,43 @@
     <t xml:space="preserve">4.74803066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72186040878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690584182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979249954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75924587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83027982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85645008087158</t>
+    <t xml:space="preserve">4.7218599319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979345321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7592453956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83027935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496084213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85644912719727</t>
   </si>
   <si>
     <t xml:space="preserve">4.81532526016235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94243812561035</t>
+    <t xml:space="preserve">4.94243764877319</t>
   </si>
   <si>
     <t xml:space="preserve">4.91252946853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90505170822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88261985778809</t>
+    <t xml:space="preserve">4.91626739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90505218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88262033462524</t>
   </si>
   <si>
     <t xml:space="preserve">4.93869876861572</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">4.96486949920654</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03216457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01720952987671</t>
+    <t xml:space="preserve">5.03216409683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01721000671387</t>
   </si>
   <si>
     <t xml:space="preserve">5.13684511184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0583348274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98356294631958</t>
+    <t xml:space="preserve">5.05833387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98356199264526</t>
   </si>
   <si>
     <t xml:space="preserve">4.89757442474365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12936735153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2490029335022</t>
+    <t xml:space="preserve">5.12936878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24900341033936</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31629848480225</t>
+    <t xml:space="preserve">5.3162989616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350173950195</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">5.34246873855591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09945964813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0134711265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17797040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20040130615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283267974854</t>
+    <t xml:space="preserve">5.09945917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01347160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17796993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283363342285</t>
   </si>
   <si>
     <t xml:space="preserve">5.19666290283203</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">5.04711866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441373825073</t>
+    <t xml:space="preserve">5.11441421508789</t>
   </si>
   <si>
     <t xml:space="preserve">5.06581163406372</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">4.97982406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95739269256592</t>
+    <t xml:space="preserve">4.95739221572876</t>
   </si>
   <si>
     <t xml:space="preserve">5.03964138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05459642410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076620101929</t>
+    <t xml:space="preserve">5.05459594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076667785645</t>
   </si>
   <si>
     <t xml:space="preserve">5.18544673919678</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">5.09572076797485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2116174697876</t>
+    <t xml:space="preserve">5.21161699295044</t>
   </si>
   <si>
     <t xml:space="preserve">4.88635873794556</t>
@@ -1568,25 +1568,25 @@
     <t xml:space="preserve">4.92000579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66951990127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71064376831055</t>
+    <t xml:space="preserve">4.77420139312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073606491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
     <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68447351455688</t>
+    <t xml:space="preserve">4.6844744682312</t>
   </si>
   <si>
     <t xml:space="preserve">4.62839508056641</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">4.5685772895813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58727025985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56110048294067</t>
+    <t xml:space="preserve">4.58727073669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56109952926636</t>
   </si>
   <si>
     <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848546981812</t>
+    <t xml:space="preserve">4.613440990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848594665527</t>
   </si>
   <si>
     <t xml:space="preserve">4.75550699234009</t>
@@ -1619,46 +1619,46 @@
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79289388656616</t>
+    <t xml:space="preserve">4.792893409729</t>
   </si>
   <si>
     <t xml:space="preserve">4.86766576766968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78915452957153</t>
+    <t xml:space="preserve">4.78915548324585</t>
   </si>
   <si>
     <t xml:space="preserve">4.78167772293091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77793884277344</t>
+    <t xml:space="preserve">4.7779393196106</t>
   </si>
   <si>
     <t xml:space="preserve">4.87140369415283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8377571105957</t>
+    <t xml:space="preserve">4.83775663375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74055290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60222482681274</t>
+    <t xml:space="preserve">4.71812152862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74055337905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5237135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997518539429</t>
+    <t xml:space="preserve">4.52371454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997566223145</t>
   </si>
   <si>
     <t xml:space="preserve">4.48632764816284</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">4.46015787124634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64334917068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204214096069</t>
+    <t xml:space="preserve">4.64334869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204261779785</t>
   </si>
   <si>
     <t xml:space="preserve">4.65456485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76298427581787</t>
+    <t xml:space="preserve">4.76298379898071</t>
   </si>
   <si>
     <t xml:space="preserve">4.73681402206421</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">4.86392688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98730039596558</t>
+    <t xml:space="preserve">4.98730134963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.14806079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927743911743</t>
+    <t xml:space="preserve">5.15927696228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.21909475326538</t>
@@ -1706,34 +1706,34 @@
     <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15180015563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20414018630981</t>
+    <t xml:space="preserve">5.15179920196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20414066314697</t>
   </si>
   <si>
     <t xml:space="preserve">5.37237739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16675424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09018993377686</t>
+    <t xml:space="preserve">5.1667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09019041061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.87335109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79484033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76119232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81353425979614</t>
+    <t xml:space="preserve">5.79483985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7611927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81353330612183</t>
   </si>
   <si>
     <t xml:space="preserve">5.79110097885132</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">5.80231761932373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75745439529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87708950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924827575684</t>
+    <t xml:space="preserve">5.75745296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87708902359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924732208252</t>
   </si>
   <si>
     <t xml:space="preserve">6.01167964935303</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0079402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92569208145142</t>
+    <t xml:space="preserve">6.00794124603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
     <t xml:space="preserve">5.93316841125488</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">5.90699863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94064569473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07897424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9369068145752</t>
+    <t xml:space="preserve">5.94064617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07897329330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93690729141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.95933818817139</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">5.88082790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94812297821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95560026168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97429275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114105224609</t>
+    <t xml:space="preserve">5.94812345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95559978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97429323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114200592041</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">5.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69474029541016</t>
+    <t xml:space="preserve">5.69474077224731</t>
   </si>
   <si>
     <t xml:space="preserve">5.71778011322021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68321990966797</t>
+    <t xml:space="preserve">5.68322038650513</t>
   </si>
   <si>
     <t xml:space="preserve">5.66401958465576</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">5.82146072387695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74850034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69858074188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64482021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60642004013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77538061141968</t>
+    <t xml:space="preserve">5.74850082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69858026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64482069015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60642051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77538108825684</t>
   </si>
   <si>
     <t xml:space="preserve">5.72162055969238</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">5.81762075424194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78690052032471</t>
+    <t xml:space="preserve">5.78690099716187</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970153808594</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">6.28226280212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17474222183228</t>
+    <t xml:space="preserve">6.17474174499512</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
@@ -1892,58 +1892,58 @@
     <t xml:space="preserve">6.12866163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22850227355957</t>
+    <t xml:space="preserve">6.22850179672241</t>
   </si>
   <si>
     <t xml:space="preserve">6.19394111633301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06722211837769</t>
+    <t xml:space="preserve">6.06722164154053</t>
   </si>
   <si>
     <t xml:space="preserve">6.10178184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25154256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17090177536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16706132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29378223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43586301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46274280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210344314575</t>
+    <t xml:space="preserve">6.25154209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17090129852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1670618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29378271102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746236801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43586254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210248947144</t>
   </si>
   <si>
     <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44738340377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52802324295044</t>
+    <t xml:space="preserve">6.44738292694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5280237197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.53954410552979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57410335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5894627571106</t>
+    <t xml:space="preserve">6.57410383224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58946323394775</t>
   </si>
   <si>
     <t xml:space="preserve">6.62018346786499</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">6.64322328567505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62786340713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80450439453125</t>
+    <t xml:space="preserve">6.62786388397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80450344085693</t>
   </si>
   <si>
     <t xml:space="preserve">6.83138465881348</t>
@@ -1973,34 +1973,34 @@
     <t xml:space="preserve">6.76610422134399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98114490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882627487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6893048286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298448562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570463180542</t>
+    <t xml:space="preserve">6.98114538192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514566421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554430007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338264465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570606231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.05026531219482</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">7.06946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642629623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00802421569824</t>
+    <t xml:space="preserve">7.04642534255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802516937256</t>
   </si>
   <si>
     <t xml:space="preserve">6.99266481399536</t>
@@ -2021,85 +2021,85 @@
     <t xml:space="preserve">7.10402536392212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18082666397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330560684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034379959106</t>
+    <t xml:space="preserve">7.18082571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06178522109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330465316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034427642822</t>
   </si>
   <si>
     <t xml:space="preserve">6.96578407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95426559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02722454071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274377822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0425853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75074338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506479263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90434312820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02338552474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346448898315</t>
+    <t xml:space="preserve">6.95426416397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02722501754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04258441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93506383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0233850479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346544265747</t>
   </si>
   <si>
     <t xml:space="preserve">7.15778541564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16930532455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138563156128</t>
+    <t xml:space="preserve">7.16546535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602527618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138706207275</t>
   </si>
   <si>
     <t xml:space="preserve">7.27682685852051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18850517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706470489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1769847869873</t>
+    <t xml:space="preserve">7.18850564956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706518173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698526382446</t>
   </si>
   <si>
     <t xml:space="preserve">7.19234561920166</t>
@@ -2108,52 +2108,52 @@
     <t xml:space="preserve">7.15010595321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26914644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210634231567</t>
+    <t xml:space="preserve">7.26914596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210586547852</t>
   </si>
   <si>
     <t xml:space="preserve">7.43426609039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.119384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2230658531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11554574966431</t>
+    <t xml:space="preserve">7.45730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978628158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658662796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2806658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22306489944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11554670333862</t>
   </si>
   <si>
     <t xml:space="preserve">7.06562519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08866453170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98498487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77378368377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762365341187</t>
+    <t xml:space="preserve">7.08866500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98498439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77378463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762413024902</t>
   </si>
   <si>
     <t xml:space="preserve">6.88898468017578</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.912024974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290456771851</t>
+    <t xml:space="preserve">6.91202402114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290361404419</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210441589355</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">6.84674406051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0809850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03106498718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05794429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842475891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218433380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87746381759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306392669678</t>
+    <t xml:space="preserve">7.08098554611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03106451034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05794477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842380523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218481063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87746429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306344985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
@@ -2207,46 +2207,46 @@
     <t xml:space="preserve">6.72002363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89282512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682397842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466375350952</t>
+    <t xml:space="preserve">6.89282464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682493209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466279983521</t>
   </si>
   <si>
     <t xml:space="preserve">6.67778348922729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78530406951904</t>
+    <t xml:space="preserve">6.7853045463562</t>
   </si>
   <si>
     <t xml:space="preserve">6.71234321594238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73538398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2077054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11170625686646</t>
+    <t xml:space="preserve">6.73538446426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410528182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20770597457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314481735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1117057800293</t>
   </si>
   <si>
     <t xml:space="preserve">7.25762605667114</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">7.29986619949341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33826589584351</t>
+    <t xml:space="preserve">7.33826637268066</t>
   </si>
   <si>
     <t xml:space="preserve">7.37282609939575</t>
@@ -2264,100 +2264,100 @@
     <t xml:space="preserve">7.58786678314209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56098651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362817764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258922576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17922878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8643479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002653121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970443725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89442110061646</t>
+    <t xml:space="preserve">7.56098699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362770080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17922782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378705978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130523681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6800274848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8944206237793</t>
   </si>
   <si>
     <t xml:space="preserve">6.27458238601685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77153968811035</t>
+    <t xml:space="preserve">5.77154064178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.26690244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1539454460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922588348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754711151123</t>
+    <t xml:space="preserve">6.336021900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922445297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018779754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754806518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.2717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88021659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57022905349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364671707153</t>
+    <t xml:space="preserve">7.88021802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364719390869</t>
   </si>
   <si>
     <t xml:space="preserve">8.13718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35335636138916</t>
+    <t xml:space="preserve">8.35335826873779</t>
   </si>
   <si>
     <t xml:space="preserve">8.72860527038574</t>
@@ -2369,31 +2369,31 @@
     <t xml:space="preserve">8.95701789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70413208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75307750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99442338943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127307891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969673156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81903553009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79864263534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679893493652</t>
+    <t xml:space="preserve">8.70413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99442386627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969530105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81903457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79864168167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679941177368</t>
   </si>
   <si>
     <t xml:space="preserve">7.68035697937012</t>
@@ -2405,34 +2405,34 @@
     <t xml:space="preserve">7.50496912002563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70482873916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653253555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94547843933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8557448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85739898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78709554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7581467628479</t>
+    <t xml:space="preserve">7.70482921600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9454779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85574436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010829925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146295547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85739803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78709602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75814819335938</t>
   </si>
   <si>
     <t xml:space="preserve">7.69611549377441</t>
@@ -2444,115 +2444,115 @@
     <t xml:space="preserve">7.600998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58032178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5182900428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73333597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65062570571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55550956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53483152389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4521222114563</t>
+    <t xml:space="preserve">7.58032274246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51829051971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73333501815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65062522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55551052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53483200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212268829346</t>
   </si>
   <si>
     <t xml:space="preserve">7.4934778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63408279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40249681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58445835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520708084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656221389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75401210784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354803085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34459972381592</t>
+    <t xml:space="preserve">7.63408327102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40249729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663194656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58445739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385099411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460020065308</t>
   </si>
   <si>
     <t xml:space="preserve">7.39009046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37768363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7374701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69198036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77468967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67543745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62167739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438623428345</t>
+    <t xml:space="preserve">7.37768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73746919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69197988510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77468824386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72506332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68784523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67543792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62167644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438575744629</t>
   </si>
   <si>
     <t xml:space="preserve">7.71265745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42317485809326</t>
+    <t xml:space="preserve">7.62581300735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4231743812561</t>
   </si>
   <si>
     <t xml:space="preserve">7.3363299369812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3652777671814</t>
+    <t xml:space="preserve">7.36527729034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.25775480270386</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">7.02203273773193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95586633682251</t>
+    <t xml:space="preserve">6.95586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09647130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07166004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534845352173</t>
+    <t xml:space="preserve">7.06752443313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09647178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07165908813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534940719604</t>
   </si>
   <si>
     <t xml:space="preserve">7.17091035842896</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98894882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93932390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05511665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90623998641968</t>
+    <t xml:space="preserve">6.98894929885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93932437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0551176071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864681243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90624046325684</t>
   </si>
   <si>
     <t xml:space="preserve">6.95173025131226</t>
@@ -2609,40 +2609,40 @@
     <t xml:space="preserve">6.8979697227478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98481416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93105268478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82353067398071</t>
+    <t xml:space="preserve">6.98481321334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93105220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82353019714355</t>
   </si>
   <si>
     <t xml:space="preserve">6.75322771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78217601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30324506759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43557977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48934173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59272861480713</t>
+    <t xml:space="preserve">6.78217506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.947594165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30324554443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43558120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700702667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48934125900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59272909164429</t>
   </si>
   <si>
     <t xml:space="preserve">7.80777263641357</t>
@@ -2651,37 +2651,37 @@
     <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71679210662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190776824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8367223739624</t>
+    <t xml:space="preserve">7.71679258346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82845067977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83672285079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.96078538894653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84912824630737</t>
+    <t xml:space="preserve">7.84912729263306</t>
   </si>
   <si>
     <t xml:space="preserve">7.66716766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67957353591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61754179000854</t>
+    <t xml:space="preserve">7.67957258224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61754083633423</t>
   </si>
   <si>
     <t xml:space="preserve">7.60513496398926</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">7.59686422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54723787307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55137395858765</t>
+    <t xml:space="preserve">7.57205104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54723834991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55137348175049</t>
   </si>
   <si>
     <t xml:space="preserve">8.03522396087646</t>
@@ -2708,19 +2708,19 @@
     <t xml:space="preserve">8.15515232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4777193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14688205718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31229972839355</t>
+    <t xml:space="preserve">8.47772026062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14688301086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31230068206787</t>
   </si>
   <si>
     <t xml:space="preserve">8.56042957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40328121185303</t>
+    <t xml:space="preserve">8.40328025817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.41155242919922</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">8.33711338043213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61005592346191</t>
+    <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
     <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55215835571289</t>
+    <t xml:space="preserve">8.55215930938721</t>
   </si>
   <si>
     <t xml:space="preserve">8.25026893615723</t>
@@ -2750,145 +2750,145 @@
     <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92435169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99051761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80028629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81682968139648</t>
+    <t xml:space="preserve">8.92435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99051856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81682872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365581512451</t>
+    <t xml:space="preserve">8.35365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21304988861084</t>
+    <t xml:space="preserve">8.21304893493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.18823719024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13860988616943</t>
+    <t xml:space="preserve">8.13861083984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.32057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24199771881104</t>
+    <t xml:space="preserve">8.24199867248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545528411865</t>
+    <t xml:space="preserve">8.22545623779297</t>
   </si>
   <si>
     <t xml:space="preserve">8.27921772003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25854015350342</t>
+    <t xml:space="preserve">8.2585391998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95664978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86980581283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85326242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574184417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476083755493</t>
+    <t xml:space="preserve">7.9566502571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86980533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85326290130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875364303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574136734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303300857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476036071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.51415491104126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44798707962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219337463379</t>
+    <t xml:space="preserve">7.4479866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219385147095</t>
   </si>
   <si>
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971729278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43144416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50588321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82018041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76228284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38182020187378</t>
+    <t xml:space="preserve">7.46866369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971586227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43144464492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50588369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8201789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76228332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38181924819946</t>
   </si>
   <si>
     <t xml:space="preserve">7.2039942741394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338834762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02616834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12541961669922</t>
+    <t xml:space="preserve">7.06338739395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02616786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09233665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12542009353638</t>
   </si>
   <si>
     <t xml:space="preserve">7.28670358657837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12955522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04271173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263961791992</t>
+    <t xml:space="preserve">7.12955570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04271125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16263914108276</t>
   </si>
   <si>
     <t xml:space="preserve">7.2991099357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22053575515747</t>
+    <t xml:space="preserve">7.22053527832031</t>
   </si>
   <si>
     <t xml:space="preserve">7.53896713256836</t>
@@ -2897,49 +2897,49 @@
     <t xml:space="preserve">7.70025110244751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80281019210815</t>
+    <t xml:space="preserve">7.80281114578247</t>
   </si>
   <si>
     <t xml:space="preserve">8.03108882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88386535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01123809814453</t>
+    <t xml:space="preserve">7.88386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01123905181885</t>
   </si>
   <si>
     <t xml:space="preserve">7.81935214996338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77137994766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79454040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190572738647</t>
+    <t xml:space="preserve">7.77138090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190525054932</t>
   </si>
   <si>
     <t xml:space="preserve">7.8673243522644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81273555755615</t>
+    <t xml:space="preserve">7.81273460388184</t>
   </si>
   <si>
     <t xml:space="preserve">7.79619407653809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6969428062439</t>
+    <t xml:space="preserve">7.69694232940674</t>
   </si>
   <si>
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635076522827</t>
+    <t xml:space="preserve">7.97319269180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635124206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.01785469055176</t>
@@ -2948,22 +2948,22 @@
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02281665802002</t>
+    <t xml:space="preserve">7.99965906143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02281761169434</t>
   </si>
   <si>
     <t xml:space="preserve">8.05093860626221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93845415115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003414154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88055658340454</t>
+    <t xml:space="preserve">7.93845319747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055753707886</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
@@ -2972,55 +2972,55 @@
     <t xml:space="preserve">7.82431554794312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90371608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84416532516479</t>
+    <t xml:space="preserve">7.90371656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01289081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84416484832764</t>
   </si>
   <si>
     <t xml:space="preserve">7.81604433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63904619216919</t>
+    <t xml:space="preserve">7.63904523849487</t>
   </si>
   <si>
     <t xml:space="preserve">7.66055107116699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73498868942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79480409622192</t>
+    <t xml:space="preserve">7.73498916625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79480361938477</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82385873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89221811294556</t>
+    <t xml:space="preserve">7.78967714309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85291051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82385730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258729934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960830688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8922176361084</t>
   </si>
   <si>
     <t xml:space="preserve">7.94006967544556</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">8.09388160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1844596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2494010925293</t>
+    <t xml:space="preserve">8.18445873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24940204620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.28699970245361</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">8.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39808654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46302795410156</t>
+    <t xml:space="preserve">8.39808559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46302700042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.44252014160156</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">8.21180248260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36390495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31947040557861</t>
+    <t xml:space="preserve">8.36390590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31947135925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.2442741394043</t>
@@ -3074,19 +3074,19 @@
     <t xml:space="preserve">8.1912956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12806129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09900856018066</t>
+    <t xml:space="preserve">8.12806224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09900760650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11951541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2271842956543</t>
+    <t xml:space="preserve">8.11951637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22718524932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.36903190612793</t>
@@ -3098,28 +3098,28 @@
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48011875152588</t>
+    <t xml:space="preserve">8.35877799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48011779785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.45619297027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44081020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40663051605225</t>
+    <t xml:space="preserve">8.44081115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46986389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40663146972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644592285156</t>
+    <t xml:space="preserve">8.46644687652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25965690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32630634307861</t>
+    <t xml:space="preserve">8.2596549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32630729675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.2425651550293</t>
@@ -3146,55 +3146,55 @@
     <t xml:space="preserve">8.2186393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1742057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28187274932861</t>
+    <t xml:space="preserve">8.17420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28187370300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365200042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45277309417725</t>
+    <t xml:space="preserve">8.35365009307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45277404785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42030239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50233554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896438598633</t>
+    <t xml:space="preserve">8.50404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42030334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50233459472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896343231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6006031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6347827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62623882293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6176929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5416431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6219654083252</t>
+    <t xml:space="preserve">8.60060214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63478374481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6262378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61769390106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54164218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62196636199951</t>
   </si>
   <si>
     <t xml:space="preserve">8.69032669067383</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051128387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5536060333252</t>
+    <t xml:space="preserve">8.63051223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5382251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55360698699951</t>
   </si>
   <si>
     <t xml:space="preserve">8.42372035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49208164215088</t>
+    <t xml:space="preserve">8.49208068847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.54506015777588</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143329620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36561489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2340202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3143424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40492153167725</t>
+    <t xml:space="preserve">8.33143424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36561393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23401927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31434345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">8.30579948425293</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">8.49720859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47840881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34681415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32459735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23231029510498</t>
+    <t xml:space="preserve">8.47840785980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34681510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2323112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.2152214050293</t>
@@ -3266,46 +3266,46 @@
     <t xml:space="preserve">8.17933082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22205638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07166481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08875465393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475908279419</t>
+    <t xml:space="preserve">8.2220573425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07166385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08875370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475860595703</t>
   </si>
   <si>
     <t xml:space="preserve">8.2391471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33485126495361</t>
+    <t xml:space="preserve">8.33485221862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40150356292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3177604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2545280456543</t>
+    <t xml:space="preserve">8.31776237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452899932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2647819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25111103057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565990447998</t>
+    <t xml:space="preserve">8.26478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2511100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565895080566</t>
   </si>
   <si>
     <t xml:space="preserve">8.31605243682861</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">8.43055725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32972526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45106506347656</t>
+    <t xml:space="preserve">8.32972431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45106410980225</t>
   </si>
   <si>
     <t xml:space="preserve">8.44935512542725</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47670078277588</t>
+    <t xml:space="preserve">8.47669982910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.02358341217041</t>
@@ -3356,19 +3356,19 @@
     <t xml:space="preserve">8.80141162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78004932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66041851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82704734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65614700317383</t>
+    <t xml:space="preserve">8.78005027770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66041946411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82704639434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168994903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65614604949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.72023391723633</t>
@@ -3377,34 +3377,34 @@
     <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63905620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6091480255127</t>
+    <t xml:space="preserve">8.6390552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60914707183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.69459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77150440216064</t>
+    <t xml:space="preserve">8.75441551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77150535583496</t>
   </si>
   <si>
     <t xml:space="preserve">8.88686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88259124755859</t>
+    <t xml:space="preserve">8.88259029388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531490325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94667816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95522212982178</t>
+    <t xml:space="preserve">8.94667911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95522308349609</t>
   </si>
   <si>
     <t xml:space="preserve">8.98085880279541</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20302963256836</t>
+    <t xml:space="preserve">9.12612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20303058624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.03212833404541</t>
@@ -3434,55 +3434,55 @@
     <t xml:space="preserve">8.70741558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5877857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28870868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26136493682861</t>
+    <t xml:space="preserve">8.58778476715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2613639831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.15882396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08021068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2066764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35706901550293</t>
+    <t xml:space="preserve">8.08020973205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20667457580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35706806182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.78454971313477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81872987747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81360292434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81018590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540504455566</t>
+    <t xml:space="preserve">7.81873083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81360387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81018543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540599822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.12635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8802547454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71106195449829</t>
+    <t xml:space="preserve">7.88025426864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71106243133545</t>
   </si>
   <si>
     <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61364889144897</t>
+    <t xml:space="preserve">7.61364841461182</t>
   </si>
   <si>
     <t xml:space="preserve">7.54699659347534</t>
@@ -3491,73 +3491,73 @@
     <t xml:space="preserve">7.45129299163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58459615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434225082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58288717269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48376417160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41369438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69055461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556676864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579685211182</t>
+    <t xml:space="preserve">7.58459663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953851699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58288669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48376369476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41369390487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69055509567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579637527466</t>
   </si>
   <si>
     <t xml:space="preserve">7.60510301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78625965118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56237888336182</t>
+    <t xml:space="preserve">7.78626012802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56237936019897</t>
   </si>
   <si>
     <t xml:space="preserve">7.72302579879761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77087783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62561225891113</t>
+    <t xml:space="preserve">7.66491985321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77087688446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62561178207397</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91785287857056</t>
+    <t xml:space="preserve">7.9178524017334</t>
   </si>
   <si>
     <t xml:space="preserve">7.95545101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07508182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14173412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20325946807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22889232635498</t>
+    <t xml:space="preserve">8.07508277893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14173316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2032585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2288932800293</t>
   </si>
   <si>
     <t xml:space="preserve">8.48182678222656</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">8.97658634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93813228607178</t>
+    <t xml:space="preserve">8.93813323974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404537200928</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">8.89113521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95095062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91677093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90395259857178</t>
+    <t xml:space="preserve">8.95095157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91677188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90395355224609</t>
   </si>
   <si>
     <t xml:space="preserve">8.81422901153564</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">8.6134204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67323589324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69887161254883</t>
+    <t xml:space="preserve">8.67323684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69887256622314</t>
   </si>
   <si>
     <t xml:space="preserve">8.70314407348633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74159622192383</t>
+    <t xml:space="preserve">8.74159717559814</t>
   </si>
   <si>
     <t xml:space="preserve">8.46131896972656</t>
@@ -70632,7 +70632,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495833333</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>536454</v>
@@ -70653,6 +70653,32 @@
         <v>1829</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.649537037</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>747045</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>9.81999969482422</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>9.8149995803833</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1831">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433905601501</t>
+    <t xml:space="preserve">3.42433857917786</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296906471252</t>
+    <t xml:space="preserve">3.46296977996826</t>
   </si>
   <si>
     <t xml:space="preserve">3.45607089996338</t>
@@ -53,34 +53,34 @@
     <t xml:space="preserve">3.46986770629883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47331666946411</t>
+    <t xml:space="preserve">3.47331643104553</t>
   </si>
   <si>
     <t xml:space="preserve">3.39812421798706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34845685958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34707689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981496810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637146949768</t>
+    <t xml:space="preserve">3.34845638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3470766544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981449127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2863712310791</t>
   </si>
   <si>
     <t xml:space="preserve">3.21324920654297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03803062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.138747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288568496704</t>
+    <t xml:space="preserve">3.03803110122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13874697685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1428861618042</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425543785095</t>
@@ -89,94 +89,94 @@
     <t xml:space="preserve">3.1649603843689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.137366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430674552917</t>
+    <t xml:space="preserve">3.13736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564442634583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430698394775</t>
   </si>
   <si>
     <t xml:space="preserve">3.27119517326355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20911002159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631920814514</t>
+    <t xml:space="preserve">3.24222159385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20910954475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2077305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631896972656</t>
   </si>
   <si>
     <t xml:space="preserve">3.06700396537781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0007803440094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0021595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9980206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115336418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151640892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046860694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14150643348694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12494993209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11805129051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1732382774353</t>
+    <t xml:space="preserve">3.00078010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00215983390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802088737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837324142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114338874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322806358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1111536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046884536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14150595664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12495040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11805152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808240890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323803901672</t>
   </si>
   <si>
     <t xml:space="preserve">3.19531321525574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18703508377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0932183265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427586555481</t>
+    <t xml:space="preserve">3.18703532218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321761131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013691902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255423545837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427562713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636101722717</t>
@@ -185,61 +185,61 @@
     <t xml:space="preserve">3.20635080337524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19807243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10563492774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906821250916</t>
+    <t xml:space="preserve">3.1980721950531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10563445091248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906845092773</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03941059112549</t>
+    <t xml:space="preserve">3.03941106796265</t>
   </si>
   <si>
     <t xml:space="preserve">3.00491881370544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0518274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.050448179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595640182495</t>
+    <t xml:space="preserve">3.05182766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05044794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595664024353</t>
   </si>
   <si>
     <t xml:space="preserve">3.01457643508911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629878044128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767850875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873676300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0876989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978408813477</t>
+    <t xml:space="preserve">3.02147531509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767827033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873652458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08769917488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978384971619</t>
   </si>
   <si>
     <t xml:space="preserve">3.05596661567688</t>
@@ -248,97 +248,97 @@
     <t xml:space="preserve">3.06838369369507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01319718360901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02975296974182</t>
+    <t xml:space="preserve">3.01319742202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0297532081604</t>
   </si>
   <si>
     <t xml:space="preserve">3.01871585845947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96766781806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249152183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94421315193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869519233704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593525886536</t>
+    <t xml:space="preserve">2.96766757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94421362876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869471549988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593549728394</t>
   </si>
   <si>
     <t xml:space="preserve">3.02235889434814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02659201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426246643066</t>
+    <t xml:space="preserve">3.02659177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837183952332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426198959351</t>
   </si>
   <si>
     <t xml:space="preserve">2.99131679534912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97861838340759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06892204284668</t>
+    <t xml:space="preserve">2.97861814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06892228126526</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01389288902283</t>
+    <t xml:space="preserve">3.01389265060425</t>
   </si>
   <si>
     <t xml:space="preserve">3.0209481716156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00683808326721</t>
+    <t xml:space="preserve">3.00683784484863</t>
   </si>
   <si>
     <t xml:space="preserve">3.03929138183594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01671504974365</t>
+    <t xml:space="preserve">3.01671528816223</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505825996399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9645082950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083227157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843728065491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205547332764</t>
+    <t xml:space="preserve">2.9997832775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96450853347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714959144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205571174622</t>
   </si>
   <si>
     <t xml:space="preserve">2.87702631950378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9108898639679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72181630134583</t>
+    <t xml:space="preserve">2.91089034080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72181677818298</t>
   </si>
   <si>
     <t xml:space="preserve">2.61034750938416</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.718994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7965989112854</t>
+    <t xml:space="preserve">2.71899461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79659962654114</t>
   </si>
   <si>
     <t xml:space="preserve">2.79518818855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85162830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610725402832</t>
+    <t xml:space="preserve">2.85162782669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83610701560974</t>
   </si>
   <si>
     <t xml:space="preserve">2.87279319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94475388526917</t>
+    <t xml:space="preserve">2.94475364685059</t>
   </si>
   <si>
     <t xml:space="preserve">2.97438526153564</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">3.00542712211609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02518153190613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211258888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597732543945</t>
+    <t xml:space="preserve">3.02518105506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597708702087</t>
   </si>
   <si>
     <t xml:space="preserve">3.03364706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07033276557922</t>
+    <t xml:space="preserve">3.07033324241638</t>
   </si>
   <si>
     <t xml:space="preserve">3.05481195449829</t>
@@ -395,37 +395,37 @@
     <t xml:space="preserve">3.03788018226624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05199003219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204810142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15499305725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14088296890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14793801307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10842990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149837493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947176933289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15076041221619</t>
+    <t xml:space="preserve">3.0519905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333579063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204762458801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1549928188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14088320732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1479377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1084303855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149813652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15075993537903</t>
   </si>
   <si>
     <t xml:space="preserve">3.10419726371765</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">3.08444333076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02800321578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01248168945312</t>
+    <t xml:space="preserve">3.02800273895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01248240470886</t>
   </si>
   <si>
     <t xml:space="preserve">3.02376985549927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0717442035675</t>
+    <t xml:space="preserve">3.07174396514893</t>
   </si>
   <si>
     <t xml:space="preserve">3.06045579910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03646874427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0900866985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732284545898</t>
+    <t xml:space="preserve">3.03646898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008717536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732332229614</t>
   </si>
   <si>
     <t xml:space="preserve">3.21002221107483</t>
@@ -464,88 +464,88 @@
     <t xml:space="preserve">3.18462371826172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21284437179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707653999329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27774953842163</t>
+    <t xml:space="preserve">3.21284365653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27774977684021</t>
   </si>
   <si>
     <t xml:space="preserve">3.27351665496826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22130990028381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873404502869</t>
+    <t xml:space="preserve">3.22130942344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861101150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873380661011</t>
   </si>
   <si>
     <t xml:space="preserve">3.18180203437805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15358138084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217065811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16628098487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12536191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125159263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08726501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09714198112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11548471450806</t>
+    <t xml:space="preserve">3.1535816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217089653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16628074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1253616809845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08726525306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0971417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11548519134521</t>
   </si>
   <si>
     <t xml:space="preserve">3.08867597579956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07738780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06186723709106</t>
+    <t xml:space="preserve">3.07738828659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06186699867249</t>
   </si>
   <si>
     <t xml:space="preserve">2.99696111679077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92923259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95322036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180869102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93910980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92076706886292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95886373519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92782211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002910614014</t>
+    <t xml:space="preserve">2.92923307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95321989059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93911004066467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92076730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9588634967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92782235145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002886772156</t>
   </si>
   <si>
     <t xml:space="preserve">3.04493498802185</t>
@@ -554,43 +554,43 @@
     <t xml:space="preserve">3.05622291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01953721046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720718383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99555039405823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04070258140564</t>
+    <t xml:space="preserve">3.01953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99555015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04070210456848</t>
   </si>
   <si>
     <t xml:space="preserve">3.01812601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9630970954895</t>
+    <t xml:space="preserve">2.96309685707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.92641091346741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98849487304688</t>
+    <t xml:space="preserve">2.98849511146545</t>
   </si>
   <si>
     <t xml:space="preserve">2.87138247489929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8572723865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86856031417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358899116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604228973389</t>
+    <t xml:space="preserve">2.85727214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86856007575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604181289673</t>
   </si>
   <si>
     <t xml:space="preserve">2.88690304756165</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">2.89819097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85303950309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034061431885</t>
+    <t xml:space="preserve">2.85303926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034013748169</t>
   </si>
   <si>
     <t xml:space="preserve">2.82199716567993</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">2.79377746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82340788841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75567984580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132440567017</t>
+    <t xml:space="preserve">2.82340836524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568056106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132416725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.80929851531982</t>
@@ -638,64 +638,64 @@
     <t xml:space="preserve">2.893958568573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89960217475891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665698051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91230130195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94052124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09432029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08021068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303141593933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560774803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585405349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523864746094</t>
+    <t xml:space="preserve">2.89960193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009430885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9123010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9405210018158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09431982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0802104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303189277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1056079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585381507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523840904236</t>
   </si>
   <si>
     <t xml:space="preserve">3.14511609077454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13806104660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063666343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051386833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20437788963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591188430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0957305431366</t>
+    <t xml:space="preserve">3.13806080818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051339149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2043776512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253999710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573125839233</t>
   </si>
   <si>
     <t xml:space="preserve">3.10278606414795</t>
@@ -704,13 +704,13 @@
     <t xml:space="preserve">3.09290862083435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751108169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1183066368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17897963523865</t>
+    <t xml:space="preserve">3.06751084327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11830711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17898011207581</t>
   </si>
   <si>
     <t xml:space="preserve">3.13664984703064</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">3.07456564903259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1070191860199</t>
+    <t xml:space="preserve">3.10701942443848</t>
   </si>
   <si>
     <t xml:space="preserve">3.098552942276</t>
@@ -737,139 +737,139 @@
     <t xml:space="preserve">3.25094056129456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29891538619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31443572044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3722870349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44565892219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41461682319641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4075620174408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40050649642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657774925232</t>
+    <t xml:space="preserve">3.29891514778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3144359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37228655815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4456582069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41461658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283628463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40756177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4005069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657751083374</t>
   </si>
   <si>
     <t xml:space="preserve">3.51338624954224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47105646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160690307617</t>
+    <t xml:space="preserve">3.47105669975281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160737991333</t>
   </si>
   <si>
     <t xml:space="preserve">3.478111743927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48798799514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185297012329</t>
+    <t xml:space="preserve">3.48798847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185225486755</t>
   </si>
   <si>
     <t xml:space="preserve">3.50633144378662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49222135543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5274965763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056408882141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099149703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209856033325</t>
+    <t xml:space="preserve">3.49222159385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5627715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53455185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866194725037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056456565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099125862122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568379402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209879875183</t>
   </si>
   <si>
     <t xml:space="preserve">3.55924415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6227388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095901489258</t>
+    <t xml:space="preserve">3.62273907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.650958776474</t>
   </si>
   <si>
     <t xml:space="preserve">3.661541223526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66506862640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921095848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804701805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73752331733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68667149543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299385070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71936178207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483350753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124629974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195924758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832789421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379866600037</t>
+    <t xml:space="preserve">3.66506886482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921143531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6333212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804606437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7375226020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68667197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299361228943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71936130523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483255386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124653816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83196020126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832765579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379890441895</t>
   </si>
   <si>
     <t xml:space="preserve">3.84285593032837</t>
@@ -878,103 +878,103 @@
     <t xml:space="preserve">3.85012102127075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88644242286682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648823738098</t>
+    <t xml:space="preserve">3.88644170761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648871421814</t>
   </si>
   <si>
     <t xml:space="preserve">3.82469534873962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83922386169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451161384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097117424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455742835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087954521179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9263961315155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823578834534</t>
+    <t xml:space="preserve">3.83922410011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451113700867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097093582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455695152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823554992676</t>
   </si>
   <si>
     <t xml:space="preserve">3.91913223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8101658821106</t>
+    <t xml:space="preserve">3.81016612052917</t>
   </si>
   <si>
     <t xml:space="preserve">3.68303990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6576144695282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330246925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313153266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150791168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.624924659729</t>
+    <t xml:space="preserve">3.65761423110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330151557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201857566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313200950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150862693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492489814758</t>
   </si>
   <si>
     <t xml:space="preserve">3.67214322090149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63073682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218927383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035009384155</t>
+    <t xml:space="preserve">3.6307361125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030427932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218951225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65034937858582</t>
   </si>
   <si>
     <t xml:space="preserve">3.71572923660278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72662544250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191295623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96635031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366122245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908665657043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998262405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356935501099</t>
+    <t xml:space="preserve">3.72662615776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191367149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96635055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998286247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356840133667</t>
   </si>
   <si>
     <t xml:space="preserve">4.05352306365967</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">4.07894849777222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00267219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9154999256134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00993633270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177575111389</t>
+    <t xml:space="preserve">4.00267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91549968719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00993728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540829658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177598953247</t>
   </si>
   <si>
     <t xml:space="preserve">4.02446603775024</t>
@@ -1013,43 +1013,43 @@
     <t xml:space="preserve">4.10437345504761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96271777153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464953422546</t>
+    <t xml:space="preserve">3.96271824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464929580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.89733862876892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9881432056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9554545879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002843856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01720237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88280916213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07531642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06805229187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14796018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06078767776489</t>
+    <t xml:space="preserve">3.98814392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545411109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002820014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01720142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88281059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07531595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0680513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14795970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04625844955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06078720092773</t>
   </si>
   <si>
     <t xml:space="preserve">4.11527013778687</t>
@@ -1058,31 +1058,31 @@
     <t xml:space="preserve">4.10800647735596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12253475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18065023422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885591506958</t>
+    <t xml:space="preserve">4.12253522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18064975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885639190674</t>
   </si>
   <si>
     <t xml:space="preserve">4.18791389465332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16612100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338609695435</t>
+    <t xml:space="preserve">4.1661205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338514328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.09710931777954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14069509506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979888916016</t>
+    <t xml:space="preserve">4.14069557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979984283447</t>
   </si>
   <si>
     <t xml:space="preserve">4.24602890014648</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">4.22060346603394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26055812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25329351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26419067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239683151245</t>
+    <t xml:space="preserve">4.26055765151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21697092056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25329303741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26419019699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27508687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239730834961</t>
   </si>
   <si>
     <t xml:space="preserve">4.17701768875122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08984470367432</t>
+    <t xml:space="preserve">4.08984518051147</t>
   </si>
   <si>
     <t xml:space="preserve">4.30777645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29687976837158</t>
+    <t xml:space="preserve">4.29688024520874</t>
   </si>
   <si>
     <t xml:space="preserve">4.4276385307312</t>
@@ -1127,58 +1127,58 @@
     <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5402364730835</t>
+    <t xml:space="preserve">4.54023694992065</t>
   </si>
   <si>
     <t xml:space="preserve">4.60198354721069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59835195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929397583008</t>
+    <t xml:space="preserve">4.59835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72184562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929349899292</t>
   </si>
   <si>
     <t xml:space="preserve">4.56202936172485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62014436721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59471940994263</t>
+    <t xml:space="preserve">4.62014484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59471845626831</t>
   </si>
   <si>
     <t xml:space="preserve">4.60924768447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48938608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844358444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52207517623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49301815032959</t>
+    <t xml:space="preserve">4.48938512802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669603347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844263076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33683347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52207565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49301862716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.50391435623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49665021896362</t>
+    <t xml:space="preserve">4.49664974212646</t>
   </si>
   <si>
     <t xml:space="preserve">4.46032810211182</t>
@@ -1187,139 +1187,139 @@
     <t xml:space="preserve">4.45306396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46759271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47848844528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750156402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53660345077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853569030762</t>
+    <t xml:space="preserve">4.46759223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4784893989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750108718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53660440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853521347046</t>
   </si>
   <si>
     <t xml:space="preserve">4.37315607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39131736755371</t>
+    <t xml:space="preserve">4.39131641387939</t>
   </si>
   <si>
     <t xml:space="preserve">4.42037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29324769973755</t>
+    <t xml:space="preserve">4.29324722290039</t>
   </si>
   <si>
     <t xml:space="preserve">4.40947771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51117849349976</t>
+    <t xml:space="preserve">4.51117897033691</t>
   </si>
   <si>
     <t xml:space="preserve">4.42400646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140899658203</t>
+    <t xml:space="preserve">4.31140851974487</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2060751914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12616634368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23150062561035</t>
+    <t xml:space="preserve">4.20607471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12616682052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23149967193604</t>
   </si>
   <si>
     <t xml:space="preserve">4.14432764053345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97361516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94092535972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97724723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258056640625</t>
+    <t xml:space="preserve">3.97361421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94092559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9772469997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16975259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44579887390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41674184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108686447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55113363265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5765585899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5293402671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52570724487305</t>
+    <t xml:space="preserve">4.16975355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44579982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40584564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108781814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61288118362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55113315582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57655811309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52933931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52570819854736</t>
   </si>
   <si>
     <t xml:space="preserve">4.53297185897827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67825984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64920282363892</t>
+    <t xml:space="preserve">4.6782603263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920234680176</t>
   </si>
   <si>
     <t xml:space="preserve">4.67099523544312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64557027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283441543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75816774368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75090360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76179981231689</t>
+    <t xml:space="preserve">4.64556980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75816822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75090408325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76179933547974</t>
   </si>
   <si>
     <t xml:space="preserve">4.72547817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68552398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911071777344</t>
+    <t xml:space="preserve">4.68552350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911024093628</t>
   </si>
   <si>
     <t xml:space="preserve">4.65646648406982</t>
@@ -1328,37 +1328,37 @@
     <t xml:space="preserve">4.84534025192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81265068054199</t>
+    <t xml:space="preserve">4.81265020370483</t>
   </si>
   <si>
     <t xml:space="preserve">4.81991481781006</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83807611465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88166236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84897232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91798448562622</t>
+    <t xml:space="preserve">4.8380765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88166189193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897327423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798400878906</t>
   </si>
   <si>
     <t xml:space="preserve">4.89255905151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95430564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94704103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93251323699951</t>
+    <t xml:space="preserve">4.95430660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94704151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9325122833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.99062776565552</t>
@@ -1367,61 +1367,61 @@
     <t xml:space="preserve">4.94340944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86713314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7330756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888193130493</t>
+    <t xml:space="preserve">4.86713361740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73307657241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888145446777</t>
   </si>
   <si>
     <t xml:space="preserve">4.86018848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82654094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75176906585693</t>
+    <t xml:space="preserve">4.82654047012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75176954269409</t>
   </si>
   <si>
     <t xml:space="preserve">4.6508264541626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49380493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62091732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74803066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7218599319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690536499023</t>
+    <t xml:space="preserve">4.49380540847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62091779708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63587236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74803018569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72185945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690584182739</t>
   </si>
   <si>
     <t xml:space="preserve">4.57979345321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7592453956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83027935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93496084213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644912719727</t>
+    <t xml:space="preserve">4.75924634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83027982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85644960403442</t>
   </si>
   <si>
     <t xml:space="preserve">4.81532526016235</t>
@@ -1430,34 +1430,34 @@
     <t xml:space="preserve">4.94243764877319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91252946853638</t>
+    <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.91626739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90505218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88262033462524</t>
+    <t xml:space="preserve">4.90505170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88261985778809</t>
   </si>
   <si>
     <t xml:space="preserve">4.93869876861572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96486949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216409683228</t>
+    <t xml:space="preserve">4.96486902236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216457366943</t>
   </si>
   <si>
     <t xml:space="preserve">5.01721000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13684511184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05833387374878</t>
+    <t xml:space="preserve">5.13684558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0583348274231</t>
   </si>
   <si>
     <t xml:space="preserve">4.98356199264526</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">5.3162989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41350173950195</t>
+    <t xml:space="preserve">5.41350221633911</t>
   </si>
   <si>
     <t xml:space="preserve">5.34246873855591</t>
@@ -1487,31 +1487,31 @@
     <t xml:space="preserve">5.09945917129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01347160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17796993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2004017829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666290283203</t>
+    <t xml:space="preserve">5.0134711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17797040939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20040130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274229049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666337966919</t>
   </si>
   <si>
     <t xml:space="preserve">5.11815214157104</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">5.04338026046753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99851703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11067533493042</t>
+    <t xml:space="preserve">4.99851655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11067485809326</t>
   </si>
   <si>
     <t xml:space="preserve">5.17049264907837</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">5.04711866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441421508789</t>
+    <t xml:space="preserve">5.11441373825073</t>
   </si>
   <si>
     <t xml:space="preserve">5.06581163406372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97982406616211</t>
+    <t xml:space="preserve">4.97982358932495</t>
   </si>
   <si>
     <t xml:space="preserve">4.95739221572876</t>
@@ -1556,22 +1556,22 @@
     <t xml:space="preserve">5.18544673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09572076797485</t>
+    <t xml:space="preserve">5.0957202911377</t>
   </si>
   <si>
     <t xml:space="preserve">5.21161699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88635873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77420139312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672315597534</t>
+    <t xml:space="preserve">4.8863582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.920006275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77420091629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672267913818</t>
   </si>
   <si>
     <t xml:space="preserve">4.68073606491089</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6844744682312</t>
+    <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
     <t xml:space="preserve">4.62839508056641</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">4.58727073669434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69568967819214</t>
+    <t xml:space="preserve">4.6956901550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.56109952926636</t>
@@ -1607,100 +1607,100 @@
     <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.613440990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550699234009</t>
+    <t xml:space="preserve">4.61344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848642349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.792893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766576766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167772293091</t>
+    <t xml:space="preserve">4.79289293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">4.7779393196106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87140369415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83775663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68821287155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71812152862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74055337905884</t>
+    <t xml:space="preserve">4.87140464782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83775615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68821239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71812105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74055290222168</t>
   </si>
   <si>
     <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54988431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52371454238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48632764816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903305053711</t>
+    <t xml:space="preserve">4.54988384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52371406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903257369995</t>
   </si>
   <si>
     <t xml:space="preserve">4.46015787124634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64334869384766</t>
+    <t xml:space="preserve">4.64334917068481</t>
   </si>
   <si>
     <t xml:space="preserve">4.66204261779785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65456485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298379898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73681402206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86392688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927696228027</t>
+    <t xml:space="preserve">4.65456533432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73681449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86392641067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927648544312</t>
   </si>
   <si>
     <t xml:space="preserve">5.21909475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22657155990601</t>
+    <t xml:space="preserve">5.22657108306885</t>
   </si>
   <si>
     <t xml:space="preserve">5.18918609619141</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">5.15179920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20414066314697</t>
+    <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
     <t xml:space="preserve">5.37237739562988</t>
@@ -1730,34 +1730,34 @@
     <t xml:space="preserve">5.79483985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7611927986145</t>
+    <t xml:space="preserve">5.76119232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.81353330612183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79110097885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75745296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87708902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167964935303</t>
+    <t xml:space="preserve">5.79110145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75745344161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87708950042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195272445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924779891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167917251587</t>
   </si>
   <si>
     <t xml:space="preserve">6.02663421630859</t>
@@ -1766,31 +1766,31 @@
     <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00794124603271</t>
+    <t xml:space="preserve">6.00794076919556</t>
   </si>
   <si>
     <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93316841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699863433838</t>
+    <t xml:space="preserve">5.93316888809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699815750122</t>
   </si>
   <si>
     <t xml:space="preserve">5.94064617156982</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07897329330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93690729141235</t>
+    <t xml:space="preserve">6.07897424697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9369068145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.95933818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89952087402344</t>
+    <t xml:space="preserve">5.8995213508606</t>
   </si>
   <si>
     <t xml:space="preserve">5.89578247070312</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">5.88082790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94812345504761</t>
+    <t xml:space="preserve">5.94812297821045</t>
   </si>
   <si>
     <t xml:space="preserve">5.95559978485107</t>
@@ -1811,25 +1811,25 @@
     <t xml:space="preserve">6.02114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9136209487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.840660572052</t>
+    <t xml:space="preserve">5.91362047195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84066104888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69474077224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68322038650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66401958465576</t>
+    <t xml:space="preserve">5.69473934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778059005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68322086334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66402006149292</t>
   </si>
   <si>
     <t xml:space="preserve">5.66786003112793</t>
@@ -1841,46 +1841,46 @@
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002073287964</t>
+    <t xml:space="preserve">5.76002025604248</t>
   </si>
   <si>
     <t xml:space="preserve">5.87522077560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82146072387695</t>
+    <t xml:space="preserve">5.82146024703979</t>
   </si>
   <si>
     <t xml:space="preserve">5.74850082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69858026504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64482069015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60642051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77538108825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72162055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81762075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78690099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95970153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0557017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28226280212402</t>
+    <t xml:space="preserve">5.69858074188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64482021331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60641956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77538061141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72162008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81762027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78690052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95970106124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05570125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28226232528687</t>
   </si>
   <si>
     <t xml:space="preserve">6.17474174499512</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">6.12866163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22850179672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19394111633301</t>
+    <t xml:space="preserve">6.22850227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19394159317017</t>
   </si>
   <si>
     <t xml:space="preserve">6.06722164154053</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">6.25154209136963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17090129852295</t>
+    <t xml:space="preserve">6.17090225219727</t>
   </si>
   <si>
     <t xml:space="preserve">6.1670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29378271102905</t>
+    <t xml:space="preserve">6.29378175735474</t>
   </si>
   <si>
     <t xml:space="preserve">6.39746236801147</t>
@@ -1922,97 +1922,97 @@
     <t xml:space="preserve">6.43586254119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210248947144</t>
+    <t xml:space="preserve">6.46274185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210391998291</t>
   </si>
   <si>
     <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44738292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5280237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58946323394775</t>
+    <t xml:space="preserve">6.44738388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52802276611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58946371078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.62018346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64322328567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786388397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80450344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78914356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76610422134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114538192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514566421509</t>
+    <t xml:space="preserve">6.64322280883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786436080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80450391769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138513565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522367477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78914403915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76610374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514471054077</t>
   </si>
   <si>
     <t xml:space="preserve">6.68930387496948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63554430007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338264465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298400878906</t>
+    <t xml:space="preserve">6.63554382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634254455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7929835319519</t>
   </si>
   <si>
     <t xml:space="preserve">7.14626550674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01570606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642534255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00802516937256</t>
+    <t xml:space="preserve">7.01570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0080246925354</t>
   </si>
   <si>
     <t xml:space="preserve">6.99266481399536</t>
@@ -2030,91 +2030,91 @@
     <t xml:space="preserve">7.06178522109985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07330465316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96578407287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426416397095</t>
+    <t xml:space="preserve">7.07330513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034475326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96578454971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
     <t xml:space="preserve">7.02722501754761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186466217041</t>
+    <t xml:space="preserve">7.01186561584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.94274425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75074434280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506383895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90434503555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0233850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346544265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15778541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16546535491943</t>
+    <t xml:space="preserve">7.04258489608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634447097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7507438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9350643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02338552474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346496582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15778493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16546487808228</t>
   </si>
   <si>
     <t xml:space="preserve">7.29602527618408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850564956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698526382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19234561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010595321655</t>
+    <t xml:space="preserve">7.16930675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682542800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706565856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19234466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010499954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.26914596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34210586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43426609039307</t>
+    <t xml:space="preserve">7.34210538864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43426561355591</t>
   </si>
   <si>
     <t xml:space="preserve">7.45730638504028</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">7.34978628158569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42658662796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2806658744812</t>
+    <t xml:space="preserve">7.42658615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066635131836</t>
   </si>
   <si>
     <t xml:space="preserve">7.11938571929932</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">7.22306489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11554670333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06562519073486</t>
+    <t xml:space="preserve">7.11554622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06562471389771</t>
   </si>
   <si>
     <t xml:space="preserve">7.08866500854492</t>
@@ -2150,25 +2150,25 @@
     <t xml:space="preserve">6.77378463745117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066394805908</t>
+    <t xml:space="preserve">6.80066347122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.77762413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9273853302002</t>
+    <t xml:space="preserve">6.88898420333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92738580703735</t>
   </si>
   <si>
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202402114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290361404419</t>
+    <t xml:space="preserve">6.91202449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210441589355</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">6.84674406051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08098554611206</t>
+    <t xml:space="preserve">7.08098602294922</t>
   </si>
   <si>
     <t xml:space="preserve">7.03106451034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05794477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218481063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602478027344</t>
+    <t xml:space="preserve">7.05794429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842428207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602430343628</t>
   </si>
   <si>
     <t xml:space="preserve">6.87746429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74306344985962</t>
+    <t xml:space="preserve">6.74306392669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
@@ -2207,112 +2207,112 @@
     <t xml:space="preserve">6.72002363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89282464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466279983521</t>
+    <t xml:space="preserve">6.89282417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682397842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466375350952</t>
   </si>
   <si>
     <t xml:space="preserve">6.67778348922729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7853045463562</t>
+    <t xml:space="preserve">6.78530406951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.71234321594238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73538446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314481735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1117057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25762605667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826637268066</t>
+    <t xml:space="preserve">6.73538494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20770645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002508163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11170625686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2576265335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826541900635</t>
   </si>
   <si>
     <t xml:space="preserve">7.37282609939575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58786678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098699569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17922782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218770980835</t>
+    <t xml:space="preserve">7.58786630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6646671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418714523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17922878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434698104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218723297119</t>
   </si>
   <si>
     <t xml:space="preserve">7.73378705978394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49186849594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130523681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858701705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6800274848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8944206237793</t>
+    <t xml:space="preserve">7.49186563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858797073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
     <t xml:space="preserve">6.27458238601685</t>
@@ -2324,55 +2324,55 @@
     <t xml:space="preserve">6.26690244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.336021900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922445297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754806518555</t>
+    <t xml:space="preserve">6.33602285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394449234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938812255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754758834839</t>
   </si>
   <si>
     <t xml:space="preserve">8.2717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88021802902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57022953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35335826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72860527038574</t>
+    <t xml:space="preserve">7.88021850585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364862442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718223571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35335636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72860431671143</t>
   </si>
   <si>
     <t xml:space="preserve">9.03043556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95701789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70413303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75307846069336</t>
+    <t xml:space="preserve">8.95701694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70413208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75307750701904</t>
   </si>
   <si>
     <t xml:space="preserve">7.99442386627197</t>
@@ -2381,73 +2381,73 @@
     <t xml:space="preserve">7.83127212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74969530105591</t>
+    <t xml:space="preserve">7.74969625473022</t>
   </si>
   <si>
     <t xml:space="preserve">7.81903457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79864168167114</t>
+    <t xml:space="preserve">7.79864263534546</t>
   </si>
   <si>
     <t xml:space="preserve">7.87613821029663</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80679941177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68035697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50904846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70482921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377511978149</t>
+    <t xml:space="preserve">7.80679893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035793304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50904655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70483016967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377559661865</t>
   </si>
   <si>
     <t xml:space="preserve">7.89653205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9454779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85574436187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010829925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146295547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85739803314209</t>
+    <t xml:space="preserve">7.94547748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85574388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146200180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85739898681641</t>
   </si>
   <si>
     <t xml:space="preserve">7.78709602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75814819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69611549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54310274124146</t>
+    <t xml:space="preserve">7.75814723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69611501693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5431022644043</t>
   </si>
   <si>
     <t xml:space="preserve">7.600998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58032274246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51829051971436</t>
+    <t xml:space="preserve">7.580322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5182900428772</t>
   </si>
   <si>
     <t xml:space="preserve">7.73333501815796</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">7.65062522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55551052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53483200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45212268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4934778213501</t>
+    <t xml:space="preserve">7.55550909042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53483152389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49347734451294</t>
   </si>
   <si>
     <t xml:space="preserve">7.63408327102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249729156494</t>
+    <t xml:space="preserve">7.40249633789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.40663194656372</t>
@@ -2480,85 +2480,85 @@
     <t xml:space="preserve">7.36941242218018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58445739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656030654907</t>
+    <t xml:space="preserve">7.58445692062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520612716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235353469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656078338623</t>
   </si>
   <si>
     <t xml:space="preserve">7.75401163101196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72919893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385099411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009046554565</t>
+    <t xml:space="preserve">7.72919940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354803085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3900899887085</t>
   </si>
   <si>
     <t xml:space="preserve">7.37768459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73746919631958</t>
+    <t xml:space="preserve">7.73746967315674</t>
   </si>
   <si>
     <t xml:space="preserve">7.69197988510132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77468824386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72506332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784523010254</t>
+    <t xml:space="preserve">7.77468872070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72506380081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68784427642822</t>
   </si>
   <si>
     <t xml:space="preserve">7.67543792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62167644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71265745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62581300735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4231743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3363299369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36527729034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25775480270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08406448364258</t>
+    <t xml:space="preserve">7.62167692184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438623428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71265697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42317485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33632946014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3652777671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2577543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08406496047974</t>
   </si>
   <si>
     <t xml:space="preserve">7.02203273773193</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752443313599</t>
+    <t xml:space="preserve">7.06752395629883</t>
   </si>
   <si>
     <t xml:space="preserve">7.09647178649902</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">7.07165908813477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24534940719604</t>
+    <t xml:space="preserve">7.24534893035889</t>
   </si>
   <si>
     <t xml:space="preserve">7.17091035842896</t>
@@ -2588,43 +2588,43 @@
     <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98894929885864</t>
+    <t xml:space="preserve">6.98894882202148</t>
   </si>
   <si>
     <t xml:space="preserve">6.93932437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864681243896</t>
+    <t xml:space="preserve">7.05511713027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864633560181</t>
   </si>
   <si>
     <t xml:space="preserve">6.90624046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95173025131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8979697227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98481321334839</t>
+    <t xml:space="preserve">6.9517297744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.93105220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82353019714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75322771072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78217506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413707733154</t>
+    <t xml:space="preserve">6.82353115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75322723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78217554092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413660049438</t>
   </si>
   <si>
     <t xml:space="preserve">6.947594165802</t>
@@ -2633,28 +2633,28 @@
     <t xml:space="preserve">7.30324554443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43558120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700702667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48934125900269</t>
+    <t xml:space="preserve">7.43558073043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700750350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48934173583984</t>
   </si>
   <si>
     <t xml:space="preserve">7.59272909164429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80777263641357</t>
+    <t xml:space="preserve">7.80777311325073</t>
   </si>
   <si>
     <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71679258346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092866897583</t>
+    <t xml:space="preserve">7.71679210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092962265015</t>
   </si>
   <si>
     <t xml:space="preserve">7.84085702896118</t>
@@ -2663,40 +2663,40 @@
     <t xml:space="preserve">7.81190824508667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82845067977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83672285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912729263306</t>
+    <t xml:space="preserve">7.82845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83672189712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912776947021</t>
   </si>
   <si>
     <t xml:space="preserve">7.66716766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67957258224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61754083633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60513496398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59686422348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57205104827881</t>
+    <t xml:space="preserve">7.67957305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61754179000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60513544082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59686374664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57205057144165</t>
   </si>
   <si>
     <t xml:space="preserve">7.54723834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55137348175049</t>
+    <t xml:space="preserve">7.5513744354248</t>
   </si>
   <si>
     <t xml:space="preserve">8.03522396087646</t>
@@ -2711,28 +2711,28 @@
     <t xml:space="preserve">8.47772026062012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14688301086426</t>
+    <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
     <t xml:space="preserve">8.31230068206787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56042957305908</t>
+    <t xml:space="preserve">8.56042861938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.40328025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41155242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28748798370361</t>
+    <t xml:space="preserve">8.41155338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748893737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.33711338043213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6100549697876</t>
+    <t xml:space="preserve">8.61005592346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.68449401855469</t>
@@ -2744,16 +2744,16 @@
     <t xml:space="preserve">8.25026893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59351253509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88299560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92435073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99051856994629</t>
+    <t xml:space="preserve">8.59351444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88299655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92434978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99051952362061</t>
   </si>
   <si>
     <t xml:space="preserve">8.8002872467041</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">8.81682872772217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7341194152832</t>
+    <t xml:space="preserve">8.73411846160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.35365676879883</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">8.10966300964355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21304893493652</t>
+    <t xml:space="preserve">8.21304988861084</t>
   </si>
   <si>
     <t xml:space="preserve">8.18823719024658</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">8.32057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24199867248535</t>
+    <t xml:space="preserve">8.24199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
@@ -2801,34 +2801,34 @@
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9566502571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86980533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85326290130615</t>
+    <t xml:space="preserve">7.95664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86980485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85326242446899</t>
   </si>
   <si>
     <t xml:space="preserve">7.89875364303589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74574136734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303300857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415491104126</t>
+    <t xml:space="preserve">7.74574089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476083755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5141544342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.4479866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33219385147095</t>
+    <t xml:space="preserve">7.33219337463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.35287141799927</t>
@@ -2837,97 +2837,97 @@
     <t xml:space="preserve">7.46866369247437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43971586227417</t>
+    <t xml:space="preserve">7.43971633911133</t>
   </si>
   <si>
     <t xml:space="preserve">7.43144464492798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50588369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8201789855957</t>
+    <t xml:space="preserve">7.50588274002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82017993927002</t>
   </si>
   <si>
     <t xml:space="preserve">7.76228332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38181924819946</t>
+    <t xml:space="preserve">7.38181972503662</t>
   </si>
   <si>
     <t xml:space="preserve">7.2039942741394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338739395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02616786956787</t>
+    <t xml:space="preserve">7.06338787078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02616834640503</t>
   </si>
   <si>
     <t xml:space="preserve">7.09233665466309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12542009353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12955570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518924713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04271125793457</t>
+    <t xml:space="preserve">7.12542057037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670454025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12955522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04271078109741</t>
   </si>
   <si>
     <t xml:space="preserve">7.16263914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2991099357605</t>
+    <t xml:space="preserve">7.29911088943481</t>
   </si>
   <si>
     <t xml:space="preserve">7.22053527832031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53896713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70025110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80281114578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03108882904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88386631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01123905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81935214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190525054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
+    <t xml:space="preserve">7.53896808624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70025062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80281066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03108978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88386535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01124000549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8193531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77138042449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190477371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86732482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619312286377</t>
   </si>
   <si>
     <t xml:space="preserve">7.69694232940674</t>
@@ -2936,61 +2936,61 @@
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319269180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01785469055176</t>
+    <t xml:space="preserve">7.97319316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01785564422607</t>
   </si>
   <si>
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99965906143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02281761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05093860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845319747925</t>
+    <t xml:space="preserve">7.99965953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02281665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05093955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845367431641</t>
   </si>
   <si>
     <t xml:space="preserve">7.95003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88055753707886</t>
+    <t xml:space="preserve">7.8805570602417</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82431554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01289081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81604433059692</t>
+    <t xml:space="preserve">7.8243145942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84416532516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81604480743408</t>
   </si>
   <si>
     <t xml:space="preserve">7.63904523849487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66055107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73498916625977</t>
+    <t xml:space="preserve">7.66055011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73498964309692</t>
   </si>
   <si>
     <t xml:space="preserve">7.79480361938477</t>
@@ -2999,28 +2999,28 @@
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967714309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85291051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258729934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8922176361084</t>
+    <t xml:space="preserve">7.78967761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847501754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82385778427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960878372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404285430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89221715927124</t>
   </si>
   <si>
     <t xml:space="preserve">7.94006967544556</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">7.98963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09046363830566</t>
+    <t xml:space="preserve">8.09046459197998</t>
   </si>
   <si>
     <t xml:space="preserve">8.09388160705566</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">8.28699970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41517543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39808559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46302700042725</t>
+    <t xml:space="preserve">8.41517448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39808654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46302795410156</t>
   </si>
   <si>
     <t xml:space="preserve">8.44252014160156</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">8.31947135925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2442741394043</t>
+    <t xml:space="preserve">8.24427318572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.1912956237793</t>
@@ -3077,22 +3077,22 @@
     <t xml:space="preserve">8.12806224822998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09900760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12293434143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11951637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22718524932861</t>
+    <t xml:space="preserve">8.09900856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12293338775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11951541900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2271842956543</t>
   </si>
   <si>
     <t xml:space="preserve">8.36903190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2459831237793</t>
+    <t xml:space="preserve">8.24598217010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.29041767120361</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">8.35877799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48011779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45619297027588</t>
+    <t xml:space="preserve">8.48011875152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45619201660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.44081115722656</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">8.46986389160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40663146972656</t>
+    <t xml:space="preserve">8.40663051605225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37245082855225</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57496738433838</t>
+    <t xml:space="preserve">8.5749683380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2596549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32630729675293</t>
+    <t xml:space="preserve">8.25965595245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32630634307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.2425651550293</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">8.15027904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2186393737793</t>
+    <t xml:space="preserve">8.21863842010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.17420482635498</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42030334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50233459472656</t>
+    <t xml:space="preserve">8.50404453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42030239105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50233554840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.66896343231201</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">8.64760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60060214996338</t>
+    <t xml:space="preserve">8.6006031036377</t>
   </si>
   <si>
     <t xml:space="preserve">8.63478374481201</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">8.61769390106201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54164218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62196636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69032669067383</t>
+    <t xml:space="preserve">8.5416431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6219654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69032764434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">8.63051223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5382251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55360698699951</t>
+    <t xml:space="preserve">8.53822422027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5536060333252</t>
   </si>
   <si>
     <t xml:space="preserve">8.42372035980225</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143424987793</t>
+    <t xml:space="preserve">8.33143329620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.36561393737793</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">8.31434345245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40492248535156</t>
+    <t xml:space="preserve">8.40492153167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.30579948425293</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">8.49720859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47840785980225</t>
+    <t xml:space="preserve">8.47840881347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459831237793</t>
+    <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.2323112487793</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">8.2220573425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08875370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475860595703</t>
+    <t xml:space="preserve">8.07166481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08875465393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475812911987</t>
   </si>
   <si>
     <t xml:space="preserve">8.2391471862793</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">8.33485221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40150356292725</t>
+    <t xml:space="preserve">8.40150451660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.31776237487793</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">8.31605243682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2169303894043</t>
+    <t xml:space="preserve">8.21692943572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055725097656</t>
+    <t xml:space="preserve">8.43055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.32972431182861</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5664234161377</t>
+    <t xml:space="preserve">8.56642246246338</t>
   </si>
   <si>
     <t xml:space="preserve">8.50575256347656</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">8.82704639434814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71168994903564</t>
+    <t xml:space="preserve">8.71168899536133</t>
   </si>
   <si>
     <t xml:space="preserve">8.65614604949951</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">8.72023391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72450637817383</t>
+    <t xml:space="preserve">8.72450542449951</t>
   </si>
   <si>
     <t xml:space="preserve">8.6390552520752</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">8.69459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441551208496</t>
+    <t xml:space="preserve">8.75441455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.77150535583496</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">8.88686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88259029388428</t>
+    <t xml:space="preserve">8.88259124755859</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531490325928</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">8.98940467834473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06630897521973</t>
+    <t xml:space="preserve">9.06630992889404</t>
   </si>
   <si>
     <t xml:space="preserve">9.12612533569336</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">9.03212833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98513126373291</t>
+    <t xml:space="preserve">8.98513221740723</t>
   </si>
   <si>
     <t xml:space="preserve">8.70741558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58778476715088</t>
+    <t xml:space="preserve">8.5877857208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.2887077331543</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20667457580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35706806182861</t>
+    <t xml:space="preserve">8.20667552947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35706901550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.78454971313477</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">7.81360387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81018543243408</t>
+    <t xml:space="preserve">7.81018495559692</t>
   </si>
   <si>
     <t xml:space="preserve">8.15540599822998</t>
@@ -3473,19 +3473,19 @@
     <t xml:space="preserve">8.12635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88025426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71106243133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60168552398682</t>
+    <t xml:space="preserve">7.8802547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71106195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60168504714966</t>
   </si>
   <si>
     <t xml:space="preserve">7.61364841461182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54699659347534</t>
+    <t xml:space="preserve">7.5469970703125</t>
   </si>
   <si>
     <t xml:space="preserve">7.45129299163818</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">7.58459663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64953851699829</t>
+    <t xml:space="preserve">7.64953804016113</t>
   </si>
   <si>
     <t xml:space="preserve">7.57434129714966</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">7.58288669586182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48376369476318</t>
+    <t xml:space="preserve">7.48376417160034</t>
   </si>
   <si>
     <t xml:space="preserve">7.41369390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055509567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556629180908</t>
+    <t xml:space="preserve">7.69055461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556581497192</t>
   </si>
   <si>
     <t xml:space="preserve">7.56579637527466</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">7.78626012802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56237936019897</t>
+    <t xml:space="preserve">7.56237888336182</t>
   </si>
   <si>
     <t xml:space="preserve">7.72302579879761</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9178524017334</t>
+    <t xml:space="preserve">7.91785192489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.95545101165771</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">8.2032585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2288932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48182678222656</t>
+    <t xml:space="preserve">8.22889232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48182773590088</t>
   </si>
   <si>
     <t xml:space="preserve">8.50062656402588</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54335117340088</t>
+    <t xml:space="preserve">8.5433521270752</t>
   </si>
   <si>
     <t xml:space="preserve">8.5578784942627</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">8.87404537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113521575928</t>
+    <t xml:space="preserve">8.89113616943359</t>
   </si>
   <si>
     <t xml:space="preserve">8.95095157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91677188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90395355224609</t>
+    <t xml:space="preserve">8.91677093505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90395259857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.81422901153564</t>
@@ -3617,22 +3617,22 @@
     <t xml:space="preserve">8.67323684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69887256622314</t>
+    <t xml:space="preserve">8.69887161254883</t>
   </si>
   <si>
     <t xml:space="preserve">8.70314407348633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74159717559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46131896972656</t>
+    <t xml:space="preserve">8.74159622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46131992340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.83131980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5621509552002</t>
+    <t xml:space="preserve">8.56215190887451</t>
   </si>
   <si>
     <t xml:space="preserve">8.92368793487549</t>
@@ -5502,6 +5502,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.77000045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8100004196167</t>
   </si>
 </sst>
 </file>
@@ -70658,7 +70661,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.649537037</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>747045</v>
@@ -70679,6 +70682,32 @@
         <v>1824</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6521064815</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>981594</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>9.81999969482422</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>9.73999977111816</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>9.8100004196167</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>9.8100004196167</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="1833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="1834">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433834075928</t>
+    <t xml:space="preserve">3.42433857917786</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">3.46986746788025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47331643104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812421798706</t>
+    <t xml:space="preserve">3.47331571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812469482422</t>
   </si>
   <si>
     <t xml:space="preserve">3.34845638275146</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">3.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26981544494629</t>
+    <t xml:space="preserve">3.26981520652771</t>
   </si>
   <si>
     <t xml:space="preserve">3.28637099266052</t>
@@ -83,40 +83,40 @@
     <t xml:space="preserve">3.14288640022278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425543785095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1649603843689</t>
+    <t xml:space="preserve">3.10425496101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16496062278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.13736701011658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14564561843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430722236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222207069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20910978317261</t>
+    <t xml:space="preserve">3.14564514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119517326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20911002159119</t>
   </si>
   <si>
     <t xml:space="preserve">3.2077305316925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06700420379639</t>
+    <t xml:space="preserve">3.08631920814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06700396537781</t>
   </si>
   <si>
     <t xml:space="preserve">3.00077962875366</t>
@@ -128,58 +128,58 @@
     <t xml:space="preserve">2.99802112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02837324142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1111536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151617050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046836853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14150619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12494993209839</t>
+    <t xml:space="preserve">3.02837347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114386558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115384101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151640892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046884536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1415057182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12495017051697</t>
   </si>
   <si>
     <t xml:space="preserve">3.11805152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808264732361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323851585388</t>
+    <t xml:space="preserve">3.23808288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1732382774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.19531321525574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18703508377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013668060303</t>
+    <t xml:space="preserve">3.18703532218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321808815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013691902161</t>
   </si>
   <si>
     <t xml:space="preserve">3.19255399703979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18427586555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636101722717</t>
+    <t xml:space="preserve">3.18427634239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636054039001</t>
   </si>
   <si>
     <t xml:space="preserve">3.20635032653809</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">3.10563492774963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906797409058</t>
+    <t xml:space="preserve">3.04906868934631</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
@@ -206,139 +206,139 @@
     <t xml:space="preserve">3.0518274307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98422431945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05044841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320763587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595640182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457643508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147459983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629830360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767827033997</t>
+    <t xml:space="preserve">2.98422384262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.050448179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595664024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457667350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767850875854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0256142616272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09873652458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0876989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0559663772583</t>
+    <t xml:space="preserve">3.09873604774475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08769869804382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978432655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05596661567688</t>
   </si>
   <si>
     <t xml:space="preserve">3.06838345527649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01319670677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02975296974182</t>
+    <t xml:space="preserve">3.01319646835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02975344657898</t>
   </si>
   <si>
     <t xml:space="preserve">3.01871562004089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96766805648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249104499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94421362876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9386944770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02235889434814</t>
+    <t xml:space="preserve">2.96766757965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94421410560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869519233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593525886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235865592957</t>
   </si>
   <si>
     <t xml:space="preserve">3.02659201622009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837231636047</t>
+    <t xml:space="preserve">2.99837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98426222801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97861790657043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06892228126526</t>
+    <t xml:space="preserve">2.9913170337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97861814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01389336585999</t>
+    <t xml:space="preserve">3.01389312744141</t>
   </si>
   <si>
     <t xml:space="preserve">3.02094793319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00683808326721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929090499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671552658081</t>
+    <t xml:space="preserve">3.00683832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0392906665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9645082950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083250999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843680381775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205547332764</t>
+    <t xml:space="preserve">2.99978256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714911460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083227157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205523490906</t>
   </si>
   <si>
     <t xml:space="preserve">2.87702608108521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91088962554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72181630134583</t>
+    <t xml:space="preserve">2.9108898639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
     <t xml:space="preserve">2.61034750938416</t>
@@ -347,100 +347,100 @@
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79659938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79518842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87279319763184</t>
+    <t xml:space="preserve">2.71899437904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7965989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79518818855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162806510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83610701560974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87279295921326</t>
   </si>
   <si>
     <t xml:space="preserve">2.94475388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97438526153564</t>
+    <t xml:space="preserve">2.97438502311707</t>
   </si>
   <si>
     <t xml:space="preserve">3.00542712211609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02518129348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597708702087</t>
+    <t xml:space="preserve">3.02518153190613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211258888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597661018372</t>
   </si>
   <si>
     <t xml:space="preserve">3.03364729881287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0703330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05481171607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03788018226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05199003219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333626747131</t>
+    <t xml:space="preserve">3.07033324241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05481195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03787994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05199027061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333579063416</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204786300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15499329566956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14088320732117</t>
+    <t xml:space="preserve">3.15499258041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14088296890259</t>
   </si>
   <si>
     <t xml:space="preserve">3.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10843062400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149765968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947153091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15075993537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419678688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444309234619</t>
+    <t xml:space="preserve">3.10842990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149813652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15076041221619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419702529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444356918335</t>
   </si>
   <si>
     <t xml:space="preserve">3.02800297737122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01248216629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02376937866211</t>
+    <t xml:space="preserve">3.0124819278717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02377009391785</t>
   </si>
   <si>
     <t xml:space="preserve">3.07174372673035</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">3.06045579910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03646922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0900866985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732332229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21002221107483</t>
+    <t xml:space="preserve">3.03646898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008717536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732284545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21002173423767</t>
   </si>
   <si>
     <t xml:space="preserve">3.18462371826172</t>
@@ -470,46 +470,46 @@
     <t xml:space="preserve">3.21707701683044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27774953842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351665496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130966186523</t>
+    <t xml:space="preserve">3.27775025367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22131013870239</t>
   </si>
   <si>
     <t xml:space="preserve">3.20861077308655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19873404502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18180227279663</t>
+    <t xml:space="preserve">3.19873380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18180179595947</t>
   </si>
   <si>
     <t xml:space="preserve">3.1535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15217065811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16628074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12536191940308</t>
+    <t xml:space="preserve">3.15217113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16628098487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1253616809845</t>
   </si>
   <si>
     <t xml:space="preserve">3.11125159263611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08726477622986</t>
+    <t xml:space="preserve">3.08726501464844</t>
   </si>
   <si>
     <t xml:space="preserve">3.09714221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548471450806</t>
+    <t xml:space="preserve">3.11548495292664</t>
   </si>
   <si>
     <t xml:space="preserve">3.08867573738098</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">3.07738780975342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06186676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696111679077</t>
+    <t xml:space="preserve">3.06186747550964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696135520935</t>
   </si>
   <si>
     <t xml:space="preserve">2.92923307418823</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">2.95180916786194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93910956382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92076683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95886373519897</t>
+    <t xml:space="preserve">2.93911004066467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92076706886292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95886421203613</t>
   </si>
   <si>
     <t xml:space="preserve">2.92782211303711</t>
@@ -548,67 +548,67 @@
     <t xml:space="preserve">2.98002910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04493498802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0195369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720694541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99554991722107</t>
+    <t xml:space="preserve">3.04493522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622267723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01953721046448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720718383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99555015563965</t>
   </si>
   <si>
     <t xml:space="preserve">3.0407018661499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01812624931335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96309661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92641139030457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849511146545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138223648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85727214813232</t>
+    <t xml:space="preserve">3.0181257724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9630970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92641115188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138247489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8572723865509</t>
   </si>
   <si>
     <t xml:space="preserve">2.86856007575989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92358922958374</t>
+    <t xml:space="preserve">2.92358946800232</t>
   </si>
   <si>
     <t xml:space="preserve">2.95604228973389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88690304756165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89819073677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303926467896</t>
+    <t xml:space="preserve">2.8869035243988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89819145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303902626038</t>
   </si>
   <si>
     <t xml:space="preserve">2.84034013748169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82199716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8445737361908</t>
+    <t xml:space="preserve">2.82199740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457349777222</t>
   </si>
   <si>
     <t xml:space="preserve">2.85021710395813</t>
@@ -617,43 +617,43 @@
     <t xml:space="preserve">2.78390049934387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79377770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82340812683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75567984580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132464408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80929803848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254713058472</t>
+    <t xml:space="preserve">2.79377746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82340788841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568032264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132440567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80929851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89254689216614</t>
   </si>
   <si>
     <t xml:space="preserve">2.893958568573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89960217475891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831377029419</t>
+    <t xml:space="preserve">2.89960241317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009430885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831400871277</t>
   </si>
   <si>
     <t xml:space="preserve">2.9123010635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94052076339722</t>
+    <t xml:space="preserve">2.94052124023438</t>
   </si>
   <si>
     <t xml:space="preserve">3.09432005882263</t>
@@ -662,64 +662,64 @@
     <t xml:space="preserve">3.08021020889282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08303213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560774803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585429191589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1352391242981</t>
+    <t xml:space="preserve">3.08303189277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10560822486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585453033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523864746094</t>
   </si>
   <si>
     <t xml:space="preserve">3.14511609077454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13806056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063666343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051410675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20437741279602</t>
+    <t xml:space="preserve">3.13806128501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051386833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20437836647034</t>
   </si>
   <si>
     <t xml:space="preserve">3.19591188430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12253952026367</t>
+    <t xml:space="preserve">3.12254023551941</t>
   </si>
   <si>
     <t xml:space="preserve">3.09573078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10278558731079</t>
+    <t xml:space="preserve">3.10278606414795</t>
   </si>
   <si>
     <t xml:space="preserve">3.09290885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751084327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830735206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13665008544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07456612586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1070191860199</t>
+    <t xml:space="preserve">3.06751132011414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11830711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17898011207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13664984703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07456564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10701870918274</t>
   </si>
   <si>
     <t xml:space="preserve">3.09855341911316</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">3.25376296043396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25094056129456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891562461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31443548202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228727340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44565868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41461682319641</t>
+    <t xml:space="preserve">3.2509400844574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891514778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31443643569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37228679656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44565892219543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41461658477783</t>
   </si>
   <si>
     <t xml:space="preserve">3.44283699989319</t>
@@ -767,61 +767,61 @@
     <t xml:space="preserve">3.4005069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48657703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338672637939</t>
+    <t xml:space="preserve">3.48657774925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338648796082</t>
   </si>
   <si>
     <t xml:space="preserve">3.47105646133423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54160642623901</t>
+    <t xml:space="preserve">3.54160666465759</t>
   </si>
   <si>
     <t xml:space="preserve">3.478111743927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48798847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633192062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222111701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277251243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5274965763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099197387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568379402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393621444702</t>
+    <t xml:space="preserve">3.48798823356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222159385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53455138206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866099357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056456565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099149703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393669128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55924415588379</t>
+    <t xml:space="preserve">3.55924439430237</t>
   </si>
   <si>
     <t xml:space="preserve">3.62273907661438</t>
@@ -830,145 +830,145 @@
     <t xml:space="preserve">3.650958776474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66154146194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506934165955</t>
+    <t xml:space="preserve">3.661541223526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506886482239</t>
   </si>
   <si>
     <t xml:space="preserve">3.61921143531799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6333212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804630279541</t>
+    <t xml:space="preserve">3.63332200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804677963257</t>
   </si>
   <si>
     <t xml:space="preserve">3.7375226020813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68667197227478</t>
+    <t xml:space="preserve">3.68667149543762</t>
   </si>
   <si>
     <t xml:space="preserve">3.72299361228943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7193615436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483350753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195948600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832789421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379890441895</t>
+    <t xml:space="preserve">3.71936178207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483326911926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124701499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195996284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379818916321</t>
   </si>
   <si>
     <t xml:space="preserve">3.84285616874695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85012030601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88644170761108</t>
+    <t xml:space="preserve">3.85012054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8864426612854</t>
   </si>
   <si>
     <t xml:space="preserve">3.86101746559143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84648823738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469534873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922362327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451113700867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455695152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087930679321</t>
+    <t xml:space="preserve">3.84648895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469487190247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922338485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097069740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087954521179</t>
   </si>
   <si>
     <t xml:space="preserve">3.92639636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90823554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913223266602</t>
+    <t xml:space="preserve">3.90823602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913199424744</t>
   </si>
   <si>
     <t xml:space="preserve">3.81016635894775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68303966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65761375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201952934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313200950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492418289185</t>
+    <t xml:space="preserve">3.68303990364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65761423110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6133017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201905250549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313153266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150815010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492489814758</t>
   </si>
   <si>
     <t xml:space="preserve">3.67214322090149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63073682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65034985542297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572947502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7266263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191367149353</t>
+    <t xml:space="preserve">3.63073658943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030451774597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035033226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7157289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662568092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191319465637</t>
   </si>
   <si>
     <t xml:space="preserve">3.96635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908641815186</t>
+    <t xml:space="preserve">3.93366122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908665657043</t>
   </si>
   <si>
     <t xml:space="preserve">3.96998286247253</t>
@@ -977,58 +977,58 @@
     <t xml:space="preserve">4.01356887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05352306365967</t>
+    <t xml:space="preserve">4.05352354049683</t>
   </si>
   <si>
     <t xml:space="preserve">4.04989099502563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0789475440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182132720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91550016403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99540829658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177598953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446603775024</t>
+    <t xml:space="preserve">4.07894802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182156562805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91549968719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00993680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177575111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446556091309</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10437345504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464953422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89733910560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98814344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9554545879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002915382385</t>
+    <t xml:space="preserve">4.10437393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86465001106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8973388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98814368247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002867698669</t>
   </si>
   <si>
     <t xml:space="preserve">4.01720142364502</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">3.88280987739563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07531642913818</t>
+    <t xml:space="preserve">4.07531595230103</t>
   </si>
   <si>
     <t xml:space="preserve">4.06805181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14795923233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06078720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11527013778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1080060005188</t>
+    <t xml:space="preserve">4.14796018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06078767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11527061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10800647735596</t>
   </si>
   <si>
     <t xml:space="preserve">4.12253475189209</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">4.18064880371094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1588568687439</t>
+    <t xml:space="preserve">4.15885591506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.18791437149048</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.24602890014648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22060346603394</t>
+    <t xml:space="preserve">4.22060394287109</t>
   </si>
   <si>
     <t xml:space="preserve">4.26055765151978</t>
@@ -1097,58 +1097,58 @@
     <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26419019699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08984565734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30777645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42763900756836</t>
+    <t xml:space="preserve">4.25329351425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26418972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27508687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17701816558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08984470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30777549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29688024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42763805389404</t>
   </si>
   <si>
     <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5402364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60198354721069</t>
+    <t xml:space="preserve">4.54023694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60198307037354</t>
   </si>
   <si>
     <t xml:space="preserve">4.59835147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72184562683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56202983856201</t>
+    <t xml:space="preserve">4.72184610366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56202936172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.62014484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59471940994263</t>
+    <t xml:space="preserve">4.59471893310547</t>
   </si>
   <si>
     <t xml:space="preserve">4.60924768447876</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">4.4893856048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45669603347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844358444214</t>
+    <t xml:space="preserve">4.4566969871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844310760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207565307617</t>
+    <t xml:space="preserve">4.52207469940186</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575401306152</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">4.49301767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50391435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665021896362</t>
+    <t xml:space="preserve">4.50391387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49665069580078</t>
   </si>
   <si>
     <t xml:space="preserve">4.46032857894897</t>
@@ -1190,40 +1190,40 @@
     <t xml:space="preserve">4.46759271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47848987579346</t>
+    <t xml:space="preserve">4.4784893989563</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750108718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5366039276123</t>
+    <t xml:space="preserve">4.53660440444946</t>
   </si>
   <si>
     <t xml:space="preserve">4.43853521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37315559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39131593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037439346313</t>
+    <t xml:space="preserve">4.37315607070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39131736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037391662598</t>
   </si>
   <si>
     <t xml:space="preserve">4.29324769973755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40947723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51117897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42400598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140851974487</t>
+    <t xml:space="preserve">4.40947771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51117849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42400646209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140899658203</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
@@ -1232,265 +1232,265 @@
     <t xml:space="preserve">4.20607471466064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12616634368896</t>
+    <t xml:space="preserve">4.12616682052612</t>
   </si>
   <si>
     <t xml:space="preserve">4.23150014877319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14432811737061</t>
+    <t xml:space="preserve">4.14432764053345</t>
   </si>
   <si>
     <t xml:space="preserve">3.97361469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94092512130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9772469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258104324341</t>
+    <t xml:space="preserve">3.94092488288879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.169753074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44580030441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41674184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288070678711</t>
+    <t xml:space="preserve">4.16975259780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44579935073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40584516525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
     <t xml:space="preserve">4.55113315582275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57655811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52933979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52570772171021</t>
+    <t xml:space="preserve">4.57655906677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5293402671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52570724487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.53297185897827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67825937271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6492018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67099523544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64556980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283441543579</t>
+    <t xml:space="preserve">4.67825984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920234680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6709942817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64557027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283489227295</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75090408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76179933547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72547817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68552350997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911024093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65646648406982</t>
+    <t xml:space="preserve">4.75090312957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76180028915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72547912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68552398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72910976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65646696090698</t>
   </si>
   <si>
     <t xml:space="preserve">4.84534025192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81265020370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8199143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83807611465454</t>
+    <t xml:space="preserve">4.81265068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81991577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83807563781738</t>
   </si>
   <si>
     <t xml:space="preserve">4.88166236877441</t>
   </si>
   <si>
+    <t xml:space="preserve">4.8489727973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89255952835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94704151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977785110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93251323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99062824249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713266372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7330756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888145446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86018848419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82654094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75176858901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6508264541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49380445480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62091732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6769962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63587188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74803066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7218599319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75924587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83027982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85644960403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81532526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94243764877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91252899169922</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.84897232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89255857467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95430612564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94704151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9325122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99062824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713361740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7330756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888193130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86018848419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82654094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75176906585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6508264541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49380493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62091732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74803066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7218599319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690584182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75924587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83027982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8153247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94243764877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91252899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84897327423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91626787185669</t>
+    <t xml:space="preserve">4.91626739501953</t>
   </si>
   <si>
     <t xml:space="preserve">4.90505170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88261985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93869876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486902236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216409683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13684558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05833435058594</t>
+    <t xml:space="preserve">4.88262033462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93869924545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216505050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01720905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13684463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05833387374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.98356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89757442474365</t>
+    <t xml:space="preserve">4.89757394790649</t>
   </si>
   <si>
     <t xml:space="preserve">5.1293683052063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24900388717651</t>
+    <t xml:space="preserve">5.24900341033936</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31629848480225</t>
+    <t xml:space="preserve">5.3162989616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350221633911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34246826171875</t>
+    <t xml:space="preserve">5.34246873855591</t>
   </si>
   <si>
     <t xml:space="preserve">5.09945917129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0134711265564</t>
+    <t xml:space="preserve">5.01347160339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.17797040939331</t>
@@ -1499,64 +1499,64 @@
     <t xml:space="preserve">5.20040130615234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23404932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11815214157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04337978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99851751327515</t>
+    <t xml:space="preserve">5.23404884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666337966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11815166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04338026046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99851703643799</t>
   </si>
   <si>
     <t xml:space="preserve">5.11067533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17049264907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04711866378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11441421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581163406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982406616211</t>
+    <t xml:space="preserve">5.17049217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11441373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982358932495</t>
   </si>
   <si>
     <t xml:space="preserve">4.95739269256592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03964138031006</t>
+    <t xml:space="preserve">5.0396409034729</t>
   </si>
   <si>
     <t xml:space="preserve">5.05459594726562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08076620101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18544721603394</t>
+    <t xml:space="preserve">5.08076572418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18544673919678</t>
   </si>
   <si>
     <t xml:space="preserve">5.09572076797485</t>
@@ -1565,79 +1565,79 @@
     <t xml:space="preserve">5.2116174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88635873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.920006275177</t>
+    <t xml:space="preserve">4.8863582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92000675201416</t>
   </si>
   <si>
     <t xml:space="preserve">4.77420043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672315597534</t>
+    <t xml:space="preserve">4.76672267913818</t>
   </si>
   <si>
     <t xml:space="preserve">4.68073558807373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66951942443848</t>
+    <t xml:space="preserve">4.66951990127563</t>
   </si>
   <si>
     <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67325782775879</t>
+    <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
     <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62839508056641</t>
+    <t xml:space="preserve">4.62839555740356</t>
   </si>
   <si>
     <t xml:space="preserve">4.5685772895813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58727025985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56109952926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40781688690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61344051361084</t>
+    <t xml:space="preserve">4.58727073669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40781736373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61344003677368</t>
   </si>
   <si>
     <t xml:space="preserve">4.59848594665527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7555079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84523391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.792893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766529083252</t>
+    <t xml:space="preserve">4.75550746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84523439407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79289388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766576766968</t>
   </si>
   <si>
     <t xml:space="preserve">4.78915500640869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78167772293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77793979644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140464782715</t>
+    <t xml:space="preserve">4.78167819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7779393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140369415283</t>
   </si>
   <si>
     <t xml:space="preserve">4.83775663375854</t>
@@ -1646,88 +1646,88 @@
     <t xml:space="preserve">4.68821239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812105178833</t>
+    <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74055242538452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60222434997559</t>
+    <t xml:space="preserve">4.6022253036499</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988384246826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5237135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.486328125</t>
+    <t xml:space="preserve">4.52371406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48632764816284</t>
   </si>
   <si>
     <t xml:space="preserve">4.41903305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46015739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64334964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204214096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456533432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298427581787</t>
+    <t xml:space="preserve">4.46015787124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64334869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298475265503</t>
   </si>
   <si>
     <t xml:space="preserve">4.73681449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86392688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730087280273</t>
+    <t xml:space="preserve">4.86392736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730134963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.14806127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927648544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21909523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22657155990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18918657302856</t>
+    <t xml:space="preserve">5.15927696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21909427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22657108306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">5.15179967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20413970947266</t>
+    <t xml:space="preserve">5.20414066314697</t>
   </si>
   <si>
     <t xml:space="preserve">5.37237739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16675424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09019088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87335014343262</t>
+    <t xml:space="preserve">5.16675472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09018993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87335062026978</t>
   </si>
   <si>
     <t xml:space="preserve">5.79483985900879</t>
@@ -1736,31 +1736,31 @@
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79110145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75745391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87708902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195272445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924827575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167917251587</t>
+    <t xml:space="preserve">5.81353330612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79110193252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231809616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75745344161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87708950042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9219536781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167964935303</t>
   </si>
   <si>
     <t xml:space="preserve">6.02663373947144</t>
@@ -1772,37 +1772,37 @@
     <t xml:space="preserve">6.0079402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92569160461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93316841125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94064617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0789737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9369068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8995213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89578294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88082790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94812250137329</t>
+    <t xml:space="preserve">5.9256911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93316888809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699815750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94064569473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07897424697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93690729141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95933771133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89952087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89578247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88082838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94812297821045</t>
   </si>
   <si>
     <t xml:space="preserve">5.95560026168823</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">5.9136209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84066104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75234031677246</t>
+    <t xml:space="preserve">5.840660572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75234079360962</t>
   </si>
   <si>
     <t xml:space="preserve">5.694739818573</t>
@@ -1841,34 +1841,34 @@
     <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70626020431519</t>
+    <t xml:space="preserve">5.70625972747803</t>
   </si>
   <si>
     <t xml:space="preserve">5.76002025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87522125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82146024703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74850034713745</t>
+    <t xml:space="preserve">5.87522077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82146120071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74850082397461</t>
   </si>
   <si>
     <t xml:space="preserve">5.69858074188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64482021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60641956329346</t>
+    <t xml:space="preserve">5.64481973648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
     <t xml:space="preserve">5.77538061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72162103652954</t>
+    <t xml:space="preserve">5.72161960601807</t>
   </si>
   <si>
     <t xml:space="preserve">5.81762027740479</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95970106124878</t>
+    <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
     <t xml:space="preserve">6.0557017326355</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">6.19394159317017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06722068786621</t>
+    <t xml:space="preserve">6.06722211837769</t>
   </si>
   <si>
     <t xml:space="preserve">6.10178184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25154256820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17090177536011</t>
+    <t xml:space="preserve">6.25154209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17090129852295</t>
   </si>
   <si>
     <t xml:space="preserve">6.1670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29378223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746189117432</t>
+    <t xml:space="preserve">6.29378175735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746236801147</t>
   </si>
   <si>
     <t xml:space="preserve">6.43586254119873</t>
@@ -1934,25 +1934,25 @@
     <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44738340377808</t>
+    <t xml:space="preserve">6.44738292694092</t>
   </si>
   <si>
     <t xml:space="preserve">6.52802324295044</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53954315185547</t>
+    <t xml:space="preserve">6.53954410552979</t>
   </si>
   <si>
     <t xml:space="preserve">6.57410335540771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58946323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322328567505</t>
+    <t xml:space="preserve">6.58946371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322376251221</t>
   </si>
   <si>
     <t xml:space="preserve">6.62786388397217</t>
@@ -1961,112 +1961,112 @@
     <t xml:space="preserve">6.66626358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80450391769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138513565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78914499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76610422134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114442825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882532119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514566421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554430007935</t>
+    <t xml:space="preserve">6.80450344085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522462844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78914451599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76610469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114538192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554382324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.61634349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54338312149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7929835319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626550674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946468353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642629623413</t>
+    <t xml:space="preserve">6.54338407516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298448562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642581939697</t>
   </si>
   <si>
     <t xml:space="preserve">7.00802421569824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99266481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10402488708496</t>
+    <t xml:space="preserve">6.9926643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10402536392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.18082571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10786628723145</t>
+    <t xml:space="preserve">7.10786485671997</t>
   </si>
   <si>
     <t xml:space="preserve">7.06178569793701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07330513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034475326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96578407287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02722501754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186561584473</t>
+    <t xml:space="preserve">7.07330560684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034379959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96578454971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426368713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02722454071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186466217041</t>
   </si>
   <si>
     <t xml:space="preserve">6.94274425506592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634494781494</t>
+    <t xml:space="preserve">7.04258489608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634447097778</t>
   </si>
   <si>
     <t xml:space="preserve">6.75074338912964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93506383895874</t>
+    <t xml:space="preserve">6.93506479263306</t>
   </si>
   <si>
     <t xml:space="preserve">6.90434455871582</t>
@@ -2081,67 +2081,67 @@
     <t xml:space="preserve">7.15778493881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2960262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16930675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706518173218</t>
+    <t xml:space="preserve">7.16546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3113865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706565856934</t>
   </si>
   <si>
     <t xml:space="preserve">7.17698574066162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19234466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010547637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914596557617</t>
+    <t xml:space="preserve">7.19234609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914548873901</t>
   </si>
   <si>
     <t xml:space="preserve">7.34210634231567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43426561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730638504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.119384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22306489944458</t>
+    <t xml:space="preserve">7.43426656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066492080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2230658531189</t>
   </si>
   <si>
     <t xml:space="preserve">7.11554574966431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06562566757202</t>
+    <t xml:space="preserve">7.06562471389771</t>
   </si>
   <si>
     <t xml:space="preserve">7.08866453170776</t>
@@ -2150,130 +2150,130 @@
     <t xml:space="preserve">6.98498487472534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7737832069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88898515701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92738580703735</t>
+    <t xml:space="preserve">6.77378416061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8889856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9273853302002</t>
   </si>
   <si>
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202402114868</t>
+    <t xml:space="preserve">6.912024974823</t>
   </si>
   <si>
     <t xml:space="preserve">6.84290409088135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8621039390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8467435836792</t>
+    <t xml:space="preserve">6.86210441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674453735352</t>
   </si>
   <si>
     <t xml:space="preserve">7.08098554611206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03106498718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05794525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218433380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87746381759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306440353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69314432144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7200231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89282512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466327667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778301239014</t>
+    <t xml:space="preserve">7.03106451034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05794477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842428207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218385696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87746477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306392669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69314384460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72002363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89282560348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682397842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466279983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778396606445</t>
   </si>
   <si>
     <t xml:space="preserve">6.78530359268188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71234369277954</t>
+    <t xml:space="preserve">6.71234321594238</t>
   </si>
   <si>
     <t xml:space="preserve">6.73538446426392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20386600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11170530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2576265335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786725997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362865447998</t>
+    <t xml:space="preserve">7.20386552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410528182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314577102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11170482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986524581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826589584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282657623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466665267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362913131714</t>
   </si>
   <si>
     <t xml:space="preserve">7.96418809890747</t>
@@ -2282,91 +2282,91 @@
     <t xml:space="preserve">8.00258827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17922782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8643479347229</t>
+    <t xml:space="preserve">8.17922878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434698104858</t>
   </si>
   <si>
     <t xml:space="preserve">7.77218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73378610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186658859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130523681641</t>
+    <t xml:space="preserve">7.73378801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130714416504</t>
   </si>
   <si>
     <t xml:space="preserve">7.56482696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61858797073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6800274848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8944206237793</t>
+    <t xml:space="preserve">7.61858749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
     <t xml:space="preserve">6.27458238601685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77154064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26690244674683</t>
+    <t xml:space="preserve">5.77154111862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26690196990967</t>
   </si>
   <si>
     <t xml:space="preserve">6.33602285385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15394496917725</t>
+    <t xml:space="preserve">7.15394401550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.21922540664673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58018779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754758834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2717809677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88021850585938</t>
+    <t xml:space="preserve">7.58018684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938859939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754901885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27178192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8802170753479</t>
   </si>
   <si>
     <t xml:space="preserve">7.57022905349731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64364862442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718223571777</t>
+    <t xml:space="preserve">7.64364767074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718032836914</t>
   </si>
   <si>
     <t xml:space="preserve">8.35335636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72860431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03043556213379</t>
+    <t xml:space="preserve">8.72860622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03043460845947</t>
   </si>
   <si>
     <t xml:space="preserve">8.95701694488525</t>
@@ -2378,211 +2378,211 @@
     <t xml:space="preserve">8.75307750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99442386627197</t>
+    <t xml:space="preserve">7.99442338943481</t>
   </si>
   <si>
     <t xml:space="preserve">7.83127212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74969625473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81903457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79864263534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613821029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68035793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50904655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70483016967773</t>
+    <t xml:space="preserve">7.74969577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81903553009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79864072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035697937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5090479850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70482873916626</t>
   </si>
   <si>
     <t xml:space="preserve">7.75377559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89653205871582</t>
+    <t xml:space="preserve">7.89653158187866</t>
   </si>
   <si>
     <t xml:space="preserve">7.94547748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85574388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146200180054</t>
+    <t xml:space="preserve">7.85574579238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146343231201</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78709602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75814723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69611501693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5431022644043</t>
+    <t xml:space="preserve">7.78709554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7581467628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69611549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54310274124146</t>
   </si>
   <si>
     <t xml:space="preserve">7.600998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.580322265625</t>
+    <t xml:space="preserve">7.58032178878784</t>
   </si>
   <si>
     <t xml:space="preserve">7.5182900428772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73333501815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65062522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55550909042358</t>
+    <t xml:space="preserve">7.73333597183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65062570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55550956726074</t>
   </si>
   <si>
     <t xml:space="preserve">7.53483152389526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45212316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49347734451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63408327102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40249633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663194656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58445692062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520612716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235353469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75401163101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919940948486</t>
+    <t xml:space="preserve">7.4521222114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4934778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63408279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40249681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58445835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520708084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919845581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.37354803085327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44385194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3900899887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73746967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69197988510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77468872070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72506380081177</t>
+    <t xml:space="preserve">7.44385147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34459972381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7374701499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69198036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77468967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72506427764893</t>
   </si>
   <si>
     <t xml:space="preserve">7.68784427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67543792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62167692184448</t>
+    <t xml:space="preserve">7.67543745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62167739868164</t>
   </si>
   <si>
     <t xml:space="preserve">7.70438623428345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71265697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62581253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242612838745</t>
+    <t xml:space="preserve">7.71265745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62581205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242565155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.42317485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33632946014404</t>
+    <t xml:space="preserve">7.3363299369812</t>
   </si>
   <si>
     <t xml:space="preserve">7.3652777671814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08406496047974</t>
+    <t xml:space="preserve">7.25775480270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08406448364258</t>
   </si>
   <si>
     <t xml:space="preserve">7.02203273773193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95586585998535</t>
+    <t xml:space="preserve">6.95586633682251</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09647178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07165908813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534893035889</t>
+    <t xml:space="preserve">7.06752347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09647130966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07166004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534845352173</t>
   </si>
   <si>
     <t xml:space="preserve">7.17091035842896</t>
@@ -2594,49 +2594,49 @@
     <t xml:space="preserve">6.98894882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93932437896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05511713027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864633560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90624046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9517297744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98481369018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93105220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82353115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75322723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78217554092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.947594165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30324554443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43558073043823</t>
+    <t xml:space="preserve">6.93932390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05511665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90623998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95173025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8979697227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98481416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93105268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82353067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75322771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78217601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30324506759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43557977676392</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700750350952</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">7.48934173583984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59272909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80777311325073</t>
+    <t xml:space="preserve">7.59272861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80777263641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.60927057266235</t>
@@ -2657,49 +2657,49 @@
     <t xml:space="preserve">7.71679210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72092962265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085702896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190824508667</t>
+    <t xml:space="preserve">7.72092819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190776824951</t>
   </si>
   <si>
     <t xml:space="preserve">7.82845115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83672189712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912776947021</t>
+    <t xml:space="preserve">7.8367223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912824630737</t>
   </si>
   <si>
     <t xml:space="preserve">7.66716766357422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67957305908203</t>
+    <t xml:space="preserve">7.67957353591919</t>
   </si>
   <si>
     <t xml:space="preserve">7.61754179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60513544082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59686374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57205057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54723834991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5513744354248</t>
+    <t xml:space="preserve">7.60513496398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59686422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57205152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54723787307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55137395858765</t>
   </si>
   <si>
     <t xml:space="preserve">8.03522396087646</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">8.15515232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47772026062012</t>
+    <t xml:space="preserve">8.4777193069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56042861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40328025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41155338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28748893737793</t>
+    <t xml:space="preserve">8.31229972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56042957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40328121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41155242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748798370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.33711338043213</t>
@@ -2741,34 +2741,34 @@
     <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55215930938721</t>
+    <t xml:space="preserve">8.55215835571289</t>
   </si>
   <si>
     <t xml:space="preserve">8.25026893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59351444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88299655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92434978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99051952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8002872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81682872772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73411846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35365676879883</t>
+    <t xml:space="preserve">8.59351253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88299560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92435169219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99051761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80028629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81682968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7341194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35365581512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">8.18823719024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13861083984375</t>
+    <t xml:space="preserve">8.13860988616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.32057285308838</t>
@@ -2792,31 +2792,31 @@
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545623779297</t>
+    <t xml:space="preserve">8.22545528411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.27921772003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2585391998291</t>
+    <t xml:space="preserve">8.25854015350342</t>
   </si>
   <si>
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86980485916138</t>
+    <t xml:space="preserve">7.95664978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86980581283569</t>
   </si>
   <si>
     <t xml:space="preserve">7.85326242446899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89875364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574089050293</t>
+    <t xml:space="preserve">7.89875411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574184417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.66303253173828</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">7.65476083755493</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5141544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4479866027832</t>
+    <t xml:space="preserve">7.51415491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44798707962036</t>
   </si>
   <si>
     <t xml:space="preserve">7.33219337463379</t>
@@ -2837,115 +2837,115 @@
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43144464492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82017993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76228332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38181972503662</t>
+    <t xml:space="preserve">7.46866416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43144416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50588321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82018041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76228284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38182020187378</t>
   </si>
   <si>
     <t xml:space="preserve">7.2039942741394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338787078857</t>
+    <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
     <t xml:space="preserve">7.02616834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09233665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12542057037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670454025269</t>
+    <t xml:space="preserve">7.09233617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12541961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670358657837</t>
   </si>
   <si>
     <t xml:space="preserve">7.12955522537231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93518877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04271078109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263914108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29911088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53896808624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70025062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80281066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03108978271484</t>
+    <t xml:space="preserve">6.93518829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04271173477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16263961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2991099357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70025110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80281019210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03108882904053</t>
   </si>
   <si>
     <t xml:space="preserve">7.88386535644531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01124000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8193531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138042449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190477371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86732482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69694232940674</t>
+    <t xml:space="preserve">8.01123809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81935214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77137994766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79454040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8673243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619407653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6969428062439</t>
   </si>
   <si>
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01785564422607</t>
+    <t xml:space="preserve">7.97319221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635076522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01785469055176</t>
   </si>
   <si>
     <t xml:space="preserve">8.05259323120117</t>
@@ -2957,25 +2957,25 @@
     <t xml:space="preserve">8.02281665802002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05093955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003366470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8805570602417</t>
+    <t xml:space="preserve">8.05093860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845415115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003414154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055658340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8243145942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371513366699</t>
+    <t xml:space="preserve">7.82431554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371608734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.0128927230835</t>
@@ -2984,19 +2984,19 @@
     <t xml:space="preserve">7.84416532516479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81604480743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63904523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66055011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73498964309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79480361938477</t>
+    <t xml:space="preserve">7.81604433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63904619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66055107116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73498868942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79480409622192</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">7.78967761993408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80847501754761</t>
+    <t xml:space="preserve">7.80847597122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82385778427124</t>
+    <t xml:space="preserve">7.82385873794556</t>
   </si>
   <si>
     <t xml:space="preserve">7.77258682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71960878372192</t>
+    <t xml:space="preserve">7.71960783004761</t>
   </si>
   <si>
     <t xml:space="preserve">7.76404285430908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89221715927124</t>
+    <t xml:space="preserve">7.89221811294556</t>
   </si>
   <si>
     <t xml:space="preserve">7.94006967544556</t>
@@ -3032,28 +3032,28 @@
     <t xml:space="preserve">7.98963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09046459197998</t>
+    <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09388160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18445873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24940204620361</t>
+    <t xml:space="preserve">8.1844596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2494010925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.28699970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41517448425293</t>
+    <t xml:space="preserve">8.41517543792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.39808654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38099479675293</t>
+    <t xml:space="preserve">8.38099575042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.46302795410156</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">8.21180248260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36390590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31947135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24427318572998</t>
+    <t xml:space="preserve">8.36390495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31947040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2442741394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.1912956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12806224822998</t>
+    <t xml:space="preserve">8.12806129455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09900856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12293338775635</t>
+    <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
     <t xml:space="preserve">8.11951541900635</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">8.36903190612793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24598217010498</t>
+    <t xml:space="preserve">8.2459831237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877799987793</t>
+    <t xml:space="preserve">8.35877704620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011875152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45619201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44081115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986389160156</t>
+    <t xml:space="preserve">8.45619297027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44081020355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46986293792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.40663051605225</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644687652588</t>
+    <t xml:space="preserve">8.46644592285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5749683380127</t>
+    <t xml:space="preserve">8.57496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25965595245361</t>
+    <t xml:space="preserve">8.25965690612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.32630634307861</t>
@@ -3146,22 +3146,22 @@
     <t xml:space="preserve">8.15027904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17420482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28187370300293</t>
+    <t xml:space="preserve">8.2186393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1742057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28187274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45277404785156</t>
+    <t xml:space="preserve">8.35365200042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45277309417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">8.50233554840088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66896343231201</t>
+    <t xml:space="preserve">8.66896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">8.6006031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63478374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6262378692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61769390106201</t>
+    <t xml:space="preserve">8.6347827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62623882293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6176929473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.5416431427002</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">8.6219654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69032764434814</t>
+    <t xml:space="preserve">8.69032669067383</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53822422027588</t>
+    <t xml:space="preserve">8.63051128387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822326660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">8.42372035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49208068847656</t>
+    <t xml:space="preserve">8.49208164215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.54506015777588</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">8.33143329620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36561393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23401927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31434345245361</t>
+    <t xml:space="preserve">8.36561489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2340202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40492153167725</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">8.47840881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34681510925293</t>
+    <t xml:space="preserve">8.34681415557861</t>
   </si>
   <si>
     <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2323112487793</t>
+    <t xml:space="preserve">8.23231029510498</t>
   </si>
   <si>
     <t xml:space="preserve">8.2152214050293</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">8.17933082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2220573425293</t>
+    <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.07166481018066</t>
@@ -3278,55 +3278,55 @@
     <t xml:space="preserve">8.08875465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99475812911987</t>
+    <t xml:space="preserve">7.99475908279419</t>
   </si>
   <si>
     <t xml:space="preserve">8.2391471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33485221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40150451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">8.33485126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40150356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3177604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2545280456543</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26478290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565895080566</t>
+    <t xml:space="preserve">8.2647819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25111103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565990447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.31605243682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21692943572998</t>
+    <t xml:space="preserve">8.2169303894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055629730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32972431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45106410980225</t>
+    <t xml:space="preserve">8.43055725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32972526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45106506347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.44935512542725</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56642246246338</t>
+    <t xml:space="preserve">8.5664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.50575256347656</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47669982910156</t>
+    <t xml:space="preserve">8.47670078277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.02358341217041</t>
@@ -3359,40 +3359,40 @@
     <t xml:space="preserve">8.80141162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78005027770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66041946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82704639434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65614604949951</t>
+    <t xml:space="preserve">8.78004932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66041851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82704734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65614700317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.72023391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72450542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60914707183838</t>
+    <t xml:space="preserve">8.72450637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63905620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6091480255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.69459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77150535583496</t>
+    <t xml:space="preserve">8.75441360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77150440216064</t>
   </si>
   <si>
     <t xml:space="preserve">8.88686275482178</t>
@@ -3404,10 +3404,10 @@
     <t xml:space="preserve">8.92531490325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94667911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95522308349609</t>
+    <t xml:space="preserve">8.94667816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95522212982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.98085880279541</t>
@@ -3419,19 +3419,19 @@
     <t xml:space="preserve">8.98940467834473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06630992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12612533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20303058624268</t>
+    <t xml:space="preserve">9.06630897521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12612438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20302963256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.03212833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98513221740723</t>
+    <t xml:space="preserve">8.98513126373291</t>
   </si>
   <si>
     <t xml:space="preserve">8.70741558074951</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">8.5877857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2613639831543</t>
+    <t xml:space="preserve">8.28870868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26136493682861</t>
   </si>
   <si>
     <t xml:space="preserve">8.15882396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08020973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20667552947998</t>
+    <t xml:space="preserve">8.08021068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2066764831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.35706901550293</t>
@@ -3461,16 +3461,16 @@
     <t xml:space="preserve">7.78454971313477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81873083114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81360387802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81018495559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540599822998</t>
+    <t xml:space="preserve">7.81872987747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81360292434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81018590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540504455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.12635231018066</t>
@@ -3482,49 +3482,49 @@
     <t xml:space="preserve">7.71106195449829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60168504714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61364841461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5469970703125</t>
+    <t xml:space="preserve">7.60168552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61364889144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54699659347534</t>
   </si>
   <si>
     <t xml:space="preserve">7.45129299163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58459663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58288669586182</t>
+    <t xml:space="preserve">7.58459615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953708648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58288717269897</t>
   </si>
   <si>
     <t xml:space="preserve">7.48376417160034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41369390487671</t>
+    <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
     <t xml:space="preserve">7.69055461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82556581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579637527466</t>
+    <t xml:space="preserve">7.82556676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579685211182</t>
   </si>
   <si>
     <t xml:space="preserve">7.60510301589966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78626012802124</t>
+    <t xml:space="preserve">7.78625965118408</t>
   </si>
   <si>
     <t xml:space="preserve">7.56237888336182</t>
@@ -3533,37 +3533,37 @@
     <t xml:space="preserve">7.72302579879761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66491985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77087688446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62561178207397</t>
+    <t xml:space="preserve">7.66491889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77087783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62561225891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91785192489624</t>
+    <t xml:space="preserve">7.91785287857056</t>
   </si>
   <si>
     <t xml:space="preserve">7.95545101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07508277893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14173316955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2032585144043</t>
+    <t xml:space="preserve">8.07508182525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14173412322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20325946807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.22889232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182773590088</t>
+    <t xml:space="preserve">8.48182678222656</t>
   </si>
   <si>
     <t xml:space="preserve">8.50062656402588</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5433521270752</t>
+    <t xml:space="preserve">8.54335117340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.5578784942627</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">8.97658634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93813323974609</t>
+    <t xml:space="preserve">8.93813228607178</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89113616943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95095157623291</t>
+    <t xml:space="preserve">8.89113521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95095062255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.91677093505859</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">8.6134204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67323684692383</t>
+    <t xml:space="preserve">8.67323589324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.69887161254883</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">8.74159622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46131992340088</t>
+    <t xml:space="preserve">8.46131896972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.83131980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56215190887451</t>
+    <t xml:space="preserve">8.5621509552002</t>
   </si>
   <si>
     <t xml:space="preserve">8.92368793487549</t>
@@ -5511,6 +5511,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.85000038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89999961853027</t>
   </si>
 </sst>
 </file>
@@ -70719,7 +70722,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6494212963</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>1077785</v>
@@ -70740,6 +70743,32 @@
         <v>1832</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495833333</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>1250782</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>9.89000034332275</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>9.78999996185303</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>9.88500022888184</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1833</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45607042312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986746788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331571578979</t>
+    <t xml:space="preserve">3.4629693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4560706615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986675262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331666946411</t>
   </si>
   <si>
     <t xml:space="preserve">3.39812469482422</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">3.34845638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34707689285278</t>
+    <t xml:space="preserve">3.34707713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.26981520652771</t>
@@ -71,148 +71,148 @@
     <t xml:space="preserve">3.28637099266052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21324896812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03803110122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13874697685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288640022278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425496101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16496062278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736701011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945216178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430746078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119517326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222230911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20911002159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2077305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631920814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06700396537781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00077962875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00215983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114386558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115384101868</t>
+    <t xml:space="preserve">3.21324825286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03803038597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.138747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14288592338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425543785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1649603843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736748695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119469642639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222207069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20910906791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0863196849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00078010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0021595954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9980206489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837324142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114291191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1111536026001</t>
   </si>
   <si>
     <t xml:space="preserve">3.18151640892029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13046884536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1415057182312</t>
+    <t xml:space="preserve">3.13046860694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14150595664978</t>
   </si>
   <si>
     <t xml:space="preserve">3.12495017051697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11805152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1732382774353</t>
+    <t xml:space="preserve">3.11805176734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808264732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323851585388</t>
   </si>
   <si>
     <t xml:space="preserve">3.19531321525574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18703532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321808815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013691902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255399703979</t>
+    <t xml:space="preserve">3.18703556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321761131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255423545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.18427634239197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24636054039001</t>
+    <t xml:space="preserve">3.24636077880859</t>
   </si>
   <si>
     <t xml:space="preserve">3.20635032653809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19807314872742</t>
+    <t xml:space="preserve">3.1980721950531</t>
   </si>
   <si>
     <t xml:space="preserve">3.10563492774963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906868934631</t>
+    <t xml:space="preserve">3.04906821250916</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03941106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00491905212402</t>
+    <t xml:space="preserve">3.03941059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00491881370544</t>
   </si>
   <si>
     <t xml:space="preserve">3.0518274307251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98422384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.050448179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320739746094</t>
+    <t xml:space="preserve">2.98422431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05044794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320763587952</t>
   </si>
   <si>
     <t xml:space="preserve">3.01595664024353</t>
@@ -224,88 +224,88 @@
     <t xml:space="preserve">3.02147483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00629854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767850875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0256142616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873604774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08769869804382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978432655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05596661567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838345527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319646835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02975344657898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01871562004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249199867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94421410560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869519233704</t>
+    <t xml:space="preserve">3.00629830360413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767827033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873652458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0876989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0559663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319718360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02975273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01871538162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766781806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94421339035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869495391846</t>
   </si>
   <si>
     <t xml:space="preserve">2.93593525886536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02235865592957</t>
+    <t xml:space="preserve">3.02235913276672</t>
   </si>
   <si>
     <t xml:space="preserve">3.02659201622009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426222801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9913170337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97861814498901</t>
+    <t xml:space="preserve">2.99837183952332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426198959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97861790657043</t>
   </si>
   <si>
     <t xml:space="preserve">3.06892204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06610012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01389312744141</t>
+    <t xml:space="preserve">3.06610059738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01389288902283</t>
   </si>
   <si>
     <t xml:space="preserve">3.02094793319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00683832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0392906665802</t>
+    <t xml:space="preserve">3.00683808326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929114341736</t>
   </si>
   <si>
     <t xml:space="preserve">3.01671504974365</t>
@@ -317,94 +317,94 @@
     <t xml:space="preserve">2.99978256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96450805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714911460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083227157593</t>
+    <t xml:space="preserve">2.9645082950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083203315735</t>
   </si>
   <si>
     <t xml:space="preserve">2.87843704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93205523490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702608108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9108898639679</t>
+    <t xml:space="preserve">2.93205547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702584266663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089034080505</t>
   </si>
   <si>
     <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61034750938416</t>
+    <t xml:space="preserve">2.61034727096558</t>
   </si>
   <si>
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899437904358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7965989112854</t>
+    <t xml:space="preserve">2.71899461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79659938812256</t>
   </si>
   <si>
     <t xml:space="preserve">2.79518818855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85162806510925</t>
+    <t xml:space="preserve">2.85162758827209</t>
   </si>
   <si>
     <t xml:space="preserve">2.83610701560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87279295921326</t>
+    <t xml:space="preserve">2.87279319763184</t>
   </si>
   <si>
     <t xml:space="preserve">2.94475388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97438502311707</t>
+    <t xml:space="preserve">2.97438478469849</t>
   </si>
   <si>
     <t xml:space="preserve">3.00542712211609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02518153190613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211258888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597661018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364729881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07033324241638</t>
+    <t xml:space="preserve">3.02518105506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0703330039978</t>
   </si>
   <si>
     <t xml:space="preserve">3.05481195449829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03787994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05199027061462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333579063416</t>
+    <t xml:space="preserve">3.03788042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05199003219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333626747131</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204786300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15499258041382</t>
+    <t xml:space="preserve">3.15499329566956</t>
   </si>
   <si>
     <t xml:space="preserve">3.14088296890259</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">3.10842990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09149813652039</t>
+    <t xml:space="preserve">3.09149789810181</t>
   </si>
   <si>
     <t xml:space="preserve">3.13241720199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13947200775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15076041221619</t>
+    <t xml:space="preserve">3.13947153091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15075969696045</t>
   </si>
   <si>
     <t xml:space="preserve">3.10419702529907</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">3.02800297737122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0124819278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02377009391785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07174372673035</t>
+    <t xml:space="preserve">3.01248240470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02376961708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0717442035675</t>
   </si>
   <si>
     <t xml:space="preserve">3.06045579910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03646898269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09008717536926</t>
+    <t xml:space="preserve">3.03646874427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008693695068</t>
   </si>
   <si>
     <t xml:space="preserve">3.19732284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21002173423767</t>
+    <t xml:space="preserve">3.21002221107483</t>
   </si>
   <si>
     <t xml:space="preserve">3.18462371826172</t>
@@ -470,37 +470,37 @@
     <t xml:space="preserve">3.21707701683044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27775025367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351641654968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22131013870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861077308655</t>
+    <t xml:space="preserve">3.27774977684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2735161781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130942344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861124992371</t>
   </si>
   <si>
     <t xml:space="preserve">3.19873380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18180179595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1535816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217113494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16628098487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1253616809845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125159263611</t>
+    <t xml:space="preserve">3.18180227279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15358209609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217089653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16628074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12536144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125183105469</t>
   </si>
   <si>
     <t xml:space="preserve">3.08726501464844</t>
@@ -509,34 +509,34 @@
     <t xml:space="preserve">3.09714221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548495292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867573738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07738780975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06186747550964</t>
+    <t xml:space="preserve">3.11548471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.077388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06186723709106</t>
   </si>
   <si>
     <t xml:space="preserve">2.99696135520935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92923307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95322012901306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180916786194</t>
+    <t xml:space="preserve">2.92923331260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95322036743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9518096446991</t>
   </si>
   <si>
     <t xml:space="preserve">2.93911004066467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92076706886292</t>
+    <t xml:space="preserve">2.92076683044434</t>
   </si>
   <si>
     <t xml:space="preserve">2.95886421203613</t>
@@ -545,28 +545,28 @@
     <t xml:space="preserve">2.92782211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98002910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622267723083</t>
+    <t xml:space="preserve">2.98002862930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622315406799</t>
   </si>
   <si>
     <t xml:space="preserve">3.01953721046448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97720718383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99555015563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0407018661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0181257724762</t>
+    <t xml:space="preserve">2.97720694541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99554991722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04070210456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01812529563904</t>
   </si>
   <si>
     <t xml:space="preserve">2.9630970954895</t>
@@ -575,37 +575,37 @@
     <t xml:space="preserve">2.92641115188599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98849487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138247489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8572723865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86856007575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358946800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8869035243988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89819145202637</t>
+    <t xml:space="preserve">2.98849511146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138223648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85727214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86855983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358899116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604205131531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88690304756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89819097518921</t>
   </si>
   <si>
     <t xml:space="preserve">2.85303902626038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034013748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199740409851</t>
+    <t xml:space="preserve">2.84034037590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199716567993</t>
   </si>
   <si>
     <t xml:space="preserve">2.84457349777222</t>
@@ -614,43 +614,43 @@
     <t xml:space="preserve">2.85021710395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78390049934387</t>
+    <t xml:space="preserve">2.78390073776245</t>
   </si>
   <si>
     <t xml:space="preserve">2.79377746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82340788841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568032264709</t>
+    <t xml:space="preserve">2.82340836524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568008422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.76132440567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80929851531982</t>
+    <t xml:space="preserve">2.8092987537384</t>
   </si>
   <si>
     <t xml:space="preserve">2.89254689216614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.893958568573</t>
+    <t xml:space="preserve">2.89395809173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.89960241317749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86009430885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665698051453</t>
+    <t xml:space="preserve">2.86009383201599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665721893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.88831400871277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9123010635376</t>
+    <t xml:space="preserve">2.91230082511902</t>
   </si>
   <si>
     <t xml:space="preserve">2.94052124023438</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">3.08021020889282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08303189277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560822486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585453033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511609077454</t>
+    <t xml:space="preserve">3.08303213119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1056079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585429191589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523888587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511561393738</t>
   </si>
   <si>
     <t xml:space="preserve">3.13806128501892</t>
@@ -686,34 +686,34 @@
     <t xml:space="preserve">3.17051386833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20437836647034</t>
+    <t xml:space="preserve">3.20437788963318</t>
   </si>
   <si>
     <t xml:space="preserve">3.19591188430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12254023551941</t>
+    <t xml:space="preserve">3.12253999710083</t>
   </si>
   <si>
     <t xml:space="preserve">3.09573078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10278606414795</t>
+    <t xml:space="preserve">3.10278654098511</t>
   </si>
   <si>
     <t xml:space="preserve">3.09290885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751132011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17898011207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13664984703064</t>
+    <t xml:space="preserve">3.06751155853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11830687522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17897987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13665008544922</t>
   </si>
   <si>
     <t xml:space="preserve">3.07456564903259</t>
@@ -722,127 +722,127 @@
     <t xml:space="preserve">3.10701870918274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09855341911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529695510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26646161079407</t>
+    <t xml:space="preserve">3.098552942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529671669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26646208763123</t>
   </si>
   <si>
     <t xml:space="preserve">3.25376296043396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2509400844574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891514778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31443643569946</t>
+    <t xml:space="preserve">3.25094103813171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891490936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31443572044373</t>
   </si>
   <si>
     <t xml:space="preserve">3.38357496261597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37228679656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651968002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44565892219543</t>
+    <t xml:space="preserve">3.37228727340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4456582069397</t>
   </si>
   <si>
     <t xml:space="preserve">3.41461658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44283699989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40756177902222</t>
+    <t xml:space="preserve">3.44283652305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40756154060364</t>
   </si>
   <si>
     <t xml:space="preserve">3.4005069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48657774925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338648796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105646133423</t>
+    <t xml:space="preserve">3.48657846450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338672637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105717658997</t>
   </si>
   <si>
     <t xml:space="preserve">3.54160666465759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.478111743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798823356628</t>
+    <t xml:space="preserve">3.47811150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798871040344</t>
   </si>
   <si>
     <t xml:space="preserve">3.52185273170471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50633120536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222159385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455138206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52749633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056456565857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099149703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393669128418</t>
+    <t xml:space="preserve">3.5063316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56277203559875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53455185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056480407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099173545837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568403244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5839364528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55924439430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273907661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.650958776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.661541223526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506886482239</t>
+    <t xml:space="preserve">3.55924415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6227388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65095925331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506838798523</t>
   </si>
   <si>
     <t xml:space="preserve">3.61921143531799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63332200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804677963257</t>
+    <t xml:space="preserve">3.6333212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804654121399</t>
   </si>
   <si>
     <t xml:space="preserve">3.7375226020813</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">3.68667149543762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72299361228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71936178207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483326911926</t>
+    <t xml:space="preserve">3.72299385070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7193615436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483303070068</t>
   </si>
   <si>
     <t xml:space="preserve">3.66124701499939</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">3.83195996284485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82832717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379818916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285616874695</t>
+    <t xml:space="preserve">3.82832789421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379914283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285593032837</t>
   </si>
   <si>
     <t xml:space="preserve">3.85012054443359</t>
@@ -881,130 +881,130 @@
     <t xml:space="preserve">3.8864426612854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86101746559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469487190247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922338485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097069740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087954521179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913199424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016635894775</t>
+    <t xml:space="preserve">3.86101675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469511032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922410011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9845118522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097117424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455671310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087906837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823578834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913175582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016683578491</t>
   </si>
   <si>
     <t xml:space="preserve">3.68303990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65761423110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6133017539978</t>
+    <t xml:space="preserve">3.65761470794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330199241638</t>
   </si>
   <si>
     <t xml:space="preserve">3.62201905250549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60313153266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150815010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492489814758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214322090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030451774597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035033226013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7157289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662568092346</t>
+    <t xml:space="preserve">3.60313200950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492418289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030427932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218903541565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035009384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71572875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662615776062</t>
   </si>
   <si>
     <t xml:space="preserve">3.87191319465637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96635055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366122245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908665657043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352354049683</t>
+    <t xml:space="preserve">3.96635031700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9590859413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352258682251</t>
   </si>
   <si>
     <t xml:space="preserve">4.04989099502563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07894802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182156562805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91549968719482</t>
+    <t xml:space="preserve">4.0789475440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182228088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9154999256134</t>
   </si>
   <si>
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540758132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177575111389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446556091309</t>
+    <t xml:space="preserve">3.9954080581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177551269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446603775024</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262638092041</t>
@@ -1013,67 +1013,67 @@
     <t xml:space="preserve">4.10437393188477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86465001106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8973388671875</t>
+    <t xml:space="preserve">3.96271872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89733910560608</t>
   </si>
   <si>
     <t xml:space="preserve">3.98814368247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95545434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002867698669</t>
+    <t xml:space="preserve">3.95545363426208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002820014954</t>
   </si>
   <si>
     <t xml:space="preserve">4.01720142364502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88280987739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07531595230103</t>
+    <t xml:space="preserve">3.88280963897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07531690597534</t>
   </si>
   <si>
     <t xml:space="preserve">4.06805181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14796018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0462589263916</t>
+    <t xml:space="preserve">4.14795970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04625940322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078767776489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11527061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10800647735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12253475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18064880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18791437149048</t>
+    <t xml:space="preserve">4.11527013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1080060005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12253522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18065023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885639190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18791389465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.16612100601196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17338562011719</t>
+    <t xml:space="preserve">4.17338514328003</t>
   </si>
   <si>
     <t xml:space="preserve">4.09710931777954</t>
@@ -1082,43 +1082,43 @@
     <t xml:space="preserve">4.14069509506226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24602890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22060394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26055765151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21697187423706</t>
+    <t xml:space="preserve">4.12979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24602937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22060441970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26055812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21697092056274</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26418972015381</t>
+    <t xml:space="preserve">4.26419019699097</t>
   </si>
   <si>
     <t xml:space="preserve">4.27508687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24239683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701816558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08984470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30777549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29688024520874</t>
+    <t xml:space="preserve">4.24239730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17701721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08984518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30777597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29687976837158</t>
   </si>
   <si>
     <t xml:space="preserve">4.42763805389404</t>
@@ -1127,64 +1127,64 @@
     <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54023694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60198307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59835147857666</t>
+    <t xml:space="preserve">4.54023599624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60198402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59835195541382</t>
   </si>
   <si>
     <t xml:space="preserve">4.72184610366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56929397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56202936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62014484405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59471893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60924768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4893856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4566969871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33683347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52207469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49301767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50391387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46032857894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306444168091</t>
+    <t xml:space="preserve">4.56929445266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56202983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62014436721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59471940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60924816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48938512802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669603347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844358444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33683395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52207517623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49301862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50391435623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49665021896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46032810211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306396484375</t>
   </si>
   <si>
     <t xml:space="preserve">4.46759271621704</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">4.54750108718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53660440444946</t>
+    <t xml:space="preserve">4.5366039276123</t>
   </si>
   <si>
     <t xml:space="preserve">4.43853521347046</t>
@@ -1205,25 +1205,25 @@
     <t xml:space="preserve">4.37315607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39131736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29324769973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40947771072388</t>
+    <t xml:space="preserve">4.39131593704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037439346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29324722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40947818756104</t>
   </si>
   <si>
     <t xml:space="preserve">4.51117849349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42400646209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140899658203</t>
+    <t xml:space="preserve">4.42400598526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140851974487</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">4.12616682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23150014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361469268799</t>
+    <t xml:space="preserve">4.23150110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361445426941</t>
   </si>
   <si>
     <t xml:space="preserve">3.94092488288879</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.97724723815918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08258008956909</t>
+    <t xml:space="preserve">4.08258056640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">4.40584516525269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4167423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108638763428</t>
+    <t xml:space="preserve">4.41674184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108781814575</t>
   </si>
   <si>
     <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55113315582275</t>
+    <t xml:space="preserve">4.5511326789856</t>
   </si>
   <si>
     <t xml:space="preserve">4.57655906677246</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570724487305</t>
+    <t xml:space="preserve">4.52570772171021</t>
   </si>
   <si>
     <t xml:space="preserve">4.53297185897827</t>
@@ -1292,85 +1292,85 @@
     <t xml:space="preserve">4.67825984954834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64920234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6709942817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64557027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283489227295</t>
+    <t xml:space="preserve">4.6492018699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67099475860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64556980133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75090312957764</t>
+    <t xml:space="preserve">4.75090360641479</t>
   </si>
   <si>
     <t xml:space="preserve">4.76180028915405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72547912597656</t>
+    <t xml:space="preserve">4.72547769546509</t>
   </si>
   <si>
     <t xml:space="preserve">4.68552398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72910976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65646696090698</t>
+    <t xml:space="preserve">4.72911071777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65646600723267</t>
   </si>
   <si>
     <t xml:space="preserve">4.84534025192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81991577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83807563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88166236877441</t>
+    <t xml:space="preserve">4.81265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81991529464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83807611465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88166189193726</t>
   </si>
   <si>
     <t xml:space="preserve">4.8489727973938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91798496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89255952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95430564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94704151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977785110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93251323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99062824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713266372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7330756187439</t>
+    <t xml:space="preserve">4.91798400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89255857467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95430612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9470419883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9325122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99062776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73307514190674</t>
   </si>
   <si>
     <t xml:space="preserve">4.87888145446777</t>
@@ -1382,28 +1382,28 @@
     <t xml:space="preserve">4.82654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75176858901978</t>
+    <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
     <t xml:space="preserve">4.6508264541626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49380445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62091732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6769962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74803066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7218599319458</t>
+    <t xml:space="preserve">4.49380493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62091684341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63587141036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74803018569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72185945510864</t>
   </si>
   <si>
     <t xml:space="preserve">4.70690536499023</t>
@@ -1412,25 +1412,25 @@
     <t xml:space="preserve">4.57979297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75924587249756</t>
+    <t xml:space="preserve">4.7592453956604</t>
   </si>
   <si>
     <t xml:space="preserve">4.83027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81532526016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94243764877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91252899169922</t>
+    <t xml:space="preserve">4.93495988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85644912719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81532573699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94243812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91252946853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.84897232055664</t>
@@ -1442,31 +1442,31 @@
     <t xml:space="preserve">4.90505170822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88262033462524</t>
+    <t xml:space="preserve">4.8826208114624</t>
   </si>
   <si>
     <t xml:space="preserve">4.93869924545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96486949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216505050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01720905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13684463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05833387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98356246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89757394790649</t>
+    <t xml:space="preserve">4.96486902236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01721000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13684511184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05833435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89757490158081</t>
   </si>
   <si>
     <t xml:space="preserve">5.1293683052063</t>
@@ -1478,25 +1478,25 @@
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3162989616394</t>
+    <t xml:space="preserve">5.31629800796509</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350221633911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34246873855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09945917129517</t>
+    <t xml:space="preserve">5.34246826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09945964813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.01347160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17797040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20040130615234</t>
+    <t xml:space="preserve">5.17796993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2004017829895</t>
   </si>
   <si>
     <t xml:space="preserve">5.23404884338379</t>
@@ -1505,79 +1505,79 @@
     <t xml:space="preserve">5.25274276733398</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20787954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283315658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666337966919</t>
+    <t xml:space="preserve">5.20787858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666290283203</t>
   </si>
   <si>
     <t xml:space="preserve">5.11815166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04338026046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99851703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11067533493042</t>
+    <t xml:space="preserve">5.04337978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99851608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11067485809326</t>
   </si>
   <si>
     <t xml:space="preserve">5.17049217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11441373825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982358932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95739269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0396409034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05459594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076572418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18544673919678</t>
+    <t xml:space="preserve">5.04711818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11441421508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95739221572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03964185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05459642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18544769287109</t>
   </si>
   <si>
     <t xml:space="preserve">5.09572076797485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2116174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8863582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073558807373</t>
+    <t xml:space="preserve">5.21161794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88635873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92000579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77419996261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073606491089</t>
   </si>
   <si>
     <t xml:space="preserve">4.66951990127563</t>
@@ -1589,58 +1589,58 @@
     <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68447399139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5685772895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58727073669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56110048294067</t>
+    <t xml:space="preserve">4.68447351455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56857776641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58727025985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56109952926636</t>
   </si>
   <si>
     <t xml:space="preserve">4.40781736373901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344003677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848594665527</t>
+    <t xml:space="preserve">4.61344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848642349243</t>
   </si>
   <si>
     <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84523439407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79289388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766576766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7779393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140369415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83775663375854</t>
+    <t xml:space="preserve">4.84523344039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.792893409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167772293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77793884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140417098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8377571105957</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821239471436</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74055242538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6022253036499</t>
+    <t xml:space="preserve">4.74055337905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60222482681274</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988384246826</t>
@@ -1661,25 +1661,25 @@
     <t xml:space="preserve">4.52371406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51997518539429</t>
+    <t xml:space="preserve">4.51997566223145</t>
   </si>
   <si>
     <t xml:space="preserve">4.48632764816284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41903305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46015787124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64334869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456485748291</t>
+    <t xml:space="preserve">4.41903209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46015691757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64334917068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204166412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456438064575</t>
   </si>
   <si>
     <t xml:space="preserve">4.76298475265503</t>
@@ -1688,22 +1688,22 @@
     <t xml:space="preserve">4.73681449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86392736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806127548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21909427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22657108306885</t>
+    <t xml:space="preserve">4.86392688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927648544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21909475326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22657203674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.18918609619141</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">5.15179967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20414066314697</t>
+    <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
     <t xml:space="preserve">5.37237739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16675472259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620714187622</t>
+    <t xml:space="preserve">5.1667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620761871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.09018993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87335062026978</t>
+    <t xml:space="preserve">5.87335109710693</t>
   </si>
   <si>
     <t xml:space="preserve">5.79483985900879</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353330612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79110193252563</t>
+    <t xml:space="preserve">5.81353378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79110097885132</t>
   </si>
   <si>
     <t xml:space="preserve">5.80231809616089</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">5.82474899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87708950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9219536781311</t>
+    <t xml:space="preserve">5.87708902359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195272445679</t>
   </si>
   <si>
     <t xml:space="preserve">5.98924732208252</t>
@@ -1763,16 +1763,16 @@
     <t xml:space="preserve">6.01167964935303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02663373947144</t>
+    <t xml:space="preserve">6.02663421630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0079402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9256911277771</t>
+    <t xml:space="preserve">6.00794076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92569208145142</t>
   </si>
   <si>
     <t xml:space="preserve">5.93316888809204</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">5.90699815750122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94064569473267</t>
+    <t xml:space="preserve">5.94064617156982</t>
   </si>
   <si>
     <t xml:space="preserve">6.07897424697876</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">5.93690729141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95933771133423</t>
+    <t xml:space="preserve">5.95933866500854</t>
   </si>
   <si>
     <t xml:space="preserve">5.89952087402344</t>
@@ -1799,67 +1799,67 @@
     <t xml:space="preserve">5.89578247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88082838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94812297821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95560026168823</t>
+    <t xml:space="preserve">5.88082790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94812250137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95560073852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.97429275512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02114152908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9136209487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.840660572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75234079360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.694739818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778011322021</t>
+    <t xml:space="preserve">6.02114200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91362047195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84066104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75234031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69474029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778059005737</t>
   </si>
   <si>
     <t xml:space="preserve">5.68321990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66402006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66786050796509</t>
+    <t xml:space="preserve">5.66401958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66786003112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70625972747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76002025604248</t>
+    <t xml:space="preserve">5.70626020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76001977920532</t>
   </si>
   <si>
     <t xml:space="preserve">5.87522077560425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82146120071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74850082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69858074188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64481973648071</t>
+    <t xml:space="preserve">5.82146072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74850034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69858026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64482021331787</t>
   </si>
   <si>
     <t xml:space="preserve">5.60642004013062</t>
@@ -1868,25 +1868,25 @@
     <t xml:space="preserve">5.77538061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72161960601807</t>
+    <t xml:space="preserve">5.72162055969238</t>
   </si>
   <si>
     <t xml:space="preserve">5.81762027740479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78690052032471</t>
+    <t xml:space="preserve">5.78689956665039</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0557017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28226280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474126815796</t>
+    <t xml:space="preserve">6.05570125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28226232528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474222183228</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">6.19394159317017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06722211837769</t>
+    <t xml:space="preserve">6.06722116470337</t>
   </si>
   <si>
     <t xml:space="preserve">6.10178184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25154209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17090129852295</t>
+    <t xml:space="preserve">6.25154304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17090177536011</t>
   </si>
   <si>
     <t xml:space="preserve">6.1670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29378175735474</t>
+    <t xml:space="preserve">6.29378223419189</t>
   </si>
   <si>
     <t xml:space="preserve">6.39746236801147</t>
@@ -1925,37 +1925,37 @@
     <t xml:space="preserve">6.43586254119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46274280548096</t>
+    <t xml:space="preserve">6.4627423286438</t>
   </si>
   <si>
     <t xml:space="preserve">6.38210296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35522222518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44738292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52802324295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58946371078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786388397217</t>
+    <t xml:space="preserve">6.35522174835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44738340377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5280237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410383224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5894627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322423934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786293029785</t>
   </si>
   <si>
     <t xml:space="preserve">6.66626358032227</t>
@@ -1964,94 +1964,94 @@
     <t xml:space="preserve">6.80450344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83138465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522462844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78914451599121</t>
+    <t xml:space="preserve">6.83138418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522367477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78914356231689</t>
   </si>
   <si>
     <t xml:space="preserve">6.76610469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98114538192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554382324219</t>
+    <t xml:space="preserve">6.98114442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554430007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.61634349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54338407516479</t>
+    <t xml:space="preserve">6.54338359832764</t>
   </si>
   <si>
     <t xml:space="preserve">6.79298448562622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14626502990723</t>
+    <t xml:space="preserve">7.14626598358154</t>
   </si>
   <si>
     <t xml:space="preserve">7.01570558547974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05026531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00802421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9926643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
+    <t xml:space="preserve">7.05026483535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99266481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1040244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082618713379</t>
   </si>
   <si>
     <t xml:space="preserve">7.10786485671997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06178569793701</t>
+    <t xml:space="preserve">7.06178426742554</t>
   </si>
   <si>
     <t xml:space="preserve">7.07330560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034379959106</t>
+    <t xml:space="preserve">7.07714605331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034475326538</t>
   </si>
   <si>
     <t xml:space="preserve">6.96578454971313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95426368713379</t>
+    <t xml:space="preserve">6.95426511764526</t>
   </si>
   <si>
     <t xml:space="preserve">7.02722454071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186466217041</t>
+    <t xml:space="preserve">7.01186418533325</t>
   </si>
   <si>
     <t xml:space="preserve">6.94274425506592</t>
@@ -2060,13 +2060,13 @@
     <t xml:space="preserve">7.04258489608765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09634447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75074338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506479263306</t>
+    <t xml:space="preserve">7.09634590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7507438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9350643157959</t>
   </si>
   <si>
     <t xml:space="preserve">6.90434455871582</t>
@@ -2075,37 +2075,37 @@
     <t xml:space="preserve">7.02338552474976</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97346496582031</t>
+    <t xml:space="preserve">6.97346544265747</t>
   </si>
   <si>
     <t xml:space="preserve">7.15778493881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3113865852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706565856934</t>
+    <t xml:space="preserve">7.16546535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2960262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16930627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682590484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850421905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706518173218</t>
   </si>
   <si>
     <t xml:space="preserve">7.17698574066162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19234609603882</t>
+    <t xml:space="preserve">7.1923451423645</t>
   </si>
   <si>
     <t xml:space="preserve">7.15010595321655</t>
@@ -2117,67 +2117,67 @@
     <t xml:space="preserve">7.34210634231567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43426656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978723526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11938667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2230658531189</t>
+    <t xml:space="preserve">7.43426704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730590820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658662796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22306537628174</t>
   </si>
   <si>
     <t xml:space="preserve">7.11554574966431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06562471389771</t>
+    <t xml:space="preserve">7.06562519073486</t>
   </si>
   <si>
     <t xml:space="preserve">7.08866453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98498487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77378416061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8889856338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9273853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90818452835083</t>
+    <t xml:space="preserve">6.98498439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77378368377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066347122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88898468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92738485336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90818405151367</t>
   </si>
   <si>
     <t xml:space="preserve">6.912024974823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84290409088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86210441589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84674453735352</t>
+    <t xml:space="preserve">6.84290456771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210489273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674501419067</t>
   </si>
   <si>
     <t xml:space="preserve">7.08098554611206</t>
@@ -2186,58 +2186,58 @@
     <t xml:space="preserve">7.03106451034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05794477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842428207397</t>
+    <t xml:space="preserve">7.05794525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842523574829</t>
   </si>
   <si>
     <t xml:space="preserve">6.81218385696411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81602382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87746477127075</t>
+    <t xml:space="preserve">6.81602430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87746381759644</t>
   </si>
   <si>
     <t xml:space="preserve">6.74306392669678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69314384460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72002363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89282560348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682397842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466279983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78530359268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770692825317</t>
+    <t xml:space="preserve">6.69314432144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72002410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89282417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682493209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78530406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20770502090454</t>
   </si>
   <si>
     <t xml:space="preserve">7.17314577102661</t>
@@ -2246,37 +2246,37 @@
     <t xml:space="preserve">7.22690534591675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20002555847168</t>
+    <t xml:space="preserve">7.20002603530884</t>
   </si>
   <si>
     <t xml:space="preserve">7.11170482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25762510299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826589584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786678314209</t>
+    <t xml:space="preserve">7.25762557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786773681641</t>
   </si>
   <si>
     <t xml:space="preserve">7.56098651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66466665267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418809890747</t>
+    <t xml:space="preserve">7.6646671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418857574463</t>
   </si>
   <si>
     <t xml:space="preserve">8.00258827209473</t>
@@ -2285,100 +2285,100 @@
     <t xml:space="preserve">8.17922878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86434698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218723297119</t>
+    <t xml:space="preserve">7.86434745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218675613403</t>
   </si>
   <si>
     <t xml:space="preserve">7.73378801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49186563491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002653121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970491409302</t>
+    <t xml:space="preserve">7.49186658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970539093018</t>
   </si>
   <si>
     <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27458238601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77154111862183</t>
+    <t xml:space="preserve">6.27458190917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77154064178467</t>
   </si>
   <si>
     <t xml:space="preserve">6.26690196990967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33602285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938859939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27178192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8802170753479</t>
+    <t xml:space="preserve">6.33602237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922588348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88021612167358</t>
   </si>
   <si>
     <t xml:space="preserve">7.57022905349731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64364767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718032836914</t>
+    <t xml:space="preserve">7.64364814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718318939209</t>
   </si>
   <si>
     <t xml:space="preserve">8.35335636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72860622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03043460845947</t>
+    <t xml:space="preserve">8.72860527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03043556213379</t>
   </si>
   <si>
     <t xml:space="preserve">8.95701694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70413208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75307750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99442338943481</t>
+    <t xml:space="preserve">8.70413303375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75307655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99442386627197</t>
   </si>
   <si>
     <t xml:space="preserve">7.83127212524414</t>
@@ -2390,52 +2390,52 @@
     <t xml:space="preserve">7.81903553009033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79864072799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68035697937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5090479850769</t>
+    <t xml:space="preserve">7.7986421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613773345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035650253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50904750823975</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496864318848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70482873916626</t>
+    <t xml:space="preserve">7.70482969284058</t>
   </si>
   <si>
     <t xml:space="preserve">7.75377559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89653158187866</t>
+    <t xml:space="preserve">7.89653253555298</t>
   </si>
   <si>
     <t xml:space="preserve">7.94547748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85574579238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146343231201</t>
+    <t xml:space="preserve">7.85574340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146295547485</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78709554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7581467628479</t>
+    <t xml:space="preserve">7.78709506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75814771652222</t>
   </si>
   <si>
     <t xml:space="preserve">7.69611549377441</t>
@@ -2444,46 +2444,46 @@
     <t xml:space="preserve">7.54310274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.600998878479</t>
+    <t xml:space="preserve">7.60099935531616</t>
   </si>
   <si>
     <t xml:space="preserve">7.58032178878784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5182900428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73333597183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65062570571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55550956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53483152389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4521222114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4934778213501</t>
+    <t xml:space="preserve">7.51828956604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73333549499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65062475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55551052093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53483200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212268829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49347734451294</t>
   </si>
   <si>
     <t xml:space="preserve">7.63408279418945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58445835113525</t>
+    <t xml:space="preserve">7.40249633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663194656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941289901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58445739746094</t>
   </si>
   <si>
     <t xml:space="preserve">7.48520708084106</t>
@@ -2498,28 +2498,28 @@
     <t xml:space="preserve">7.75401210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72919845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354803085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34459972381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7374701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69198036193848</t>
+    <t xml:space="preserve">7.72919988632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460020065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009141921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73746967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69197988510132</t>
   </si>
   <si>
     <t xml:space="preserve">7.77468967437744</t>
@@ -2528,46 +2528,46 @@
     <t xml:space="preserve">7.72506427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68784427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67543745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62167739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438623428345</t>
+    <t xml:space="preserve">7.68784475326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67543697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6216778755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438671112061</t>
   </si>
   <si>
     <t xml:space="preserve">7.71265745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42317485809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3363299369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3652777671814</t>
+    <t xml:space="preserve">7.62581157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33632898330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36527729034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.25775480270386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08406448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02203273773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95586633682251</t>
+    <t xml:space="preserve">7.08406496047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02203321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95586538314819</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
@@ -2576,10 +2576,10 @@
     <t xml:space="preserve">7.06752347946167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09647130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07166004180908</t>
+    <t xml:space="preserve">7.09647178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07165908813477</t>
   </si>
   <si>
     <t xml:space="preserve">7.24534845352173</t>
@@ -2588,28 +2588,28 @@
     <t xml:space="preserve">7.17091035842896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03444004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98894882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93932390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05511665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90623998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95173025131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8979697227478</t>
+    <t xml:space="preserve">7.03443956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98894929885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93932437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05511713027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864633560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90624046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95173072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.98481416702271</t>
@@ -2618,67 +2618,67 @@
     <t xml:space="preserve">6.93105268478394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82353067398071</t>
+    <t xml:space="preserve">6.82353115081787</t>
   </si>
   <si>
     <t xml:space="preserve">6.75322771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78217601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759368896484</t>
+    <t xml:space="preserve">6.78217554092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413660049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.947594165802</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324506759644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43557977676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48934173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59272861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80777263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60927057266235</t>
+    <t xml:space="preserve">7.43558025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700654983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.489342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59272956848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80777215957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60927104949951</t>
   </si>
   <si>
     <t xml:space="preserve">7.71679210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72092819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190776824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845115661621</t>
+    <t xml:space="preserve">7.72092771530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82845067977905</t>
   </si>
   <si>
     <t xml:space="preserve">7.8367223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912824630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716766357422</t>
+    <t xml:space="preserve">7.96078443527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912633895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716814041138</t>
   </si>
   <si>
     <t xml:space="preserve">7.67957353591919</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">7.61754179000854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60513496398926</t>
+    <t xml:space="preserve">7.60513401031494</t>
   </si>
   <si>
     <t xml:space="preserve">7.59686422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57205152511597</t>
+    <t xml:space="preserve">7.57205104827881</t>
   </si>
   <si>
     <t xml:space="preserve">7.54723787307739</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.03522396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20064353942871</t>
+    <t xml:space="preserve">8.20064258575439</t>
   </si>
   <si>
     <t xml:space="preserve">8.15515232086182</t>
@@ -2717,58 +2717,58 @@
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31229972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56042957305908</t>
+    <t xml:space="preserve">8.31230068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5604305267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.40328121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41155242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28748798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33711338043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61005592346191</t>
+    <t xml:space="preserve">8.4115514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33711433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
     <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55215835571289</t>
+    <t xml:space="preserve">8.55215930938721</t>
   </si>
   <si>
     <t xml:space="preserve">8.25026893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59351253509521</t>
+    <t xml:space="preserve">8.59351348876953</t>
   </si>
   <si>
     <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92435169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99051761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80028629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81682968139648</t>
+    <t xml:space="preserve">8.92435073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99051856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81682872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365581512451</t>
+    <t xml:space="preserve">8.35365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">8.21304988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18823719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13860988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32057285308838</t>
+    <t xml:space="preserve">8.18823623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13861179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32057189941406</t>
   </si>
   <si>
     <t xml:space="preserve">8.24199771881104</t>
@@ -2792,19 +2792,19 @@
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27921772003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25854015350342</t>
+    <t xml:space="preserve">8.22545623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27921676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2585391998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95664978027344</t>
+    <t xml:space="preserve">7.95665073394775</t>
   </si>
   <si>
     <t xml:space="preserve">7.86980581283569</t>
@@ -2813,25 +2813,25 @@
     <t xml:space="preserve">7.85326242446899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89875411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574184417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415491104126</t>
+    <t xml:space="preserve">7.89875316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574136734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303157806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415395736694</t>
   </si>
   <si>
     <t xml:space="preserve">7.44798707962036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33219337463379</t>
+    <t xml:space="preserve">7.33219480514526</t>
   </si>
   <si>
     <t xml:space="preserve">7.35287141799927</t>
@@ -2840,22 +2840,22 @@
     <t xml:space="preserve">7.46866416931152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43971729278564</t>
+    <t xml:space="preserve">7.43971586227417</t>
   </si>
   <si>
     <t xml:space="preserve">7.43144416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50588321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82018041610718</t>
+    <t xml:space="preserve">7.50588417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82017946243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.76228284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38182020187378</t>
+    <t xml:space="preserve">7.38181924819946</t>
   </si>
   <si>
     <t xml:space="preserve">7.2039942741394</t>
@@ -2870,25 +2870,25 @@
     <t xml:space="preserve">7.09233617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12541961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12955522537231</t>
+    <t xml:space="preserve">7.12542009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670454025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12955570220947</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2991099357605</t>
+    <t xml:space="preserve">7.04271078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16263914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29910945892334</t>
   </si>
   <si>
     <t xml:space="preserve">7.22053575515747</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">7.70025110244751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80281019210815</t>
+    <t xml:space="preserve">7.80281066894531</t>
   </si>
   <si>
     <t xml:space="preserve">8.03108882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88386535644531</t>
+    <t xml:space="preserve">7.88386631011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.01123809814453</t>
@@ -2915,19 +2915,19 @@
     <t xml:space="preserve">7.81935214996338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77137994766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79454040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273555755615</t>
+    <t xml:space="preserve">7.77138090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86732339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273603439331</t>
   </si>
   <si>
     <t xml:space="preserve">7.79619407653809</t>
@@ -2936,46 +2936,46 @@
     <t xml:space="preserve">7.6969428062439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05590152740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97319221496582</t>
+    <t xml:space="preserve">8.05590057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97319269180298</t>
   </si>
   <si>
     <t xml:space="preserve">7.99635076522827</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01785469055176</t>
+    <t xml:space="preserve">8.01785564422607</t>
   </si>
   <si>
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02281665802002</t>
+    <t xml:space="preserve">7.9996600151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02281856536865</t>
   </si>
   <si>
     <t xml:space="preserve">8.05093860626221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93845415115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003414154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88055658340454</t>
+    <t xml:space="preserve">7.93845367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055801391602</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82431554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371608734131</t>
+    <t xml:space="preserve">7.82431507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371561050415</t>
   </si>
   <si>
     <t xml:space="preserve">8.0128927230835</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">7.84416532516479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81604433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63904619216919</t>
+    <t xml:space="preserve">7.81604480743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63904523849487</t>
   </si>
   <si>
     <t xml:space="preserve">7.66055107116699</t>
@@ -2996,52 +2996,52 @@
     <t xml:space="preserve">7.73498868942261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79480409622192</t>
+    <t xml:space="preserve">7.79480504989624</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847597122192</t>
+    <t xml:space="preserve">7.78967714309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847549438477</t>
   </si>
   <si>
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82385873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89221811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94006967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98963212966919</t>
+    <t xml:space="preserve">7.82385683059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404237747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89221715927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94007015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98963165283203</t>
   </si>
   <si>
     <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09388160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1844596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2494010925293</t>
+    <t xml:space="preserve">8.09388065338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18445873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24940204620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.28699970245361</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">8.39808654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38099575042725</t>
+    <t xml:space="preserve">8.38099479675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.46302795410156</t>
@@ -3062,22 +3062,22 @@
     <t xml:space="preserve">8.44252014160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21180248260498</t>
+    <t xml:space="preserve">8.2118034362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.36390495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31947040557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2442741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1912956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12806129455566</t>
+    <t xml:space="preserve">8.31947135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12806224822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.09900856018066</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11951541900635</t>
+    <t xml:space="preserve">8.11951637268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.2271842956543</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48011875152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45619297027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44081020355225</t>
+    <t xml:space="preserve">8.35877895355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48011779785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45619106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44081115722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.46986293792725</t>
@@ -3128,28 +3128,28 @@
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57496738433838</t>
+    <t xml:space="preserve">8.5749683380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25965690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32630634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2425651550293</t>
+    <t xml:space="preserve">8.25965595245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32630729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24256420135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2186393737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1742057800293</t>
+    <t xml:space="preserve">8.21863842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17420482635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.28187274932861</t>
@@ -3158,19 +3158,19 @@
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365200042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45277309417725</t>
+    <t xml:space="preserve">8.35365104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42030239105225</t>
+    <t xml:space="preserve">8.50404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42030334472656</t>
   </si>
   <si>
     <t xml:space="preserve">8.50233554840088</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">8.64760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6006031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6347827911377</t>
+    <t xml:space="preserve">8.60060214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63478374481201</t>
   </si>
   <si>
     <t xml:space="preserve">8.62623882293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6176929473877</t>
+    <t xml:space="preserve">8.61769390106201</t>
   </si>
   <si>
     <t xml:space="preserve">8.5416431427002</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">8.6219654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69032669067383</t>
+    <t xml:space="preserve">8.69032764434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051128387451</t>
+    <t xml:space="preserve">8.63051223754883</t>
   </si>
   <si>
     <t xml:space="preserve">8.53822326660156</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">8.42372035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49208164215088</t>
+    <t xml:space="preserve">8.49208068847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.54506015777588</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143329620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36561489105225</t>
+    <t xml:space="preserve">8.33143424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36561393737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.2340202331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3143424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40492153167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30579948425293</t>
+    <t xml:space="preserve">8.31434440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40492248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30579853057861</t>
   </si>
   <si>
     <t xml:space="preserve">8.49720859527588</t>
@@ -3251,46 +3251,46 @@
     <t xml:space="preserve">8.47840881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34681415557861</t>
+    <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23231029510498</t>
+    <t xml:space="preserve">8.2323112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.2152214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2083854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17933082580566</t>
+    <t xml:space="preserve">8.20838451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1793327331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166481018066</t>
+    <t xml:space="preserve">8.07166385650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.08875465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99475908279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2391471862793</t>
+    <t xml:space="preserve">7.99475860595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23914813995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.33485126495361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40150356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3177604675293</t>
+    <t xml:space="preserve">8.40150260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.2545280456543</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">8.17762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2647819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25111103057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31605243682861</t>
+    <t xml:space="preserve">8.26478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2511100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31605434417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.2169303894043</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055725097656</t>
+    <t xml:space="preserve">8.43055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.32972526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45106506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44935512542725</t>
+    <t xml:space="preserve">8.45106601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.53480625152588</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">8.5664234161377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50575256347656</t>
+    <t xml:space="preserve">8.50575351715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47670078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02358341217041</t>
+    <t xml:space="preserve">8.47669982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02358531951904</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
@@ -3368,19 +3368,19 @@
     <t xml:space="preserve">8.82704734802246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71168804168701</t>
+    <t xml:space="preserve">8.71168899536133</t>
   </si>
   <si>
     <t xml:space="preserve">8.65614700317383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72023391723633</t>
+    <t xml:space="preserve">8.72023487091064</t>
   </si>
   <si>
     <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63905620574951</t>
+    <t xml:space="preserve">8.6390552520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.6091480255127</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">8.69459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77150440216064</t>
+    <t xml:space="preserve">8.75441551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77150535583496</t>
   </si>
   <si>
     <t xml:space="preserve">8.88686275482178</t>
@@ -3404,10 +3404,10 @@
     <t xml:space="preserve">8.92531490325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94667816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95522212982178</t>
+    <t xml:space="preserve">8.94667911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95522308349609</t>
   </si>
   <si>
     <t xml:space="preserve">8.98085880279541</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">8.92104244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98940467834473</t>
+    <t xml:space="preserve">8.98940372467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.06630897521973</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">9.12612438201904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20302963256836</t>
+    <t xml:space="preserve">9.20303058624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.03212833404541</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">8.98513126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70741558074951</t>
+    <t xml:space="preserve">8.70741653442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.5877857208252</t>
@@ -3443,37 +3443,37 @@
     <t xml:space="preserve">8.28870868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26136493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15882396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08021068572998</t>
+    <t xml:space="preserve">8.26136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1588249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
     <t xml:space="preserve">8.2066764831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35706901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78454971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81872987747192</t>
+    <t xml:space="preserve">8.35706806182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78455066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81873083114624</t>
   </si>
   <si>
     <t xml:space="preserve">7.81360292434692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81018590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12635231018066</t>
+    <t xml:space="preserve">7.8101863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12635326385498</t>
   </si>
   <si>
     <t xml:space="preserve">7.8802547454834</t>
@@ -3485,25 +3485,25 @@
     <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61364889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54699659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45129299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58459615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434225082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58288717269897</t>
+    <t xml:space="preserve">7.61364841461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54699754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45129346847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58459711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953756332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58288621902466</t>
   </si>
   <si>
     <t xml:space="preserve">7.48376417160034</t>
@@ -3512,61 +3512,61 @@
     <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556676864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78625965118408</t>
+    <t xml:space="preserve">7.69055557250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5657958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78625917434692</t>
   </si>
   <si>
     <t xml:space="preserve">7.56237888336182</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72302579879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66491889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77087783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62561225891113</t>
+    <t xml:space="preserve">7.72302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66491937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77087736129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62561178207397</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91785287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95545101165771</t>
+    <t xml:space="preserve">7.9178524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95545244216919</t>
   </si>
   <si>
     <t xml:space="preserve">8.07508182525635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14173412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20325946807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22889232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48182678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50062656402588</t>
+    <t xml:space="preserve">8.14173316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2032585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2288932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48182582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50062561035156</t>
   </si>
   <si>
     <t xml:space="preserve">8.39466762542725</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">8.54335117340088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5578784942627</t>
+    <t xml:space="preserve">8.55787754058838</t>
   </si>
   <si>
     <t xml:space="preserve">8.68178081512451</t>
@@ -3584,49 +3584,49 @@
     <t xml:space="preserve">8.68605422973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73732471466064</t>
+    <t xml:space="preserve">8.73732376098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93813228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404537200928</t>
+    <t xml:space="preserve">8.97658538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93813323974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404441833496</t>
   </si>
   <si>
     <t xml:space="preserve">8.89113521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95095062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91677093505859</t>
+    <t xml:space="preserve">8.95095157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91676998138428</t>
   </si>
   <si>
     <t xml:space="preserve">8.90395259857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81422901153564</t>
+    <t xml:space="preserve">8.81422996520996</t>
   </si>
   <si>
     <t xml:space="preserve">8.6134204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67323589324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69887161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70314407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74159622192383</t>
+    <t xml:space="preserve">8.6732349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69887256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70314502716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74159717559814</t>
   </si>
   <si>
     <t xml:space="preserve">8.46131896972656</t>
@@ -3641,22 +3641,22 @@
     <t xml:space="preserve">8.92368793487549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16629981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26775550842285</t>
+    <t xml:space="preserve">9.16630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26775455474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600032806396</t>
+    <t xml:space="preserve">9.20599937438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.14424324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1883544921875</t>
+    <t xml:space="preserve">9.18835544586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.1927661895752</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">8.23820114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23996543884277</t>
+    <t xml:space="preserve">8.23996448516846</t>
   </si>
   <si>
     <t xml:space="preserve">8.25760936737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21702766418457</t>
+    <t xml:space="preserve">8.21702671051025</t>
   </si>
   <si>
     <t xml:space="preserve">8.31583499908447</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">8.58932590484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57521057128906</t>
+    <t xml:space="preserve">8.57520961761475</t>
   </si>
   <si>
     <t xml:space="preserve">8.54344940185547</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">8.71636581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86634254455566</t>
+    <t xml:space="preserve">8.86634349822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.82223224639893</t>
@@ -3725,22 +3725,22 @@
     <t xml:space="preserve">8.80458736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77635669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91486549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93692111968994</t>
+    <t xml:space="preserve">8.7763557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91486644744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93692207336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.84428787231445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85310935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517505645752</t>
+    <t xml:space="preserve">8.85311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">8.78694438934326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03396606445312</t>
+    <t xml:space="preserve">8.75341892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03396701812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.91045570373535</t>
@@ -3767,22 +3767,22 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5575647354126</t>
+    <t xml:space="preserve">8.55756568908691</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58756160736084</t>
+    <t xml:space="preserve">8.58756065368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.6157922744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77106380462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74459648132324</t>
+    <t xml:space="preserve">8.77106475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74459552764893</t>
   </si>
   <si>
     <t xml:space="preserve">8.90163230895996</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">8.84869861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8354663848877</t>
+    <t xml:space="preserve">8.83546543121338</t>
   </si>
   <si>
     <t xml:space="preserve">8.68460559844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56638813018799</t>
+    <t xml:space="preserve">8.56638717651367</t>
   </si>
   <si>
     <t xml:space="preserve">8.63167285919189</t>
@@ -3809,16 +3809,16 @@
     <t xml:space="preserve">8.34936046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29995632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10763168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25584506988525</t>
+    <t xml:space="preserve">8.29995536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16938781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10763072967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25584411621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">8.32818698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70754337310791</t>
+    <t xml:space="preserve">8.70754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">8.45699214935303</t>
@@ -3842,22 +3842,22 @@
     <t xml:space="preserve">8.39347171783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08292961120605</t>
+    <t xml:space="preserve">8.08292865753174</t>
   </si>
   <si>
     <t xml:space="preserve">8.22584915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0035285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412540435791</t>
+    <t xml:space="preserve">8.00352954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412397384644</t>
   </si>
   <si>
     <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92589426040649</t>
+    <t xml:space="preserve">7.92589378356934</t>
   </si>
   <si>
     <t xml:space="preserve">7.90471982955933</t>
@@ -3866,40 +3866,40 @@
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91354322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94706726074219</t>
+    <t xml:space="preserve">7.9135422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94706773757935</t>
   </si>
   <si>
     <t xml:space="preserve">8.15703678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04411220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78473806381226</t>
+    <t xml:space="preserve">8.04411125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78473854064941</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64534759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39479541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40538167953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51124811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64711141586304</t>
+    <t xml:space="preserve">7.64534711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39479494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40538215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51124858856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64711093902588</t>
   </si>
   <si>
     <t xml:space="preserve">7.43890619277954</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">7.3101019859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50948476791382</t>
+    <t xml:space="preserve">7.50948429107666</t>
   </si>
   <si>
     <t xml:space="preserve">7.73180437088013</t>
@@ -3920,46 +3920,46 @@
     <t xml:space="preserve">7.73709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75297737121582</t>
+    <t xml:space="preserve">7.75297832489014</t>
   </si>
   <si>
     <t xml:space="preserve">7.87472438812256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88001823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85355091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94353818893433</t>
+    <t xml:space="preserve">7.88001775741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85355138778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94353771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08822250366211</t>
+    <t xml:space="preserve">8.08822345733643</t>
   </si>
   <si>
     <t xml:space="preserve">8.14291954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3881778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76047706604004</t>
+    <t xml:space="preserve">8.38817882537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76047611236572</t>
   </si>
   <si>
     <t xml:space="preserve">8.69872093200684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50286769866943</t>
+    <t xml:space="preserve">8.50286674499512</t>
   </si>
   <si>
     <t xml:space="preserve">8.4005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33524513244629</t>
+    <t xml:space="preserve">8.33524608612061</t>
   </si>
   <si>
     <t xml:space="preserve">8.48698711395264</t>
@@ -3971,10 +3971,10 @@
     <t xml:space="preserve">8.48169422149658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40935230255127</t>
+    <t xml:space="preserve">8.49404525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40935134887695</t>
   </si>
   <si>
     <t xml:space="preserve">8.28054714202881</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">8.47640132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46757793426514</t>
+    <t xml:space="preserve">8.46757888793945</t>
   </si>
   <si>
     <t xml:space="preserve">8.4269962310791</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">8.37053394317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36347675323486</t>
+    <t xml:space="preserve">8.36347579956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.53286361694336</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">8.2152624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26466751098633</t>
+    <t xml:space="preserve">8.26466655731201</t>
   </si>
   <si>
     <t xml:space="preserve">8.16232967376709</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">8.37582874298096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35112476348877</t>
+    <t xml:space="preserve">8.35112571716309</t>
   </si>
   <si>
     <t xml:space="preserve">8.29642772674561</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">8.22937870025635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29819107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41640853881836</t>
+    <t xml:space="preserve">8.29819202423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41641044616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4075870513916</t>
+    <t xml:space="preserve">8.40758800506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4049,13 +4049,13 @@
     <t xml:space="preserve">8.55227184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64402389526367</t>
+    <t xml:space="preserve">8.64402294158936</t>
   </si>
   <si>
     <t xml:space="preserve">8.67049026489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61226367950439</t>
+    <t xml:space="preserve">8.61226272583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.7887077331543</t>
@@ -4070,31 +4070,31 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456600189209</t>
+    <t xml:space="preserve">8.95456504821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86193180084229</t>
+    <t xml:space="preserve">8.91927719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8619327545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.89280986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11336517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89722156524658</t>
+    <t xml:space="preserve">9.11336612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867725372314</t>
+    <t xml:space="preserve">8.99867630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4103,16 +4103,16 @@
     <t xml:space="preserve">9.21041011810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26334476470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28098964691162</t>
+    <t xml:space="preserve">9.26334381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2809886932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15306568145752</t>
+    <t xml:space="preserve">9.15306663513184</t>
   </si>
   <si>
     <t xml:space="preserve">9.14865493774414</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">9.13101005554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13983249664307</t>
+    <t xml:space="preserve">9.13983154296875</t>
   </si>
   <si>
     <t xml:space="preserve">9.08248805999756</t>
@@ -4133,31 +4133,31 @@
     <t xml:space="preserve">9.93383407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74415588378906</t>
+    <t xml:space="preserve">10.0485229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">10.1411561965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1720333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0264663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78385543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07057762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87207794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706630706787</t>
+    <t xml:space="preserve">10.1720342636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0264673233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78385639190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0705785751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87207698822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706726074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.77944469451904</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.5778560638428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6131458282471</t>
+    <t xml:space="preserve">10.6131448745728</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">10.7278347015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8425235748291</t>
+    <t xml:space="preserve">10.8425226211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.0013236999512</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">10.8601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7895889282227</t>
+    <t xml:space="preserve">10.789589881897</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160572052002</t>
@@ -4223,7 +4223,7 @@
     <t xml:space="preserve">10.868989944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9395685195923</t>
+    <t xml:space="preserve">10.939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">10.8248796463013</t>
@@ -4232,43 +4232,43 @@
     <t xml:space="preserve">10.9439792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.018967628479</t>
+    <t xml:space="preserve">11.0189685821533</t>
   </si>
   <si>
     <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0454349517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1248350143433</t>
+    <t xml:space="preserve">11.0454359054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0983686447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8645792007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660785675049</t>
+    <t xml:space="preserve">11.09836769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8645782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6969566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660795211792</t>
   </si>
   <si>
     <t xml:space="preserve">10.639612197876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6352014541626</t>
+    <t xml:space="preserve">10.4852228164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6352005004883</t>
   </si>
   <si>
     <t xml:space="preserve">10.8274974822998</t>
@@ -70748,13 +70748,13 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495833333</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>1250782</v>
       </c>
       <c r="C2497" t="n">
-        <v>9.89000034332275</v>
+        <v>9.89999961853027</v>
       </c>
       <c r="D2497" t="n">
         <v>9.78999996185303</v>
@@ -70769,6 +70769,32 @@
         <v>1833</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912384259</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>1359644</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>9.94499969482422</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>9.86499977111816</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>9.94499969482422</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1821</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="1834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="1835">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433857917786</t>
+    <t xml:space="preserve">3.42433834075928</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4629693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4560706615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986675262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331666946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812469482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34707713127136</t>
+    <t xml:space="preserve">3.46296906471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45607113838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986794471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331690788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3981249332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34707689285278</t>
   </si>
   <si>
     <t xml:space="preserve">3.26981520652771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28637099266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324825286865</t>
+    <t xml:space="preserve">3.2863712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324872970581</t>
   </si>
   <si>
     <t xml:space="preserve">3.03803038597107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.138747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288592338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425543785095</t>
+    <t xml:space="preserve">3.13874673843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14288568496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425519943237</t>
   </si>
   <si>
     <t xml:space="preserve">3.1649603843689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13736748695374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564490318298</t>
+    <t xml:space="preserve">3.13736701011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564538002014</t>
   </si>
   <si>
     <t xml:space="preserve">3.19945240020752</t>
@@ -107,55 +107,55 @@
     <t xml:space="preserve">3.24222207069397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20910906791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20773029327393</t>
+    <t xml:space="preserve">3.20911002159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20773005485535</t>
   </si>
   <si>
     <t xml:space="preserve">3.0863196849823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06700420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00078010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0021595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9980206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837324142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114291191101</t>
+    <t xml:space="preserve">3.06700372695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00077986717224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00215935707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802088737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114315032959</t>
   </si>
   <si>
     <t xml:space="preserve">3.13322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1111536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151640892029</t>
+    <t xml:space="preserve">3.11115336418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151688575745</t>
   </si>
   <si>
     <t xml:space="preserve">3.13046860694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14150595664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12495017051697</t>
+    <t xml:space="preserve">3.14150619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12495040893555</t>
   </si>
   <si>
     <t xml:space="preserve">3.11805176734924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808264732361</t>
+    <t xml:space="preserve">3.23808312416077</t>
   </si>
   <si>
     <t xml:space="preserve">3.17323851585388</t>
@@ -164,43 +164,43 @@
     <t xml:space="preserve">3.19531321525574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18703556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321761131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013715744019</t>
+    <t xml:space="preserve">3.18703508377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321808815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013644218445</t>
   </si>
   <si>
     <t xml:space="preserve">3.19255423545837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18427634239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20635032653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1980721950531</t>
+    <t xml:space="preserve">3.18427586555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636125564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20635056495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19807291030884</t>
   </si>
   <si>
     <t xml:space="preserve">3.10563492774963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906821250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05458688735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03941059112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00491881370544</t>
+    <t xml:space="preserve">3.04906797409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05458664894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03941035270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00491905212402</t>
   </si>
   <si>
     <t xml:space="preserve">3.0518274307251</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">3.05044794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05320763587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595664024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457667350769</t>
+    <t xml:space="preserve">3.05320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457619667053</t>
   </si>
   <si>
     <t xml:space="preserve">3.02147483825684</t>
@@ -230,25 +230,25 @@
     <t xml:space="preserve">3.00767827033997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02561378479004</t>
+    <t xml:space="preserve">3.02561402320862</t>
   </si>
   <si>
     <t xml:space="preserve">3.09873652458191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0876989364624</t>
+    <t xml:space="preserve">3.08769869804382</t>
   </si>
   <si>
     <t xml:space="preserve">3.14978408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0559663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319718360901</t>
+    <t xml:space="preserve">3.05596685409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319742202759</t>
   </si>
   <si>
     <t xml:space="preserve">3.02975273132324</t>
@@ -260,106 +260,106 @@
     <t xml:space="preserve">2.96766781806946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95249176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94421339035034</t>
+    <t xml:space="preserve">2.95249199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94421410560608</t>
   </si>
   <si>
     <t xml:space="preserve">2.93869495391846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93593525886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02235913276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02659201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837183952332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426198959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97861790657043</t>
+    <t xml:space="preserve">2.93593549728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235960960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02659225463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426222801208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9913170337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97861814498901</t>
   </si>
   <si>
     <t xml:space="preserve">3.06892204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06610059738159</t>
+    <t xml:space="preserve">3.06610035896301</t>
   </si>
   <si>
     <t xml:space="preserve">3.01389288902283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02094793319702</t>
+    <t xml:space="preserve">3.0209481716156</t>
   </si>
   <si>
     <t xml:space="preserve">3.00683808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03929114341736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671504974365</t>
+    <t xml:space="preserve">3.03929138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671528816223</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978256225586</t>
+    <t xml:space="preserve">2.99978303909302</t>
   </si>
   <si>
     <t xml:space="preserve">2.9645082950592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86714935302734</t>
+    <t xml:space="preserve">2.86714959144592</t>
   </si>
   <si>
     <t xml:space="preserve">2.80083203315735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87843704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702584266663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089034080505</t>
+    <t xml:space="preserve">2.87843728065491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205523490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702631950378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089010238647</t>
   </si>
   <si>
     <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61034727096558</t>
+    <t xml:space="preserve">2.61034774780273</t>
   </si>
   <si>
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899461746216</t>
+    <t xml:space="preserve">2.71899437904358</t>
   </si>
   <si>
     <t xml:space="preserve">2.79659938812256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79518818855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162758827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610701560974</t>
+    <t xml:space="preserve">2.79518842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162830352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83610725402832</t>
   </si>
   <si>
     <t xml:space="preserve">2.87279319763184</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">2.94475388526917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97438478469849</t>
+    <t xml:space="preserve">2.97438502311707</t>
   </si>
   <si>
     <t xml:space="preserve">3.00542712211609</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">3.04211282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07597732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364706039429</t>
+    <t xml:space="preserve">3.07597684860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364729881287</t>
   </si>
   <si>
     <t xml:space="preserve">3.0703330039978</t>
@@ -392,49 +392,49 @@
     <t xml:space="preserve">3.05481195449829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03788042068481</t>
+    <t xml:space="preserve">3.03788018226624</t>
   </si>
   <si>
     <t xml:space="preserve">3.05199003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17333626747131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16204786300659</t>
+    <t xml:space="preserve">3.17333602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16204762458801</t>
   </si>
   <si>
     <t xml:space="preserve">3.15499329566956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14088296890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10842990875244</t>
+    <t xml:space="preserve">3.14088273048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843014717102</t>
   </si>
   <si>
     <t xml:space="preserve">3.09149789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13241720199585</t>
+    <t xml:space="preserve">3.13241672515869</t>
   </si>
   <si>
     <t xml:space="preserve">3.13947153091431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15075969696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419702529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444356918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02800297737122</t>
+    <t xml:space="preserve">3.15076017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419678688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02800321578979</t>
   </si>
   <si>
     <t xml:space="preserve">3.01248240470886</t>
@@ -452,16 +452,16 @@
     <t xml:space="preserve">3.03646874427795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09008693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732284545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21002221107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18462371826172</t>
+    <t xml:space="preserve">3.0900866985321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732308387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21002197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1846239566803</t>
   </si>
   <si>
     <t xml:space="preserve">3.2128438949585</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">3.27774977684021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2735161781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130942344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861124992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873380661011</t>
+    <t xml:space="preserve">3.27351641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861101150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873356819153</t>
   </si>
   <si>
     <t xml:space="preserve">3.18180227279663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15358209609985</t>
+    <t xml:space="preserve">3.1535816192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.15217089653015</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">3.16628074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12536144256592</t>
+    <t xml:space="preserve">3.12536191940308</t>
   </si>
   <si>
     <t xml:space="preserve">3.11125183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08726501464844</t>
+    <t xml:space="preserve">3.08726453781128</t>
   </si>
   <si>
     <t xml:space="preserve">3.09714221954346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0886754989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.077388048172</t>
+    <t xml:space="preserve">3.11548495292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08867573738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07738757133484</t>
   </si>
   <si>
     <t xml:space="preserve">3.06186723709106</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">2.92923331260681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95322036743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9518096446991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93911004066467</t>
+    <t xml:space="preserve">2.95322012901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180916786194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93910980224609</t>
   </si>
   <si>
     <t xml:space="preserve">2.92076683044434</t>
@@ -545,46 +545,46 @@
     <t xml:space="preserve">2.92782211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98002862930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493498802185</t>
+    <t xml:space="preserve">2.98002886772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493522644043</t>
   </si>
   <si>
     <t xml:space="preserve">3.05622315406799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01953721046448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720694541931</t>
+    <t xml:space="preserve">3.01953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720718383789</t>
   </si>
   <si>
     <t xml:space="preserve">2.99554991722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04070210456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01812529563904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9630970954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92641115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849511146545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138223648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85727214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86855983734131</t>
+    <t xml:space="preserve">3.0407018661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0181257724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96309733390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92641067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138247489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8572723865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86856007575989</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358899116516</t>
@@ -599,124 +599,124 @@
     <t xml:space="preserve">2.89819097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85303902626038</t>
+    <t xml:space="preserve">2.85303926467896</t>
   </si>
   <si>
     <t xml:space="preserve">2.84034037590027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82199716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84457349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85021710395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78390073776245</t>
+    <t xml:space="preserve">2.82199740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457325935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85021734237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78390002250671</t>
   </si>
   <si>
     <t xml:space="preserve">2.79377746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82340836524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132440567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8092987537384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254689216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89395809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89960241317749</t>
+    <t xml:space="preserve">2.82340812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568056106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132416725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80929827690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8925473690033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89395833015442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89960217475891</t>
   </si>
   <si>
     <t xml:space="preserve">2.86009383201599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831400871277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91230082511902</t>
+    <t xml:space="preserve">2.90665698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831424713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9123010635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.94052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09432005882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08021020889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303213119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1056079864502</t>
+    <t xml:space="preserve">3.09432029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08020997047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10560750961304</t>
   </si>
   <si>
     <t xml:space="preserve">3.08585429191589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13523888587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511561393738</t>
+    <t xml:space="preserve">3.13523864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511585235596</t>
   </si>
   <si>
     <t xml:space="preserve">3.13806128501892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16063690185547</t>
+    <t xml:space="preserve">3.16063714027405</t>
   </si>
   <si>
     <t xml:space="preserve">3.17051386833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20437788963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591188430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253999710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278654098511</t>
+    <t xml:space="preserve">3.20437812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591212272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253975868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278606414795</t>
   </si>
   <si>
     <t xml:space="preserve">3.09290885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751155853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830687522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13665008544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07456564903259</t>
+    <t xml:space="preserve">3.06751132011414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1183066368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17898011207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13664937019348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07456612586975</t>
   </si>
   <si>
     <t xml:space="preserve">3.10701870918274</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">3.098552942276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24529671669006</t>
+    <t xml:space="preserve">3.24529695510864</t>
   </si>
   <si>
     <t xml:space="preserve">3.26646208763123</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">3.25376296043396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25094103813171</t>
+    <t xml:space="preserve">3.25094056129456</t>
   </si>
   <si>
     <t xml:space="preserve">3.29891490936279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31443572044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228727340698</t>
+    <t xml:space="preserve">3.31443500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37228655815125</t>
   </si>
   <si>
     <t xml:space="preserve">3.37651920318604</t>
@@ -755,46 +755,46 @@
     <t xml:space="preserve">3.4456582069397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41461658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283652305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40756154060364</t>
+    <t xml:space="preserve">3.41461682319641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283628463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4075620174408</t>
   </si>
   <si>
     <t xml:space="preserve">3.4005069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48657846450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105717658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160666465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47811150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798871040344</t>
+    <t xml:space="preserve">3.48657774925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105669975281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.478111743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798847198486</t>
   </si>
   <si>
     <t xml:space="preserve">3.52185273170471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5063316822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277203559875</t>
+    <t xml:space="preserve">3.50633144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222111701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56277179718018</t>
   </si>
   <si>
     <t xml:space="preserve">3.53455185890198</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">3.52749681472778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54866123199463</t>
+    <t xml:space="preserve">3.54866218566895</t>
   </si>
   <si>
     <t xml:space="preserve">3.51056480407715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59099173545837</t>
+    <t xml:space="preserve">3.59099149703979</t>
   </si>
   <si>
     <t xml:space="preserve">3.61568403244019</t>
@@ -818,25 +818,25 @@
     <t xml:space="preserve">3.5839364528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50209903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6227388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095925331116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66154193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506838798523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921143531799</t>
+    <t xml:space="preserve">3.50209879875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924367904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62273931503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.650958776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154170036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506910324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921167373657</t>
   </si>
   <si>
     <t xml:space="preserve">3.6333212852478</t>
@@ -848,85 +848,85 @@
     <t xml:space="preserve">3.7375226020813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68667149543762</t>
+    <t xml:space="preserve">3.68667197227478</t>
   </si>
   <si>
     <t xml:space="preserve">3.72299385070801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7193615436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483303070068</t>
+    <t xml:space="preserve">3.71936202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483326911926</t>
   </si>
   <si>
     <t xml:space="preserve">3.66124701499939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83195996284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832789421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379914283752</t>
+    <t xml:space="preserve">3.83195924758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832741737366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379818916321</t>
   </si>
   <si>
     <t xml:space="preserve">3.84285593032837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85012054443359</t>
+    <t xml:space="preserve">3.85012102127075</t>
   </si>
   <si>
     <t xml:space="preserve">3.8864426612854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86101675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648847579956</t>
+    <t xml:space="preserve">3.86101651191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648823738098</t>
   </si>
   <si>
     <t xml:space="preserve">3.82469511032104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83922410011292</t>
+    <t xml:space="preserve">3.83922362327576</t>
   </si>
   <si>
     <t xml:space="preserve">3.9845118522644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90097117424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087906837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639684677124</t>
+    <t xml:space="preserve">3.90097165107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087954521179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9263973236084</t>
   </si>
   <si>
     <t xml:space="preserve">3.90823578834534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91913175582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016683578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68303990364075</t>
+    <t xml:space="preserve">3.91913270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8101658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68303966522217</t>
   </si>
   <si>
     <t xml:space="preserve">3.65761470794678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61330199241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201905250549</t>
+    <t xml:space="preserve">3.6133017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201833724976</t>
   </si>
   <si>
     <t xml:space="preserve">3.60313200950623</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">3.59150838851929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62492418289185</t>
+    <t xml:space="preserve">3.62492442131042</t>
   </si>
   <si>
     <t xml:space="preserve">3.67214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63073635101318</t>
+    <t xml:space="preserve">3.63073658943176</t>
   </si>
   <si>
     <t xml:space="preserve">3.69030427932739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63218903541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035009384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572875976562</t>
+    <t xml:space="preserve">3.63218951225281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035057067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7157289981842</t>
   </si>
   <si>
     <t xml:space="preserve">3.72662615776062</t>
@@ -962,52 +962,52 @@
     <t xml:space="preserve">3.87191319465637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96635031700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366050720215</t>
+    <t xml:space="preserve">3.96635127067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366122245789</t>
   </si>
   <si>
     <t xml:space="preserve">3.9590859413147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96998262405396</t>
+    <t xml:space="preserve">3.96998310089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.01356935501099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05352258682251</t>
+    <t xml:space="preserve">4.05352306365967</t>
   </si>
   <si>
     <t xml:space="preserve">4.04989099502563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0789475440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267314910889</t>
+    <t xml:space="preserve">4.07894849777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267267227173</t>
   </si>
   <si>
     <t xml:space="preserve">3.95182228088379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9154999256134</t>
+    <t xml:space="preserve">3.91550040245056</t>
   </si>
   <si>
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04262638092041</t>
+    <t xml:space="preserve">3.99540901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177598953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446508407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04262781143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.10437393188477</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">3.96271872520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86464977264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89733910560608</t>
+    <t xml:space="preserve">3.86464929580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89733982086182</t>
   </si>
   <si>
     <t xml:space="preserve">3.98814368247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95545363426208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002820014954</t>
+    <t xml:space="preserve">3.95545411109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002867698669</t>
   </si>
   <si>
     <t xml:space="preserve">4.01720142364502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88280963897705</t>
+    <t xml:space="preserve">3.88281011581421</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531690597534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06805181503296</t>
+    <t xml:space="preserve">4.06805229187012</t>
   </si>
   <si>
     <t xml:space="preserve">4.14795970916748</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">4.04625940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06078767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11527013778687</t>
+    <t xml:space="preserve">4.06078815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11527061462402</t>
   </si>
   <si>
     <t xml:space="preserve">4.1080060005188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12253522872925</t>
+    <t xml:space="preserve">4.12253427505493</t>
   </si>
   <si>
     <t xml:space="preserve">4.18065023422241</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">4.15885639190674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18791389465332</t>
+    <t xml:space="preserve">4.18791484832764</t>
   </si>
   <si>
     <t xml:space="preserve">4.16612100601196</t>
@@ -1076,25 +1076,25 @@
     <t xml:space="preserve">4.17338514328003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09710931777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14069509506226</t>
+    <t xml:space="preserve">4.0971097946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14069604873657</t>
   </si>
   <si>
     <t xml:space="preserve">4.12979888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24602937698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22060441970825</t>
+    <t xml:space="preserve">4.24602842330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22060394287109</t>
   </si>
   <si>
     <t xml:space="preserve">4.26055812835693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21697092056274</t>
+    <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
@@ -1103,43 +1103,43 @@
     <t xml:space="preserve">4.26419019699097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27508687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239730834961</t>
+    <t xml:space="preserve">4.27508640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239683151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17701721191406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08984518051147</t>
+    <t xml:space="preserve">4.08984565734863</t>
   </si>
   <si>
     <t xml:space="preserve">4.30777597427368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29687976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42763805389404</t>
+    <t xml:space="preserve">4.29687929153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4276385307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54023599624634</t>
+    <t xml:space="preserve">4.5402364730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60198402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59835195541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929445266724</t>
+    <t xml:space="preserve">4.59835147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72184562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929397583008</t>
   </si>
   <si>
     <t xml:space="preserve">4.56202983856201</t>
@@ -1151,37 +1151,37 @@
     <t xml:space="preserve">4.59471940994263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60924816131592</t>
+    <t xml:space="preserve">4.60924768447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.48938512802124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45669603347778</t>
+    <t xml:space="preserve">4.45669651031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.51844358444214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33683395385742</t>
+    <t xml:space="preserve">4.33683443069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.52207517623901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48575353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49301862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50391435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665021896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46032810211182</t>
+    <t xml:space="preserve">4.48575401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49301815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50391483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49665069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46032762527466</t>
   </si>
   <si>
     <t xml:space="preserve">4.45306396484375</t>
@@ -1190,145 +1190,145 @@
     <t xml:space="preserve">4.46759271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4784893989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750108718872</t>
+    <t xml:space="preserve">4.47848987579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750156402588</t>
   </si>
   <si>
     <t xml:space="preserve">4.5366039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43853521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315607070923</t>
+    <t xml:space="preserve">4.4385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315559387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.39131593704224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42037439346313</t>
+    <t xml:space="preserve">4.42037391662598</t>
   </si>
   <si>
     <t xml:space="preserve">4.29324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40947818756104</t>
+    <t xml:space="preserve">4.40947866439819</t>
   </si>
   <si>
     <t xml:space="preserve">4.51117849349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42400598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140851974487</t>
+    <t xml:space="preserve">4.42400646209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140899658203</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20607471466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12616682052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23150110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361445426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94092488288879</t>
+    <t xml:space="preserve">4.2060751914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12616634368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23150014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361540794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94092535972595</t>
   </si>
   <si>
     <t xml:space="preserve">3.97724723815918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08258056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15522432327271</t>
+    <t xml:space="preserve">4.08258104324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15522384643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.16975259780884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44579935073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584516525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41674184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108781814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288022994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5511326789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655906677246</t>
+    <t xml:space="preserve">4.44579887390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40584564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61287975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55113315582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5765585899353</t>
   </si>
   <si>
     <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53297185897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67825984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6492018699646</t>
+    <t xml:space="preserve">4.52570819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53297233581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67825937271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920234680176</t>
   </si>
   <si>
     <t xml:space="preserve">4.67099475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64556980133057</t>
+    <t xml:space="preserve">4.64557027816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75816774368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75090360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76180028915405</t>
+    <t xml:space="preserve">4.7581672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75090265274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76179981231689</t>
   </si>
   <si>
     <t xml:space="preserve">4.72547769546509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68552398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911071777344</t>
+    <t xml:space="preserve">4.68552350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72910976409912</t>
   </si>
   <si>
     <t xml:space="preserve">4.65646600723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84534025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81265115737915</t>
+    <t xml:space="preserve">4.84534072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81265068054199</t>
   </si>
   <si>
     <t xml:space="preserve">4.81991529464722</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">4.83807611465454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166189193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8489727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91798400878906</t>
+    <t xml:space="preserve">4.8816614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897184371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798448562622</t>
   </si>
   <si>
     <t xml:space="preserve">4.89255857467651</t>
@@ -1352,34 +1352,34 @@
     <t xml:space="preserve">4.95430612564087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9470419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977737426758</t>
+    <t xml:space="preserve">4.94704103469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977785110474</t>
   </si>
   <si>
     <t xml:space="preserve">4.9325122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99062776565552</t>
+    <t xml:space="preserve">4.99062824249268</t>
   </si>
   <si>
     <t xml:space="preserve">4.94340896606445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86713314056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73307514190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888145446777</t>
+    <t xml:space="preserve">4.86713266372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7330756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888193130493</t>
   </si>
   <si>
     <t xml:space="preserve">4.86018848419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82654094696045</t>
+    <t xml:space="preserve">4.82654047012329</t>
   </si>
   <si>
     <t xml:space="preserve">4.75176906585693</t>
@@ -1394,43 +1394,43 @@
     <t xml:space="preserve">4.62091684341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67699766159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63587141036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74803018569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72185945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7592453956604</t>
+    <t xml:space="preserve">4.67699670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63587236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74803066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7218599319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979345321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75924634933472</t>
   </si>
   <si>
     <t xml:space="preserve">4.83027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93495988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644912719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81532573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94243812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91252946853638</t>
+    <t xml:space="preserve">4.93496036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85644960403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81532526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94243764877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.84897232055664</t>
@@ -1445,31 +1445,31 @@
     <t xml:space="preserve">4.8826208114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93869924545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486902236938</t>
+    <t xml:space="preserve">4.93869876861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96486949920654</t>
   </si>
   <si>
     <t xml:space="preserve">5.03216457366943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01721000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13684511184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05833435058594</t>
+    <t xml:space="preserve">5.01720952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13684558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0583348274231</t>
   </si>
   <si>
     <t xml:space="preserve">4.98356294631958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89757490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1293683052063</t>
+    <t xml:space="preserve">4.89757442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12936878204346</t>
   </si>
   <si>
     <t xml:space="preserve">5.24900341033936</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31629800796509</t>
+    <t xml:space="preserve">5.31629848480225</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350221633911</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">5.01347160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17796993255615</t>
+    <t xml:space="preserve">5.17797040939331</t>
   </si>
   <si>
     <t xml:space="preserve">5.2004017829895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23404884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787858963013</t>
+    <t xml:space="preserve">5.23404979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274229049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787906646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.21535634994507</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">5.22283267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19666290283203</t>
+    <t xml:space="preserve">5.19666337966919</t>
   </si>
   <si>
     <t xml:space="preserve">5.11815166473389</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">5.04337978363037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99851608276367</t>
+    <t xml:space="preserve">4.99851655960083</t>
   </si>
   <si>
     <t xml:space="preserve">5.11067485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17049217224121</t>
+    <t xml:space="preserve">5.17049264907837</t>
   </si>
   <si>
     <t xml:space="preserve">5.04711818695068</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">5.11441421508789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06581115722656</t>
+    <t xml:space="preserve">5.06581163406372</t>
   </si>
   <si>
     <t xml:space="preserve">4.97982406616211</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">4.95739221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03964185714722</t>
+    <t xml:space="preserve">5.03964138031006</t>
   </si>
   <si>
     <t xml:space="preserve">5.05459642410278</t>
@@ -1565,91 +1565,91 @@
     <t xml:space="preserve">5.21161794662476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88635873794556</t>
+    <t xml:space="preserve">4.8863582611084</t>
   </si>
   <si>
     <t xml:space="preserve">4.92000579833984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77419996261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073606491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66951990127563</t>
+    <t xml:space="preserve">4.77420043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073654174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66951942443848</t>
   </si>
   <si>
     <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67325830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68447351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56857776641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58727025985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69568967819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56109952926636</t>
+    <t xml:space="preserve">4.67325782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68447399139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5685772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58727121353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6956901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110000610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.40781736373901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848642349243</t>
+    <t xml:space="preserve">4.613440990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848594665527</t>
   </si>
   <si>
     <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84523344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.792893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167772293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77793884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140417098999</t>
+    <t xml:space="preserve">4.84523391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79289293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7779393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140369415283</t>
   </si>
   <si>
     <t xml:space="preserve">4.8377571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68821239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71812152862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74055337905884</t>
+    <t xml:space="preserve">4.68821334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71812105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74055290222168</t>
   </si>
   <si>
     <t xml:space="preserve">4.60222482681274</t>
@@ -1661,52 +1661,52 @@
     <t xml:space="preserve">4.52371406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51997566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48632764816284</t>
+    <t xml:space="preserve">4.51997470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.486328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.41903209686279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46015691757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64334917068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298475265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73681449890137</t>
+    <t xml:space="preserve">4.46015739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64334869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73681497573853</t>
   </si>
   <si>
     <t xml:space="preserve">4.86392688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98730182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927648544312</t>
+    <t xml:space="preserve">4.98730134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927696228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.21909475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22657203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18918609619141</t>
+    <t xml:space="preserve">5.22657155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18918561935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.15179967880249</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353378295898</t>
+    <t xml:space="preserve">5.81353330612183</t>
   </si>
   <si>
     <t xml:space="preserve">5.79110097885132</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">5.80231809616089</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75745344161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474899291992</t>
+    <t xml:space="preserve">5.75745391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474946975708</t>
   </si>
   <si>
     <t xml:space="preserve">5.87708902359009</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">5.98924732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01167964935303</t>
+    <t xml:space="preserve">6.01167869567871</t>
   </si>
   <si>
     <t xml:space="preserve">6.02663421630859</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00794076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92569208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93316888809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699815750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94064617156982</t>
+    <t xml:space="preserve">6.0079402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92569160461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699863433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94064569473267</t>
   </si>
   <si>
     <t xml:space="preserve">6.07897424697876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93690729141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95933866500854</t>
+    <t xml:space="preserve">5.9369068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95933818817139</t>
   </si>
   <si>
     <t xml:space="preserve">5.89952087402344</t>
@@ -1799,73 +1799,73 @@
     <t xml:space="preserve">5.89578247070312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88082790374756</t>
+    <t xml:space="preserve">5.88082838058472</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812250137329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95560073852539</t>
+    <t xml:space="preserve">5.95560026168823</t>
   </si>
   <si>
     <t xml:space="preserve">5.97429275512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91362047195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84066104888916</t>
+    <t xml:space="preserve">6.02114152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9136209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.840660572052</t>
   </si>
   <si>
     <t xml:space="preserve">5.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69474029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778059005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68321990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66401958465576</t>
+    <t xml:space="preserve">5.694739818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68322086334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66402006149292</t>
   </si>
   <si>
     <t xml:space="preserve">5.66786003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7830605506897</t>
+    <t xml:space="preserve">5.78306102752686</t>
   </si>
   <si>
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76001977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87522077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82146072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74850034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69858026504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64482021331787</t>
+    <t xml:space="preserve">5.76002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87522029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82146024703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74850082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69858074188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64481973648071</t>
   </si>
   <si>
     <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77538061141968</t>
+    <t xml:space="preserve">5.77537965774536</t>
   </si>
   <si>
     <t xml:space="preserve">5.72162055969238</t>
@@ -1874,40 +1874,40 @@
     <t xml:space="preserve">5.81762027740479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78689956665039</t>
+    <t xml:space="preserve">5.78690099716187</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05570125579834</t>
+    <t xml:space="preserve">6.0557017326355</t>
   </si>
   <si>
     <t xml:space="preserve">6.28226232528687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17474222183228</t>
+    <t xml:space="preserve">6.17474174499512</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12866163253784</t>
+    <t xml:space="preserve">6.128662109375</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19394159317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06722116470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10178184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25154304504395</t>
+    <t xml:space="preserve">6.19394207000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06722164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10178136825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25154256820679</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090177536011</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">6.39746236801147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43586254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4627423286438</t>
+    <t xml:space="preserve">6.43586301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46274280548096</t>
   </si>
   <si>
     <t xml:space="preserve">6.38210296630859</t>
@@ -1934,25 +1934,25 @@
     <t xml:space="preserve">6.35522174835205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44738340377808</t>
+    <t xml:space="preserve">6.44738292694092</t>
   </si>
   <si>
     <t xml:space="preserve">6.5280237197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53954267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5894627571106</t>
+    <t xml:space="preserve">6.53954362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58946371078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.62018346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64322423934937</t>
+    <t xml:space="preserve">6.64322376251221</t>
   </si>
   <si>
     <t xml:space="preserve">6.62786293029785</t>
@@ -1961,10 +1961,10 @@
     <t xml:space="preserve">6.66626358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80450344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138418197632</t>
+    <t xml:space="preserve">6.80450439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138465881348</t>
   </si>
   <si>
     <t xml:space="preserve">6.83522367477417</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">6.78914356231689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76610469818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114442825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554430007935</t>
+    <t xml:space="preserve">6.76610422134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554382324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.61634349822998</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">6.79298448562622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14626598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570558547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946516036987</t>
+    <t xml:space="preserve">7.14626550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026578903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946468353271</t>
   </si>
   <si>
     <t xml:space="preserve">7.04642486572266</t>
@@ -2018,118 +2018,118 @@
     <t xml:space="preserve">7.00802516937256</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99266481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1040244102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786485671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330560684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714605331421</t>
+    <t xml:space="preserve">6.9926643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10402536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0617847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330465316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714509963989</t>
   </si>
   <si>
     <t xml:space="preserve">7.00034475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96578454971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02722454071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186418533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04258489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7507438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9350643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90434455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02338552474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346544265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15778493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16546535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2960262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16930627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138610839844</t>
+    <t xml:space="preserve">6.96578407287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02722406387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274377822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04258441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93506383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434503555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02338457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346448898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15778541564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16546583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3113865852356</t>
   </si>
   <si>
     <t xml:space="preserve">7.27682590484619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18850421905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698574066162</t>
+    <t xml:space="preserve">7.18850469589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706470489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698526382446</t>
   </si>
   <si>
     <t xml:space="preserve">7.1923451423645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15010595321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210634231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43426704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730590820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978580474854</t>
+    <t xml:space="preserve">7.15010547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43426609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730638504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978675842285</t>
   </si>
   <si>
     <t xml:space="preserve">7.42658662796021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28066635131836</t>
+    <t xml:space="preserve">7.2806658744812</t>
   </si>
   <si>
     <t xml:space="preserve">7.11938619613647</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">7.22306537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11554574966431</t>
+    <t xml:space="preserve">7.11554622650146</t>
   </si>
   <si>
     <t xml:space="preserve">7.06562519073486</t>
@@ -2147,76 +2147,76 @@
     <t xml:space="preserve">7.08866453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98498439788818</t>
+    <t xml:space="preserve">6.98498487472534</t>
   </si>
   <si>
     <t xml:space="preserve">6.77378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066347122192</t>
+    <t xml:space="preserve">6.80066442489624</t>
   </si>
   <si>
     <t xml:space="preserve">6.77762365341187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92738485336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.912024974823</t>
+    <t xml:space="preserve">6.88898515701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92738437652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90818500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91202449798584</t>
   </si>
   <si>
     <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84674501419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08098554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03106451034546</t>
+    <t xml:space="preserve">6.8621039390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674453735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08098459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03106498718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.05794525146484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75842523574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218385696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602430343628</t>
+    <t xml:space="preserve">6.75842475891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218290328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602382659912</t>
   </si>
   <si>
     <t xml:space="preserve">6.87746381759644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74306392669678</t>
+    <t xml:space="preserve">6.74306440353394</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314432144165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72002410888672</t>
+    <t xml:space="preserve">6.72002363204956</t>
   </si>
   <si>
     <t xml:space="preserve">6.89282417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79682493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466327667236</t>
+    <t xml:space="preserve">6.79682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466375350952</t>
   </si>
   <si>
     <t xml:space="preserve">6.67778348922729</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">6.78530406951904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71234369277954</t>
+    <t xml:space="preserve">6.71234321594238</t>
   </si>
   <si>
     <t xml:space="preserve">6.73538398742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20386648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410575866699</t>
+    <t xml:space="preserve">7.20386600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410623550415</t>
   </si>
   <si>
     <t xml:space="preserve">7.20770502090454</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">7.17314577102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22690534591675</t>
+    <t xml:space="preserve">7.22690486907959</t>
   </si>
   <si>
     <t xml:space="preserve">7.20002603530884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11170482635498</t>
+    <t xml:space="preserve">7.1117057800293</t>
   </si>
   <si>
     <t xml:space="preserve">7.25762557983398</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">7.29986619949341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33826637268066</t>
+    <t xml:space="preserve">7.33826589584351</t>
   </si>
   <si>
     <t xml:space="preserve">7.37282609939575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58786773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6646671295166</t>
+    <t xml:space="preserve">7.58786725997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098794937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466665267944</t>
   </si>
   <si>
     <t xml:space="preserve">7.83362865447998</t>
@@ -2282,37 +2282,37 @@
     <t xml:space="preserve">8.00258827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17922878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218675613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186658859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858701705933</t>
+    <t xml:space="preserve">8.17922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858749389648</t>
   </si>
   <si>
     <t xml:space="preserve">7.68002796173096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970539093018</t>
+    <t xml:space="preserve">7.3689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9197039604187</t>
   </si>
   <si>
     <t xml:space="preserve">5.89442110061646</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">6.27458190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77154064178467</t>
+    <t xml:space="preserve">5.77154016494751</t>
   </si>
   <si>
     <t xml:space="preserve">6.26690196990967</t>
@@ -2330,25 +2330,25 @@
     <t xml:space="preserve">6.33602237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15394496917725</t>
+    <t xml:space="preserve">7.15394592285156</t>
   </si>
   <si>
     <t xml:space="preserve">7.21922588348389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754854202271</t>
+    <t xml:space="preserve">7.58018684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938669204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754758834839</t>
   </si>
   <si>
     <t xml:space="preserve">8.2717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88021612167358</t>
+    <t xml:space="preserve">7.8802170753479</t>
   </si>
   <si>
     <t xml:space="preserve">7.57022905349731</t>
@@ -2357,34 +2357,34 @@
     <t xml:space="preserve">7.64364814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13718318939209</t>
+    <t xml:space="preserve">8.13718223571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.35335636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72860527038574</t>
+    <t xml:space="preserve">8.72860622406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.03043556213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95701694488525</t>
+    <t xml:space="preserve">8.95701599121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.70413303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75307655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99442386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969577789307</t>
+    <t xml:space="preserve">8.75307750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99442291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969720840454</t>
   </si>
   <si>
     <t xml:space="preserve">7.81903553009033</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">7.87613773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80679893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68035650253296</t>
+    <t xml:space="preserve">7.80679988861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
     <t xml:space="preserve">7.50904750823975</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">7.50496864318848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70482969284058</t>
+    <t xml:space="preserve">7.70482873916626</t>
   </si>
   <si>
     <t xml:space="preserve">7.75377559661865</t>
@@ -2417,22 +2417,22 @@
     <t xml:space="preserve">7.89653253555298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94547748565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85574340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010877609253</t>
+    <t xml:space="preserve">7.94547843933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85574436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010782241821</t>
   </si>
   <si>
     <t xml:space="preserve">7.98146295547485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85739898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78709506988525</t>
+    <t xml:space="preserve">7.85739994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78709554672241</t>
   </si>
   <si>
     <t xml:space="preserve">7.75814771652222</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">7.60099935531616</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58032178878784</t>
+    <t xml:space="preserve">7.58032274246216</t>
   </si>
   <si>
     <t xml:space="preserve">7.51828956604004</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">7.73333549499512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65062475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55551052093506</t>
+    <t xml:space="preserve">7.65062427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5555100440979</t>
   </si>
   <si>
     <t xml:space="preserve">7.53483200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45212268829346</t>
+    <t xml:space="preserve">7.45212316513062</t>
   </si>
   <si>
     <t xml:space="preserve">7.49347734451294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63408279418945</t>
+    <t xml:space="preserve">7.63408327102661</t>
   </si>
   <si>
     <t xml:space="preserve">7.40249633789062</t>
@@ -2483,25 +2483,25 @@
     <t xml:space="preserve">7.36941289901733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58445739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520708084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235401153564</t>
+    <t xml:space="preserve">7.5844578742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6423544883728</t>
   </si>
   <si>
     <t xml:space="preserve">7.52656221389771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75401210784912</t>
+    <t xml:space="preserve">7.75401258468628</t>
   </si>
   <si>
     <t xml:space="preserve">7.72919988632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37354898452759</t>
+    <t xml:space="preserve">7.37354850769043</t>
   </si>
   <si>
     <t xml:space="preserve">7.44385242462158</t>
@@ -2510,64 +2510,64 @@
     <t xml:space="preserve">7.34460020065308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39009141921997</t>
+    <t xml:space="preserve">7.39009094238281</t>
   </si>
   <si>
     <t xml:space="preserve">7.37768459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73746967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69197988510132</t>
+    <t xml:space="preserve">7.73746871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69198036193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.77468967437744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784475326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67543697357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6216778755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438671112061</t>
+    <t xml:space="preserve">7.72506475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68784427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67543745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62167739868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438575744629</t>
   </si>
   <si>
     <t xml:space="preserve">7.71265745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42317390441895</t>
+    <t xml:space="preserve">7.62581205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4231743812561</t>
   </si>
   <si>
     <t xml:space="preserve">7.33632898330688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36527729034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25775480270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08406496047974</t>
+    <t xml:space="preserve">7.3652777671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25775527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08406543731689</t>
   </si>
   <si>
     <t xml:space="preserve">7.02203321456909</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95586538314819</t>
+    <t xml:space="preserve">6.95586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
@@ -2597,22 +2597,22 @@
     <t xml:space="preserve">6.93932437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05511713027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864633560181</t>
+    <t xml:space="preserve">7.05511665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864585876465</t>
   </si>
   <si>
     <t xml:space="preserve">6.90624046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95173072814941</t>
+    <t xml:space="preserve">6.95173025131226</t>
   </si>
   <si>
     <t xml:space="preserve">6.89796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98481416702271</t>
+    <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.93105268478394</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">6.82353115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75322771072388</t>
+    <t xml:space="preserve">6.75322723388672</t>
   </si>
   <si>
     <t xml:space="preserve">6.78217554092407</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">6.96413660049438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.947594165802</t>
+    <t xml:space="preserve">6.94759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324506759644</t>
@@ -2642,28 +2642,28 @@
     <t xml:space="preserve">7.35700654983521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.489342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59272956848145</t>
+    <t xml:space="preserve">7.48934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59272909164429</t>
   </si>
   <si>
     <t xml:space="preserve">7.80777215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60927104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71679210662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092771530151</t>
+    <t xml:space="preserve">7.6092700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71679162979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092819213867</t>
   </si>
   <si>
     <t xml:space="preserve">7.84085702896118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81190919876099</t>
+    <t xml:space="preserve">7.81190824508667</t>
   </si>
   <si>
     <t xml:space="preserve">7.82845067977905</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">7.8367223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078443527222</t>
+    <t xml:space="preserve">7.96078538894653</t>
   </si>
   <si>
     <t xml:space="preserve">7.84912633895874</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">7.67957353591919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61754179000854</t>
+    <t xml:space="preserve">7.6175422668457</t>
   </si>
   <si>
     <t xml:space="preserve">7.60513401031494</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">7.57205104827881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54723787307739</t>
+    <t xml:space="preserve">7.54723882675171</t>
   </si>
   <si>
     <t xml:space="preserve">7.55137395858765</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">8.03522396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20064258575439</t>
+    <t xml:space="preserve">8.20064353942871</t>
   </si>
   <si>
     <t xml:space="preserve">8.15515232086182</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5604305267334</t>
+    <t xml:space="preserve">8.31230163574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56042957305908</t>
   </si>
   <si>
     <t xml:space="preserve">8.40328121185303</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">8.33711433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6100549697876</t>
+    <t xml:space="preserve">8.61005401611328</t>
   </si>
   <si>
     <t xml:space="preserve">8.68449401855469</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92435073852539</t>
+    <t xml:space="preserve">8.92434978485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.99051856994629</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">8.35365676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10966300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21304988861084</t>
+    <t xml:space="preserve">8.10966396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21304893493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.18823623657227</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">8.13861179351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32057189941406</t>
+    <t xml:space="preserve">8.32057094573975</t>
   </si>
   <si>
     <t xml:space="preserve">8.24199771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.304030418396</t>
+    <t xml:space="preserve">8.30402946472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.22545623779297</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95665073394775</t>
+    <t xml:space="preserve">7.95664978027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.86980581283569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85326242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574136734009</t>
+    <t xml:space="preserve">7.85326290130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574184417725</t>
   </si>
   <si>
     <t xml:space="preserve">7.66303157806396</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">7.51415395736694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44798707962036</t>
+    <t xml:space="preserve">7.4479866027832</t>
   </si>
   <si>
     <t xml:space="preserve">7.33219480514526</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971586227417</t>
+    <t xml:space="preserve">7.46866369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971633911133</t>
   </si>
   <si>
     <t xml:space="preserve">7.43144416809082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50588417053223</t>
+    <t xml:space="preserve">7.50588369369507</t>
   </si>
   <si>
     <t xml:space="preserve">7.82017946243286</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">7.76228284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38181924819946</t>
+    <t xml:space="preserve">7.3818187713623</t>
   </si>
   <si>
     <t xml:space="preserve">7.2039942741394</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">7.09233617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12542009353638</t>
+    <t xml:space="preserve">7.12541961669922</t>
   </si>
   <si>
     <t xml:space="preserve">7.28670454025269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12955570220947</t>
+    <t xml:space="preserve">7.12955617904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518829345703</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">7.22053575515747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53896713256836</t>
+    <t xml:space="preserve">7.5389666557312</t>
   </si>
   <si>
     <t xml:space="preserve">7.70025110244751</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">8.03108882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88386631011963</t>
+    <t xml:space="preserve">7.88386535644531</t>
   </si>
   <si>
     <t xml:space="preserve">8.01123809814453</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">7.79453992843628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70190525054932</t>
+    <t xml:space="preserve">7.70190477371216</t>
   </si>
   <si>
     <t xml:space="preserve">7.86732339859009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81273603439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6969428062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05590057373047</t>
+    <t xml:space="preserve">7.81273508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69694328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
     <t xml:space="preserve">7.97319269180298</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9996600151062</t>
+    <t xml:space="preserve">7.99965906143188</t>
   </si>
   <si>
     <t xml:space="preserve">8.02281856536865</t>
@@ -2966,22 +2966,22 @@
     <t xml:space="preserve">7.95003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88055801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86897802352905</t>
+    <t xml:space="preserve">7.8805570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86897897720337</t>
   </si>
   <si>
     <t xml:space="preserve">7.82431507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90371561050415</t>
+    <t xml:space="preserve">7.90371465682983</t>
   </si>
   <si>
     <t xml:space="preserve">8.0128927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84416532516479</t>
+    <t xml:space="preserve">7.84416484832764</t>
   </si>
   <si>
     <t xml:space="preserve">7.81604480743408</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">7.63904523849487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66055107116699</t>
+    <t xml:space="preserve">7.66055059432983</t>
   </si>
   <si>
     <t xml:space="preserve">7.73498868942261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79480504989624</t>
+    <t xml:space="preserve">7.79480409622192</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82385683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258777618408</t>
+    <t xml:space="preserve">7.82385778427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258682250977</t>
   </si>
   <si>
     <t xml:space="preserve">7.71960735321045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76404237747192</t>
+    <t xml:space="preserve">7.76404190063477</t>
   </si>
   <si>
     <t xml:space="preserve">7.89221715927124</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09388065338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18445873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24940204620361</t>
+    <t xml:space="preserve">8.09388160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1844596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2494010925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.28699970245361</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">8.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39808654785156</t>
+    <t xml:space="preserve">8.39808559417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.38099479675293</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">8.19129467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12806224822998</t>
+    <t xml:space="preserve">8.12806129455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09900856018066</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">8.11951637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2271842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36903190612793</t>
+    <t xml:space="preserve">8.22718524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36903285980225</t>
   </si>
   <si>
     <t xml:space="preserve">8.2459831237793</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877895355225</t>
+    <t xml:space="preserve">8.35877799987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">8.45619106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44081115722656</t>
+    <t xml:space="preserve">8.44081020355225</t>
   </si>
   <si>
     <t xml:space="preserve">8.46986293792725</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644592285156</t>
+    <t xml:space="preserve">8.46644687652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">8.32630729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24256420135498</t>
+    <t xml:space="preserve">8.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">8.35365104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45277500152588</t>
+    <t xml:space="preserve">8.45277404785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404357910156</t>
+    <t xml:space="preserve">8.50404453277588</t>
   </si>
   <si>
     <t xml:space="preserve">8.42030334472656</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051223754883</t>
+    <t xml:space="preserve">8.63051128387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.53822326660156</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">8.5536060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42372035980225</t>
+    <t xml:space="preserve">8.42372131347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.49208068847656</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">8.54506015777588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33656120300293</t>
+    <t xml:space="preserve">8.33656024932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.33143424987793</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">8.49720859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47840881347656</t>
+    <t xml:space="preserve">8.47840976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.34681510925293</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">8.2152214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1793327331543</t>
+    <t xml:space="preserve">8.2083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17933177947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">8.07166385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08875465393066</t>
+    <t xml:space="preserve">8.08875370025635</t>
   </si>
   <si>
     <t xml:space="preserve">7.99475860595703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23914813995361</t>
+    <t xml:space="preserve">8.23914909362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.33485126495361</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">8.31776237487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2545280456543</t>
+    <t xml:space="preserve">8.25452899932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
@@ -3305,19 +3305,19 @@
     <t xml:space="preserve">8.36048793792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31605434417725</t>
+    <t xml:space="preserve">8.25111103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31605339050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.2169303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16053295135498</t>
+    <t xml:space="preserve">8.1605339050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.43055629730225</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">8.47669982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02358531951904</t>
+    <t xml:space="preserve">9.02358436584473</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86977291107178</t>
+    <t xml:space="preserve">8.86977195739746</t>
   </si>
   <si>
     <t xml:space="preserve">8.80141162872314</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704734802246</t>
+    <t xml:space="preserve">8.82704639434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.71168899536133</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6091480255127</t>
+    <t xml:space="preserve">8.63905620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60914707183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.69459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441551208496</t>
+    <t xml:space="preserve">8.75441455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.77150535583496</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">8.95522308349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98085880279541</t>
+    <t xml:space="preserve">8.98085975646973</t>
   </si>
   <si>
     <t xml:space="preserve">8.92104244232178</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">9.20303058624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212833404541</t>
+    <t xml:space="preserve">9.03212928771973</t>
   </si>
   <si>
     <t xml:space="preserve">8.98513126373291</t>
@@ -3437,31 +3437,31 @@
     <t xml:space="preserve">8.70741653442383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5877857208252</t>
+    <t xml:space="preserve">8.58778476715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.28870868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1588249206543</t>
+    <t xml:space="preserve">8.26136493682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15882396697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2066764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35706806182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78455066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81873083114624</t>
+    <t xml:space="preserve">8.20667552947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35706901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81872987747192</t>
   </si>
   <si>
     <t xml:space="preserve">7.81360292434692</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">7.8101863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15540599822998</t>
+    <t xml:space="preserve">8.15540504455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.12635326385498</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">7.71106195449829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60168552398682</t>
+    <t xml:space="preserve">7.60168600082397</t>
   </si>
   <si>
     <t xml:space="preserve">7.61364841461182</t>
@@ -3503,25 +3503,25 @@
     <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58288621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48376417160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41369438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69055557250977</t>
+    <t xml:space="preserve">7.5828857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48376369476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41369485855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69055509567261</t>
   </si>
   <si>
     <t xml:space="preserve">7.82556629180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5657958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6051025390625</t>
+    <t xml:space="preserve">7.56579685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510301589966</t>
   </si>
   <si>
     <t xml:space="preserve">7.78625917434692</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">7.72302532196045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66491937637329</t>
+    <t xml:space="preserve">7.66491985321045</t>
   </si>
   <si>
     <t xml:space="preserve">7.77087736129761</t>
@@ -3545,16 +3545,16 @@
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9178524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95545244216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07508182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14173316955566</t>
+    <t xml:space="preserve">7.91785287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95545148849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07508277893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14173412322998</t>
   </si>
   <si>
     <t xml:space="preserve">8.2032585144043</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">8.97658538818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93813323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87404441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89113521575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95095157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91676998138428</t>
+    <t xml:space="preserve">8.93813419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87404537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89113426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95095062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91677093505859</t>
   </si>
   <si>
     <t xml:space="preserve">8.90395259857178</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">8.46131896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83131980895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5621509552002</t>
+    <t xml:space="preserve">8.83132076263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56215000152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.92368793487549</t>
@@ -5514,6 +5514,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.89999961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -70774,7 +70777,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912384259</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>1359644</v>
@@ -70795,6 +70798,32 @@
         <v>1821</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.693599537</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>1078785</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>9.97500038146973</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>9.8149995803833</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>9.94499969482422</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="1835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="1836">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4243381023407</t>
+    <t xml:space="preserve">3.42433905601501</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">3.46296882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45607089996338</t>
+    <t xml:space="preserve">3.4560706615448</t>
   </si>
   <si>
     <t xml:space="preserve">3.46986699104309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47331666946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3981249332428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3470766544342</t>
+    <t xml:space="preserve">3.47331619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812421798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845590591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34707713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.26981520652771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28637170791626</t>
+    <t xml:space="preserve">3.28637146949768</t>
   </si>
   <si>
     <t xml:space="preserve">3.21324920654297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03803062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13874697685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288592338562</t>
+    <t xml:space="preserve">3.03803086280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13874673843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14288568496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425519943237</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">3.16496062278748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.137366771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564538002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430722236633</t>
+    <t xml:space="preserve">3.13736701011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945192337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430698394775</t>
   </si>
   <si>
     <t xml:space="preserve">3.27119469642639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222159385681</t>
+    <t xml:space="preserve">3.24222183227539</t>
   </si>
   <si>
     <t xml:space="preserve">3.20911026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08631944656372</t>
+    <t xml:space="preserve">3.2077305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631920814514</t>
   </si>
   <si>
     <t xml:space="preserve">3.06700396537781</t>
@@ -122,94 +122,94 @@
     <t xml:space="preserve">3.00077962875366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0021595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802041053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837324142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114291191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322854042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115407943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151640892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046836853027</t>
+    <t xml:space="preserve">3.00216007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802088737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0283727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1111536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046860694885</t>
   </si>
   <si>
     <t xml:space="preserve">3.14150595664978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12494993209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11805129051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323875427246</t>
+    <t xml:space="preserve">3.12495040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11805176734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808240890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1732382774353</t>
   </si>
   <si>
     <t xml:space="preserve">3.19531273841858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18703532218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321737289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013715744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255399703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427562713623</t>
+    <t xml:space="preserve">3.18703579902649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321761131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013691902161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255375862122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427538871765</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636101722717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20634984970093</t>
+    <t xml:space="preserve">3.20635008811951</t>
   </si>
   <si>
     <t xml:space="preserve">3.19807291030884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1056342124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0545871257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03941106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00491881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0518274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422360420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05044746398926</t>
+    <t xml:space="preserve">3.10563445091248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906797409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05458664894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03941082954407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00491905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05182766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05044770240784</t>
   </si>
   <si>
     <t xml:space="preserve">3.05320739746094</t>
@@ -218,49 +218,49 @@
     <t xml:space="preserve">3.01595640182495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01457643508911</t>
+    <t xml:space="preserve">3.01457619667053</t>
   </si>
   <si>
     <t xml:space="preserve">3.02147459983826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00629901885986</t>
+    <t xml:space="preserve">3.00629854202271</t>
   </si>
   <si>
     <t xml:space="preserve">3.00767827033997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02561378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873676300049</t>
+    <t xml:space="preserve">3.02561450004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873604774475</t>
   </si>
   <si>
     <t xml:space="preserve">3.0876989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14978432655334</t>
+    <t xml:space="preserve">3.14978361129761</t>
   </si>
   <si>
     <t xml:space="preserve">3.05596685409546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06838417053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319670677185</t>
+    <t xml:space="preserve">3.06838345527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319718360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.02975273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01871585845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249199867249</t>
+    <t xml:space="preserve">3.01871562004089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766781806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249176025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.94421362876892</t>
@@ -269,55 +269,55 @@
     <t xml:space="preserve">2.93869495391846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93593573570251</t>
+    <t xml:space="preserve">2.93593525886536</t>
   </si>
   <si>
     <t xml:space="preserve">3.02235913276672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02659201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837183952332</t>
+    <t xml:space="preserve">3.02659225463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98426222801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99131727218628</t>
+    <t xml:space="preserve">2.99131679534912</t>
   </si>
   <si>
     <t xml:space="preserve">2.97861814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06892204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06609964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01389288902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0209481716156</t>
+    <t xml:space="preserve">3.0689218044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610035896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01389312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02094793319702</t>
   </si>
   <si>
     <t xml:space="preserve">3.00683832168579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671504974365</t>
+    <t xml:space="preserve">3.03929090499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671481132507</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96450781822205</t>
+    <t xml:space="preserve">2.99978280067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96450853347778</t>
   </si>
   <si>
     <t xml:space="preserve">2.86714911460876</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">2.80083227157593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87843728065491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702608108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9108898639679</t>
+    <t xml:space="preserve">2.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702631950378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089010238647</t>
   </si>
   <si>
     <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61034750938416</t>
+    <t xml:space="preserve">2.61034798622131</t>
   </si>
   <si>
     <t xml:space="preserve">2.67525339126587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71899461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79659914970398</t>
+    <t xml:space="preserve">2.71899437904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7965989112854</t>
   </si>
   <si>
     <t xml:space="preserve">2.79518842697144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85162806510925</t>
+    <t xml:space="preserve">2.85162782669067</t>
   </si>
   <si>
     <t xml:space="preserve">2.83610725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87279319763184</t>
+    <t xml:space="preserve">2.87279343605042</t>
   </si>
   <si>
     <t xml:space="preserve">2.94475412368774</t>
@@ -374,25 +374,25 @@
     <t xml:space="preserve">3.00542736053467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02518105506897</t>
+    <t xml:space="preserve">3.02518081665039</t>
   </si>
   <si>
     <t xml:space="preserve">3.04211282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07597732543945</t>
+    <t xml:space="preserve">3.07597708702087</t>
   </si>
   <si>
     <t xml:space="preserve">3.03364706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0703330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05481195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03788018226624</t>
+    <t xml:space="preserve">3.07033348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05481219291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03788042068481</t>
   </si>
   <si>
     <t xml:space="preserve">3.05199027061462</t>
@@ -407,52 +407,52 @@
     <t xml:space="preserve">3.1549928188324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14088320732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14793801307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1084303855896</t>
+    <t xml:space="preserve">3.14088273048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1479377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843014717102</t>
   </si>
   <si>
     <t xml:space="preserve">3.09149765968323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13241696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947200775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15076017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419702529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444333076477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02800273895264</t>
+    <t xml:space="preserve">3.13241744041443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947248458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15075993537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419678688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02800297737122</t>
   </si>
   <si>
     <t xml:space="preserve">3.0124819278717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02376961708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07174372673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646898269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09008741378784</t>
+    <t xml:space="preserve">3.02376937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0717442035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646922111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0900866985321</t>
   </si>
   <si>
     <t xml:space="preserve">3.19732284545898</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">3.21002173423767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18462347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21284341812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707701683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27774930000305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351689338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22131037712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861101150513</t>
+    <t xml:space="preserve">3.18462371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21284365653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707653999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27775001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351713180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861077308655</t>
   </si>
   <si>
     <t xml:space="preserve">3.19873380661011</t>
@@ -491,52 +491,52 @@
     <t xml:space="preserve">3.15358185768127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15217089653015</t>
+    <t xml:space="preserve">3.15217065811157</t>
   </si>
   <si>
     <t xml:space="preserve">3.16628074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12536191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125183105469</t>
+    <t xml:space="preserve">3.12536215782166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125159263611</t>
   </si>
   <si>
     <t xml:space="preserve">3.08726501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09714221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11548519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867573738098</t>
+    <t xml:space="preserve">3.09714150428772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11548495292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08867621421814</t>
   </si>
   <si>
     <t xml:space="preserve">3.07738828659058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06186699867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696159362793</t>
+    <t xml:space="preserve">3.06186676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696135520935</t>
   </si>
   <si>
     <t xml:space="preserve">2.92923307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95322012901306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180892944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93910980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92076683044434</t>
+    <t xml:space="preserve">2.95321989059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180940628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93911027908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92076706886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.95886373519897</t>
@@ -548,22 +548,22 @@
     <t xml:space="preserve">2.98002886772156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04493474960327</t>
+    <t xml:space="preserve">3.04493498802185</t>
   </si>
   <si>
     <t xml:space="preserve">3.05622291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0195369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97720742225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99554991722107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04070162773132</t>
+    <t xml:space="preserve">3.01953744888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97720694541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99554967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0407018661499</t>
   </si>
   <si>
     <t xml:space="preserve">3.01812601089478</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">2.98849534988403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87138223648071</t>
+    <t xml:space="preserve">2.87138247489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.85727262496948</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">2.86856007575989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92358946800232</t>
+    <t xml:space="preserve">2.92358922958374</t>
   </si>
   <si>
     <t xml:space="preserve">2.95604228973389</t>
@@ -596,67 +596,67 @@
     <t xml:space="preserve">2.88690328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89819097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303926467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034013748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199740409851</t>
+    <t xml:space="preserve">2.89819073677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034037590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199692726135</t>
   </si>
   <si>
     <t xml:space="preserve">2.84457349777222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85021686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78390026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377770423889</t>
+    <t xml:space="preserve">2.85021758079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78390049934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377746582031</t>
   </si>
   <si>
     <t xml:space="preserve">2.82340812683105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75568008422852</t>
+    <t xml:space="preserve">2.75568032264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.76132464408875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80929851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254689216614</t>
+    <t xml:space="preserve">2.80929827690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89254713058472</t>
   </si>
   <si>
     <t xml:space="preserve">2.893958568573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89960241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009430885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831400871277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91230130195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9405210018158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09432029724121</t>
+    <t xml:space="preserve">2.89960217475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665745735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9123010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94052124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09432053565979</t>
   </si>
   <si>
     <t xml:space="preserve">3.08021020889282</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">3.08303165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10560774803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585429191589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523864746094</t>
+    <t xml:space="preserve">3.10560822486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585405349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523840904236</t>
   </si>
   <si>
     <t xml:space="preserve">3.14511632919312</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">3.13806104660034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16063690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051410675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20437812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591212272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573078155518</t>
+    <t xml:space="preserve">3.16063737869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051386833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20437788963318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253999710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573101997375</t>
   </si>
   <si>
     <t xml:space="preserve">3.10278582572937</t>
@@ -704,40 +704,40 @@
     <t xml:space="preserve">3.09290885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751084327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17898011207581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13665008544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07456588745117</t>
+    <t xml:space="preserve">3.0675106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1183066368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17897987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13664984703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07456564903259</t>
   </si>
   <si>
     <t xml:space="preserve">3.10701870918274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529671669006</t>
+    <t xml:space="preserve">3.098552942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529647827148</t>
   </si>
   <si>
     <t xml:space="preserve">3.26646208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25376296043396</t>
+    <t xml:space="preserve">3.25376272201538</t>
   </si>
   <si>
     <t xml:space="preserve">3.25094056129456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29891514778137</t>
+    <t xml:space="preserve">3.29891538619995</t>
   </si>
   <si>
     <t xml:space="preserve">3.31443572044373</t>
@@ -746,115 +746,115 @@
     <t xml:space="preserve">3.38357496261597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3722870349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651944160461</t>
+    <t xml:space="preserve">3.37228727340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651968002319</t>
   </si>
   <si>
     <t xml:space="preserve">3.44565844535828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41461682319641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40756154060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40050673484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338648796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105693817139</t>
+    <t xml:space="preserve">3.41461706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283699989319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40756177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4005069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657727241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338696479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105646133423</t>
   </si>
   <si>
     <t xml:space="preserve">3.54160666465759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.478111743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185297012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222111701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52749705314636</t>
+    <t xml:space="preserve">3.47811126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798871040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5063316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222087860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5627715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5345516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749681472778</t>
   </si>
   <si>
     <t xml:space="preserve">3.54866147041321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51056408882141</t>
+    <t xml:space="preserve">3.51056385040283</t>
   </si>
   <si>
     <t xml:space="preserve">3.59099149703979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61568403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273859977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095925331116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66154146194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506838798523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921143531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332104682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804654121399</t>
+    <t xml:space="preserve">3.61568427085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209951400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924439430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62273931503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65095901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154170036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506886482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332152366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804677963257</t>
   </si>
   <si>
     <t xml:space="preserve">3.73752284049988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68667221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299385070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71936202049255</t>
+    <t xml:space="preserve">3.68667197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299361228943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7193615436554</t>
   </si>
   <si>
     <t xml:space="preserve">3.70483303070068</t>
@@ -863,100 +863,100 @@
     <t xml:space="preserve">3.66124677658081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83195948600769</t>
+    <t xml:space="preserve">3.83195972442627</t>
   </si>
   <si>
     <t xml:space="preserve">3.82832717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81379795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285593032837</t>
+    <t xml:space="preserve">3.81379842758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285616874695</t>
   </si>
   <si>
     <t xml:space="preserve">3.85012102127075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8864426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101746559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648823738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469511032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922410011292</t>
+    <t xml:space="preserve">3.88644218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469582557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922386169434</t>
   </si>
   <si>
     <t xml:space="preserve">3.98451161384583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90097141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455742835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087978363037</t>
+    <t xml:space="preserve">3.90097093582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455790519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087930679321</t>
   </si>
   <si>
     <t xml:space="preserve">3.92639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90823554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913175582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016635894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68303990364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6576144695282</t>
+    <t xml:space="preserve">3.9082350730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016683578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68303942680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65761423110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.6133017539978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62201881408691</t>
+    <t xml:space="preserve">3.62201905250549</t>
   </si>
   <si>
     <t xml:space="preserve">3.60313177108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59150838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492513656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214345932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030427932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035057067871</t>
+    <t xml:space="preserve">3.59150886535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492418289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218903541565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65034985542297</t>
   </si>
   <si>
     <t xml:space="preserve">3.71572947502136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72662591934204</t>
+    <t xml:space="preserve">3.7266263961792</t>
   </si>
   <si>
     <t xml:space="preserve">3.87191367149353</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">3.96635055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9590859413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998333930969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356887817383</t>
+    <t xml:space="preserve">3.93366050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998286247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356840133667</t>
   </si>
   <si>
     <t xml:space="preserve">4.05352306365967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989051818848</t>
+    <t xml:space="preserve">4.04989147186279</t>
   </si>
   <si>
     <t xml:space="preserve">4.07894802093506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00267171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182204246521</t>
+    <t xml:space="preserve">4.00267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182156562805</t>
   </si>
   <si>
     <t xml:space="preserve">3.91549968719482</t>
@@ -998,58 +998,58 @@
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540781974792</t>
+    <t xml:space="preserve">3.99540829658508</t>
   </si>
   <si>
     <t xml:space="preserve">3.99177598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0244665145874</t>
+    <t xml:space="preserve">4.02446603775024</t>
   </si>
   <si>
     <t xml:space="preserve">4.04262638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10437440872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464929580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89733910560608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98814344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9554545879364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002915382385</t>
+    <t xml:space="preserve">4.10437345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464953422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89733862876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98814392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002867698669</t>
   </si>
   <si>
     <t xml:space="preserve">4.01720190048218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88281035423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07531642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06805181503296</t>
+    <t xml:space="preserve">3.88280987739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07531595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0680513381958</t>
   </si>
   <si>
     <t xml:space="preserve">4.14796018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04625797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06078767776489</t>
+    <t xml:space="preserve">4.04625844955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06078815460205</t>
   </si>
   <si>
     <t xml:space="preserve">4.11527013778687</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">4.1080060005188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12253522872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1806492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885591506958</t>
+    <t xml:space="preserve">4.12253475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18064975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885639190674</t>
   </si>
   <si>
     <t xml:space="preserve">4.18791437149048</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">4.16612100601196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17338562011719</t>
+    <t xml:space="preserve">4.17338466644287</t>
   </si>
   <si>
     <t xml:space="preserve">4.09710884094238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1406946182251</t>
+    <t xml:space="preserve">4.14069557189941</t>
   </si>
   <si>
     <t xml:space="preserve">4.12979888916016</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">4.22060346603394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26055812835693</t>
+    <t xml:space="preserve">4.26055765151978</t>
   </si>
   <si>
     <t xml:space="preserve">4.21697187423706</t>
@@ -1100,49 +1100,49 @@
     <t xml:space="preserve">4.25329351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26418972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27508640289307</t>
+    <t xml:space="preserve">4.26419019699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27508687973022</t>
   </si>
   <si>
     <t xml:space="preserve">4.24239778518677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17701816558838</t>
+    <t xml:space="preserve">4.17701768875122</t>
   </si>
   <si>
     <t xml:space="preserve">4.08984470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30777597427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4276385307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51481151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5402364730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60198307037354</t>
+    <t xml:space="preserve">4.30777645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29687976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42763900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51481103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54023599624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60198402404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.59835147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5620288848877</t>
+    <t xml:space="preserve">4.72184562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56202983856201</t>
   </si>
   <si>
     <t xml:space="preserve">4.62014436721802</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">4.59471940994263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60924768447876</t>
+    <t xml:space="preserve">4.60924816131592</t>
   </si>
   <si>
     <t xml:space="preserve">4.4893856048584</t>
@@ -1166,64 +1166,64 @@
     <t xml:space="preserve">4.33683347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207517623901</t>
+    <t xml:space="preserve">4.52207565307617</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49301815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50391435623169</t>
+    <t xml:space="preserve">4.49301767349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50391483306885</t>
   </si>
   <si>
     <t xml:space="preserve">4.49665021896362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46032905578613</t>
+    <t xml:space="preserve">4.46032762527466</t>
   </si>
   <si>
     <t xml:space="preserve">4.45306396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4675931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4784893989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750108718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39131689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037487030029</t>
+    <t xml:space="preserve">4.46759271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47848987579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53660345077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853521347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39131641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.29324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40947818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51117897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42400598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140804290771</t>
+    <t xml:space="preserve">4.40947771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51117849349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42400693893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140899658203</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">4.20607471466064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12616634368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23150014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361516952515</t>
+    <t xml:space="preserve">4.12616682052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23150062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432716369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361469268799</t>
   </si>
   <si>
     <t xml:space="preserve">3.94092559814453</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">4.15522480010986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16975259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44579935073853</t>
+    <t xml:space="preserve">4.169753074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44580030441284</t>
   </si>
   <si>
     <t xml:space="preserve">4.40584516525269</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">4.4167423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288022994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55113315582275</t>
+    <t xml:space="preserve">4.59108686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61288070678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55113363265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.57655763626099</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53297233581543</t>
+    <t xml:space="preserve">4.52570819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53297185897827</t>
   </si>
   <si>
     <t xml:space="preserve">4.67825984954834</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">4.67099475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64557027816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65283536911011</t>
+    <t xml:space="preserve">4.64556932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75090360641479</t>
+    <t xml:space="preserve">4.75090312957764</t>
   </si>
   <si>
     <t xml:space="preserve">4.76179933547974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7254786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68552446365356</t>
+    <t xml:space="preserve">4.72547817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68552398681641</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911024093628</t>
@@ -1337,46 +1337,46 @@
     <t xml:space="preserve">4.83807563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8816614151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84897232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89255857467651</t>
+    <t xml:space="preserve">4.88166236877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897327423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798448562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89255905151367</t>
   </si>
   <si>
     <t xml:space="preserve">4.95430612564087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9470419883728</t>
+    <t xml:space="preserve">4.94704151153564</t>
   </si>
   <si>
     <t xml:space="preserve">4.93977737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9325122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99062824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340944290161</t>
+    <t xml:space="preserve">4.93251276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99062776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340991973877</t>
   </si>
   <si>
     <t xml:space="preserve">4.86713266372681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7330756187439</t>
+    <t xml:space="preserve">4.73307609558105</t>
   </si>
   <si>
     <t xml:space="preserve">4.87888193130493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86018848419189</t>
+    <t xml:space="preserve">4.86018896102905</t>
   </si>
   <si>
     <t xml:space="preserve">4.82654094696045</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">4.49380493164062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62091732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699718475342</t>
+    <t xml:space="preserve">4.62091779708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699670791626</t>
   </si>
   <si>
     <t xml:space="preserve">4.63587188720703</t>
@@ -1406,22 +1406,22 @@
     <t xml:space="preserve">4.7218599319458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70690584182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979345321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75924587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83028030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93495988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644960403442</t>
+    <t xml:space="preserve">4.70690536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75924634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83027982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85644912719727</t>
   </si>
   <si>
     <t xml:space="preserve">4.8153247833252</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">4.94243812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91252994537354</t>
+    <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.91626691818237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90505218505859</t>
+    <t xml:space="preserve">4.90505170822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.88262033462524</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">4.96486902236938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03216409683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01720952987671</t>
+    <t xml:space="preserve">5.03216361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01721048355103</t>
   </si>
   <si>
     <t xml:space="preserve">5.13684558868408</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">5.05833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98356199264526</t>
+    <t xml:space="preserve">4.98356246948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.89757490158081</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">5.1293683052063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24900341033936</t>
+    <t xml:space="preserve">5.24900388717651</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
@@ -1478,10 +1478,10 @@
     <t xml:space="preserve">5.31629848480225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41350173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34246873855591</t>
+    <t xml:space="preserve">5.41350126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34246921539307</t>
   </si>
   <si>
     <t xml:space="preserve">5.09945917129517</t>
@@ -1490,67 +1490,67 @@
     <t xml:space="preserve">5.0134711265564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17797040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20040130615234</t>
+    <t xml:space="preserve">5.17796993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2004017829895</t>
   </si>
   <si>
     <t xml:space="preserve">5.23404932022095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25274181365967</t>
+    <t xml:space="preserve">5.25274229049683</t>
   </si>
   <si>
     <t xml:space="preserve">5.20787906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21535587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283315658569</t>
+    <t xml:space="preserve">5.21535634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283267974854</t>
   </si>
   <si>
     <t xml:space="preserve">5.19666290283203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11815214157104</t>
+    <t xml:space="preserve">5.1181526184082</t>
   </si>
   <si>
     <t xml:space="preserve">5.04338026046753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99851655960083</t>
+    <t xml:space="preserve">4.99851703643799</t>
   </si>
   <si>
     <t xml:space="preserve">5.11067533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17049264907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04711866378784</t>
+    <t xml:space="preserve">5.17049217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.047119140625</t>
   </si>
   <si>
     <t xml:space="preserve">5.11441421508789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06581163406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982358932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95739269256592</t>
+    <t xml:space="preserve">5.06581211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9573917388916</t>
   </si>
   <si>
     <t xml:space="preserve">5.03964138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05459594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076572418213</t>
+    <t xml:space="preserve">5.05459642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076667785645</t>
   </si>
   <si>
     <t xml:space="preserve">5.18544721603394</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">5.0957202911377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21161699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8863582611084</t>
+    <t xml:space="preserve">5.21161794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88635921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.92000675201416</t>
@@ -1571,34 +1571,34 @@
     <t xml:space="preserve">4.77420043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073606491089</t>
+    <t xml:space="preserve">4.7667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073511123657</t>
   </si>
   <si>
     <t xml:space="preserve">4.66951942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71064424514771</t>
+    <t xml:space="preserve">4.71064472198486</t>
   </si>
   <si>
     <t xml:space="preserve">4.67325782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68447351455688</t>
+    <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
     <t xml:space="preserve">4.62839555740356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56857681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58727025985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69568920135498</t>
+    <t xml:space="preserve">4.5685772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58726978302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568967819214</t>
   </si>
   <si>
     <t xml:space="preserve">4.56110000610352</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848642349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550746917725</t>
+    <t xml:space="preserve">4.61344003677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848546981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7555079460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.84523391723633</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">4.792893409729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86766576766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915548324585</t>
+    <t xml:space="preserve">4.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915500640869</t>
   </si>
   <si>
     <t xml:space="preserve">4.78167772293091</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">4.68821239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812105178833</t>
+    <t xml:space="preserve">4.71812057495117</t>
   </si>
   <si>
     <t xml:space="preserve">4.74055290222168</t>
@@ -1652,127 +1652,127 @@
     <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54988431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5237135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997518539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48632764816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903257369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46015787124634</t>
+    <t xml:space="preserve">4.54988384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52371406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46015739440918</t>
   </si>
   <si>
     <t xml:space="preserve">4.64334917068481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66204309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73681354522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86392736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730087280273</t>
+    <t xml:space="preserve">4.66204261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456533432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73681402206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86392688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730134963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.14806127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21909523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22657203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18918657302856</t>
+    <t xml:space="preserve">5.15927648544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21909427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22657108306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
     <t xml:space="preserve">5.15179967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20414066314697</t>
+    <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
     <t xml:space="preserve">5.37237739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620666503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09018993377686</t>
+    <t xml:space="preserve">5.16675424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09019041061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.87335062026978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79483985900879</t>
+    <t xml:space="preserve">5.79484033584595</t>
   </si>
   <si>
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353282928467</t>
+    <t xml:space="preserve">5.81353330612183</t>
   </si>
   <si>
     <t xml:space="preserve">5.79110145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80231809616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75745391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474851608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87708902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924779891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167917251587</t>
+    <t xml:space="preserve">5.80231761932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75745439529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8770899772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195272445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167964935303</t>
   </si>
   <si>
     <t xml:space="preserve">6.02663421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96307802200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00794076919556</t>
+    <t xml:space="preserve">5.96307754516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00793981552124</t>
   </si>
   <si>
     <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93316841125488</t>
+    <t xml:space="preserve">5.93316793441772</t>
   </si>
   <si>
     <t xml:space="preserve">5.90699815750122</t>
@@ -1781,46 +1781,46 @@
     <t xml:space="preserve">5.94064569473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07897424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93690729141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95933771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89952087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89578247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88082838058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94812297821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95559978485107</t>
+    <t xml:space="preserve">6.0789737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9369068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95933818817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8995213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89578342437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8808274269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94812250137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95560026168823</t>
   </si>
   <si>
     <t xml:space="preserve">5.97429275512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91362047195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84066104888916</t>
+    <t xml:space="preserve">6.02114152908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9136209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.840660572052</t>
   </si>
   <si>
     <t xml:space="preserve">5.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.694739818573</t>
+    <t xml:space="preserve">5.69474029541016</t>
   </si>
   <si>
     <t xml:space="preserve">5.71778059005737</t>
@@ -1829,31 +1829,31 @@
     <t xml:space="preserve">5.68322038650513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66402006149292</t>
+    <t xml:space="preserve">5.66401958465576</t>
   </si>
   <si>
     <t xml:space="preserve">5.66786050796509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78306007385254</t>
+    <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002073287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87522077560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82146072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74850130081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69858074188232</t>
+    <t xml:space="preserve">5.76002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87522125244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82146024703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74850082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69857978820801</t>
   </si>
   <si>
     <t xml:space="preserve">5.64482021331787</t>
@@ -1865,37 +1865,37 @@
     <t xml:space="preserve">5.77538061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72162008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81762027740479</t>
+    <t xml:space="preserve">5.72162055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81762075424194</t>
   </si>
   <si>
     <t xml:space="preserve">5.78690004348755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95970106124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05570125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28226232528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474222183228</t>
+    <t xml:space="preserve">5.95970058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05570220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28226280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474174499512</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12866163253784</t>
+    <t xml:space="preserve">6.12866115570068</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19394207000732</t>
+    <t xml:space="preserve">6.19394159317017</t>
   </si>
   <si>
     <t xml:space="preserve">6.06722164154053</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">6.29378175735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39746236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43586301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46274280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210344314575</t>
+    <t xml:space="preserve">6.39746189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43586206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46274375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210296630859</t>
   </si>
   <si>
     <t xml:space="preserve">6.35522222518921</t>
@@ -1934,28 +1934,28 @@
     <t xml:space="preserve">6.44738340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52802276611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58946371078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018299102783</t>
+    <t xml:space="preserve">6.5280237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954410552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5894627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018346786499</t>
   </si>
   <si>
     <t xml:space="preserve">6.64322328567505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62786388397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626405715942</t>
+    <t xml:space="preserve">6.62786340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626358032227</t>
   </si>
   <si>
     <t xml:space="preserve">6.80450391769409</t>
@@ -1970,94 +1970,94 @@
     <t xml:space="preserve">6.78914403915405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76610374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114442825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882532119751</t>
+    <t xml:space="preserve">6.76610469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114538192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882389068604</t>
   </si>
   <si>
     <t xml:space="preserve">6.88514471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68930339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338359832764</t>
+    <t xml:space="preserve">6.68930387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554430007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634397506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338312149048</t>
   </si>
   <si>
     <t xml:space="preserve">6.79298400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14626502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570558547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0464243888855</t>
+    <t xml:space="preserve">7.14626598358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642534255981</t>
   </si>
   <si>
     <t xml:space="preserve">7.0080246925354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99266481399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786485671997</t>
+    <t xml:space="preserve">6.99266529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10402584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786628723145</t>
   </si>
   <si>
     <t xml:space="preserve">7.06178522109985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07330465316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714605331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034475326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96578502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426464080811</t>
+    <t xml:space="preserve">7.07330513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96578454971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426511764526</t>
   </si>
   <si>
     <t xml:space="preserve">7.02722501754761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186561584473</t>
+    <t xml:space="preserve">7.01186513900757</t>
   </si>
   <si>
     <t xml:space="preserve">6.94274473190308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04258489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634494781494</t>
+    <t xml:space="preserve">7.04258441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634447097778</t>
   </si>
   <si>
     <t xml:space="preserve">6.7507438659668</t>
@@ -2069,88 +2069,88 @@
     <t xml:space="preserve">6.90434455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0233850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346448898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15778541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16546535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602575302124</t>
+    <t xml:space="preserve">7.02338457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346591949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15778493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16546440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2960262298584</t>
   </si>
   <si>
     <t xml:space="preserve">7.1693058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3113865852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850517272949</t>
+    <t xml:space="preserve">7.31138610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682542800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850564956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.12706470489502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17698669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19234561920166</t>
+    <t xml:space="preserve">7.17698574066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1923451423645</t>
   </si>
   <si>
     <t xml:space="preserve">7.15010499954224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26914644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210538864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43426513671875</t>
+    <t xml:space="preserve">7.26914548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210681915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43426656723022</t>
   </si>
   <si>
     <t xml:space="preserve">7.45730638504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34978628158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658662796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11938571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22306537628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11554622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06562471389771</t>
+    <t xml:space="preserve">7.34978580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2806658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22306632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11554574966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06562519073486</t>
   </si>
   <si>
     <t xml:space="preserve">7.08866500854492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98498439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77378416061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066299438477</t>
+    <t xml:space="preserve">6.98498487472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77378368377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066347122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.77762413024902</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">6.92738485336304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90818452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91202449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290409088135</t>
+    <t xml:space="preserve">6.90818405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91202402114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
     <t xml:space="preserve">6.86210441589355</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">7.05794429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75842380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218385696411</t>
+    <t xml:space="preserve">6.75842332839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218481063843</t>
   </si>
   <si>
     <t xml:space="preserve">6.81602430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87746429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306392669678</t>
+    <t xml:space="preserve">6.87746381759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306344985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.69314384460449</t>
@@ -2210,100 +2210,100 @@
     <t xml:space="preserve">6.89282417297363</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79682397842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466375350952</t>
+    <t xml:space="preserve">6.79682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466279983521</t>
   </si>
   <si>
     <t xml:space="preserve">6.67778396606445</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314577102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11170625686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2576265335083</t>
+    <t xml:space="preserve">6.7853045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7353835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386695861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410528182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20770597457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002508163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1117057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762557983398</t>
   </si>
   <si>
     <t xml:space="preserve">7.29986619949341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33826589584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786725997925</t>
+    <t xml:space="preserve">7.33826684951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786773681641</t>
   </si>
   <si>
     <t xml:space="preserve">7.56098699569702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6646671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418714523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17922878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434698104858</t>
+    <t xml:space="preserve">7.66466569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362770080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418809890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8643479347229</t>
   </si>
   <si>
     <t xml:space="preserve">7.77218723297119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858701705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002700805664</t>
+    <t xml:space="preserve">7.73378610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186754226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6800274848938</t>
   </si>
   <si>
     <t xml:space="preserve">7.3689866065979</t>
@@ -2312,37 +2312,37 @@
     <t xml:space="preserve">6.91970539093018</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89442110061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27458190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77154064178467</t>
+    <t xml:space="preserve">5.8944206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.274582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77154016494751</t>
   </si>
   <si>
     <t xml:space="preserve">6.26690244674683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922588348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018636703491</t>
+    <t xml:space="preserve">6.33602285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394449234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018684387207</t>
   </si>
   <si>
     <t xml:space="preserve">7.59938764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78754901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2717809677124</t>
+    <t xml:space="preserve">7.78754758834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27178001403809</t>
   </si>
   <si>
     <t xml:space="preserve">7.88021755218506</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">7.57022905349731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64364814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718223571777</t>
+    <t xml:space="preserve">7.64364719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718128204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.35335636138916</t>
@@ -2366,37 +2366,37 @@
     <t xml:space="preserve">9.03043460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95701599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70413112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75307750701904</t>
+    <t xml:space="preserve">8.95701694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70413208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75307655334473</t>
   </si>
   <si>
     <t xml:space="preserve">7.99442386627197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8312726020813</t>
+    <t xml:space="preserve">7.83127212524414</t>
   </si>
   <si>
     <t xml:space="preserve">7.74969625473022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81903457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79864120483398</t>
+    <t xml:space="preserve">7.81903553009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79864263534546</t>
   </si>
   <si>
     <t xml:space="preserve">7.87613821029663</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80679988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68035650253296</t>
+    <t xml:space="preserve">7.80679893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035745620728</t>
   </si>
   <si>
     <t xml:space="preserve">7.5090479850769</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">7.50496912002563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70483016967773</t>
+    <t xml:space="preserve">7.70482921600342</t>
   </si>
   <si>
     <t xml:space="preserve">7.75377559661865</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">7.89653301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94547748565674</t>
+    <t xml:space="preserve">7.94547843933105</t>
   </si>
   <si>
     <t xml:space="preserve">7.8557448387146</t>
@@ -5517,6 +5517,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.6850004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54500007629395</t>
   </si>
 </sst>
 </file>
@@ -70829,7 +70832,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6931365741</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>1330901</v>
@@ -70850,6 +70853,32 @@
         <v>1834</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.69125</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>2108341</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>9.70499992370605</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>9.52999973297119</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>9.70499992370605</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>9.54500007629395</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="1836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="1837">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433905601501</t>
+    <t xml:space="preserve">3.42433834075928</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
@@ -47,61 +47,61 @@
     <t xml:space="preserve">3.46296882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4560706615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986699104309</t>
+    <t xml:space="preserve">3.45607137680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986746788025</t>
   </si>
   <si>
     <t xml:space="preserve">3.47331619262695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39812421798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845590591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34707713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981520652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637146949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324920654297</t>
+    <t xml:space="preserve">3.39812445640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3470766544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981568336487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2863712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324896812439</t>
   </si>
   <si>
     <t xml:space="preserve">3.03803086280823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13874673843384</t>
+    <t xml:space="preserve">3.13874697685242</t>
   </si>
   <si>
     <t xml:space="preserve">3.14288568496704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10425519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16496062278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736701011658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14564490318298</t>
+    <t xml:space="preserve">3.10425543785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16495990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564514160156</t>
   </si>
   <si>
     <t xml:space="preserve">3.19945192337036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30430698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119469642639</t>
+    <t xml:space="preserve">3.30430722236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119517326355</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222183227539</t>
@@ -110,148 +110,148 @@
     <t xml:space="preserve">3.20911026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2077305316925</t>
+    <t xml:space="preserve">3.20773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631920814514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06700396537781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00077962875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00216007232666</t>
+    <t xml:space="preserve">3.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00077986717224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00215935707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.99802088737488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0283727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1111536026001</t>
+    <t xml:space="preserve">3.02837371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115407943726</t>
   </si>
   <si>
     <t xml:space="preserve">3.18151664733887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13046860694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14150595664978</t>
+    <t xml:space="preserve">3.13046932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14150619506836</t>
   </si>
   <si>
     <t xml:space="preserve">3.12495040893555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11805176734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808240890503</t>
+    <t xml:space="preserve">3.11805200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808264732361</t>
   </si>
   <si>
     <t xml:space="preserve">3.1732382774353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19531273841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18703579902649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09321761131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013691902161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255375862122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427538871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636101722717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20635008811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19807291030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10563445091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906797409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05458664894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03941082954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00491905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05182766914368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422431945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05044770240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595640182495</t>
+    <t xml:space="preserve">3.19531345367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18703484535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09321808815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20635080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19807267189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10563492774963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906868934631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0545871257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03941059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00491881370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0518274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422408103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05044794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595664024353</t>
   </si>
   <si>
     <t xml:space="preserve">3.01457619667053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02147459983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767827033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873604774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0876989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978361129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05596685409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838345527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319718360901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02975273132324</t>
+    <t xml:space="preserve">3.02147483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629878044128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561402320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08769917488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0559663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319670677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02975344657898</t>
   </si>
   <si>
     <t xml:space="preserve">3.01871562004089</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">2.95249176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94421362876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593525886536</t>
+    <t xml:space="preserve">2.94421339035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869519233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593549728394</t>
   </si>
   <si>
     <t xml:space="preserve">3.02235913276672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02659225463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99837207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426222801208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97861814498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0689218044281</t>
+    <t xml:space="preserve">3.02659201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99837231636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426198959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9913170337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97861790657043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610035896301</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">3.01389312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02094793319702</t>
+    <t xml:space="preserve">3.0209481716156</t>
   </si>
   <si>
     <t xml:space="preserve">3.00683832168579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03929090499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671481132507</t>
+    <t xml:space="preserve">3.03929114341736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978280067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96450853347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714911460876</t>
+    <t xml:space="preserve">2.99978303909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9645082950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714935302734</t>
   </si>
   <si>
     <t xml:space="preserve">2.80083227157593</t>
@@ -329,43 +329,43 @@
     <t xml:space="preserve">2.87843704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93205547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702631950378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089010238647</t>
+    <t xml:space="preserve">2.93205499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702584266663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089034080505</t>
   </si>
   <si>
     <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61034798622131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67525339126587</t>
+    <t xml:space="preserve">2.61034727096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67525315284729</t>
   </si>
   <si>
     <t xml:space="preserve">2.71899437904358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7965989112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79518842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162782669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610725402832</t>
+    <t xml:space="preserve">2.79659938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79518818855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162806510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8361074924469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87279343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94475412368774</t>
+    <t xml:space="preserve">2.94475364685059</t>
   </si>
   <si>
     <t xml:space="preserve">2.97438526153564</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">3.02518081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04211282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597708702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364706039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07033348083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05481219291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03788042068481</t>
+    <t xml:space="preserve">3.04211258888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597684860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364729881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07033276557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05481195449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03788018226624</t>
   </si>
   <si>
     <t xml:space="preserve">3.05199027061462</t>
@@ -404,43 +404,43 @@
     <t xml:space="preserve">3.16204786300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1549928188324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14088273048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10843014717102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149765968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241744041443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947248458862</t>
+    <t xml:space="preserve">3.15499305725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14088296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793753623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10842990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947176933289</t>
   </si>
   <si>
     <t xml:space="preserve">3.15075993537903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10419678688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444309234619</t>
+    <t xml:space="preserve">3.10419702529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444333076477</t>
   </si>
   <si>
     <t xml:space="preserve">3.02800297737122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0124819278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02376937866211</t>
+    <t xml:space="preserve">3.01248216629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02376961708069</t>
   </si>
   <si>
     <t xml:space="preserve">3.0717442035675</t>
@@ -449,109 +449,109 @@
     <t xml:space="preserve">3.06045579910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03646922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0900866985321</t>
+    <t xml:space="preserve">3.03646874427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008693695068</t>
   </si>
   <si>
     <t xml:space="preserve">3.19732284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21002173423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18462371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21284365653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707653999329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27775001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861077308655</t>
+    <t xml:space="preserve">3.21002197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18462419509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2128438949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707677841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27774977684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.273517370224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130990028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861101150513</t>
   </si>
   <si>
     <t xml:space="preserve">3.19873380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18180227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15358185768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217065811157</t>
+    <t xml:space="preserve">3.18180251121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15358138084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217089653015</t>
   </si>
   <si>
     <t xml:space="preserve">3.16628074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12536215782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125159263611</t>
+    <t xml:space="preserve">3.1253616809845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125183105469</t>
   </si>
   <si>
     <t xml:space="preserve">3.08726501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09714150428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11548495292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867621421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07738828659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06186676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696135520935</t>
+    <t xml:space="preserve">3.09714245796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11548471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.077388048172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06186699867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696111679077</t>
   </si>
   <si>
     <t xml:space="preserve">2.92923307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95321989059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180940628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93911027908325</t>
+    <t xml:space="preserve">2.95322012901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93911004066467</t>
   </si>
   <si>
     <t xml:space="preserve">2.92076706886292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95886373519897</t>
+    <t xml:space="preserve">2.95886421203613</t>
   </si>
   <si>
     <t xml:space="preserve">2.92782211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98002886772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493498802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622291564941</t>
+    <t xml:space="preserve">2.98002910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622243881226</t>
   </si>
   <si>
     <t xml:space="preserve">3.01953744888306</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">3.0407018661499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01812601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96309685707092</t>
+    <t xml:space="preserve">3.0181257724762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96309733390808</t>
   </si>
   <si>
     <t xml:space="preserve">2.92641115188599</t>
@@ -578,46 +578,46 @@
     <t xml:space="preserve">2.98849534988403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87138247489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85727262496948</t>
+    <t xml:space="preserve">2.87138223648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85727190971375</t>
   </si>
   <si>
     <t xml:space="preserve">2.86856007575989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92358922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88690328598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89819073677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034037590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84457349777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85021758079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78390049934387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377746582031</t>
+    <t xml:space="preserve">2.92358946800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604205131531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88690304756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89819121360779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84033989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85021734237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78390073776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377722740173</t>
   </si>
   <si>
     <t xml:space="preserve">2.82340812683105</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">2.75568032264709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76132464408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80929827690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254713058472</t>
+    <t xml:space="preserve">2.76132440567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8092987537384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89254689216614</t>
   </si>
   <si>
     <t xml:space="preserve">2.893958568573</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">2.86009407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90665745735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9123010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94052124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09432053565979</t>
+    <t xml:space="preserve">2.90665698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831400871277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91230154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94052147865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09432005882263</t>
   </si>
   <si>
     <t xml:space="preserve">3.08021020889282</t>
@@ -665,64 +665,64 @@
     <t xml:space="preserve">3.08303165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10560822486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585405349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523840904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511632919312</t>
+    <t xml:space="preserve">3.10560774803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585429191589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511609077454</t>
   </si>
   <si>
     <t xml:space="preserve">3.13806104660034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16063737869263</t>
+    <t xml:space="preserve">3.16063690185547</t>
   </si>
   <si>
     <t xml:space="preserve">3.17051386833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20437788963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253999710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573101997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278582572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0675106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1183066368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13664984703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07456564903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10701870918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.098552942276</t>
+    <t xml:space="preserve">3.2043776512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591212272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253975868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290909767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06751108169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11830735206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17898011207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13665008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07456612586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855341911316</t>
   </si>
   <si>
     <t xml:space="preserve">3.24529647827148</t>
@@ -731,58 +731,58 @@
     <t xml:space="preserve">3.26646208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25376272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094056129456</t>
+    <t xml:space="preserve">3.25376296043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094079971313</t>
   </si>
   <si>
     <t xml:space="preserve">3.29891538619995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31443572044373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357496261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228727340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651968002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44565844535828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41461706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283699989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40756177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4005069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657727241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338696479797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160666465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47811126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798871040344</t>
+    <t xml:space="preserve">3.31443548202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357520103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3722870349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651991844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4456582069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41461634635925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4075620174408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40050673484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338648796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105669975281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47811150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798847198486</t>
   </si>
   <si>
     <t xml:space="preserve">3.52185273170471</t>
@@ -791,43 +791,43 @@
     <t xml:space="preserve">3.5063316822052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49222087860107</t>
+    <t xml:space="preserve">3.49222135543823</t>
   </si>
   <si>
     <t xml:space="preserve">3.5627715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5345516204834</t>
+    <t xml:space="preserve">3.53455233573914</t>
   </si>
   <si>
     <t xml:space="preserve">3.52749681472778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54866147041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099149703979</t>
+    <t xml:space="preserve">3.54866170883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056504249573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099197387695</t>
   </si>
   <si>
     <t xml:space="preserve">3.61568427085876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58393621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209951400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924439430237</t>
+    <t xml:space="preserve">3.58393597602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924415588379</t>
   </si>
   <si>
     <t xml:space="preserve">3.62273931503296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65095901489258</t>
+    <t xml:space="preserve">3.65095925331116</t>
   </si>
   <si>
     <t xml:space="preserve">3.66154170036316</t>
@@ -836,142 +836,142 @@
     <t xml:space="preserve">3.66506886482239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61921191215515</t>
+    <t xml:space="preserve">3.61921143531799</t>
   </si>
   <si>
     <t xml:space="preserve">3.63332152366638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59804677963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73752284049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68667197227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299361228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7193615436554</t>
+    <t xml:space="preserve">3.59804654121399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7375226020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6866717338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299408912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71936130523682</t>
   </si>
   <si>
     <t xml:space="preserve">3.70483303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66124677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195972442627</t>
+    <t xml:space="preserve">3.66124701499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195924758911</t>
   </si>
   <si>
     <t xml:space="preserve">3.82832717895508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81379842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285616874695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85012102127075</t>
+    <t xml:space="preserve">3.81379890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285593032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85012030601501</t>
   </si>
   <si>
     <t xml:space="preserve">3.88644218444824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86101698875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469582557678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922386169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451161384583</t>
+    <t xml:space="preserve">3.86101722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8464879989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469534873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8392231464386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451137542725</t>
   </si>
   <si>
     <t xml:space="preserve">3.90097093582153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94455790519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639684677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016683578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68303942680359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65761423110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6133017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201905250549</t>
+    <t xml:space="preserve">3.94455718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087954521179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92639636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823531150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913175582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016635894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68303966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65761399269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330151557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201833724976</t>
   </si>
   <si>
     <t xml:space="preserve">3.60313177108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59150886535645</t>
+    <t xml:space="preserve">3.59150862693787</t>
   </si>
   <si>
     <t xml:space="preserve">3.62492418289185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67214298248291</t>
+    <t xml:space="preserve">3.67214345932007</t>
   </si>
   <si>
     <t xml:space="preserve">3.63073635101318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69030380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218903541565</t>
+    <t xml:space="preserve">3.69030356407166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218951225281</t>
   </si>
   <si>
     <t xml:space="preserve">3.65034985542297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71572947502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7266263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191367149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96635055541992</t>
+    <t xml:space="preserve">3.71572971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662615776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9663507938385</t>
   </si>
   <si>
     <t xml:space="preserve">3.93366050720215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95908546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998286247253</t>
+    <t xml:space="preserve">3.9590859413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998262405396</t>
   </si>
   <si>
     <t xml:space="preserve">4.01356840133667</t>
@@ -980,136 +980,136 @@
     <t xml:space="preserve">4.05352306365967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989147186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07894802093506</t>
+    <t xml:space="preserve">4.04989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894849777222</t>
   </si>
   <si>
     <t xml:space="preserve">4.00267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95182156562805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91549968719482</t>
+    <t xml:space="preserve">3.95182180404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9154999256134</t>
   </si>
   <si>
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540829658508</t>
+    <t xml:space="preserve">3.99540781974792</t>
   </si>
   <si>
     <t xml:space="preserve">3.99177598953247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02446603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04262638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10437345504761</t>
+    <t xml:space="preserve">4.02446556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04262733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10437393188477</t>
   </si>
   <si>
     <t xml:space="preserve">3.96271872520447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86464953422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89733862876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98814392089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002867698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01720190048218</t>
+    <t xml:space="preserve">3.86464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89733910560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9881432056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9554545879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002820014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01720142364502</t>
   </si>
   <si>
     <t xml:space="preserve">3.88280987739563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07531595230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0680513381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14796018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625844955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06078815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11527013778687</t>
+    <t xml:space="preserve">4.07531690597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06805181503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14795970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06078720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11526966094971</t>
   </si>
   <si>
     <t xml:space="preserve">4.1080060005188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12253475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18064975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18791437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16612100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338466644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09710884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14069557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979888916016</t>
+    <t xml:space="preserve">4.12253522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18065023422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18791389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16612148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09710931777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14069604873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979984283447</t>
   </si>
   <si>
     <t xml:space="preserve">4.24602890014648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22060346603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26055765151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21697187423706</t>
+    <t xml:space="preserve">4.22060394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26055812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2169713973999</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26419019699097</t>
+    <t xml:space="preserve">4.26418972015381</t>
   </si>
   <si>
     <t xml:space="preserve">4.27508687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24239778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701768875122</t>
+    <t xml:space="preserve">4.24239683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17701721191406</t>
   </si>
   <si>
     <t xml:space="preserve">4.08984470367432</t>
@@ -1121,28 +1121,28 @@
     <t xml:space="preserve">4.29687976837158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42763900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51481103897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54023599624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60198402404785</t>
+    <t xml:space="preserve">4.42763805389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51481151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54023694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60198354721069</t>
   </si>
   <si>
     <t xml:space="preserve">4.59835147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72184562683105</t>
+    <t xml:space="preserve">4.72184610366821</t>
   </si>
   <si>
     <t xml:space="preserve">4.56929397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56202983856201</t>
+    <t xml:space="preserve">4.56202936172485</t>
   </si>
   <si>
     <t xml:space="preserve">4.62014436721802</t>
@@ -1154,34 +1154,34 @@
     <t xml:space="preserve">4.60924816131592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4893856048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844358444214</t>
+    <t xml:space="preserve">4.48938608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844310760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207565307617</t>
+    <t xml:space="preserve">4.52207469940186</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49301767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50391483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665021896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46032762527466</t>
+    <t xml:space="preserve">4.49301862716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50391435623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49664974212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46032857894897</t>
   </si>
   <si>
     <t xml:space="preserve">4.45306396484375</t>
@@ -1190,28 +1190,28 @@
     <t xml:space="preserve">4.46759271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47848987579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53660345077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853521347046</t>
+    <t xml:space="preserve">4.47848892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750108718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5366039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853569030762</t>
   </si>
   <si>
     <t xml:space="preserve">4.37315559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39131641387939</t>
+    <t xml:space="preserve">4.39131689071655</t>
   </si>
   <si>
     <t xml:space="preserve">4.42037439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29324722290039</t>
+    <t xml:space="preserve">4.29324769973755</t>
   </si>
   <si>
     <t xml:space="preserve">4.40947771072388</t>
@@ -1220,127 +1220,127 @@
     <t xml:space="preserve">4.51117849349976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42400693893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28235101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20607471466064</t>
+    <t xml:space="preserve">4.42400598526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140851974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28235054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2060751914978</t>
   </si>
   <si>
     <t xml:space="preserve">4.12616682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23150062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432716369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94092559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97724747657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15522480010986</t>
+    <t xml:space="preserve">4.23150110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361493110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94092488288879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724771499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258008956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15522432327271</t>
   </si>
   <si>
     <t xml:space="preserve">4.169753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44580030441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584516525269</t>
+    <t xml:space="preserve">4.44579935073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40584564208984</t>
   </si>
   <si>
     <t xml:space="preserve">4.4167423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59108686447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55113363265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655763626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5293402671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52570819854736</t>
+    <t xml:space="preserve">4.59108734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61288022994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55113315582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5765585899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52933979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52570772171021</t>
   </si>
   <si>
     <t xml:space="preserve">4.53297185897827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67825984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6492018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67099475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64556932449341</t>
+    <t xml:space="preserve">4.67825889587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920282363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67099523544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64556980133057</t>
   </si>
   <si>
     <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75816774368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75090312957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76179933547974</t>
+    <t xml:space="preserve">4.75816822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75090360641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76180028915405</t>
   </si>
   <si>
     <t xml:space="preserve">4.72547817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68552398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911024093628</t>
+    <t xml:space="preserve">4.68552303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911071777344</t>
   </si>
   <si>
     <t xml:space="preserve">4.65646648406982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84534025192261</t>
+    <t xml:space="preserve">4.84534072875977</t>
   </si>
   <si>
     <t xml:space="preserve">4.81265115737915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81991529464722</t>
+    <t xml:space="preserve">4.81991481781006</t>
   </si>
   <si>
     <t xml:space="preserve">4.83807563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84897327423096</t>
+    <t xml:space="preserve">4.88166189193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897232055664</t>
   </si>
   <si>
     <t xml:space="preserve">4.91798448562622</t>
@@ -1349,31 +1349,31 @@
     <t xml:space="preserve">4.89255905151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95430612564087</t>
+    <t xml:space="preserve">4.95430660247803</t>
   </si>
   <si>
     <t xml:space="preserve">4.94704151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93977737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93251276016235</t>
+    <t xml:space="preserve">4.93977689743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93251323699951</t>
   </si>
   <si>
     <t xml:space="preserve">4.99062776565552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94340991973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713266372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73307609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888193130493</t>
+    <t xml:space="preserve">4.94340896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713314056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7330756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888145446777</t>
   </si>
   <si>
     <t xml:space="preserve">4.86018896102905</t>
@@ -1382,94 +1382,94 @@
     <t xml:space="preserve">4.82654094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75176906585693</t>
+    <t xml:space="preserve">4.75176858901978</t>
   </si>
   <si>
     <t xml:space="preserve">4.6508264541626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49380493164062</t>
+    <t xml:space="preserve">4.49380540847778</t>
   </si>
   <si>
     <t xml:space="preserve">4.62091779708862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67699670791626</t>
+    <t xml:space="preserve">4.67699766159058</t>
   </si>
   <si>
     <t xml:space="preserve">4.63587188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74803018569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7218599319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690536499023</t>
+    <t xml:space="preserve">4.74803066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690584182739</t>
   </si>
   <si>
     <t xml:space="preserve">4.57979297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75924634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83027982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85644912719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8153247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94243812561035</t>
+    <t xml:space="preserve">4.75924587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83027935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93496084213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85645008087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81532526016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94243860244751</t>
   </si>
   <si>
     <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90505170822144</t>
+    <t xml:space="preserve">4.91626739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90505218505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.88262033462524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93869924545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486902236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01721048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13684558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05833435058594</t>
+    <t xml:space="preserve">4.93869972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01720952987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13684511184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05833387374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.98356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89757490158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1293683052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24900388717651</t>
+    <t xml:space="preserve">4.89757442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12936878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2490029335022</t>
   </si>
   <si>
     <t xml:space="preserve">5.37985467910767</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">5.31629848480225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41350126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34246921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09945917129517</t>
+    <t xml:space="preserve">5.41350173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34246873855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09945964813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.0134711265564</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">5.23404932022095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25274229049683</t>
+    <t xml:space="preserve">5.25274181365967</t>
   </si>
   <si>
     <t xml:space="preserve">5.20787906646729</t>
@@ -1508,121 +1508,121 @@
     <t xml:space="preserve">5.21535634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22283267974854</t>
+    <t xml:space="preserve">5.22283315658569</t>
   </si>
   <si>
     <t xml:space="preserve">5.19666290283203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1181526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04338026046753</t>
+    <t xml:space="preserve">5.11815214157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04337978363037</t>
   </si>
   <si>
     <t xml:space="preserve">4.99851703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11067533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17049217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11441421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982406616211</t>
+    <t xml:space="preserve">5.1106743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17049312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04711866378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11441326141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581163406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982311248779</t>
   </si>
   <si>
     <t xml:space="preserve">4.9573917388916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03964138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05459642410278</t>
+    <t xml:space="preserve">5.03964185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05459547042847</t>
   </si>
   <si>
     <t xml:space="preserve">5.08076667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18544721603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0957202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21161794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88635921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66951942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71064472198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67325782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68447399139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5685772895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58726978302002</t>
+    <t xml:space="preserve">5.18544673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09572076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2116174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8863582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92000579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77420091629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073606491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71064424514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67325830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68447351455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56857776641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58727025985718</t>
   </si>
   <si>
     <t xml:space="preserve">4.69568967819214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56110000610352</t>
+    <t xml:space="preserve">4.56109952926636</t>
   </si>
   <si>
     <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344003677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848546981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7555079460144</t>
+    <t xml:space="preserve">4.613440990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.792893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766529083252</t>
+    <t xml:space="preserve">4.79289293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766576766968</t>
   </si>
   <si>
     <t xml:space="preserve">4.78915500640869</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">4.78167772293091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7779393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87140464782715</t>
+    <t xml:space="preserve">4.77793884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87140417098999</t>
   </si>
   <si>
     <t xml:space="preserve">4.83775663375854</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">4.68821239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812057495117</t>
+    <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74055290222168</t>
@@ -1652,19 +1652,19 @@
     <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54988384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52371406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903305053711</t>
+    <t xml:space="preserve">4.54988431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52371454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997566223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48632764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903257369995</t>
   </si>
   <si>
     <t xml:space="preserve">4.46015739440918</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">4.64334917068481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66204261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456533432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73681402206421</t>
+    <t xml:space="preserve">4.66204214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298475265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73681449890137</t>
   </si>
   <si>
     <t xml:space="preserve">4.86392688751221</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">5.14806127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927648544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21909427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22657108306885</t>
+    <t xml:space="preserve">5.15927696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21909475326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22657155990601</t>
   </si>
   <si>
     <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15179967880249</t>
+    <t xml:space="preserve">5.15179920196533</t>
   </si>
   <si>
     <t xml:space="preserve">5.20414018630981</t>
@@ -1724,79 +1724,79 @@
     <t xml:space="preserve">6.09019041061401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87335062026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79484033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7611927986145</t>
+    <t xml:space="preserve">5.87335109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79483985900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76119232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.81353330612183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79110145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75745439529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82474899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8770899772644</t>
+    <t xml:space="preserve">5.79110097885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75745391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82474946975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87708950042725</t>
   </si>
   <si>
     <t xml:space="preserve">5.92195272445679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98924827575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02663421630859</t>
+    <t xml:space="preserve">5.98924779891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02663373947144</t>
   </si>
   <si>
     <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00793981552124</t>
+    <t xml:space="preserve">6.00794076919556</t>
   </si>
   <si>
     <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93316793441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699815750122</t>
+    <t xml:space="preserve">5.93316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699863433838</t>
   </si>
   <si>
     <t xml:space="preserve">5.94064569473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0789737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9369068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95933818817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8995213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89578342437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8808274269104</t>
+    <t xml:space="preserve">6.07897472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93690729141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95933866500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89952087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89578247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88082838058472</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812250137329</t>
@@ -1814,46 +1814,46 @@
     <t xml:space="preserve">5.9136209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.840660572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75234031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69474029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778059005737</t>
+    <t xml:space="preserve">5.84066152572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7523398399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.694739818573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778011322021</t>
   </si>
   <si>
     <t xml:space="preserve">5.68322038650513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66401958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66786050796509</t>
+    <t xml:space="preserve">5.66402006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66786003112793</t>
   </si>
   <si>
     <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70626020431519</t>
+    <t xml:space="preserve">5.70626068115234</t>
   </si>
   <si>
     <t xml:space="preserve">5.76002025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87522125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82146024703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74850082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69857978820801</t>
+    <t xml:space="preserve">5.87522077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82146072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74850034713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69858074188232</t>
   </si>
   <si>
     <t xml:space="preserve">5.64482021331787</t>
@@ -1862,73 +1862,73 @@
     <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77538061141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72162055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81762075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78690004348755</t>
+    <t xml:space="preserve">5.77537965774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72161960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81762027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05570220947266</t>
+    <t xml:space="preserve">6.0557017326355</t>
   </si>
   <si>
     <t xml:space="preserve">6.28226280212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17474174499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09026145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12866115570068</t>
+    <t xml:space="preserve">6.17474222183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09026098251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128662109375</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19394159317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06722164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10178136825562</t>
+    <t xml:space="preserve">6.19394207000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06722211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10178184509277</t>
   </si>
   <si>
     <t xml:space="preserve">6.25154256820679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17090177536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1670618057251</t>
+    <t xml:space="preserve">6.17090225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16706228256226</t>
   </si>
   <si>
     <t xml:space="preserve">6.29378175735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39746189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43586206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46274375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35522222518921</t>
+    <t xml:space="preserve">6.39746284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43586301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46274280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210248947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35522174835205</t>
   </si>
   <si>
     <t xml:space="preserve">6.44738340377808</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">6.5280237197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53954410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5894627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322328567505</t>
+    <t xml:space="preserve">6.53954315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410383224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58946323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018299102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322423934937</t>
   </si>
   <si>
     <t xml:space="preserve">6.62786340713501</t>
@@ -1964,58 +1964,58 @@
     <t xml:space="preserve">6.83138513565063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83522415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78914403915405</t>
+    <t xml:space="preserve">6.83522367477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78914451599121</t>
   </si>
   <si>
     <t xml:space="preserve">6.76610469818115</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98114538192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882389068604</t>
+    <t xml:space="preserve">6.98114442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">6.88514471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68930387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554430007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634397506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338312149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026531219482</t>
+    <t xml:space="preserve">6.68930339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298448562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026483535767</t>
   </si>
   <si>
     <t xml:space="preserve">7.06946563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642534255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0080246925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99266529083252</t>
+    <t xml:space="preserve">7.04642629623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9926643371582</t>
   </si>
   <si>
     <t xml:space="preserve">7.10402584075928</t>
@@ -2024,43 +2024,43 @@
     <t xml:space="preserve">7.18082523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10786628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178522109985</t>
+    <t xml:space="preserve">7.10786533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0617847442627</t>
   </si>
   <si>
     <t xml:space="preserve">7.07330513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96578454971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426511764526</t>
+    <t xml:space="preserve">7.07714557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034475326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96578502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
     <t xml:space="preserve">7.02722501754761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186513900757</t>
+    <t xml:space="preserve">7.01186561584473</t>
   </si>
   <si>
     <t xml:space="preserve">6.94274473190308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7507438659668</t>
+    <t xml:space="preserve">7.04258489608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074434280396</t>
   </si>
   <si>
     <t xml:space="preserve">6.93506479263306</t>
@@ -2069,76 +2069,76 @@
     <t xml:space="preserve">6.90434455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02338457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346591949463</t>
+    <t xml:space="preserve">7.02338552474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346496582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.15778493881226</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546440124512</t>
+    <t xml:space="preserve">7.16546535491943</t>
   </si>
   <si>
     <t xml:space="preserve">7.2960262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850564956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706470489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17698574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1923451423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010499954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914548873901</t>
+    <t xml:space="preserve">7.16930532455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850612640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706613540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698526382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19234561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914644241333</t>
   </si>
   <si>
     <t xml:space="preserve">7.34210681915283</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43426656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730638504028</t>
+    <t xml:space="preserve">7.43426561355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730590820312</t>
   </si>
   <si>
     <t xml:space="preserve">7.34978580474854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42658615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2806658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11938524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22306632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11554574966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06562519073486</t>
+    <t xml:space="preserve">7.42658567428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11938571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2230658531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11554527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06562423706055</t>
   </si>
   <si>
     <t xml:space="preserve">7.08866500854492</t>
@@ -2150,169 +2150,169 @@
     <t xml:space="preserve">6.77378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066347122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92738485336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91202402114868</t>
+    <t xml:space="preserve">6.80066394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762365341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88898372650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92738580703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90818452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91202545166016</t>
   </si>
   <si>
     <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210441589355</t>
+    <t xml:space="preserve">6.86210489273071</t>
   </si>
   <si>
     <t xml:space="preserve">6.84674453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08098554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03106498718262</t>
+    <t xml:space="preserve">7.0809850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03106451034546</t>
   </si>
   <si>
     <t xml:space="preserve">7.05794429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75842332839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218481063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87746381759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74306344985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69314384460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72002363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89282417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466279983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7853045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7353835105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386695861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20770597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002508163452</t>
+    <t xml:space="preserve">6.75842475891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87746477127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74306440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69314432144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7200231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89282464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682493209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78530406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73538398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2077054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002555847168</t>
   </si>
   <si>
     <t xml:space="preserve">7.1117057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25762557983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826684951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098699569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466569900513</t>
+    <t xml:space="preserve">7.25762510299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786725997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466665267944</t>
   </si>
   <si>
     <t xml:space="preserve">7.83362770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96418809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258922576904</t>
+    <t xml:space="preserve">7.96418857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258827209473</t>
   </si>
   <si>
     <t xml:space="preserve">8.17922973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8643479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6800274848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8944206237793</t>
+    <t xml:space="preserve">7.86434650421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482648849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
     <t xml:space="preserve">6.274582862854</t>
@@ -2321,46 +2321,46 @@
     <t xml:space="preserve">5.77154016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26690244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33602285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15394449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938764572144</t>
+    <t xml:space="preserve">6.26690196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33602333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1539454460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018636703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938669204712</t>
   </si>
   <si>
     <t xml:space="preserve">7.78754758834839</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27178001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88021755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57022905349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364719390869</t>
+    <t xml:space="preserve">8.2717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88021802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57023048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364862442017</t>
   </si>
   <si>
     <t xml:space="preserve">8.13718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35335636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72860431671143</t>
+    <t xml:space="preserve">8.35335540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72860527038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.03043460845947</t>
@@ -2372,82 +2372,82 @@
     <t xml:space="preserve">8.70413208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75307655334473</t>
+    <t xml:space="preserve">8.75307846069336</t>
   </si>
   <si>
     <t xml:space="preserve">7.99442386627197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83127212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969625473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81903553009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79864263534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613821029663</t>
+    <t xml:space="preserve">7.83127117156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81903648376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7986421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613868713379</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68035745620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5090479850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496912002563</t>
+    <t xml:space="preserve">7.68035697937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50904846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496816635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.70482921600342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75377559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653301239014</t>
+    <t xml:space="preserve">7.75377511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653205871582</t>
   </si>
   <si>
     <t xml:space="preserve">7.94547843933105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8557448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010972976685</t>
+    <t xml:space="preserve">7.85574436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010877609253</t>
   </si>
   <si>
     <t xml:space="preserve">7.98146295547485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85739898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78709506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75814914703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69611549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5431022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.600998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58032131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51829099655151</t>
+    <t xml:space="preserve">7.85739803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78709554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75814723968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69611501693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54310178756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60099935531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.580322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5182900428772</t>
   </si>
   <si>
     <t xml:space="preserve">7.73333501815796</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">7.65062475204468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55550956726074</t>
+    <t xml:space="preserve">7.5555100440979</t>
   </si>
   <si>
     <t xml:space="preserve">7.53483247756958</t>
@@ -2465,34 +2465,34 @@
     <t xml:space="preserve">7.45212268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4934778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63408231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40249681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663194656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941289901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58445739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520565032959</t>
+    <t xml:space="preserve">7.49347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63408327102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40249729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663242340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58445692062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520660400391</t>
   </si>
   <si>
     <t xml:space="preserve">7.64235353469849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52656126022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75401163101196</t>
+    <t xml:space="preserve">7.52656221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401258468628</t>
   </si>
   <si>
     <t xml:space="preserve">7.72919940948486</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">7.37354850769043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44385194778442</t>
+    <t xml:space="preserve">7.44385242462158</t>
   </si>
   <si>
     <t xml:space="preserve">7.34460020065308</t>
@@ -2516,31 +2516,31 @@
     <t xml:space="preserve">7.73746967315674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69197988510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77468872070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72506380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784427642822</t>
+    <t xml:space="preserve">7.69198036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77468967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72506332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6878457069397</t>
   </si>
   <si>
     <t xml:space="preserve">7.67543745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62167692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438623428345</t>
+    <t xml:space="preserve">7.6216778755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438575744629</t>
   </si>
   <si>
     <t xml:space="preserve">7.71265697479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581348419189</t>
+    <t xml:space="preserve">7.62581253051758</t>
   </si>
   <si>
     <t xml:space="preserve">7.52242517471313</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">7.42317485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3363299369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3652777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25775480270386</t>
+    <t xml:space="preserve">7.33632946014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36527681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25775527954102</t>
   </si>
   <si>
     <t xml:space="preserve">7.08406496047974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02203273773193</t>
+    <t xml:space="preserve">7.02203321456909</t>
   </si>
   <si>
     <t xml:space="preserve">6.95586585998535</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">6.98067855834961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752395629883</t>
+    <t xml:space="preserve">7.06752347946167</t>
   </si>
   <si>
     <t xml:space="preserve">7.09647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07165956497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534940719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17091131210327</t>
+    <t xml:space="preserve">7.07165861129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17091035842896</t>
   </si>
   <si>
     <t xml:space="preserve">7.03444004058838</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">6.98894929885864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93932390213013</t>
+    <t xml:space="preserve">6.93932437896729</t>
   </si>
   <si>
     <t xml:space="preserve">7.05511665344238</t>
@@ -2606,34 +2606,34 @@
     <t xml:space="preserve">6.9517297744751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8979697227478</t>
+    <t xml:space="preserve">6.89796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93105220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82353067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75322723388672</t>
+    <t xml:space="preserve">6.93105268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82353115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75322771072388</t>
   </si>
   <si>
     <t xml:space="preserve">6.78217554092407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96413660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.947594165802</t>
+    <t xml:space="preserve">6.9641375541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324506759644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43558025360107</t>
+    <t xml:space="preserve">7.43558073043823</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700702667236</t>
@@ -2642,52 +2642,52 @@
     <t xml:space="preserve">7.48934173583984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59272956848145</t>
+    <t xml:space="preserve">7.59272909164429</t>
   </si>
   <si>
     <t xml:space="preserve">7.80777311325073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60927057266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71679306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092914581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085607528687</t>
+    <t xml:space="preserve">7.60926961898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71679162979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085702896118</t>
   </si>
   <si>
     <t xml:space="preserve">7.81190919876099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82845115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83672285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912776947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6671667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67957305908203</t>
+    <t xml:space="preserve">7.82845067977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83672142028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912633895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716814041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67957448959351</t>
   </si>
   <si>
     <t xml:space="preserve">7.61754131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60513496398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59686374664307</t>
+    <t xml:space="preserve">7.60513401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59686470031738</t>
   </si>
   <si>
     <t xml:space="preserve">7.57205104827881</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">7.54723882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5513744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03522396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20064258575439</t>
+    <t xml:space="preserve">7.55137348175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03522300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20064353942871</t>
   </si>
   <si>
     <t xml:space="preserve">8.15515232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4777193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14688301086426</t>
+    <t xml:space="preserve">8.47772026062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
     <t xml:space="preserve">8.31230068206787</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">8.41155242919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28748798370361</t>
+    <t xml:space="preserve">8.28748893737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.33711433410645</t>
@@ -2735,16 +2735,16 @@
     <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68449306488037</t>
+    <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.55215930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25026988983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59351348876953</t>
+    <t xml:space="preserve">8.25026893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59351444244385</t>
   </si>
   <si>
     <t xml:space="preserve">8.88299560546875</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">8.99051856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80028820037842</t>
+    <t xml:space="preserve">8.8002872467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.81682872772217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7341194152832</t>
+    <t xml:space="preserve">8.73412036895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.35365676879883</t>
@@ -2780,19 +2780,19 @@
     <t xml:space="preserve">8.13861083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32057285308838</t>
+    <t xml:space="preserve">8.32057189941406</t>
   </si>
   <si>
     <t xml:space="preserve">8.24199771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.304030418396</t>
+    <t xml:space="preserve">8.30402946472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.22545623779297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27921772003174</t>
+    <t xml:space="preserve">8.27921676635742</t>
   </si>
   <si>
     <t xml:space="preserve">8.2585391998291</t>
@@ -2801,52 +2801,52 @@
     <t xml:space="preserve">8.2378625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9566502571106</t>
+    <t xml:space="preserve">7.95664978027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.86980485916138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85326242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875364303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303300857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44798612594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35287141799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46866369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43144416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82017993927002</t>
+    <t xml:space="preserve">7.85326290130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574136734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303157806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415395736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44798707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219432830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35287189483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46866416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43144369125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50588417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82018041610718</t>
   </si>
   <si>
     <t xml:space="preserve">7.76228284835815</t>
@@ -2855,52 +2855,52 @@
     <t xml:space="preserve">7.38181972503662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2039942741394</t>
+    <t xml:space="preserve">7.20399475097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338787078857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02616834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09233665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12542057037354</t>
+    <t xml:space="preserve">7.02616882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09233617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12541961669922</t>
   </si>
   <si>
     <t xml:space="preserve">7.28670406341553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12955570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93518877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04271030426025</t>
+    <t xml:space="preserve">7.12955522537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93518829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04271125793457</t>
   </si>
   <si>
     <t xml:space="preserve">7.16263914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29911088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53896760940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70025062561035</t>
+    <t xml:space="preserve">7.29910898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70025157928467</t>
   </si>
   <si>
     <t xml:space="preserve">7.80281066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03108978271484</t>
+    <t xml:space="preserve">8.03108787536621</t>
   </si>
   <si>
     <t xml:space="preserve">7.88386535644531</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">8.01123905181885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8193531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138137817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190477371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86732387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
+    <t xml:space="preserve">7.81935214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77138090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453897476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8673243522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619359970093</t>
   </si>
   <si>
     <t xml:space="preserve">7.69694185256958</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635028839111</t>
+    <t xml:space="preserve">7.97319269180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635171890259</t>
   </si>
   <si>
     <t xml:space="preserve">8.01785564422607</t>
@@ -2948,55 +2948,55 @@
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02281665802002</t>
+    <t xml:space="preserve">7.99965906143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02281761169434</t>
   </si>
   <si>
     <t xml:space="preserve">8.05093860626221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93845367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003366470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8805570602417</t>
+    <t xml:space="preserve">7.93845462799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055801391602</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82431554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371513366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01289176940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84416437149048</t>
+    <t xml:space="preserve">7.82431507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84416627883911</t>
   </si>
   <si>
     <t xml:space="preserve">7.81604385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63904571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66055059432983</t>
+    <t xml:space="preserve">7.63904523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66054964065552</t>
   </si>
   <si>
     <t xml:space="preserve">7.73498964309692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79480361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72473526000977</t>
+    <t xml:space="preserve">7.79480504989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
     <t xml:space="preserve">7.78967714309692</t>
@@ -3008,31 +3008,31 @@
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8238582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960830688477</t>
+    <t xml:space="preserve">7.82385683059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960735321045</t>
   </si>
   <si>
     <t xml:space="preserve">7.76404237747192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8922176361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94006967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98963212966919</t>
+    <t xml:space="preserve">7.89221715927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94007015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98963165283203</t>
   </si>
   <si>
     <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09388160705566</t>
+    <t xml:space="preserve">8.09388065338135</t>
   </si>
   <si>
     <t xml:space="preserve">8.18445873260498</t>
@@ -3041,43 +3041,43 @@
     <t xml:space="preserve">8.24940204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2869987487793</t>
+    <t xml:space="preserve">8.28699970245361</t>
   </si>
   <si>
     <t xml:space="preserve">8.41517543792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39808559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46302700042725</t>
+    <t xml:space="preserve">8.39808654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46302795410156</t>
   </si>
   <si>
     <t xml:space="preserve">8.44252014160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21180248260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36390590667725</t>
+    <t xml:space="preserve">8.2118034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36390495300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.31947135925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2442741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1912956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12806129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09900760650635</t>
+    <t xml:space="preserve">8.24427318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12806224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09900856018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">8.11951637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22718524932861</t>
+    <t xml:space="preserve">8.2271842956543</t>
   </si>
   <si>
     <t xml:space="preserve">8.36903190612793</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877704620361</t>
+    <t xml:space="preserve">8.35877895355225</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45619297027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44081020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46986389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40663146972656</t>
+    <t xml:space="preserve">8.45619106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44081115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46986293792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40663051605225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37245082855225</t>
@@ -3137,67 +3137,67 @@
     <t xml:space="preserve">8.32630729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24256610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1502799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2186393737793</t>
+    <t xml:space="preserve">8.24256420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15027904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21863842010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.17420482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28187370300293</t>
+    <t xml:space="preserve">8.28187274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365009307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45277309417725</t>
+    <t xml:space="preserve">8.35365104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45277500152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404453277588</t>
+    <t xml:space="preserve">8.50404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.42030334472656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50233459472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896343231201</t>
+    <t xml:space="preserve">8.50233554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6006031036377</t>
+    <t xml:space="preserve">8.60060214996338</t>
   </si>
   <si>
     <t xml:space="preserve">8.63478374481201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6262378692627</t>
+    <t xml:space="preserve">8.62623882293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.61769390106201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54164218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62196636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69032669067383</t>
+    <t xml:space="preserve">8.5416431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6219654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69032764434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">8.63051223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5382251739502</t>
+    <t xml:space="preserve">8.53822326660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143329620361</t>
+    <t xml:space="preserve">8.33143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.36561393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23401927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31434345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40492153167725</t>
+    <t xml:space="preserve">8.2340202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31434440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">8.30579853057861</t>
@@ -3251,19 +3251,19 @@
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459831237793</t>
+    <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.2323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21522235870361</t>
+    <t xml:space="preserve">8.2152214050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.20838451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17933082580566</t>
+    <t xml:space="preserve">8.1793327331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
@@ -3272,28 +3272,28 @@
     <t xml:space="preserve">8.07166385650635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08875370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2391471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33485221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40150356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31776142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452899932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1776237487793</t>
+    <t xml:space="preserve">8.08875465393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475860595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23914813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33485126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40150260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31776237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2545280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">8.26478290557861</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">8.16565895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31605243682861</t>
+    <t xml:space="preserve">8.31605434417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.2169303894043</t>
@@ -3317,25 +3317,25 @@
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055725097656</t>
+    <t xml:space="preserve">8.43055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.32972526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45106506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44935512542725</t>
+    <t xml:space="preserve">8.45106601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56642246246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50575256347656</t>
+    <t xml:space="preserve">8.5664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50575351715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.49891757965088</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">8.47669982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02358436584473</t>
+    <t xml:space="preserve">9.02358531951904</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">8.86977291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80141258239746</t>
+    <t xml:space="preserve">8.80141162872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.78004932403564</t>
@@ -3365,28 +3365,28 @@
     <t xml:space="preserve">8.82704734802246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71168994903564</t>
+    <t xml:space="preserve">8.71168899536133</t>
   </si>
   <si>
     <t xml:space="preserve">8.65614700317383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72023391723633</t>
+    <t xml:space="preserve">8.72023487091064</t>
   </si>
   <si>
     <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63905620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60914707183838</t>
+    <t xml:space="preserve">8.6390552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6091480255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.69459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441455841064</t>
+    <t xml:space="preserve">8.75441551208496</t>
   </si>
   <si>
     <t xml:space="preserve">8.77150535583496</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">8.88686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88259029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92531585693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94667816162109</t>
+    <t xml:space="preserve">8.88259124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92531490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94667911529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.95522308349609</t>
@@ -3419,37 +3419,37 @@
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20302963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212928771973</t>
+    <t xml:space="preserve">9.12612438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20303058624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98513126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70741558074951</t>
+    <t xml:space="preserve">8.70741653442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.5877857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2613639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15882396697998</t>
+    <t xml:space="preserve">8.28870868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1588249206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20667552947998</t>
+    <t xml:space="preserve">8.2066764831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.35706806182861</t>
@@ -3461,46 +3461,46 @@
     <t xml:space="preserve">7.81873083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81360387802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81018543243408</t>
+    <t xml:space="preserve">7.81360292434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8101863861084</t>
   </si>
   <si>
     <t xml:space="preserve">8.15540599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12635231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88025426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71106243133545</t>
+    <t xml:space="preserve">8.12635326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8802547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71106195449829</t>
   </si>
   <si>
     <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61364889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54699659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45129251480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58459663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953851699829</t>
+    <t xml:space="preserve">7.61364841461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54699754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45129346847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58459711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953756332397</t>
   </si>
   <si>
     <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58288669586182</t>
+    <t xml:space="preserve">7.58288621902466</t>
   </si>
   <si>
     <t xml:space="preserve">7.48376417160034</t>
@@ -3509,16 +3509,16 @@
     <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055461883545</t>
+    <t xml:space="preserve">7.69055557250977</t>
   </si>
   <si>
     <t xml:space="preserve">7.82556629180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510349273682</t>
+    <t xml:space="preserve">7.5657958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6051025390625</t>
   </si>
   <si>
     <t xml:space="preserve">7.78625917434692</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">7.66491937637329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77087783813477</t>
+    <t xml:space="preserve">7.77087736129761</t>
   </si>
   <si>
     <t xml:space="preserve">7.62561178207397</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">7.9178524017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95545101165771</t>
+    <t xml:space="preserve">7.95545244216919</t>
   </si>
   <si>
     <t xml:space="preserve">8.07508182525635</t>
@@ -3554,25 +3554,25 @@
     <t xml:space="preserve">8.14173316955566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20325946807861</t>
+    <t xml:space="preserve">8.2032585144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.2288932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50062656402588</t>
+    <t xml:space="preserve">8.48182582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50062561035156</t>
   </si>
   <si>
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5433521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5578784942627</t>
+    <t xml:space="preserve">8.54335117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55787754058838</t>
   </si>
   <si>
     <t xml:space="preserve">8.68178081512451</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">8.68605422973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73732471466064</t>
+    <t xml:space="preserve">8.73732376098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658634185791</t>
+    <t xml:space="preserve">8.97658538818359</t>
   </si>
   <si>
     <t xml:space="preserve">8.93813323974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87404537200928</t>
+    <t xml:space="preserve">8.87404441833496</t>
   </si>
   <si>
     <t xml:space="preserve">8.89113521575928</t>
@@ -3602,28 +3602,28 @@
     <t xml:space="preserve">8.95095157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91677188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90395355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81422901153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61342144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69887161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70314407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74159622192383</t>
+    <t xml:space="preserve">8.91676998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90395259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81422996520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6134204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6732349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69887256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70314502716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74159717559814</t>
   </si>
   <si>
     <t xml:space="preserve">8.46131896972656</t>
@@ -3635,19 +3635,19 @@
     <t xml:space="preserve">8.5621509552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92368698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16629981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26775550842285</t>
+    <t xml:space="preserve">8.92368793487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26775455474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20600032806396</t>
+    <t xml:space="preserve">9.20599937438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.14424324035645</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">8.98985385894775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7498893737793</t>
+    <t xml:space="preserve">8.74989032745361</t>
   </si>
   <si>
     <t xml:space="preserve">8.43229007720947</t>
@@ -3677,25 +3677,25 @@
     <t xml:space="preserve">8.23820114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23996543884277</t>
+    <t xml:space="preserve">8.23996448516846</t>
   </si>
   <si>
     <t xml:space="preserve">8.25760936737061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21702766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31583595275879</t>
+    <t xml:space="preserve">8.21702671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31583499908447</t>
   </si>
   <si>
     <t xml:space="preserve">8.4234676361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73224449157715</t>
+    <t xml:space="preserve">8.79929447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73224544525146</t>
   </si>
   <si>
     <t xml:space="preserve">8.58932590484619</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">8.54344940185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77988624572754</t>
+    <t xml:space="preserve">8.77988529205322</t>
   </si>
   <si>
     <t xml:space="preserve">8.71636581420898</t>
@@ -3719,40 +3719,40 @@
     <t xml:space="preserve">8.82223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80458641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77635669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91486549377441</t>
+    <t xml:space="preserve">8.80458736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7763557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91486644744873</t>
   </si>
   <si>
     <t xml:space="preserve">8.93692207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84428691864014</t>
+    <t xml:space="preserve">8.84428787231445</t>
   </si>
   <si>
     <t xml:space="preserve">8.85311031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81517505645752</t>
+    <t xml:space="preserve">8.8151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57168102264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78694343566895</t>
+    <t xml:space="preserve">8.57168006896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78694438934326</t>
   </si>
   <si>
     <t xml:space="preserve">8.75341892242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03396606445312</t>
+    <t xml:space="preserve">9.03396701812744</t>
   </si>
   <si>
     <t xml:space="preserve">8.91045570373535</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5575647354126</t>
+    <t xml:space="preserve">8.55756568908691</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">8.6157922744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77106380462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74459648132324</t>
+    <t xml:space="preserve">8.77106475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74459552764893</t>
   </si>
   <si>
     <t xml:space="preserve">8.90163230895996</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">8.84869861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8354663848877</t>
+    <t xml:space="preserve">8.83546543121338</t>
   </si>
   <si>
     <t xml:space="preserve">8.68460559844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56638813018799</t>
+    <t xml:space="preserve">8.56638717651367</t>
   </si>
   <si>
     <t xml:space="preserve">8.63167285919189</t>
@@ -3803,34 +3803,34 @@
     <t xml:space="preserve">8.37935638427734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3493595123291</t>
+    <t xml:space="preserve">8.34936046600342</t>
   </si>
   <si>
     <t xml:space="preserve">8.29995536804199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693868637085</t>
+    <t xml:space="preserve">8.16938781738281</t>
   </si>
   <si>
     <t xml:space="preserve">8.10763072967529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25584506988525</t>
+    <t xml:space="preserve">8.25584411621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53639221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39700126647949</t>
+    <t xml:space="preserve">8.53639125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39700031280518</t>
   </si>
   <si>
     <t xml:space="preserve">8.32818698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70754337310791</t>
+    <t xml:space="preserve">8.70754241943359</t>
   </si>
   <si>
     <t xml:space="preserve">8.45699214935303</t>
@@ -3842,28 +3842,28 @@
     <t xml:space="preserve">8.08292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22585010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0035285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412445068359</t>
+    <t xml:space="preserve">8.22584915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00352954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412397384644</t>
   </si>
   <si>
     <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92589426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90472030639648</t>
+    <t xml:space="preserve">7.92589378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90471982955933</t>
   </si>
   <si>
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91354274749756</t>
+    <t xml:space="preserve">7.9135422706604</t>
   </si>
   <si>
     <t xml:space="preserve">7.94706773757935</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">8.15703678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04411220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78473806381226</t>
+    <t xml:space="preserve">8.04411125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78473854064941</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.39479494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40538167953491</t>
+    <t xml:space="preserve">7.40538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">7.51124858856201</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">7.43890619277954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52359914779663</t>
+    <t xml:space="preserve">7.52359962463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.3101019859314</t>
@@ -3917,25 +3917,25 @@
     <t xml:space="preserve">7.73709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75297689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8747239112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88001871109009</t>
+    <t xml:space="preserve">7.75297832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87472438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88001775741577</t>
   </si>
   <si>
     <t xml:space="preserve">7.85355138778687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94353818893433</t>
+    <t xml:space="preserve">7.94353771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08822250366211</t>
+    <t xml:space="preserve">8.08822345733643</t>
   </si>
   <si>
     <t xml:space="preserve">8.14291954040527</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">8.38817882537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76047706604004</t>
+    <t xml:space="preserve">8.76047611236572</t>
   </si>
   <si>
     <t xml:space="preserve">8.69872093200684</t>
@@ -3956,40 +3956,40 @@
     <t xml:space="preserve">8.4005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33524513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48698806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46934413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4816951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49404621124268</t>
+    <t xml:space="preserve">8.33524608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48698711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4693431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48169422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49404525756836</t>
   </si>
   <si>
     <t xml:space="preserve">8.40935134887695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28054809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53109836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47640037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46757793426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42699718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37053489685059</t>
+    <t xml:space="preserve">8.28054714202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53109931945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47640132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46757888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.36347579956055</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">8.53286361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55580043792725</t>
+    <t xml:space="preserve">8.55580139160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.4305248260498</t>
@@ -4013,10 +4013,10 @@
     <t xml:space="preserve">8.16232967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37582778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35112476348877</t>
+    <t xml:space="preserve">8.37582874298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35112571716309</t>
   </si>
   <si>
     <t xml:space="preserve">8.29642772674561</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">8.29819202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41640853881836</t>
+    <t xml:space="preserve">8.41641044616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4075870513916</t>
+    <t xml:space="preserve">8.40758800506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4046,19 +4046,19 @@
     <t xml:space="preserve">8.55227184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64402389526367</t>
+    <t xml:space="preserve">8.64402294158936</t>
   </si>
   <si>
     <t xml:space="preserve">8.67049026489258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61226367950439</t>
+    <t xml:space="preserve">8.61226272583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.7887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82046890258789</t>
+    <t xml:space="preserve">8.82046794891357</t>
   </si>
   <si>
     <t xml:space="preserve">8.73400974273682</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456600189209</t>
+    <t xml:space="preserve">8.95456504821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
@@ -4079,19 +4079,19 @@
     <t xml:space="preserve">8.8619327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8928108215332</t>
+    <t xml:space="preserve">8.89280986785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.11336612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89722156524658</t>
+    <t xml:space="preserve">8.89722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867725372314</t>
+    <t xml:space="preserve">8.99867630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4109,22 +4109,22 @@
     <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15306568145752</t>
+    <t xml:space="preserve">9.15306663513184</t>
   </si>
   <si>
     <t xml:space="preserve">9.14865493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13101100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13983249664307</t>
+    <t xml:space="preserve">9.13101005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13983154296875</t>
   </si>
   <si>
     <t xml:space="preserve">9.08248805999756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04278755187988</t>
+    <t xml:space="preserve">9.0427885055542</t>
   </si>
   <si>
     <t xml:space="preserve">9.93383407592773</t>
@@ -4142,19 +4142,19 @@
     <t xml:space="preserve">10.1720342636108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0264663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78385543823242</t>
+    <t xml:space="preserve">10.0264673233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78385639190674</t>
   </si>
   <si>
     <t xml:space="preserve">10.0705785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87207794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706630706787</t>
+    <t xml:space="preserve">9.87207698822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706726074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.77944469451904</t>
@@ -4166,16 +4166,16 @@
     <t xml:space="preserve">9.99117755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5116901397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3440685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778570175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6131458282471</t>
+    <t xml:space="preserve">10.5116891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3440675735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778560638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6131448745728</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4187,16 +4187,16 @@
     <t xml:space="preserve">10.6925458908081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7278337478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8425235748291</t>
+    <t xml:space="preserve">10.7278347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8425226211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.0013236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9219236373901</t>
+    <t xml:space="preserve">10.9219245910645</t>
   </si>
   <si>
     <t xml:space="preserve">10.9175128936768</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">10.789589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160581588745</t>
+    <t xml:space="preserve">10.8160572052002</t>
   </si>
   <si>
     <t xml:space="preserve">10.868989944458</t>
@@ -4238,37 +4238,37 @@
     <t xml:space="preserve">11.0454359054565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1248350143433</t>
+    <t xml:space="preserve">11.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0983686447144</t>
+    <t xml:space="preserve">11.09836769104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8645782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6396131515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4852237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8274984359741</t>
+    <t xml:space="preserve">10.6969566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660795211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.639612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4852228164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6352005004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8274974822998</t>
   </si>
   <si>
     <t xml:space="preserve">10.7820806503296</t>
@@ -4280,22 +4280,22 @@
     <t xml:space="preserve">10.6276607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6594543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6639947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684545516968</t>
+    <t xml:space="preserve">10.6594533920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6639957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684555053711</t>
   </si>
   <si>
     <t xml:space="preserve">10.8093309402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7593727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.732120513916</t>
+    <t xml:space="preserve">10.7593717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7321214675903</t>
   </si>
   <si>
     <t xml:space="preserve">10.7366628646851</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">10.5913276672363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5686187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6231203079224</t>
+    <t xml:space="preserve">10.5686197280884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.623119354248</t>
   </si>
   <si>
     <t xml:space="preserve">10.8138723373413</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">10.5822439193726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775382995605</t>
+    <t xml:space="preserve">10.7775392532349</t>
   </si>
   <si>
     <t xml:space="preserve">10.8774576187134</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">10.6776208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5958690643311</t>
+    <t xml:space="preserve">10.5958700180054</t>
   </si>
   <si>
     <t xml:space="preserve">10.5640773773193</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">10.9910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9773750305176</t>
+    <t xml:space="preserve">10.9773759841919</t>
   </si>
   <si>
     <t xml:space="preserve">10.8729152679443</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">10.5277433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5549945831299</t>
+    <t xml:space="preserve">10.5549936294556</t>
   </si>
   <si>
     <t xml:space="preserve">10.3687829971313</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">10.3778667449951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3824090957642</t>
+    <t xml:space="preserve">10.3824081420898</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597808837891</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">10.2416143417358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598634719849</t>
+    <t xml:space="preserve">10.1598625183105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1462373733521</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">10.0826539993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236110687256</t>
+    <t xml:space="preserve">10.0236101150513</t>
   </si>
   <si>
     <t xml:space="preserve">10.1916551589966</t>
@@ -4448,16 +4448,16 @@
     <t xml:space="preserve">10.1416959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1099033355713</t>
+    <t xml:space="preserve">10.1099042892456</t>
   </si>
   <si>
     <t xml:space="preserve">10.3642406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4187412261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414501190186</t>
+    <t xml:space="preserve">10.4187421798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414510726929</t>
   </si>
   <si>
     <t xml:space="preserve">10.4459924697876</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">10.3551568984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4278249740601</t>
+    <t xml:space="preserve">10.4278240203857</t>
   </si>
   <si>
     <t xml:space="preserve">10.5413684844971</t>
@@ -4481,16 +4481,16 @@
     <t xml:space="preserve">10.7275800704956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912469863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4505348205566</t>
+    <t xml:space="preserve">10.6912460327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4505338668823</t>
   </si>
   <si>
     <t xml:space="preserve">10.4596176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3006572723389</t>
+    <t xml:space="preserve">10.3006563186646</t>
   </si>
   <si>
     <t xml:space="preserve">10.1734886169434</t>
@@ -4499,25 +4499,25 @@
     <t xml:space="preserve">10.059944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2325315475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0917367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89190101623535</t>
+    <t xml:space="preserve">10.2325305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0917358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89190006256104</t>
   </si>
   <si>
     <t xml:space="preserve">9.62847995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48768615722656</t>
+    <t xml:space="preserve">9.48768520355225</t>
   </si>
   <si>
     <t xml:space="preserve">9.5648946762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62393856048584</t>
+    <t xml:space="preserve">9.62393760681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.79652404785156</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">9.65573024749756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75564861297607</t>
+    <t xml:space="preserve">9.75564765930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.64210510253906</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">9.71023082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72385692596436</t>
+    <t xml:space="preserve">9.72385597229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.59668731689453</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">9.65118885040283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68752288818359</t>
+    <t xml:space="preserve">9.68752193450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.67389678955078</t>
@@ -4598,16 +4598,16 @@
     <t xml:space="preserve">9.9009838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7738151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83285713195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8146915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7465648651123</t>
+    <t xml:space="preserve">9.77381610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83285808563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81469058990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74656391143799</t>
   </si>
   <si>
     <t xml:space="preserve">9.80106544494629</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">10.2961149215698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3460750579834</t>
+    <t xml:space="preserve">10.3460741043091</t>
   </si>
   <si>
     <t xml:space="preserve">10.3279066085815</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">10.4868679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.396032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3506155014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051170349121</t>
+    <t xml:space="preserve">10.3960332870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3506164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051160812378</t>
   </si>
   <si>
     <t xml:space="preserve">10.2279891967773</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">10.2734069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4550752639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4323663711548</t>
+    <t xml:space="preserve">10.4550762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4323673248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.4005746841431</t>
@@ -4670,10 +4670,10 @@
     <t xml:space="preserve">10.3324489593506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3188228607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0690288543701</t>
+    <t xml:space="preserve">10.3188238143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0690279006958</t>
   </si>
   <si>
     <t xml:space="preserve">10.0190687179565</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">10.0463199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009031295776</t>
+    <t xml:space="preserve">10.0009021759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.1280708312988</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">10.2143630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1189870834351</t>
+    <t xml:space="preserve">10.1189880371094</t>
   </si>
   <si>
     <t xml:space="preserve">9.94185924530029</t>
@@ -4706,28 +4706,28 @@
     <t xml:space="preserve">9.75110626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80560684204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66027164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73748111724854</t>
+    <t xml:space="preserve">9.80560779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6602725982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73748207092285</t>
   </si>
   <si>
     <t xml:space="preserve">9.74202346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78289890289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70114803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46043491363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2969331741333</t>
+    <t xml:space="preserve">9.78289985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70114707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46043586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29693222045898</t>
   </si>
   <si>
     <t xml:space="preserve">9.51493740081787</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">9.49676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41047668457031</t>
+    <t xml:space="preserve">9.410475730896</t>
   </si>
   <si>
     <t xml:space="preserve">9.35143375396729</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">9.57397937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63302040100098</t>
+    <t xml:space="preserve">9.63302135467529</t>
   </si>
   <si>
     <t xml:space="preserve">9.34689235687256</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">9.20155715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06530475616455</t>
+    <t xml:space="preserve">9.06530380249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.03805446624756</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">8.85184288024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90634346008301</t>
+    <t xml:space="preserve">8.90634441375732</t>
   </si>
   <si>
     <t xml:space="preserve">8.95176029205322</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">9.21972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3650598526001</t>
+    <t xml:space="preserve">9.36505889892578</t>
   </si>
   <si>
     <t xml:space="preserve">9.29239082336426</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">9.31964206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4377269744873</t>
+    <t xml:space="preserve">9.43772792816162</t>
   </si>
   <si>
     <t xml:space="preserve">9.40139293670654</t>
@@ -5520,6 +5520,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.54500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52499961853027</t>
   </si>
 </sst>
 </file>
@@ -70858,7 +70861,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.69125</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>2108341</v>
@@ -70879,6 +70882,32 @@
         <v>1835</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6910763889</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>2203266</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>9.58500003814697</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>9.52499961853027</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>9.52499961853027</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -38,148 +38,148 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433834075928</t>
+    <t xml:space="preserve">3.42433786392212</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45607089996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986746788025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331595420837</t>
+    <t xml:space="preserve">3.46296906471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4560706615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331643104553</t>
   </si>
   <si>
     <t xml:space="preserve">3.39812445640564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34845662117004</t>
+    <t xml:space="preserve">3.34845638275146</t>
   </si>
   <si>
     <t xml:space="preserve">3.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26981520652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324896812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03803133964539</t>
+    <t xml:space="preserve">3.26981496810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28637099266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324872970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03803086280823</t>
   </si>
   <si>
     <t xml:space="preserve">3.13874650001526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1428861618042</t>
+    <t xml:space="preserve">3.14288640022278</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1649603843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.137366771698</t>
+    <t xml:space="preserve">3.16496014595032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736701011658</t>
   </si>
   <si>
     <t xml:space="preserve">3.14564514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19945192337036</t>
+    <t xml:space="preserve">3.1994526386261</t>
   </si>
   <si>
     <t xml:space="preserve">3.30430674552917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27119541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222183227539</t>
+    <t xml:space="preserve">3.27119517326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222159385681</t>
   </si>
   <si>
     <t xml:space="preserve">3.20911002159119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20773100852966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0863196849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06700420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00077986717224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00215983390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9980206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1111536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151664733887</t>
+    <t xml:space="preserve">3.20773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08631920814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06700444221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00077962875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0021595954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802088737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837324142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322806358337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115384101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151640892029</t>
   </si>
   <si>
     <t xml:space="preserve">3.13046884536743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14150619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12495017051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11805152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808264732361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531321525574</t>
+    <t xml:space="preserve">3.1415057182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12495040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11805200576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808288574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323851585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531297683716</t>
   </si>
   <si>
     <t xml:space="preserve">3.18703532218933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09321808815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013715744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255328178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427610397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636077880859</t>
+    <t xml:space="preserve">3.09321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013739585876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636101722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.20635032653809</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">3.10563445091248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906845092773</t>
+    <t xml:space="preserve">3.04906868934631</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
@@ -200,88 +200,88 @@
     <t xml:space="preserve">3.03941082954407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00491857528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05182719230652</t>
+    <t xml:space="preserve">3.00491905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0518274307251</t>
   </si>
   <si>
     <t xml:space="preserve">2.98422408103943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05044841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595616340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629830360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561450004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08769917488098</t>
+    <t xml:space="preserve">3.05044794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595664024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457667350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147459983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767874717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02561402320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873676300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0876989364624</t>
   </si>
   <si>
     <t xml:space="preserve">3.14978432655334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05596661567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838345527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319694519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02975296974182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01871538162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766805648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249152183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9442138671875</t>
+    <t xml:space="preserve">3.0559663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319670677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0297532081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01871562004089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766781806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249199867249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94421339035034</t>
   </si>
   <si>
     <t xml:space="preserve">2.93869519233704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93593549728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02235889434814</t>
+    <t xml:space="preserve">2.93593525886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235913276672</t>
   </si>
   <si>
     <t xml:space="preserve">3.02659201622009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426246643066</t>
+    <t xml:space="preserve">2.99837231636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426222801208</t>
   </si>
   <si>
     <t xml:space="preserve">2.99131679534912</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">2.97861814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0689218044281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06610059738159</t>
+    <t xml:space="preserve">3.06892204284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610035896301</t>
   </si>
   <si>
     <t xml:space="preserve">3.01389288902283</t>
@@ -302,43 +302,43 @@
     <t xml:space="preserve">3.0209481716156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00683784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671481132507</t>
+    <t xml:space="preserve">3.00683832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929114341736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671528816223</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505825996399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96450805664062</t>
+    <t xml:space="preserve">2.99978280067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9645082950592</t>
   </si>
   <si>
     <t xml:space="preserve">2.86714935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80083250999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843680381775</t>
+    <t xml:space="preserve">2.80083227157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843704223633</t>
   </si>
   <si>
     <t xml:space="preserve">2.93205547332764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87702631950378</t>
+    <t xml:space="preserve">2.87702608108521</t>
   </si>
   <si>
     <t xml:space="preserve">2.91089010238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72181630134583</t>
+    <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
     <t xml:space="preserve">2.61034727096558</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">2.67525362968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.718994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79659914970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7951877117157</t>
+    <t xml:space="preserve">2.71899437904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79659938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79518818855286</t>
   </si>
   <si>
     <t xml:space="preserve">2.85162806510925</t>
@@ -362,28 +362,28 @@
     <t xml:space="preserve">2.83610701560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87279343605042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94475412368774</t>
+    <t xml:space="preserve">2.87279319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94475388526917</t>
   </si>
   <si>
     <t xml:space="preserve">2.97438526153564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00542736053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02518105506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0421130657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597684860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364682197571</t>
+    <t xml:space="preserve">3.00542712211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02518129348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211258888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597661018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364729881287</t>
   </si>
   <si>
     <t xml:space="preserve">3.07033324241638</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">3.05481195449829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03788042068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0519905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17333602905273</t>
+    <t xml:space="preserve">3.03788018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05199027061462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17333579063416</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204786300659</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">3.1549928188324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14088273048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1479377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1084303855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149765968323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241696357727</t>
+    <t xml:space="preserve">3.14088296890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793825149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843014717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149789810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241672515869</t>
   </si>
   <si>
     <t xml:space="preserve">3.13947153091431</t>
@@ -428,37 +428,37 @@
     <t xml:space="preserve">3.15075993537903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10419726371765</t>
+    <t xml:space="preserve">3.10419678688049</t>
   </si>
   <si>
     <t xml:space="preserve">3.08444333076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02800297737122</t>
+    <t xml:space="preserve">3.02800273895264</t>
   </si>
   <si>
     <t xml:space="preserve">3.01248216629028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02377009391785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07174372673035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045603752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646922111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0900866985321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732308387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21002149581909</t>
+    <t xml:space="preserve">3.02376985549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07174444198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646874427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09008693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732332229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21002173423767</t>
   </si>
   <si>
     <t xml:space="preserve">3.18462419509888</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">3.21284413337708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21707677841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27775001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351689338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22131013870239</t>
+    <t xml:space="preserve">3.21707701683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27774953842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351641654968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130966186523</t>
   </si>
   <si>
     <t xml:space="preserve">3.20861053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19873380661011</t>
+    <t xml:space="preserve">3.19873356819153</t>
   </si>
   <si>
     <t xml:space="preserve">3.18180227279663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1535816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217065811157</t>
+    <t xml:space="preserve">3.15358185768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217113494873</t>
   </si>
   <si>
     <t xml:space="preserve">3.16628074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1253616809845</t>
+    <t xml:space="preserve">3.12536215782166</t>
   </si>
   <si>
     <t xml:space="preserve">3.11125183105469</t>
@@ -509,73 +509,73 @@
     <t xml:space="preserve">3.09714198112488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867573738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.077388048172</t>
+    <t xml:space="preserve">3.11548519134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08867621421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07738780975342</t>
   </si>
   <si>
     <t xml:space="preserve">3.06186699867249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99696183204651</t>
+    <t xml:space="preserve">2.99696111679077</t>
   </si>
   <si>
     <t xml:space="preserve">2.92923331260681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95321941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180892944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93911004066467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92076730728149</t>
+    <t xml:space="preserve">2.95322060585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180940628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93910980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92076706886292</t>
   </si>
   <si>
     <t xml:space="preserve">2.95886397361755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92782211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002886772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493546485901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622267723083</t>
+    <t xml:space="preserve">2.92782163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622315406799</t>
   </si>
   <si>
     <t xml:space="preserve">3.0195369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97720670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99554967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04070210456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01812553405762</t>
+    <t xml:space="preserve">2.97720694541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99554991722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04070162773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0181257724762</t>
   </si>
   <si>
     <t xml:space="preserve">2.9630970954895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92641091346741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849511146545</t>
+    <t xml:space="preserve">2.92641067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849534988403</t>
   </si>
   <si>
     <t xml:space="preserve">2.87138223648071</t>
@@ -584,31 +584,31 @@
     <t xml:space="preserve">2.8572723865509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86856007575989</t>
+    <t xml:space="preserve">2.86856031417847</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95604181289673</t>
+    <t xml:space="preserve">2.95604228973389</t>
   </si>
   <si>
     <t xml:space="preserve">2.88690328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89819097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303926467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84034013748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82199716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84457325935364</t>
+    <t xml:space="preserve">2.89819121360779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303950309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84034037590027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82199740409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457302093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.85021734237671</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">2.79377746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82340836524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568008422852</t>
+    <t xml:space="preserve">2.82340812683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568032264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.76132440567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80929851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254689216614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89395833015442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89960265159607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009430885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665745735168</t>
+    <t xml:space="preserve">2.80929827690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8925473690033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89960217475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665721893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.88831424713135</t>
@@ -656,91 +656,91 @@
     <t xml:space="preserve">2.94052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09432029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08020973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303189277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560822486877</t>
+    <t xml:space="preserve">3.09432005882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08020997047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1056079864502</t>
   </si>
   <si>
     <t xml:space="preserve">3.08585381507874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13523864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511656761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13806080818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063737869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2043776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591164588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573101997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278582572937</t>
+    <t xml:space="preserve">3.1352391242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13806104660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051434516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20437788963318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591212272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253975868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278606414795</t>
   </si>
   <si>
     <t xml:space="preserve">3.09290885925293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06751108169556</t>
+    <t xml:space="preserve">3.06751084327698</t>
   </si>
   <si>
     <t xml:space="preserve">3.11830711364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13664984703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07456541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1070191860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529671669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26646208763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25376272201538</t>
+    <t xml:space="preserve">3.17898011207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13665008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07456564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2664623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25376296043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.25094079971313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29891467094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31443572044373</t>
+    <t xml:space="preserve">3.29891443252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31443524360657</t>
   </si>
   <si>
     <t xml:space="preserve">3.38357472419739</t>
@@ -749,46 +749,46 @@
     <t xml:space="preserve">3.37228679656982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37651944160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44565844535828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41461658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283628463745</t>
+    <t xml:space="preserve">3.37651968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4456582069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41461706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283652305603</t>
   </si>
   <si>
     <t xml:space="preserve">3.40756154060364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40050745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338648796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160618782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.478111743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798799514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185297012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5063316822052</t>
+    <t xml:space="preserve">3.40050673484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4865779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105717658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160666465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47811198234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798871040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50633096694946</t>
   </si>
   <si>
     <t xml:space="preserve">3.49222135543823</t>
@@ -797,85 +797,85 @@
     <t xml:space="preserve">3.56277132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53455185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5274965763092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866147041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099173545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568379402161</t>
+    <t xml:space="preserve">3.53455090522766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749752998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866170883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056456565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099149703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568355560303</t>
   </si>
   <si>
     <t xml:space="preserve">3.58393669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50209879875183</t>
+    <t xml:space="preserve">3.50209808349609</t>
   </si>
   <si>
     <t xml:space="preserve">3.55924415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6227388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.661541223526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506934165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332200050354</t>
+    <t xml:space="preserve">3.62273907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65095949172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154170036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506838798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332176208496</t>
   </si>
   <si>
     <t xml:space="preserve">3.59804630279541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7375226020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68667197227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299408912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71936225891113</t>
+    <t xml:space="preserve">3.73752236366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68667149543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299361228943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7193615436554</t>
   </si>
   <si>
     <t xml:space="preserve">3.70483303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66124677658081</t>
+    <t xml:space="preserve">3.66124629974365</t>
   </si>
   <si>
     <t xml:space="preserve">3.83195948600769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82832813262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379890441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285569190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85012030601501</t>
+    <t xml:space="preserve">3.8283269405365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379842758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285616874695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85012054443359</t>
   </si>
   <si>
     <t xml:space="preserve">3.88644218444824</t>
@@ -884,85 +884,85 @@
     <t xml:space="preserve">3.86101698875427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84648847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469534873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922386169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097165107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087954521179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639684677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823554992676</t>
+    <t xml:space="preserve">3.84648823738098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8246955871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922410011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451161384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097141265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087859153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92639636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9082350730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.91913247108459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81016683578491</t>
+    <t xml:space="preserve">3.81016635894775</t>
   </si>
   <si>
     <t xml:space="preserve">3.68303990364075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65761351585388</t>
+    <t xml:space="preserve">3.6576144695282</t>
   </si>
   <si>
     <t xml:space="preserve">3.6133017539978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62201905250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313153266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492442131042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214345932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030404090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218903541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035033226013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572947502136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662615776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191414833069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96635055541992</t>
+    <t xml:space="preserve">3.62201833724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313200950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150862693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.624924659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307361125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030427932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218998908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035080909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7157289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662687301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191367149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96635127067566</t>
   </si>
   <si>
     <t xml:space="preserve">3.93366098403931</t>
@@ -971,52 +971,52 @@
     <t xml:space="preserve">3.95908570289612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96998286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04989099502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07894897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91549968719482</t>
+    <t xml:space="preserve">3.96998357772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04989004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182180404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9154999256134</t>
   </si>
   <si>
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9954080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02446603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04262685775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10437393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271872520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464905738831</t>
+    <t xml:space="preserve">3.99540901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177575111389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02446556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04262638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10437440872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271824836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464953422546</t>
   </si>
   <si>
     <t xml:space="preserve">3.8973388671875</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">3.98814368247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95545434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002867698669</t>
+    <t xml:space="preserve">3.95545363426208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002820014954</t>
   </si>
   <si>
     <t xml:space="preserve">4.01720142364502</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">4.06805181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1479606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625844955444</t>
+    <t xml:space="preserve">4.14795923233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04625940322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078767776489</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">4.1080060005188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12253522872925</t>
+    <t xml:space="preserve">4.12253475189209</t>
   </si>
   <si>
     <t xml:space="preserve">4.18065023422241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15885591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18791437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16612100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338466644287</t>
+    <t xml:space="preserve">4.1588568687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18791389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1661205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338562011719</t>
   </si>
   <si>
     <t xml:space="preserve">4.09710931777954</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">4.14069557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979984283447</t>
+    <t xml:space="preserve">4.12979936599731</t>
   </si>
   <si>
     <t xml:space="preserve">4.24602890014648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22060394287109</t>
+    <t xml:space="preserve">4.22060346603394</t>
   </si>
   <si>
     <t xml:space="preserve">4.26055765151978</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">4.25329351425171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26419067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27508735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701721191406</t>
+    <t xml:space="preserve">4.26419019699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27508640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17701816558838</t>
   </si>
   <si>
     <t xml:space="preserve">4.08984470367432</t>
@@ -1118,34 +1118,34 @@
     <t xml:space="preserve">4.30777597427368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29688024520874</t>
+    <t xml:space="preserve">4.29687976837158</t>
   </si>
   <si>
     <t xml:space="preserve">4.4276385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51481103897095</t>
+    <t xml:space="preserve">4.51481151580811</t>
   </si>
   <si>
     <t xml:space="preserve">4.54023599624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60198354721069</t>
+    <t xml:space="preserve">4.60198402404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.59835147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929397583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56202983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62014436721802</t>
+    <t xml:space="preserve">4.72184562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56202936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62014484405518</t>
   </si>
   <si>
     <t xml:space="preserve">4.59471893310547</t>
@@ -1154,103 +1154,103 @@
     <t xml:space="preserve">4.60924768447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48938608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669603347778</t>
+    <t xml:space="preserve">4.48938512802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669651031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.51844310760498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33683347702026</t>
+    <t xml:space="preserve">4.33683395385742</t>
   </si>
   <si>
     <t xml:space="preserve">4.52207565307617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48575401306152</t>
+    <t xml:space="preserve">4.48575353622437</t>
   </si>
   <si>
     <t xml:space="preserve">4.49301767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50391435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49665021896362</t>
+    <t xml:space="preserve">4.50391483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49665069580078</t>
   </si>
   <si>
     <t xml:space="preserve">4.46032810211182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45306444168091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46759223937988</t>
+    <t xml:space="preserve">4.45306348800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46759271621704</t>
   </si>
   <si>
     <t xml:space="preserve">4.4784893989563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750156402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53660440444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39131641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037487030029</t>
+    <t xml:space="preserve">4.54750108718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5366039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39131689071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.29324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40947771072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51117897033691</t>
+    <t xml:space="preserve">4.40947818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5111780166626</t>
   </si>
   <si>
     <t xml:space="preserve">4.42400646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28235101699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20607566833496</t>
+    <t xml:space="preserve">4.31140851974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28235054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2060751914978</t>
   </si>
   <si>
     <t xml:space="preserve">4.12616682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23150014877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94092488288879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9772469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258008956909</t>
+    <t xml:space="preserve">4.23150062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432716369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94092535972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258104324341</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522432327271</t>
@@ -1259,67 +1259,67 @@
     <t xml:space="preserve">4.16975259780884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44579935073853</t>
+    <t xml:space="preserve">4.44579982757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.40584516525269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41674184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59108686447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61288022994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5511326789856</t>
+    <t xml:space="preserve">4.4167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59108734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61287975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55113315582275</t>
   </si>
   <si>
     <t xml:space="preserve">4.57655906677246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52934074401855</t>
+    <t xml:space="preserve">4.52933979034424</t>
   </si>
   <si>
     <t xml:space="preserve">4.52570772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53297138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67825984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6492018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67099475860596</t>
+    <t xml:space="preserve">4.53297233581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67825937271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920282363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67099523544312</t>
   </si>
   <si>
     <t xml:space="preserve">4.64557027816772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65283489227295</t>
+    <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75090312957764</t>
+    <t xml:space="preserve">4.75090360641479</t>
   </si>
   <si>
     <t xml:space="preserve">4.76180028915405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72547817230225</t>
+    <t xml:space="preserve">4.7254786491394</t>
   </si>
   <si>
     <t xml:space="preserve">4.68552446365356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72911071777344</t>
+    <t xml:space="preserve">4.72911024093628</t>
   </si>
   <si>
     <t xml:space="preserve">4.65646648406982</t>
@@ -1328,40 +1328,40 @@
     <t xml:space="preserve">4.84534025192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81991481781006</t>
+    <t xml:space="preserve">4.81265115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81991529464722</t>
   </si>
   <si>
     <t xml:space="preserve">4.83807563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166284561157</t>
+    <t xml:space="preserve">4.88166236877441</t>
   </si>
   <si>
     <t xml:space="preserve">4.8489727973938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9179835319519</t>
+    <t xml:space="preserve">4.91798448562622</t>
   </si>
   <si>
     <t xml:space="preserve">4.89255905151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95430660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9470419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977785110474</t>
+    <t xml:space="preserve">4.95430612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94704151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977737426758</t>
   </si>
   <si>
     <t xml:space="preserve">4.93251276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99062824249268</t>
+    <t xml:space="preserve">4.99062728881836</t>
   </si>
   <si>
     <t xml:space="preserve">4.94340896606445</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">4.87888193130493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86018848419189</t>
+    <t xml:space="preserve">4.86018800735474</t>
   </si>
   <si>
     <t xml:space="preserve">4.82654142379761</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">4.75176858901978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65082693099976</t>
+    <t xml:space="preserve">4.6508264541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.49380540847778</t>
@@ -1394,61 +1394,61 @@
     <t xml:space="preserve">4.62091732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63587188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74803066253662</t>
+    <t xml:space="preserve">4.67699718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63587141036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7480297088623</t>
   </si>
   <si>
     <t xml:space="preserve">4.72185945510864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70690536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979249954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75924587249756</t>
+    <t xml:space="preserve">4.70690584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75924634933472</t>
   </si>
   <si>
     <t xml:space="preserve">4.83027982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93496084213257</t>
+    <t xml:space="preserve">4.93496036529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.85644960403442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81532573699951</t>
+    <t xml:space="preserve">4.81532526016235</t>
   </si>
   <si>
     <t xml:space="preserve">4.94243812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91252946853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91626691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90505123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88261985778809</t>
+    <t xml:space="preserve">4.91252899169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91626787185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90505170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8826208114624</t>
   </si>
   <si>
     <t xml:space="preserve">4.93869924545288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96486902236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216409683228</t>
+    <t xml:space="preserve">4.96486949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216457366943</t>
   </si>
   <si>
     <t xml:space="preserve">5.01721000671387</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">5.13684511184692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05833435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98356199264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89757442474365</t>
+    <t xml:space="preserve">5.05833387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98356342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89757537841797</t>
   </si>
   <si>
     <t xml:space="preserve">5.1293683052063</t>
@@ -1475,34 +1475,34 @@
     <t xml:space="preserve">5.37985467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3162989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41350126266479</t>
+    <t xml:space="preserve">5.31629848480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41350173950195</t>
   </si>
   <si>
     <t xml:space="preserve">5.34246873855591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09945964813232</t>
+    <t xml:space="preserve">5.09945917129517</t>
   </si>
   <si>
     <t xml:space="preserve">5.01347160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17797040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2004017829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274276733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787906646729</t>
+    <t xml:space="preserve">5.17796945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20040130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274229049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787954330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.21535587310791</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">5.19666242599487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11815214157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04338026046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99851703643799</t>
+    <t xml:space="preserve">5.11815166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04337978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99851655960083</t>
   </si>
   <si>
     <t xml:space="preserve">5.11067533493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17049264907837</t>
+    <t xml:space="preserve">5.17049217224121</t>
   </si>
   <si>
     <t xml:space="preserve">5.04711866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441373825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581211090088</t>
+    <t xml:space="preserve">5.11441421508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581163406372</t>
   </si>
   <si>
     <t xml:space="preserve">4.97982406616211</t>
@@ -1547,25 +1547,25 @@
     <t xml:space="preserve">5.03964138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05459594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076572418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18544721603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09572076797485</t>
+    <t xml:space="preserve">5.05459642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18544769287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09572172164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.2116174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8863582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000675201416</t>
+    <t xml:space="preserve">4.88635873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92000579833984</t>
   </si>
   <si>
     <t xml:space="preserve">4.77420043945312</t>
@@ -1583,52 +1583,52 @@
     <t xml:space="preserve">4.71064472198486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67325782775879</t>
+    <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
     <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5685772895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58726978302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56110048294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40781688690186</t>
+    <t xml:space="preserve">4.62839555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56857776641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58727121353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40781736373901</t>
   </si>
   <si>
     <t xml:space="preserve">4.61344051361084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59848642349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7555079460144</t>
+    <t xml:space="preserve">4.59848594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550699234009</t>
   </si>
   <si>
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79289388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766624450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167772293091</t>
+    <t xml:space="preserve">4.79289293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915548324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167819976807</t>
   </si>
   <si>
     <t xml:space="preserve">4.77793884277344</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">4.87140417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83775615692139</t>
+    <t xml:space="preserve">4.8377571105957</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812105178833</t>
+    <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
     <t xml:space="preserve">4.74055337905884</t>
@@ -1652,55 +1652,55 @@
     <t xml:space="preserve">4.60222482681274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54988479614258</t>
+    <t xml:space="preserve">4.54988431930542</t>
   </si>
   <si>
     <t xml:space="preserve">4.5237135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51997470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903305053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46015787124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64334869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204261779785</t>
+    <t xml:space="preserve">4.51997518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48632764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46015739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6433482170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204166412354</t>
   </si>
   <si>
     <t xml:space="preserve">4.65456485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76298475265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73681402206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86392736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98730087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21909475326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22657155990601</t>
+    <t xml:space="preserve">4.76298427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73681449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86392688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98730134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21909427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22657203674316</t>
   </si>
   <si>
     <t xml:space="preserve">5.18918609619141</t>
@@ -1712,25 +1712,25 @@
     <t xml:space="preserve">5.20414066314697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37237787246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16675472259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620714187622</t>
+    <t xml:space="preserve">5.37237739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620761871338</t>
   </si>
   <si>
     <t xml:space="preserve">6.09018993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87335062026978</t>
+    <t xml:space="preserve">5.87335109710693</t>
   </si>
   <si>
     <t xml:space="preserve">5.79483985900879</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76119232177734</t>
+    <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.81353378295898</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">5.87708950042725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92195320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924732208252</t>
+    <t xml:space="preserve">5.92195272445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924779891968</t>
   </si>
   <si>
     <t xml:space="preserve">6.01167964935303</t>
@@ -1763,25 +1763,25 @@
     <t xml:space="preserve">6.02663421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96307706832886</t>
+    <t xml:space="preserve">5.96307754516602</t>
   </si>
   <si>
     <t xml:space="preserve">6.0079402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9256911277771</t>
+    <t xml:space="preserve">5.92569208145142</t>
   </si>
   <si>
     <t xml:space="preserve">5.93316888809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90699863433838</t>
+    <t xml:space="preserve">5.90699911117554</t>
   </si>
   <si>
     <t xml:space="preserve">5.94064569473267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07897424697876</t>
+    <t xml:space="preserve">6.0789737701416</t>
   </si>
   <si>
     <t xml:space="preserve">5.93690729141235</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">5.95933866500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8995213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89578247070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88082790374756</t>
+    <t xml:space="preserve">5.89952087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89578199386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8808274269104</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812250137329</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">5.95560026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97429323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114105224609</t>
+    <t xml:space="preserve">5.97429275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114152908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.840660572052</t>
+    <t xml:space="preserve">5.84066104888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.75234031677246</t>
@@ -1823,31 +1823,31 @@
     <t xml:space="preserve">5.694739818573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71778011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68321943283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66401958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66786050796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78306007385254</t>
+    <t xml:space="preserve">5.71777963638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68321990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66402006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66786003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78306102752686</t>
   </si>
   <si>
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002073287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87522125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82146072387695</t>
+    <t xml:space="preserve">5.76002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87522077560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82146024703979</t>
   </si>
   <si>
     <t xml:space="preserve">5.74850034713745</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">5.69858026504517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64482021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60642051696777</t>
+    <t xml:space="preserve">5.64481973648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
     <t xml:space="preserve">5.77538061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72162055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81762027740479</t>
+    <t xml:space="preserve">5.72162008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81762075424194</t>
   </si>
   <si>
     <t xml:space="preserve">5.78690052032471</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0557017326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28226280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474222183228</t>
+    <t xml:space="preserve">6.05570125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28226232528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474174499512</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.128662109375</t>
+    <t xml:space="preserve">6.12866163253784</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850179672241</t>
@@ -1910,61 +1910,61 @@
     <t xml:space="preserve">6.17090177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16706132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29378223419189</t>
+    <t xml:space="preserve">6.16706228256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29378271102905</t>
   </si>
   <si>
     <t xml:space="preserve">6.39746284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43586349487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46274280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210344314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35522222518921</t>
+    <t xml:space="preserve">6.43586301803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210248947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35522174835205</t>
   </si>
   <si>
     <t xml:space="preserve">6.44738340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5280237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410335540771</t>
+    <t xml:space="preserve">6.52802276611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410383224487</t>
   </si>
   <si>
     <t xml:space="preserve">6.58946323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62018299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322328567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786340713501</t>
+    <t xml:space="preserve">6.62018346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786388397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.66626358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80450344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522367477417</t>
+    <t xml:space="preserve">6.80450487136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522319793701</t>
   </si>
   <si>
     <t xml:space="preserve">6.78914403915405</t>
@@ -1976,154 +1976,154 @@
     <t xml:space="preserve">6.98114490509033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98882532119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6893048286438</t>
+    <t xml:space="preserve">6.98882436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930387496948</t>
   </si>
   <si>
     <t xml:space="preserve">6.63554430007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61634254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298448562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026483535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642534255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0080246925354</t>
+    <t xml:space="preserve">6.61634302139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570510864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946420669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802564620972</t>
   </si>
   <si>
     <t xml:space="preserve">6.9926643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0617847442627</t>
+    <t xml:space="preserve">7.10402488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06178522109985</t>
   </si>
   <si>
     <t xml:space="preserve">7.07330560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07714462280273</t>
+    <t xml:space="preserve">7.07714509963989</t>
   </si>
   <si>
     <t xml:space="preserve">7.00034427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96578454971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02722454071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274473190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04258489608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75074338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506479263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9043436050415</t>
+    <t xml:space="preserve">6.96578407287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02722406387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274425506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04258441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634447097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93506383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434503555298</t>
   </si>
   <si>
     <t xml:space="preserve">7.0233850479126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.973464012146</t>
+    <t xml:space="preserve">6.97346496582031</t>
   </si>
   <si>
     <t xml:space="preserve">7.15778589248657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29602527618408</t>
+    <t xml:space="preserve">7.16546535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29602575302124</t>
   </si>
   <si>
     <t xml:space="preserve">7.16930532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31138610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682685852051</t>
+    <t xml:space="preserve">7.31138706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682542800903</t>
   </si>
   <si>
     <t xml:space="preserve">7.18850517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12706518173218</t>
+    <t xml:space="preserve">7.12706470489502</t>
   </si>
   <si>
     <t xml:space="preserve">7.17698574066162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19234561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010595321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210681915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43426561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730543136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658567428589</t>
+    <t xml:space="preserve">7.19234466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210634231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43426704406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730590820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658519744873</t>
   </si>
   <si>
     <t xml:space="preserve">7.28066539764404</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">7.11938571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2230658531189</t>
+    <t xml:space="preserve">7.22306537628174</t>
   </si>
   <si>
     <t xml:space="preserve">7.11554622650146</t>
@@ -2144,34 +2144,34 @@
     <t xml:space="preserve">7.08866453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98498439788818</t>
+    <t xml:space="preserve">6.98498487472534</t>
   </si>
   <si>
     <t xml:space="preserve">6.77378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066347122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762365341187</t>
+    <t xml:space="preserve">6.80066394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762413024902</t>
   </si>
   <si>
     <t xml:space="preserve">6.88898468017578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9273853302002</t>
+    <t xml:space="preserve">6.92738485336304</t>
   </si>
   <si>
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.912024974823</t>
+    <t xml:space="preserve">6.91202449798584</t>
   </si>
   <si>
     <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210536956787</t>
+    <t xml:space="preserve">6.86210441589355</t>
   </si>
   <si>
     <t xml:space="preserve">6.84674453735352</t>
@@ -2183,37 +2183,37 @@
     <t xml:space="preserve">7.03106451034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05794477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75842428207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218433380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602430343628</t>
+    <t xml:space="preserve">7.05794525146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7584228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602382659912</t>
   </si>
   <si>
     <t xml:space="preserve">6.87746429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74306392669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69314432144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72002410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89282512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79682397842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70466423034668</t>
+    <t xml:space="preserve">6.74306440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69314384460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72002363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89282464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70466375350952</t>
   </si>
   <si>
     <t xml:space="preserve">6.67778348922729</t>
@@ -2222,97 +2222,97 @@
     <t xml:space="preserve">6.78530406951904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71234369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7353835105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410480499268</t>
+    <t xml:space="preserve">6.71234321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73538446426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386695861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410671234131</t>
   </si>
   <si>
     <t xml:space="preserve">7.2077054977417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17314624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690534591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002460479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1117057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25762557983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986476898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56098747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66466617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83362722396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418714523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258922576904</t>
+    <t xml:space="preserve">7.17314481735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002603530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11170625686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762605667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786725997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56098699569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66466665267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83362770080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258827209473</t>
   </si>
   <si>
     <t xml:space="preserve">8.17922878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8643479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218723297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378658294678</t>
+    <t xml:space="preserve">7.86434745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378753662109</t>
   </si>
   <si>
     <t xml:space="preserve">7.49186706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36130714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6800274848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898708343506</t>
+    <t xml:space="preserve">7.36130666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898612976074</t>
   </si>
   <si>
     <t xml:space="preserve">6.91970443725586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8944206237793</t>
+    <t xml:space="preserve">5.89442110061646</t>
   </si>
   <si>
     <t xml:space="preserve">6.27458190917969</t>
@@ -2321,40 +2321,40 @@
     <t xml:space="preserve">5.77154016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26690244674683</t>
+    <t xml:space="preserve">6.26690196990967</t>
   </si>
   <si>
     <t xml:space="preserve">6.33602237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15394592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21922492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938812255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754901885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27178192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8802170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57023000717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364671707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718128204346</t>
+    <t xml:space="preserve">7.1539454460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21922588348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018636703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754758834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88021802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718223571777</t>
   </si>
   <si>
     <t xml:space="preserve">8.35335731506348</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">8.72860527038574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03043556213379</t>
+    <t xml:space="preserve">9.03043460845947</t>
   </si>
   <si>
     <t xml:space="preserve">8.95701789855957</t>
@@ -2372,79 +2372,79 @@
     <t xml:space="preserve">8.70413303375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75307750701904</t>
+    <t xml:space="preserve">8.75307846069336</t>
   </si>
   <si>
     <t xml:space="preserve">7.99442338943481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83127307891846</t>
+    <t xml:space="preserve">7.83127212524414</t>
   </si>
   <si>
     <t xml:space="preserve">7.74969577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81903648376465</t>
+    <t xml:space="preserve">7.81903505325317</t>
   </si>
   <si>
     <t xml:space="preserve">7.79864263534546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87613964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6803560256958</t>
+    <t xml:space="preserve">7.87613773345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
     <t xml:space="preserve">7.5090479850769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70482969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653158187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94547843933105</t>
+    <t xml:space="preserve">7.50496912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70482921600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94547700881958</t>
   </si>
   <si>
     <t xml:space="preserve">7.8557448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94010972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146438598633</t>
+    <t xml:space="preserve">7.94010829925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9814624786377</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739850997925</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7870945930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7581467628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69611644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54310321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.600998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58032131195068</t>
+    <t xml:space="preserve">7.78709602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75814819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69611597061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54310274124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60099983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58032178878784</t>
   </si>
   <si>
     <t xml:space="preserve">7.5182900428772</t>
@@ -2453,121 +2453,121 @@
     <t xml:space="preserve">7.73333501815796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65062570571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55551052093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53483152389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4521222114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4934778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63408279418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40249681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663242340088</t>
+    <t xml:space="preserve">7.65062427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5555100440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53483247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63408327102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40249586105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663146972656</t>
   </si>
   <si>
     <t xml:space="preserve">7.36941337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5844578742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520708084106</t>
+    <t xml:space="preserve">7.58445739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520660400391</t>
   </si>
   <si>
     <t xml:space="preserve">7.64235401153564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52656173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7540111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34459972381592</t>
+    <t xml:space="preserve">7.52656221389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919988632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354898452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460020065308</t>
   </si>
   <si>
     <t xml:space="preserve">7.39009094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37768363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7374701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69198131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77468872070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72506427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67543840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62167692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438718795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71265745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62581253051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42317485809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33632946014404</t>
+    <t xml:space="preserve">7.37768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73746824264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69198083877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7746901512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72506332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68784427642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67543792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6216778755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438623428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71265697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62581205368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42317390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33632898330688</t>
   </si>
   <si>
     <t xml:space="preserve">7.3652777671814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25775527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08406448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02203321456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95586585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98067760467529</t>
+    <t xml:space="preserve">7.2577543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08406543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02203273773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95586490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
     <t xml:space="preserve">7.06752347946167</t>
@@ -2576,64 +2576,64 @@
     <t xml:space="preserve">7.09647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07165956497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534940719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17091083526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03444004058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98894929885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93932390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05511665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90623998641968</t>
+    <t xml:space="preserve">7.07165908813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17091035842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03443956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9889497756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93932342529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0551176071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864633560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90624141693115</t>
   </si>
   <si>
     <t xml:space="preserve">6.95173025131226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8979697227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98481416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93105316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82353067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75322771072388</t>
+    <t xml:space="preserve">6.89796876907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98481369018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93105268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82353115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75322723388672</t>
   </si>
   <si>
     <t xml:space="preserve">6.78217601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96413660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30324459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43557977676392</t>
+    <t xml:space="preserve">6.96413707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759511947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30324554443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43558073043823</t>
   </si>
   <si>
     <t xml:space="preserve">7.35700702667236</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">7.489342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59272861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80777263641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6092700958252</t>
+    <t xml:space="preserve">7.59272909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80777215957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
     <t xml:space="preserve">7.71679306030273</t>
@@ -2657,55 +2657,55 @@
     <t xml:space="preserve">7.72092819213867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84085655212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845020294189</t>
+    <t xml:space="preserve">7.84085702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82845115661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.8367223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912824630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67957353591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61754131317139</t>
+    <t xml:space="preserve">7.96078443527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912729263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716718673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67957401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61754179000854</t>
   </si>
   <si>
     <t xml:space="preserve">7.6051344871521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59686374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57205104827881</t>
+    <t xml:space="preserve">7.59686470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57205057144165</t>
   </si>
   <si>
     <t xml:space="preserve">7.54723834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55137395858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03522396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20064353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15515232086182</t>
+    <t xml:space="preserve">7.55137348175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03522300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20064258575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15515422821045</t>
   </si>
   <si>
     <t xml:space="preserve">8.4777193069458</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230068206787</t>
+    <t xml:space="preserve">8.31230163574219</t>
   </si>
   <si>
     <t xml:space="preserve">8.56042957305908</t>
@@ -2723,25 +2723,25 @@
     <t xml:space="preserve">8.40328121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41155338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2874870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33711338043213</t>
+    <t xml:space="preserve">8.41155242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33711433410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68449401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55215930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25026893615723</t>
+    <t xml:space="preserve">8.68449306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55215835571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25026988983154</t>
   </si>
   <si>
     <t xml:space="preserve">8.59351253509521</t>
@@ -2750,19 +2750,19 @@
     <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92435169219971</t>
+    <t xml:space="preserve">8.92435073852539</t>
   </si>
   <si>
     <t xml:space="preserve">8.99051761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80028629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81682968139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73411846160889</t>
+    <t xml:space="preserve">8.8002872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81682777404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.35365581512451</t>
@@ -2771,31 +2771,31 @@
     <t xml:space="preserve">8.10966300964355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21304988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18823719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13860988616943</t>
+    <t xml:space="preserve">8.21304893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18823623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13861083984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.32057189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24199771881104</t>
+    <t xml:space="preserve">8.24199867248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545528411865</t>
+    <t xml:space="preserve">8.22545623779297</t>
   </si>
   <si>
     <t xml:space="preserve">8.27921676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25854015350342</t>
+    <t xml:space="preserve">8.25853824615479</t>
   </si>
   <si>
     <t xml:space="preserve">8.2378625869751</t>
@@ -2804,85 +2804,85 @@
     <t xml:space="preserve">7.9566502571106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86980533599854</t>
+    <t xml:space="preserve">7.86980628967285</t>
   </si>
   <si>
     <t xml:space="preserve">7.85326337814331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89875411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51415491104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4479866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219289779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35287189483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46866464614868</t>
+    <t xml:space="preserve">7.89875316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574136734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303205490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65475988388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5141544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44798755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35287094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46866369247437</t>
   </si>
   <si>
     <t xml:space="preserve">7.43971633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43144416809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50588274002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82018041610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76228284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38182020187378</t>
+    <t xml:space="preserve">7.43144512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50588369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8201789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.762282371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38181924819946</t>
   </si>
   <si>
     <t xml:space="preserve">7.20399475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06338787078857</t>
+    <t xml:space="preserve">7.06338834762573</t>
   </si>
   <si>
     <t xml:space="preserve">7.02616882324219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12541961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12955522537231</t>
+    <t xml:space="preserve">7.09233570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12542057037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670501708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12955617904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263961791992</t>
+    <t xml:space="preserve">7.04271125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16263914108276</t>
   </si>
   <si>
     <t xml:space="preserve">7.2991099357605</t>
@@ -2891,25 +2891,25 @@
     <t xml:space="preserve">7.22053623199463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53896713256836</t>
+    <t xml:space="preserve">7.5389666557312</t>
   </si>
   <si>
     <t xml:space="preserve">7.70025110244751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80281019210815</t>
+    <t xml:space="preserve">7.80281066894531</t>
   </si>
   <si>
     <t xml:space="preserve">8.03108787536621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88386535644531</t>
+    <t xml:space="preserve">7.88386631011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.01123905181885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8193531036377</t>
+    <t xml:space="preserve">7.81935262680054</t>
   </si>
   <si>
     <t xml:space="preserve">7.77138090133667</t>
@@ -2918,154 +2918,154 @@
     <t xml:space="preserve">7.79453945159912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70190572738647</t>
+    <t xml:space="preserve">7.70190620422363</t>
   </si>
   <si>
     <t xml:space="preserve">7.8673243522644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81273555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
+    <t xml:space="preserve">7.81273508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619359970093</t>
   </si>
   <si>
     <t xml:space="preserve">7.6969428062439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05590152740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97319316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635076522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01785469055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05259227752686</t>
+    <t xml:space="preserve">8.05590057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97319221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01785659790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
     <t xml:space="preserve">7.99965953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02281665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05093860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003318786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88055849075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86897802352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82431554794312</t>
+    <t xml:space="preserve">8.02281761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05094051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845415115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86897754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82431507110596</t>
   </si>
   <si>
     <t xml:space="preserve">7.90371513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84416532516479</t>
+    <t xml:space="preserve">8.01289176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84416484832764</t>
   </si>
   <si>
     <t xml:space="preserve">7.81604337692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63904523849487</t>
+    <t xml:space="preserve">7.63904571533203</t>
   </si>
   <si>
     <t xml:space="preserve">7.66055011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73498964309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79480409622192</t>
+    <t xml:space="preserve">7.73498916625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79480361938477</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85291004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82385778427124</t>
+    <t xml:space="preserve">7.78967666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85291051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8238582611084</t>
   </si>
   <si>
     <t xml:space="preserve">7.77258682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71960783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89221715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94006967544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09388256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1844596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2494010925293</t>
+    <t xml:space="preserve">7.71960830688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404190063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89221811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94007015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98963117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09388160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18445873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24940204620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.28699970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41517448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39808654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099575042725</t>
+    <t xml:space="preserve">8.41517543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39808464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099479675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.46302795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44252014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21180248260498</t>
+    <t xml:space="preserve">8.44251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21180152893066</t>
   </si>
   <si>
     <t xml:space="preserve">8.36390495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3194694519043</t>
+    <t xml:space="preserve">8.31947135925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.2442741394043</t>
@@ -3074,31 +3074,31 @@
     <t xml:space="preserve">8.1912956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12806129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09900856018066</t>
+    <t xml:space="preserve">8.12806224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09900760650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11951541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22718334197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36903285980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24598407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29041862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35877799987793</t>
+    <t xml:space="preserve">8.11951637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2271842956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29041767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35877704620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">8.44081020355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46986293792725</t>
+    <t xml:space="preserve">8.46986389160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.40663051605225</t>
@@ -3119,25 +3119,25 @@
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644592285156</t>
+    <t xml:space="preserve">8.46644687652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57496738433838</t>
+    <t xml:space="preserve">8.5749683380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25965690612793</t>
+    <t xml:space="preserve">8.25965595245361</t>
   </si>
   <si>
     <t xml:space="preserve">8.32630729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2425651550293</t>
+    <t xml:space="preserve">8.24256610870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">8.21863842010498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17420482635498</t>
+    <t xml:space="preserve">8.17420387268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.28187370300293</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">8.42030239105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50233554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896533966064</t>
+    <t xml:space="preserve">8.50233459472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896343231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">8.6347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62623882293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6176929473877</t>
+    <t xml:space="preserve">8.6262378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61769390106201</t>
   </si>
   <si>
     <t xml:space="preserve">8.5416431427002</t>
@@ -3206,34 +3206,34 @@
     <t xml:space="preserve">8.63051128387451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53822422027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55360507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42371940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49208164215088</t>
+    <t xml:space="preserve">8.5382251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5536060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42372035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49208068847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.54506015777588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33656024932861</t>
+    <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.33143329620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36561489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2340202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3143424987793</t>
+    <t xml:space="preserve">8.36561393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23401927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31434440612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40492153167725</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23231029510498</t>
+    <t xml:space="preserve">8.32459831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2323112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.2152214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2083854675293</t>
+    <t xml:space="preserve">8.20838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.17933082580566</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166385650635</t>
+    <t xml:space="preserve">8.07166481018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.08875370025635</t>
@@ -3278,16 +3278,16 @@
     <t xml:space="preserve">7.99475812911987</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2391471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33485221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40150356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31776142120361</t>
+    <t xml:space="preserve">8.23914813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33485126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40150260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452899932861</t>
@@ -3299,31 +3299,31 @@
     <t xml:space="preserve">8.26478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36048793792725</t>
+    <t xml:space="preserve">8.36048698425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.25111103057861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16565895080566</t>
+    <t xml:space="preserve">8.16565990447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.31605243682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2169303894043</t>
+    <t xml:space="preserve">8.21692943572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32972526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45106506347656</t>
+    <t xml:space="preserve">8.43055629730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32972621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45106410980225</t>
   </si>
   <si>
     <t xml:space="preserve">8.44935512542725</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">8.47670078277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02358341217041</t>
+    <t xml:space="preserve">9.02358436584473</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
@@ -3359,22 +3359,22 @@
     <t xml:space="preserve">8.78004932403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66041946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82704734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65614700317383</t>
+    <t xml:space="preserve">8.66041851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82704639434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65614604949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.72023391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72450637817383</t>
+    <t xml:space="preserve">8.72450733184814</t>
   </si>
   <si>
     <t xml:space="preserve">8.63905620574951</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">8.75441455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77150440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88686275482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88259124755859</t>
+    <t xml:space="preserve">8.77150535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88686180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88259029388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531490325928</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">8.95522308349609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98085975646973</t>
+    <t xml:space="preserve">8.98085880279541</t>
   </si>
   <si>
     <t xml:space="preserve">8.92104244232178</t>
@@ -3425,49 +3425,49 @@
     <t xml:space="preserve">9.20303058624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212833404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98513221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70741558074951</t>
+    <t xml:space="preserve">9.03212928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98513126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70741653442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.5877857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2887077331543</t>
+    <t xml:space="preserve">8.28870868682861</t>
   </si>
   <si>
     <t xml:space="preserve">8.26136493682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15882396697998</t>
+    <t xml:space="preserve">8.15882301330566</t>
   </si>
   <si>
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2066764831543</t>
+    <t xml:space="preserve">8.20667552947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.35706901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78454971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81872987747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81360292434692</t>
+    <t xml:space="preserve">7.78454923629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81873083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8136043548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.81018590927124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15540599822998</t>
+    <t xml:space="preserve">8.15540504455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.12635231018066</t>
@@ -3476,28 +3476,28 @@
     <t xml:space="preserve">7.8802547454834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71106195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60168504714966</t>
+    <t xml:space="preserve">7.71106290817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
     <t xml:space="preserve">7.61364889144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5469970703125</t>
+    <t xml:space="preserve">7.54699611663818</t>
   </si>
   <si>
     <t xml:space="preserve">7.45129299163818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58459615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64953708648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57434177398682</t>
+    <t xml:space="preserve">7.58459568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64953851699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
     <t xml:space="preserve">7.58288669586182</t>
@@ -3515,25 +3515,25 @@
     <t xml:space="preserve">7.82556676864624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579685211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510301589966</t>
+    <t xml:space="preserve">7.5657958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510396957397</t>
   </si>
   <si>
     <t xml:space="preserve">7.78625965118408</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56237840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72302579879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66491985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77087783813477</t>
+    <t xml:space="preserve">7.56237888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72302532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66491937637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77087736129761</t>
   </si>
   <si>
     <t xml:space="preserve">7.62561225891113</t>
@@ -3542,43 +3542,43 @@
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91785287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95545196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07508182525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14173412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20325946807861</t>
+    <t xml:space="preserve">7.9178524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95545101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07508277893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14173316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20325756072998</t>
   </si>
   <si>
     <t xml:space="preserve">8.2288932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182678222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50062561035156</t>
+    <t xml:space="preserve">8.48182773590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50062656402588</t>
   </si>
   <si>
     <t xml:space="preserve">8.39466762542725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54335117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55787754058838</t>
+    <t xml:space="preserve">8.5433521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5578784942627</t>
   </si>
   <si>
     <t xml:space="preserve">8.68178176879883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68605518341064</t>
+    <t xml:space="preserve">8.68605422973633</t>
   </si>
   <si>
     <t xml:space="preserve">8.73732471466064</t>
@@ -3587,10 +3587,10 @@
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93813323974609</t>
+    <t xml:space="preserve">8.97658634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93813419342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404537200928</t>
@@ -3605,22 +3605,22 @@
     <t xml:space="preserve">8.91677093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90395259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81422901153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6134204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69887161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70314407348633</t>
+    <t xml:space="preserve">8.90395355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81422996520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61342144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67323589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69887256622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70314502716064</t>
   </si>
   <si>
     <t xml:space="preserve">8.74159622192383</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">8.83131980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56215000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92368793487549</t>
+    <t xml:space="preserve">8.5621509552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92368698120117</t>
   </si>
   <si>
     <t xml:space="preserve">9.16629981994629</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">9.24128913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20599937438965</t>
+    <t xml:space="preserve">9.20600032806396</t>
   </si>
   <si>
     <t xml:space="preserve">9.14424324035645</t>
@@ -3659,13 +3659,13 @@
     <t xml:space="preserve">9.1927661895752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98985481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74989032745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43228912353516</t>
+    <t xml:space="preserve">8.98985385894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7498893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43229007720947</t>
   </si>
   <si>
     <t xml:space="preserve">8.15350723266602</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">8.23820114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23996448516846</t>
+    <t xml:space="preserve">8.23996543884277</t>
   </si>
   <si>
     <t xml:space="preserve">8.25760936737061</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">8.4234676361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79929447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73224544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58932495117188</t>
+    <t xml:space="preserve">8.79929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73224449157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58932590484619</t>
   </si>
   <si>
     <t xml:space="preserve">8.57520961761475</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">8.54344940185547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77988529205322</t>
+    <t xml:space="preserve">8.77988624572754</t>
   </si>
   <si>
     <t xml:space="preserve">8.71636581420898</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">8.82223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80458736419678</t>
+    <t xml:space="preserve">8.80458641052246</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635669708252</t>
@@ -3728,25 +3728,25 @@
     <t xml:space="preserve">8.91486549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93692111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84428787231445</t>
+    <t xml:space="preserve">8.93692207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84428691864014</t>
   </si>
   <si>
     <t xml:space="preserve">8.85311031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8151741027832</t>
+    <t xml:space="preserve">8.81517505645752</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57168006896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78694438934326</t>
+    <t xml:space="preserve">8.57168102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78694343566895</t>
   </si>
   <si>
     <t xml:space="preserve">8.75341892242432</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">9.03396606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91045475006104</t>
+    <t xml:space="preserve">8.91045570373535</t>
   </si>
   <si>
     <t xml:space="preserve">8.97662162780762</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55756568908691</t>
+    <t xml:space="preserve">8.5575647354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58756160736084</t>
+    <t xml:space="preserve">8.58756065368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.6157922744751</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">8.8354663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68460655212402</t>
+    <t xml:space="preserve">8.68460559844971</t>
   </si>
   <si>
     <t xml:space="preserve">8.56638813018799</t>
@@ -3803,16 +3803,16 @@
     <t xml:space="preserve">8.37935638427734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34936046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29995632171631</t>
+    <t xml:space="preserve">8.3493595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29995536804199</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10763168334961</t>
+    <t xml:space="preserve">8.10763072967529</t>
   </si>
   <si>
     <t xml:space="preserve">8.25584506988525</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">8.28407669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53639125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39700031280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32818794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70754241943359</t>
+    <t xml:space="preserve">8.53639221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39700126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32818698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70754337310791</t>
   </si>
   <si>
     <t xml:space="preserve">8.45699214935303</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">8.08292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22584915161133</t>
+    <t xml:space="preserve">8.22585010528564</t>
   </si>
   <si>
     <t xml:space="preserve">8.0035285949707</t>
@@ -3851,22 +3851,22 @@
     <t xml:space="preserve">7.95412445068359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9082498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92589378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90471982955933</t>
+    <t xml:space="preserve">7.90824890136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92589426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90472030639648</t>
   </si>
   <si>
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9135422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94706726074219</t>
+    <t xml:space="preserve">7.91354274749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94706773757935</t>
   </si>
   <si>
     <t xml:space="preserve">8.15703678131104</t>
@@ -3875,34 +3875,34 @@
     <t xml:space="preserve">8.04411220550537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78473901748657</t>
+    <t xml:space="preserve">7.78473806381226</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64534664154053</t>
+    <t xml:space="preserve">7.64534711837769</t>
   </si>
   <si>
     <t xml:space="preserve">7.52007150650024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39479541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40538215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51124811172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64711141586304</t>
+    <t xml:space="preserve">7.39479494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40538167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51124858856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64711093902588</t>
   </si>
   <si>
     <t xml:space="preserve">7.43890619277954</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52359962463379</t>
+    <t xml:space="preserve">7.52359914779663</t>
   </si>
   <si>
     <t xml:space="preserve">7.3101019859314</t>
@@ -3917,19 +3917,19 @@
     <t xml:space="preserve">7.73709774017334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75297832489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87472343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88001823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85355091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94353723526001</t>
+    <t xml:space="preserve">7.75297689437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8747239112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88001871109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85355138778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94353818893433</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
@@ -3947,67 +3947,67 @@
     <t xml:space="preserve">8.76047706604004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69871997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50286769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40053081512451</t>
+    <t xml:space="preserve">8.69872093200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50286674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.33524513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48698711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4693431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48169326782227</t>
+    <t xml:space="preserve">8.48698806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46934413909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4816951751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.49404621124268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40935230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28054714202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53109931945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46757888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42699527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37053394317627</t>
+    <t xml:space="preserve">8.40935134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28054809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53109836578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47640037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46757793426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42699718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37053489685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.36347579956055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53286266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55580139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43052577972412</t>
+    <t xml:space="preserve">8.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55580043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4305248260498</t>
   </si>
   <si>
     <t xml:space="preserve">8.2152624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26466751098633</t>
+    <t xml:space="preserve">8.26466655731201</t>
   </si>
   <si>
     <t xml:space="preserve">8.16232967376709</t>
@@ -4028,13 +4028,13 @@
     <t xml:space="preserve">8.29819202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41640949249268</t>
+    <t xml:space="preserve">8.41640853881836</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37406349182129</t>
+    <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
     <t xml:space="preserve">8.4075870513916</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">8.55227184295654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64402294158936</t>
+    <t xml:space="preserve">8.64402389526367</t>
   </si>
   <si>
     <t xml:space="preserve">8.67049026489258</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">8.7887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82046794891357</t>
+    <t xml:space="preserve">8.82046890258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.73400974273682</t>
@@ -4067,25 +4067,25 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456504821777</t>
+    <t xml:space="preserve">8.95456600189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89280986785889</t>
+    <t xml:space="preserve">8.91927719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8619327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8928108215332</t>
   </si>
   <si>
     <t xml:space="preserve">9.11336612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89722061157227</t>
+    <t xml:space="preserve">8.89722156524658</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">9.2809886932373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22805595397949</t>
+    <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
     <t xml:space="preserve">9.15306568145752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14865398406982</t>
+    <t xml:space="preserve">9.14865493774414</t>
   </si>
   <si>
     <t xml:space="preserve">9.13101100921631</t>
@@ -4124,22 +4124,22 @@
     <t xml:space="preserve">9.08248805999756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0427885055542</t>
+    <t xml:space="preserve">9.04278755187988</t>
   </si>
   <si>
     <t xml:space="preserve">9.93383407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74415588378906</t>
+    <t xml:space="preserve">10.0485229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">10.1411561965942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1720333099365</t>
+    <t xml:space="preserve">10.1720342636108</t>
   </si>
   <si>
     <t xml:space="preserve">10.0264663696289</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">10.0705785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87207698822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706726074219</t>
+    <t xml:space="preserve">9.87207794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706630706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.77944469451904</t>
@@ -4163,16 +4163,16 @@
     <t xml:space="preserve">10.1191005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99117851257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5116891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3440675735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5778560638428</t>
+    <t xml:space="preserve">9.99117755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5116901397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3440685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5778570175171</t>
   </si>
   <si>
     <t xml:space="preserve">10.6131458282471</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">10.6925458908081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7278347015381</t>
+    <t xml:space="preserve">10.7278337478638</t>
   </si>
   <si>
     <t xml:space="preserve">10.8425235748291</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">11.0013236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9219245910645</t>
+    <t xml:space="preserve">10.9219236373901</t>
   </si>
   <si>
     <t xml:space="preserve">10.9175128936768</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">10.789589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160572052002</t>
+    <t xml:space="preserve">10.8160581588745</t>
   </si>
   <si>
     <t xml:space="preserve">10.868989944458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9395685195923</t>
+    <t xml:space="preserve">10.939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">10.8248796463013</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">10.9439792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.018967628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116027832031</t>
+    <t xml:space="preserve">11.0189685821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
     <t xml:space="preserve">11.0454359054565</t>
@@ -4244,22 +4244,22 @@
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.09836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8645792007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6969566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660795211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.639612197876</t>
+    <t xml:space="preserve">11.0983686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8645782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528453826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6396131515503</t>
   </si>
   <si>
     <t xml:space="preserve">10.4852237701416</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">10.6352014541626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8274974822998</t>
+    <t xml:space="preserve">10.8274984359741</t>
   </si>
   <si>
     <t xml:space="preserve">10.7820806503296</t>
@@ -4280,22 +4280,22 @@
     <t xml:space="preserve">10.6276607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6594533920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6639957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7684555053711</t>
+    <t xml:space="preserve">10.6594543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6639947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7684545516968</t>
   </si>
   <si>
     <t xml:space="preserve">10.8093309402466</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7593717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7321214675903</t>
+    <t xml:space="preserve">10.7593727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.732120513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7366628646851</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">10.5913276672363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5686197280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.623119354248</t>
+    <t xml:space="preserve">10.5686187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6231203079224</t>
   </si>
   <si>
     <t xml:space="preserve">10.8138723373413</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">10.5822439193726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775392532349</t>
+    <t xml:space="preserve">10.7775382995605</t>
   </si>
   <si>
     <t xml:space="preserve">10.8774576187134</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">10.6776208877563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5958700180054</t>
+    <t xml:space="preserve">10.5958690643311</t>
   </si>
   <si>
     <t xml:space="preserve">10.5640773773193</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">10.9910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9773759841919</t>
+    <t xml:space="preserve">10.9773750305176</t>
   </si>
   <si>
     <t xml:space="preserve">10.8729152679443</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">10.5277433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5549936294556</t>
+    <t xml:space="preserve">10.5549945831299</t>
   </si>
   <si>
     <t xml:space="preserve">10.3687829971313</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">10.3778667449951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3824081420898</t>
+    <t xml:space="preserve">10.3824090957642</t>
   </si>
   <si>
     <t xml:space="preserve">10.2597808837891</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">10.2416143417358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1598625183105</t>
+    <t xml:space="preserve">10.1598634719849</t>
   </si>
   <si>
     <t xml:space="preserve">10.1462373733521</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">10.0826539993286</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0236101150513</t>
+    <t xml:space="preserve">10.0236110687256</t>
   </si>
   <si>
     <t xml:space="preserve">10.1916551589966</t>
@@ -4448,16 +4448,16 @@
     <t xml:space="preserve">10.1416959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1099042892456</t>
+    <t xml:space="preserve">10.1099033355713</t>
   </si>
   <si>
     <t xml:space="preserve">10.3642406463623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4187421798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4414510726929</t>
+    <t xml:space="preserve">10.4187412261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4414501190186</t>
   </si>
   <si>
     <t xml:space="preserve">10.4459924697876</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">10.3551568984985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4278240203857</t>
+    <t xml:space="preserve">10.4278249740601</t>
   </si>
   <si>
     <t xml:space="preserve">10.5413684844971</t>
@@ -4481,16 +4481,16 @@
     <t xml:space="preserve">10.7275800704956</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912460327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4505338668823</t>
+    <t xml:space="preserve">10.6912469863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4505348205566</t>
   </si>
   <si>
     <t xml:space="preserve">10.4596176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3006563186646</t>
+    <t xml:space="preserve">10.3006572723389</t>
   </si>
   <si>
     <t xml:space="preserve">10.1734886169434</t>
@@ -4499,25 +4499,25 @@
     <t xml:space="preserve">10.059944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0917358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89190006256104</t>
+    <t xml:space="preserve">10.2325315475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0917367935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89190101623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.62847995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48768520355225</t>
+    <t xml:space="preserve">9.48768615722656</t>
   </si>
   <si>
     <t xml:space="preserve">9.5648946762085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62393760681152</t>
+    <t xml:space="preserve">9.62393856048584</t>
   </si>
   <si>
     <t xml:space="preserve">9.79652404785156</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">9.65573024749756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75564765930176</t>
+    <t xml:space="preserve">9.75564861297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.64210510253906</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">9.71023082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72385597229004</t>
+    <t xml:space="preserve">9.72385692596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.59668731689453</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">9.65118885040283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68752193450928</t>
+    <t xml:space="preserve">9.68752288818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.67389678955078</t>
@@ -4598,16 +4598,16 @@
     <t xml:space="preserve">9.9009838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77381610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83285808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81469058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74656391143799</t>
+    <t xml:space="preserve">9.7738151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83285713195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7465648651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.80106544494629</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">10.2961149215698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3460741043091</t>
+    <t xml:space="preserve">10.3460750579834</t>
   </si>
   <si>
     <t xml:space="preserve">10.3279066085815</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">10.4868679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3960332870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3506164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4051160812378</t>
+    <t xml:space="preserve">10.396032333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3506155014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4051170349121</t>
   </si>
   <si>
     <t xml:space="preserve">10.2279891967773</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">10.2734069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4550762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4323673248291</t>
+    <t xml:space="preserve">10.4550752639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4323663711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.4005746841431</t>
@@ -4670,10 +4670,10 @@
     <t xml:space="preserve">10.3324489593506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3188238143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0690279006958</t>
+    <t xml:space="preserve">10.3188228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0690288543701</t>
   </si>
   <si>
     <t xml:space="preserve">10.0190687179565</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">10.0463199615479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009021759033</t>
+    <t xml:space="preserve">10.0009031295776</t>
   </si>
   <si>
     <t xml:space="preserve">10.1280708312988</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">10.2143630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1189880371094</t>
+    <t xml:space="preserve">10.1189870834351</t>
   </si>
   <si>
     <t xml:space="preserve">9.94185924530029</t>
@@ -4706,28 +4706,28 @@
     <t xml:space="preserve">9.75110626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80560779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6602725982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73748207092285</t>
+    <t xml:space="preserve">9.80560684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66027164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73748111724854</t>
   </si>
   <si>
     <t xml:space="preserve">9.74202346801758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78289985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70114707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46043586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29693222045898</t>
+    <t xml:space="preserve">9.78289890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70114803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46043491363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2969331741333</t>
   </si>
   <si>
     <t xml:space="preserve">9.51493740081787</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">9.49676895141602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.410475730896</t>
+    <t xml:space="preserve">9.41047668457031</t>
   </si>
   <si>
     <t xml:space="preserve">9.35143375396729</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">9.57397937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63302135467529</t>
+    <t xml:space="preserve">9.63302040100098</t>
   </si>
   <si>
     <t xml:space="preserve">9.34689235687256</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">9.20155715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06530380249023</t>
+    <t xml:space="preserve">9.06530475616455</t>
   </si>
   <si>
     <t xml:space="preserve">9.03805446624756</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">8.85184288024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90634441375732</t>
+    <t xml:space="preserve">8.90634346008301</t>
   </si>
   <si>
     <t xml:space="preserve">8.95176029205322</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">9.21972274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36505889892578</t>
+    <t xml:space="preserve">9.3650598526001</t>
   </si>
   <si>
     <t xml:space="preserve">9.29239082336426</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">9.31964206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43772792816162</t>
+    <t xml:space="preserve">9.4377269744873</t>
   </si>
   <si>
     <t xml:space="preserve">9.40139293670654</t>
@@ -5531,7 +5531,7 @@
     <t xml:space="preserve">9.41499996185303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53499984741211</t>
+    <t xml:space="preserve">9.44499969482422</t>
   </si>
 </sst>
 </file>
@@ -70974,22 +70974,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6931712963</v>
+        <v>45968.6939236111</v>
       </c>
       <c r="B2505" t="n">
-        <v>1135493</v>
+        <v>1354762</v>
       </c>
       <c r="C2505" t="n">
-        <v>9.55000019073486</v>
+        <v>9.57999992370605</v>
       </c>
       <c r="D2505" t="n">
-        <v>9.42000007629395</v>
+        <v>9.32999992370605</v>
       </c>
       <c r="E2505" t="n">
-        <v>9.44999980926514</v>
+        <v>9.57999992370605</v>
       </c>
       <c r="F2505" t="n">
-        <v>9.53499984741211</v>
+        <v>9.44499969482422</v>
       </c>
       <c r="G2505" t="s">
         <v>1839</v>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="1843">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,145 +38,145 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433786392212</t>
+    <t xml:space="preserve">3.4243381023407</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296906471252</t>
+    <t xml:space="preserve">3.46296882629395</t>
   </si>
   <si>
     <t xml:space="preserve">3.4560706615448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46986722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331643104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845638275146</t>
+    <t xml:space="preserve">3.46986770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812421798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845614433289</t>
   </si>
   <si>
     <t xml:space="preserve">3.34707689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26981496810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637099266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324872970581</t>
+    <t xml:space="preserve">3.26981472969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28637146949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324896812439</t>
   </si>
   <si>
     <t xml:space="preserve">3.03803086280823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13874650001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288640022278</t>
+    <t xml:space="preserve">3.13874697685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1428861618042</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16496014595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736701011658</t>
+    <t xml:space="preserve">3.16496062278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736724853516</t>
   </si>
   <si>
     <t xml:space="preserve">3.14564514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1994526386261</t>
+    <t xml:space="preserve">3.19945216178894</t>
   </si>
   <si>
     <t xml:space="preserve">3.30430674552917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27119517326355</t>
+    <t xml:space="preserve">3.27119565010071</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222159385681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20911002159119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20773029327393</t>
+    <t xml:space="preserve">3.20911026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2077305316925</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631920814514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06700444221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00077962875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0021595954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802088737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837324142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114315032959</t>
+    <t xml:space="preserve">3.06700396537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00078010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00216007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802041053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837300300598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114291191101</t>
   </si>
   <si>
     <t xml:space="preserve">3.13322806358337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11115384101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151640892029</t>
+    <t xml:space="preserve">3.11115312576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151688575745</t>
   </si>
   <si>
     <t xml:space="preserve">3.13046884536743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1415057182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12495040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11805200576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808288574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17323851585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531297683716</t>
+    <t xml:space="preserve">3.14150643348694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12494993209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11805152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808264732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1732382774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531273841858</t>
   </si>
   <si>
     <t xml:space="preserve">3.18703532218933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013739585876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427562713623</t>
+    <t xml:space="preserve">3.09321761131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255399703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427610397339</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636101722717</t>
@@ -185,94 +185,94 @@
     <t xml:space="preserve">3.20635032653809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19807267189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10563445091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04906868934631</t>
+    <t xml:space="preserve">3.19807314872742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10563468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04906797409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.05458688735962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03941082954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00491905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0518274307251</t>
+    <t xml:space="preserve">3.03941059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00491881370544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05182790756226</t>
   </si>
   <si>
     <t xml:space="preserve">2.98422408103943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05044794082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05320715904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595664024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457667350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147459983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767874717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561402320862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873676300049</t>
+    <t xml:space="preserve">3.05044841766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0532078742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595616340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147436141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629830360413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767850875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0256142616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873628616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.0876989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14978432655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0559663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01319670677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0297532081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01871562004089</t>
+    <t xml:space="preserve">3.14978361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05596685409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838345527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01319742202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02975296974182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01871538162231</t>
   </si>
   <si>
     <t xml:space="preserve">2.96766781806946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95249199867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94421339035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869519233704</t>
+    <t xml:space="preserve">2.95249152183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94421362876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869471549988</t>
   </si>
   <si>
     <t xml:space="preserve">2.93593525886536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02235913276672</t>
+    <t xml:space="preserve">3.02235889434814</t>
   </si>
   <si>
     <t xml:space="preserve">3.02659201622009</t>
@@ -293,46 +293,46 @@
     <t xml:space="preserve">3.06892204284668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06610035896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01389288902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0209481716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00683832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929114341736</t>
+    <t xml:space="preserve">3.06609988212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01389312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02094793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00683760643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929138183594</t>
   </si>
   <si>
     <t xml:space="preserve">3.01671528816223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03505825996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99978280067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9645082950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083227157593</t>
+    <t xml:space="preserve">3.03505802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99978303909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714959144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083203315735</t>
   </si>
   <si>
     <t xml:space="preserve">2.87843704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93205547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702608108521</t>
+    <t xml:space="preserve">2.93205499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702631950378</t>
   </si>
   <si>
     <t xml:space="preserve">2.91089010238647</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61034727096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67525362968445</t>
+    <t xml:space="preserve">2.61034750938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67525315284729</t>
   </si>
   <si>
     <t xml:space="preserve">2.71899437904358</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">2.79659938812256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79518818855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162806510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610701560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87279319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94475388526917</t>
+    <t xml:space="preserve">2.79518842697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162782669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83610725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87279367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94475412368774</t>
   </si>
   <si>
     <t xml:space="preserve">2.97438526153564</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">3.02518129348755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04211258888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597661018372</t>
+    <t xml:space="preserve">3.04211330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597708702087</t>
   </si>
   <si>
     <t xml:space="preserve">3.03364729881287</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">3.07033324241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05481195449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03788018226624</t>
+    <t xml:space="preserve">3.05481171607971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03787994384766</t>
   </si>
   <si>
     <t xml:space="preserve">3.05199027061462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17333579063416</t>
+    <t xml:space="preserve">3.17333626747131</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204786300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1549928188324</t>
+    <t xml:space="preserve">3.15499305725098</t>
   </si>
   <si>
     <t xml:space="preserve">3.14088296890259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14793825149536</t>
+    <t xml:space="preserve">3.14793801307678</t>
   </si>
   <si>
     <t xml:space="preserve">3.10843014717102</t>
@@ -419,43 +419,43 @@
     <t xml:space="preserve">3.09149789810181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13241672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947153091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15075993537903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419678688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08444333076477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02800273895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01248216629028</t>
+    <t xml:space="preserve">3.13241696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947200775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15076041221619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419726371765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08444309234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02800321578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0124819278717</t>
   </si>
   <si>
     <t xml:space="preserve">3.02376985549927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07174444198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045579910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03646874427795</t>
+    <t xml:space="preserve">3.07174396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604555606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03646898269653</t>
   </si>
   <si>
     <t xml:space="preserve">3.09008693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19732332229614</t>
+    <t xml:space="preserve">3.19732260704041</t>
   </si>
   <si>
     <t xml:space="preserve">3.21002173423767</t>
@@ -464,73 +464,73 @@
     <t xml:space="preserve">3.18462419509888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21284413337708</t>
+    <t xml:space="preserve">3.2128438949585</t>
   </si>
   <si>
     <t xml:space="preserve">3.21707701683044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27774953842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351641654968</t>
+    <t xml:space="preserve">3.27774977684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351665496826</t>
   </si>
   <si>
     <t xml:space="preserve">3.22130966186523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20861053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19873356819153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18180227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15358185768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15217113494873</t>
+    <t xml:space="preserve">3.20861101150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19873380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18180179595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1535816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15217065811157</t>
   </si>
   <si>
     <t xml:space="preserve">3.16628074645996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12536215782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08726477622986</t>
+    <t xml:space="preserve">3.12536191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125206947327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08726501464844</t>
   </si>
   <si>
     <t xml:space="preserve">3.09714198112488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867621421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07738780975342</t>
+    <t xml:space="preserve">3.11548471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.077388048172</t>
   </si>
   <si>
     <t xml:space="preserve">3.06186699867249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99696111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92923331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95322060585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95180940628052</t>
+    <t xml:space="preserve">2.99696159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92923307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95322012901306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95180916786194</t>
   </si>
   <si>
     <t xml:space="preserve">2.93910980224609</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">2.95886397361755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92782163619995</t>
+    <t xml:space="preserve">2.92782211303711</t>
   </si>
   <si>
     <t xml:space="preserve">2.98002910614014</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">3.04493498802185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05622315406799</t>
+    <t xml:space="preserve">3.05622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.0195369720459</t>
@@ -563,31 +563,31 @@
     <t xml:space="preserve">2.99554991722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04070162773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0181257724762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9630970954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92641067504883</t>
+    <t xml:space="preserve">3.04070210456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01812601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96309661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92641091346741</t>
   </si>
   <si>
     <t xml:space="preserve">2.98849534988403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87138223648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8572723865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86856031417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358922958374</t>
+    <t xml:space="preserve">2.87138247489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85727190971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86856007575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358899116516</t>
   </si>
   <si>
     <t xml:space="preserve">2.95604228973389</t>
@@ -596,58 +596,58 @@
     <t xml:space="preserve">2.88690328598022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89819121360779</t>
+    <t xml:space="preserve">2.89819097518921</t>
   </si>
   <si>
     <t xml:space="preserve">2.85303950309753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034037590027</t>
+    <t xml:space="preserve">2.84034013748169</t>
   </si>
   <si>
     <t xml:space="preserve">2.82199740409851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84457302093506</t>
+    <t xml:space="preserve">2.84457325935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.85021734237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78390026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82340812683105</t>
+    <t xml:space="preserve">2.78390049934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377770423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82340836524963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75568032264709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76132440567017</t>
+    <t xml:space="preserve">2.76132464408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.80929827690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8925473690033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89395809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89960217475891</t>
+    <t xml:space="preserve">2.89254713058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893958568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89960241317749</t>
   </si>
   <si>
     <t xml:space="preserve">2.86009407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90665721893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831424713135</t>
+    <t xml:space="preserve">2.90665698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831400871277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91230082511902</t>
@@ -659,58 +659,58 @@
     <t xml:space="preserve">3.09432005882263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08020997047424</t>
+    <t xml:space="preserve">3.08021020889282</t>
   </si>
   <si>
     <t xml:space="preserve">3.08303165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1056079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585381507874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1352391242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13806104660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051434516907</t>
+    <t xml:space="preserve">3.10560846328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585405349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511609077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13806080818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063714027405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051339149475</t>
   </si>
   <si>
     <t xml:space="preserve">3.20437788963318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19591212272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12253975868225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278606414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06751084327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17898011207581</t>
+    <t xml:space="preserve">3.19591188430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12254047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573101997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290909767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06751132011414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1183066368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17898035049438</t>
   </si>
   <si>
     <t xml:space="preserve">3.13665008544922</t>
@@ -719,46 +719,46 @@
     <t xml:space="preserve">3.07456564903259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10701894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09855270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529647827148</t>
+    <t xml:space="preserve">3.10701870918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529671669006</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25376296043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31443524360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228679656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651968002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4456582069397</t>
+    <t xml:space="preserve">3.25376319885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891514778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3144359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3722870349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651944160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44565868377686</t>
   </si>
   <si>
     <t xml:space="preserve">3.41461706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44283652305603</t>
+    <t xml:space="preserve">3.44283676147461</t>
   </si>
   <si>
     <t xml:space="preserve">3.40756154060364</t>
@@ -767,40 +767,40 @@
     <t xml:space="preserve">3.40050673484802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105717658997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160666465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47811198234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48798871040344</t>
+    <t xml:space="preserve">3.48657703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338696479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105669975281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47811150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48798847198486</t>
   </si>
   <si>
     <t xml:space="preserve">3.52185273170471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50633096694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222135543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455090522766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52749752998352</t>
+    <t xml:space="preserve">3.50633120536804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222111701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53455185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5274965763092</t>
   </si>
   <si>
     <t xml:space="preserve">3.54866170883179</t>
@@ -809,64 +809,64 @@
     <t xml:space="preserve">3.51056456565857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59099149703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924415588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273907661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65095949172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66154170036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506838798523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921215057373</t>
+    <t xml:space="preserve">3.59099125862122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568379402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393621444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209832191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924391746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6227388381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.650958776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.661541223526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506886482239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921167373657</t>
   </si>
   <si>
     <t xml:space="preserve">3.63332176208496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59804630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73752236366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68667149543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72299361228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7193615436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70483303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124629974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195948600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8283269405365</t>
+    <t xml:space="preserve">3.59804606437683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73752284049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68667197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72299385070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71936202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7048327922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124677658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195996284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832765579224</t>
   </si>
   <si>
     <t xml:space="preserve">3.81379842758179</t>
@@ -875,37 +875,37 @@
     <t xml:space="preserve">3.84285616874695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85012054443359</t>
+    <t xml:space="preserve">3.85012006759644</t>
   </si>
   <si>
     <t xml:space="preserve">3.88644218444824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86101698875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648823738098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8246955871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922410011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451161384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097141265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455766677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087859153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639636993408</t>
+    <t xml:space="preserve">3.86101746559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648871421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469534873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922433853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451066017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097093582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455647468567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92639589309692</t>
   </si>
   <si>
     <t xml:space="preserve">3.9082350730896</t>
@@ -914,94 +914,94 @@
     <t xml:space="preserve">3.91913247108459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81016635894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68303990364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6576144695282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6133017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201833724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60313200950623</t>
+    <t xml:space="preserve">3.81016659736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65761399269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330151557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201857566833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6031322479248</t>
   </si>
   <si>
     <t xml:space="preserve">3.59150862693787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.624924659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214298248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6307361125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030427932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218998908997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65035080909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7157289981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662687301636</t>
+    <t xml:space="preserve">3.62492442131042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214345932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030332565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65034937858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71572971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662615776062</t>
   </si>
   <si>
     <t xml:space="preserve">3.87191367149353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96635127067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908570289612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356935501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352306365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04989004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07894802093506</t>
+    <t xml:space="preserve">3.96635007858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366050720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908641815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998286247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04989147186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894897460938</t>
   </si>
   <si>
     <t xml:space="preserve">4.00267219543457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95182180404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9154999256134</t>
+    <t xml:space="preserve">3.95182156562805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91549968719482</t>
   </si>
   <si>
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177575111389</t>
+    <t xml:space="preserve">3.99540829658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177598953247</t>
   </si>
   <si>
     <t xml:space="preserve">4.02446556091309</t>
@@ -1010,46 +1010,46 @@
     <t xml:space="preserve">4.04262638092041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10437440872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271824836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464953422546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8973388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98814368247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545363426208</t>
+    <t xml:space="preserve">4.10437345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271872520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89733862876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98814344406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9554545879364</t>
   </si>
   <si>
     <t xml:space="preserve">3.93002820014954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01720142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88280987739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07531595230103</t>
+    <t xml:space="preserve">4.01720094680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88281035423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07531642913818</t>
   </si>
   <si>
     <t xml:space="preserve">4.06805181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14795923233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06078767776489</t>
+    <t xml:space="preserve">4.14795970916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04625844955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06078720092773</t>
   </si>
   <si>
     <t xml:space="preserve">4.11527013778687</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">4.12253475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18065023422241</t>
+    <t xml:space="preserve">4.18064975738525</t>
   </si>
   <si>
     <t xml:space="preserve">4.1588568687439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18791389465332</t>
+    <t xml:space="preserve">4.18791437149048</t>
   </si>
   <si>
     <t xml:space="preserve">4.1661205291748</t>
@@ -1076,25 +1076,25 @@
     <t xml:space="preserve">4.17338562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09710931777954</t>
+    <t xml:space="preserve">4.09710884094238</t>
   </si>
   <si>
     <t xml:space="preserve">4.14069557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24602890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22060346603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26055765151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2169713973999</t>
+    <t xml:space="preserve">4.12979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24602842330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22060298919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26055812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
     <t xml:space="preserve">4.25329351425171</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">4.26419019699097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27508640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701816558838</t>
+    <t xml:space="preserve">4.27508735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17701768875122</t>
   </si>
   <si>
     <t xml:space="preserve">4.08984470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30777597427368</t>
+    <t xml:space="preserve">4.30777645111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.29687976837158</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">4.4276385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51481151580811</t>
+    <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
     <t xml:space="preserve">4.54023599624634</t>
@@ -1136,55 +1136,55 @@
     <t xml:space="preserve">4.59835147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72184562683105</t>
+    <t xml:space="preserve">4.72184610366821</t>
   </si>
   <si>
     <t xml:space="preserve">4.56929349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56202936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62014484405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59471893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60924768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48938512802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45669651031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51844310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52207565307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49301767349243</t>
+    <t xml:space="preserve">4.56202983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62014532089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59471940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6092472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4893856048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45669555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51844358444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33683347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52207469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49301815032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.50391483306885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49665069580078</t>
+    <t xml:space="preserve">4.49665021896362</t>
   </si>
   <si>
     <t xml:space="preserve">4.46032810211182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45306348800659</t>
+    <t xml:space="preserve">4.45306396484375</t>
   </si>
   <si>
     <t xml:space="preserve">4.46759271621704</t>
@@ -1196,88 +1196,88 @@
     <t xml:space="preserve">4.54750108718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43853569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37315559387207</t>
+    <t xml:space="preserve">4.53660345077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37315607070923</t>
   </si>
   <si>
     <t xml:space="preserve">4.39131689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42037439346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29324722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40947818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5111780166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42400646209717</t>
+    <t xml:space="preserve">4.42037391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29324769973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40947771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51117897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42400598526001</t>
   </si>
   <si>
     <t xml:space="preserve">4.31140851974487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28235054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2060751914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12616682052612</t>
+    <t xml:space="preserve">4.28235149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20607423782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12616634368896</t>
   </si>
   <si>
     <t xml:space="preserve">4.23150062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14432716369629</t>
+    <t xml:space="preserve">4.14432764053345</t>
   </si>
   <si>
     <t xml:space="preserve">3.97361469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94092535972595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97724723815918</t>
+    <t xml:space="preserve">3.94092559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9772469997406</t>
   </si>
   <si>
     <t xml:space="preserve">4.08258104324341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15522432327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16975259780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44579982757568</t>
+    <t xml:space="preserve">4.15522480010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.169753074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44579935073853</t>
   </si>
   <si>
     <t xml:space="preserve">4.40584516525269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4167423248291</t>
+    <t xml:space="preserve">4.41674137115479</t>
   </si>
   <si>
     <t xml:space="preserve">4.59108734130859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61287975311279</t>
+    <t xml:space="preserve">4.61288070678711</t>
   </si>
   <si>
     <t xml:space="preserve">4.55113315582275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57655906677246</t>
+    <t xml:space="preserve">4.57655811309814</t>
   </si>
   <si>
     <t xml:space="preserve">4.52933979034424</t>
@@ -1286,37 +1286,37 @@
     <t xml:space="preserve">4.52570772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53297233581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67825937271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64920282363892</t>
+    <t xml:space="preserve">4.53297138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67825984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920139312744</t>
   </si>
   <si>
     <t xml:space="preserve">4.67099523544312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64557027816772</t>
+    <t xml:space="preserve">4.64556980133057</t>
   </si>
   <si>
     <t xml:space="preserve">4.65283441543579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75816774368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75090360641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76180028915405</t>
+    <t xml:space="preserve">4.75816822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75090312957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76179981231689</t>
   </si>
   <si>
     <t xml:space="preserve">4.7254786491394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68552446365356</t>
+    <t xml:space="preserve">4.68552398681641</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911024093628</t>
@@ -1325,64 +1325,64 @@
     <t xml:space="preserve">4.65646648406982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84534025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81265115737915</t>
+    <t xml:space="preserve">4.84533977508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81265068054199</t>
   </si>
   <si>
     <t xml:space="preserve">4.81991529464722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83807563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88166236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8489727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91798448562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89255905151367</t>
+    <t xml:space="preserve">4.83807611465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88166189193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84897232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91798400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89255857467651</t>
   </si>
   <si>
     <t xml:space="preserve">4.95430612564087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94704151153564</t>
+    <t xml:space="preserve">4.9470419883728</t>
   </si>
   <si>
     <t xml:space="preserve">4.93977737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93251276016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99062728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340896606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713314056396</t>
+    <t xml:space="preserve">4.93251323699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99062776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713266372681</t>
   </si>
   <si>
     <t xml:space="preserve">4.7330756187439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87888193130493</t>
+    <t xml:space="preserve">4.87888145446777</t>
   </si>
   <si>
     <t xml:space="preserve">4.86018800735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82654142379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75176858901978</t>
+    <t xml:space="preserve">4.82654094696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
     <t xml:space="preserve">4.6508264541626</t>
@@ -1391,28 +1391,28 @@
     <t xml:space="preserve">4.49380540847778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62091732025146</t>
+    <t xml:space="preserve">4.62091779708862</t>
   </si>
   <si>
     <t xml:space="preserve">4.67699718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63587141036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7480297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72185945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690584182739</t>
+    <t xml:space="preserve">4.63587236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74803018569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7218599319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690536499023</t>
   </si>
   <si>
     <t xml:space="preserve">4.57979297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75924634933472</t>
+    <t xml:space="preserve">4.75924587249756</t>
   </si>
   <si>
     <t xml:space="preserve">4.83027982711792</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">4.93496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85644960403442</t>
+    <t xml:space="preserve">4.85645008087158</t>
   </si>
   <si>
     <t xml:space="preserve">4.81532526016235</t>
@@ -1433,46 +1433,46 @@
     <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91626787185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90505170822144</t>
+    <t xml:space="preserve">4.91626739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90505218505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.8826208114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93869924545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03216457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01721000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13684511184692</t>
+    <t xml:space="preserve">4.93869972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9648699760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03216409683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01721048355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13684558868408</t>
   </si>
   <si>
     <t xml:space="preserve">5.05833387374878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98356342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89757537841797</t>
+    <t xml:space="preserve">4.98356246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89757442474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.1293683052063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24900341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37985467910767</t>
+    <t xml:space="preserve">5.2490029335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37985515594482</t>
   </si>
   <si>
     <t xml:space="preserve">5.31629848480225</t>
@@ -1484,61 +1484,61 @@
     <t xml:space="preserve">5.34246873855591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09945917129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01347160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17796945571899</t>
+    <t xml:space="preserve">5.09945964813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0134711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17796993255615</t>
   </si>
   <si>
     <t xml:space="preserve">5.20040130615234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23404979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787954330444</t>
+    <t xml:space="preserve">5.23404932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787858963013</t>
   </si>
   <si>
     <t xml:space="preserve">5.21535587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22283315658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666242599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11815166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04337978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99851655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11067533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17049217224121</t>
+    <t xml:space="preserve">5.22283267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11815214157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04338073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99851703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11067485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17049264907837</t>
   </si>
   <si>
     <t xml:space="preserve">5.04711866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441421508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581163406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97982406616211</t>
+    <t xml:space="preserve">5.11441326141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97982358932495</t>
   </si>
   <si>
     <t xml:space="preserve">4.95739221572876</t>
@@ -1547,64 +1547,64 @@
     <t xml:space="preserve">5.03964138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05459642410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18544769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09572172164917</t>
+    <t xml:space="preserve">5.05459594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08076620101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18544721603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09572076797485</t>
   </si>
   <si>
     <t xml:space="preserve">5.2116174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88635873794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92000579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77420043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073606491089</t>
+    <t xml:space="preserve">4.8863582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.920006275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77420091629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073511123657</t>
   </si>
   <si>
     <t xml:space="preserve">4.66951942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71064472198486</t>
+    <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
     <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68447399139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56857776641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58727121353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69568967819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56110000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40781736373901</t>
+    <t xml:space="preserve">4.68447351455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5685772895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58727073669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6956901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
     <t xml:space="preserve">4.61344051361084</t>
@@ -1613,55 +1613,55 @@
     <t xml:space="preserve">4.59848594665527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75550699234009</t>
+    <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79289293289185</t>
+    <t xml:space="preserve">4.79289245605469</t>
   </si>
   <si>
     <t xml:space="preserve">4.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78915548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77793884277344</t>
+    <t xml:space="preserve">4.78915500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167772293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7779393196106</t>
   </si>
   <si>
     <t xml:space="preserve">4.87140417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8377571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68821287155151</t>
+    <t xml:space="preserve">4.83775615692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68821239471436</t>
   </si>
   <si>
     <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74055337905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60222482681274</t>
+    <t xml:space="preserve">4.74055242538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60222434997559</t>
   </si>
   <si>
     <t xml:space="preserve">4.54988431930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5237135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997518539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48632764816284</t>
+    <t xml:space="preserve">4.52371406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.486328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.41903209686279</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">4.46015739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6433482170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456485748291</t>
+    <t xml:space="preserve">4.64334917068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204214096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456581115723</t>
   </si>
   <si>
     <t xml:space="preserve">4.76298427581787</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">4.98730134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14806127548218</t>
+    <t xml:space="preserve">5.14806175231934</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927696228027</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">5.21909427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22657203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18918609619141</t>
+    <t xml:space="preserve">5.22657108306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18918561935425</t>
   </si>
   <si>
     <t xml:space="preserve">5.15179967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20414066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37237739562988</t>
+    <t xml:space="preserve">5.20414018630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37237787246704</t>
   </si>
   <si>
     <t xml:space="preserve">5.1667537689209</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">5.34620761871338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09018993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87335109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79483985900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7611927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81353378295898</t>
+    <t xml:space="preserve">6.09019041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87335157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79484081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81353330612183</t>
   </si>
   <si>
     <t xml:space="preserve">5.79110145568848</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">5.87708950042725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92195272445679</t>
+    <t xml:space="preserve">5.92195320129395</t>
   </si>
   <si>
     <t xml:space="preserve">5.98924779891968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01167964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02663421630859</t>
+    <t xml:space="preserve">6.01167917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02663373947144</t>
   </si>
   <si>
     <t xml:space="preserve">5.96307754516602</t>
@@ -1769,19 +1769,19 @@
     <t xml:space="preserve">6.0079402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92569208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93316888809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90699911117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94064569473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0789737701416</t>
+    <t xml:space="preserve">5.92569160461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93316841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90699815750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94064617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07897424697876</t>
   </si>
   <si>
     <t xml:space="preserve">5.93690729141235</t>
@@ -1790,61 +1790,61 @@
     <t xml:space="preserve">5.95933866500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89952087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89578199386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8808274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94812250137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95560026168823</t>
+    <t xml:space="preserve">5.89952182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89578294754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88082838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94812297821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95560073852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.97429275512695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02114152908325</t>
+    <t xml:space="preserve">6.02114200592041</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84066104888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75234031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.694739818573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71777963638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68321990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66402006149292</t>
+    <t xml:space="preserve">5.84066152572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7523398399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69474029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778059005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68322086334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66402053833008</t>
   </si>
   <si>
     <t xml:space="preserve">5.66786003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78306102752686</t>
+    <t xml:space="preserve">5.7830605506897</t>
   </si>
   <si>
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87522077560425</t>
+    <t xml:space="preserve">5.76002073287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87522125244141</t>
   </si>
   <si>
     <t xml:space="preserve">5.82146024703979</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">5.69858026504517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64481973648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60642004013062</t>
+    <t xml:space="preserve">5.64482021331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60641956329346</t>
   </si>
   <si>
     <t xml:space="preserve">5.77538061141968</t>
@@ -1868,25 +1868,25 @@
     <t xml:space="preserve">5.72162008285522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81762075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78690052032471</t>
+    <t xml:space="preserve">5.81762027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78690004348755</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05570125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28226232528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474174499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09026145935059</t>
+    <t xml:space="preserve">6.05570220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28226280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474126815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09026098251343</t>
   </si>
   <si>
     <t xml:space="preserve">6.12866163253784</t>
@@ -1895,76 +1895,76 @@
     <t xml:space="preserve">6.22850179672241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19394159317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06722211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10178184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25154256820679</t>
+    <t xml:space="preserve">6.19394207000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06722116470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10178136825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25154304504395</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090177536011</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16706228256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29378271102905</t>
+    <t xml:space="preserve">6.1670618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29378175735474</t>
   </si>
   <si>
     <t xml:space="preserve">6.39746284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43586301803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46274328231812</t>
+    <t xml:space="preserve">6.43586254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4627423286438</t>
   </si>
   <si>
     <t xml:space="preserve">6.38210248947144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35522174835205</t>
+    <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
     <t xml:space="preserve">6.44738340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52802276611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954315185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57410383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58946323394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786388397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80450487136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138465881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522319793701</t>
+    <t xml:space="preserve">6.5280237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57410335540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58946371078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018299102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322328567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80450391769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522367477417</t>
   </si>
   <si>
     <t xml:space="preserve">6.78914403915405</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">6.76610422134399</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98114490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88514471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554430007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634302139282</t>
+    <t xml:space="preserve">6.98114395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88514423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68930339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634349822998</t>
   </si>
   <si>
     <t xml:space="preserve">6.54338359832764</t>
@@ -2000,73 +2000,73 @@
     <t xml:space="preserve">7.14626550674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01570510864258</t>
+    <t xml:space="preserve">7.01570606231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.05026531219482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06946420669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00802564620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9926643371582</t>
+    <t xml:space="preserve">7.06946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802373886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99266529083252</t>
   </si>
   <si>
     <t xml:space="preserve">7.10402488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18082523345947</t>
+    <t xml:space="preserve">7.18082571029663</t>
   </si>
   <si>
     <t xml:space="preserve">7.10786581039429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06178522109985</t>
+    <t xml:space="preserve">7.06178426742554</t>
   </si>
   <si>
     <t xml:space="preserve">7.07330560684204</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07714509963989</t>
+    <t xml:space="preserve">7.07714557647705</t>
   </si>
   <si>
     <t xml:space="preserve">7.00034427642822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96578407287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95426511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02722406387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186561584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274425506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04258441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09634447097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75074434280396</t>
+    <t xml:space="preserve">6.96578502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95426464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02722454071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04258584976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09634494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7507438659668</t>
   </si>
   <si>
     <t xml:space="preserve">6.93506383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90434503555298</t>
+    <t xml:space="preserve">6.90434455871582</t>
   </si>
   <si>
     <t xml:space="preserve">7.0233850479126</t>
@@ -2075,58 +2075,58 @@
     <t xml:space="preserve">6.97346496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15778589248657</t>
+    <t xml:space="preserve">7.15778541564941</t>
   </si>
   <si>
     <t xml:space="preserve">7.16546535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29602575302124</t>
+    <t xml:space="preserve">7.29602527618408</t>
   </si>
   <si>
     <t xml:space="preserve">7.16930532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31138706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850517272949</t>
+    <t xml:space="preserve">7.31138563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850469589233</t>
   </si>
   <si>
     <t xml:space="preserve">7.12706470489502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17698574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19234466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15010643005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26914548873901</t>
+    <t xml:space="preserve">7.1769847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1923451423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15010547637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26914644241333</t>
   </si>
   <si>
     <t xml:space="preserve">7.34210634231567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43426704406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730590820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978675842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28066539764404</t>
+    <t xml:space="preserve">7.43426656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45730543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978628158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658662796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2806658744812</t>
   </si>
   <si>
     <t xml:space="preserve">7.11938571929932</t>
@@ -2138,73 +2138,73 @@
     <t xml:space="preserve">7.11554622650146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06562471389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08866453170776</t>
+    <t xml:space="preserve">7.06562519073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08866548538208</t>
   </si>
   <si>
     <t xml:space="preserve">6.98498487472534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77378368377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80066394805908</t>
+    <t xml:space="preserve">6.77378416061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80066347122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.77762413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92738485336304</t>
+    <t xml:space="preserve">6.88898420333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9273853302002</t>
   </si>
   <si>
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202449798584</t>
+    <t xml:space="preserve">6.91202402114868</t>
   </si>
   <si>
     <t xml:space="preserve">6.84290456771851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86210441589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84674453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0809850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03106451034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05794525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7584228515625</t>
+    <t xml:space="preserve">6.8621039390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08098459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0310640335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05794429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75842428207397</t>
   </si>
   <si>
     <t xml:space="preserve">6.81218338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81602382659912</t>
+    <t xml:space="preserve">6.81602478027344</t>
   </si>
   <si>
     <t xml:space="preserve">6.87746429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74306440353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69314384460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72002363204956</t>
+    <t xml:space="preserve">6.74306392669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69314336776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7200231552124</t>
   </si>
   <si>
     <t xml:space="preserve">6.89282464981079</t>
@@ -2213,55 +2213,55 @@
     <t xml:space="preserve">6.79682445526123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70466375350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778348922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234321594238</t>
+    <t xml:space="preserve">6.70466423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778396606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7853045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234369277954</t>
   </si>
   <si>
     <t xml:space="preserve">6.73538446426392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20386695861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410671234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2077054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17314481735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002603530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11170625686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25762605667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29986619949341</t>
+    <t xml:space="preserve">7.20386600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20770597457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17314577102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11170530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25762557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29986572265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.33826637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37282609939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786725997925</t>
+    <t xml:space="preserve">7.37282657623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786678314209</t>
   </si>
   <si>
     <t xml:space="preserve">7.56098699569702</t>
@@ -2273,61 +2273,61 @@
     <t xml:space="preserve">7.83362770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96418857574463</t>
+    <t xml:space="preserve">7.96418809890747</t>
   </si>
   <si>
     <t xml:space="preserve">8.00258827209473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17922878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218770980835</t>
+    <t xml:space="preserve">8.17922973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434698104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218818664551</t>
   </si>
   <si>
     <t xml:space="preserve">7.73378753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49186706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858701705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002843856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970443725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89442110061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27458190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77154016494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26690196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1539454460144</t>
+    <t xml:space="preserve">7.49186563491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482648849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002796173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8944206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27458238601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77154064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26690149307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33602333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15394496917725</t>
   </si>
   <si>
     <t xml:space="preserve">7.21922588348389</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">7.58018636703491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59938621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78754758834839</t>
+    <t xml:space="preserve">7.59938716888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78754806518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.2717809677124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88021802902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57022953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718223571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35335731506348</t>
+    <t xml:space="preserve">7.88021659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57023000717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35335540771484</t>
   </si>
   <si>
     <t xml:space="preserve">8.72860527038574</t>
@@ -2366,70 +2366,70 @@
     <t xml:space="preserve">9.03043460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95701789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70413303375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75307846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99442338943481</t>
+    <t xml:space="preserve">8.95701694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70413208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75307750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99442481994629</t>
   </si>
   <si>
     <t xml:space="preserve">7.83127212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74969577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81903505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79864263534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613773345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679941177368</t>
+    <t xml:space="preserve">7.74969530105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81903553009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79864168167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679845809937</t>
   </si>
   <si>
     <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5090479850769</t>
+    <t xml:space="preserve">7.50904846191406</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496912002563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70482921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377559661865</t>
+    <t xml:space="preserve">7.70482969284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377464294434</t>
   </si>
   <si>
     <t xml:space="preserve">7.89653301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94547700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8557448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010829925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9814624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85739850997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78709602355957</t>
+    <t xml:space="preserve">7.94547843933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85574388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98146200180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85739803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78709506988525</t>
   </si>
   <si>
     <t xml:space="preserve">7.75814819335938</t>
@@ -2441,58 +2441,58 @@
     <t xml:space="preserve">7.54310274124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60099983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58032178878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5182900428772</t>
+    <t xml:space="preserve">7.600998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58032131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51829051971436</t>
   </si>
   <si>
     <t xml:space="preserve">7.73333501815796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5555100440979</t>
+    <t xml:space="preserve">7.65062522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55550909042358</t>
   </si>
   <si>
     <t xml:space="preserve">7.53483247756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45212316513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49347686767578</t>
+    <t xml:space="preserve">7.4521222114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4934778213501</t>
   </si>
   <si>
     <t xml:space="preserve">7.63408327102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40249586105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36941337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58445739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520660400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656221389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75401306152344</t>
+    <t xml:space="preserve">7.40249633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663194656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36941289901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58445835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235353469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401258468628</t>
   </si>
   <si>
     <t xml:space="preserve">7.72919988632202</t>
@@ -2504,76 +2504,76 @@
     <t xml:space="preserve">7.44385242462158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34460020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73746824264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69198083877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7746901512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72506332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784427642822</t>
+    <t xml:space="preserve">7.34460067749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73746967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69198036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77468872070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72506427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68784475326538</t>
   </si>
   <si>
     <t xml:space="preserve">7.67543792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6216778755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438623428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71265697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62581205368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242612838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42317390441895</t>
+    <t xml:space="preserve">7.62167692184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71265745162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62581253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42317485809326</t>
   </si>
   <si>
     <t xml:space="preserve">7.33632898330688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3652777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2577543258667</t>
+    <t xml:space="preserve">7.36527729034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25775575637817</t>
   </si>
   <si>
     <t xml:space="preserve">7.08406543731689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02203273773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95586490631104</t>
+    <t xml:space="preserve">7.02203321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95586538314819</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09647178649902</t>
+    <t xml:space="preserve">7.06752395629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09647226333618</t>
   </si>
   <si>
     <t xml:space="preserve">7.07165908813477</t>
@@ -2582,28 +2582,28 @@
     <t xml:space="preserve">7.24534893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17091035842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03443956375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9889497756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93932342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0551176071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91864633560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90624141693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95173025131226</t>
+    <t xml:space="preserve">7.1709098815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03444051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98894929885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93932437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05511665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91864681243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90624094009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9517297744751</t>
   </si>
   <si>
     <t xml:space="preserve">6.89796876907349</t>
@@ -2612,37 +2612,37 @@
     <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93105268478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82353115081787</t>
+    <t xml:space="preserve">6.93105316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82353019714355</t>
   </si>
   <si>
     <t xml:space="preserve">6.75322723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78217601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413707733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759511947632</t>
+    <t xml:space="preserve">6.78217506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413660049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324554443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43558073043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700702667236</t>
+    <t xml:space="preserve">7.43558025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700654983521</t>
   </si>
   <si>
     <t xml:space="preserve">7.489342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59272909164429</t>
+    <t xml:space="preserve">7.59272861480713</t>
   </si>
   <si>
     <t xml:space="preserve">7.80777215957642</t>
@@ -2651,76 +2651,76 @@
     <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71679306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092819213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085702896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190824508667</t>
+    <t xml:space="preserve">7.71679258346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092866897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085607528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190729141235</t>
   </si>
   <si>
     <t xml:space="preserve">7.82845115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8367223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912729263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67957401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61754179000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6051344871521</t>
+    <t xml:space="preserve">7.83672094345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912776947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6671667098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67957305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61754131317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60513401031494</t>
   </si>
   <si>
     <t xml:space="preserve">7.59686470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57205057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54723834991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55137348175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03522300720215</t>
+    <t xml:space="preserve">7.57205104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54723787307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55137300491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03522491455078</t>
   </si>
   <si>
     <t xml:space="preserve">8.20064258575439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15515422821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4777193069458</t>
+    <t xml:space="preserve">8.15515327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47772026062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230163574219</t>
+    <t xml:space="preserve">8.31230068206787</t>
   </si>
   <si>
     <t xml:space="preserve">8.56042957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40328121185303</t>
+    <t xml:space="preserve">8.40328025817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.41155242919922</t>
@@ -2729,43 +2729,43 @@
     <t xml:space="preserve">8.28748798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33711433410645</t>
+    <t xml:space="preserve">8.33711338043213</t>
   </si>
   <si>
     <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68449306488037</t>
+    <t xml:space="preserve">8.68449401855469</t>
   </si>
   <si>
     <t xml:space="preserve">8.55215835571289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25026988983154</t>
+    <t xml:space="preserve">8.25026893615723</t>
   </si>
   <si>
     <t xml:space="preserve">8.59351253509521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88299560546875</t>
+    <t xml:space="preserve">8.88299655914307</t>
   </si>
   <si>
     <t xml:space="preserve">8.92435073852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99051761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8002872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81682777404785</t>
+    <t xml:space="preserve">8.99051856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80028629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81682872772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365581512451</t>
+    <t xml:space="preserve">8.35365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.10966300964355</t>
@@ -2774,124 +2774,124 @@
     <t xml:space="preserve">8.21304893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18823623657227</t>
+    <t xml:space="preserve">8.18823719024658</t>
   </si>
   <si>
     <t xml:space="preserve">8.13861083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24199867248535</t>
+    <t xml:space="preserve">8.32057285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27921676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25853824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2378625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9566502571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86980628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85326337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574136734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303205490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65475988388062</t>
+    <t xml:space="preserve">8.22545528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27921772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25854015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23786163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95664930343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86980581283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85326433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875459671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303300857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476083755493</t>
   </si>
   <si>
     <t xml:space="preserve">7.5141544342041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44798755645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35287094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46866369247437</t>
+    <t xml:space="preserve">7.44798707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219289779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35287237167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46866464614868</t>
   </si>
   <si>
     <t xml:space="preserve">7.43971633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43144512176514</t>
+    <t xml:space="preserve">7.43144464492798</t>
   </si>
   <si>
     <t xml:space="preserve">7.50588369369507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8201789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38181924819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20399475097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338834762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02616882324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09233570098877</t>
+    <t xml:space="preserve">7.82017993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76228189468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38181972503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2039942741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338787078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02616834640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09233617782593</t>
   </si>
   <si>
     <t xml:space="preserve">7.12542057037354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28670501708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12955617904663</t>
+    <t xml:space="preserve">7.28670406341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12955570220947</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16263914108276</t>
+    <t xml:space="preserve">7.04271030426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16264057159424</t>
   </si>
   <si>
     <t xml:space="preserve">7.2991099357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22053623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5389666557312</t>
+    <t xml:space="preserve">7.22053575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896808624268</t>
   </si>
   <si>
     <t xml:space="preserve">7.70025110244751</t>
@@ -2900,49 +2900,49 @@
     <t xml:space="preserve">7.80281066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03108787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88386631011963</t>
+    <t xml:space="preserve">8.03108882904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88386535644531</t>
   </si>
   <si>
     <t xml:space="preserve">8.01123905181885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81935262680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138090133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70190620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8673243522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273508071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619359970093</t>
+    <t xml:space="preserve">7.8193531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77138137817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453897476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70190525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86732387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619407653809</t>
   </si>
   <si>
     <t xml:space="preserve">7.6969428062439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97319221496582</t>
+    <t xml:space="preserve">8.05590152740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97319316864014</t>
   </si>
   <si>
     <t xml:space="preserve">7.99635124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01785659790039</t>
+    <t xml:space="preserve">8.01785564422607</t>
   </si>
   <si>
     <t xml:space="preserve">8.05259323120117</t>
@@ -2954,22 +2954,22 @@
     <t xml:space="preserve">8.02281761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05094051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845415115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88055801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86897754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82431507110596</t>
+    <t xml:space="preserve">8.05093955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003366470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8805570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86897802352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8243145942688</t>
   </si>
   <si>
     <t xml:space="preserve">7.90371513366699</t>
@@ -2978,37 +2978,37 @@
     <t xml:space="preserve">8.01289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81604337692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63904571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66055011749268</t>
+    <t xml:space="preserve">7.84416532516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81604385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63904523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66055059432983</t>
   </si>
   <si>
     <t xml:space="preserve">7.73498916625977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79480361938477</t>
+    <t xml:space="preserve">7.79480409622192</t>
   </si>
   <si>
     <t xml:space="preserve">7.72473478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78967666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85291051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8238582611084</t>
+    <t xml:space="preserve">7.78967714309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85291004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82385778427124</t>
   </si>
   <si>
     <t xml:space="preserve">7.77258682250977</t>
@@ -3020,16 +3020,16 @@
     <t xml:space="preserve">7.76404190063477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89221811294556</t>
+    <t xml:space="preserve">7.89221715927124</t>
   </si>
   <si>
     <t xml:space="preserve">7.94007015228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98963117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046459197998</t>
+    <t xml:space="preserve">7.98963165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046268463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.09388160705566</t>
@@ -3038,28 +3038,28 @@
     <t xml:space="preserve">8.18445873260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24940204620361</t>
+    <t xml:space="preserve">8.2494010925293</t>
   </si>
   <si>
     <t xml:space="preserve">8.28699970245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41517543792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39808464050293</t>
+    <t xml:space="preserve">8.41517448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39808654785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.38099479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46302795410156</t>
+    <t xml:space="preserve">8.46302890777588</t>
   </si>
   <si>
     <t xml:space="preserve">8.44251918792725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21180152893066</t>
+    <t xml:space="preserve">8.21180438995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.36390495300293</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">8.2442741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1912956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12806224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09900760650635</t>
+    <t xml:space="preserve">8.19129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12806129455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09900856018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">8.2271842956543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36903190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2459831237793</t>
+    <t xml:space="preserve">8.36903285980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24598217010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877704620361</t>
+    <t xml:space="preserve">8.35877799987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45619201660156</t>
+    <t xml:space="preserve">8.45619106292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.44081020355225</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">8.40663051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37245082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46644687652588</t>
+    <t xml:space="preserve">8.37245178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46644592285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5749683380127</t>
+    <t xml:space="preserve">8.57496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">8.25965595245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32630729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24256610870361</t>
+    <t xml:space="preserve">8.32630634307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.15027904510498</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">8.21863842010498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17420387268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28187370300293</t>
+    <t xml:space="preserve">8.1742057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28187274932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365104675293</t>
+    <t xml:space="preserve">8.35365009307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.45277404785156</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">8.42030239105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50233459472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896343231201</t>
+    <t xml:space="preserve">8.50233554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896438598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
@@ -3185,34 +3185,34 @@
     <t xml:space="preserve">8.6347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6262378692627</t>
+    <t xml:space="preserve">8.62623882293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.61769390106201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5416431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6219654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69032764434814</t>
+    <t xml:space="preserve">8.54164218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62196636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69032669067383</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051128387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5382251739502</t>
+    <t xml:space="preserve">8.63051223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822422027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42372035980225</t>
+    <t xml:space="preserve">8.42372131347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.49208068847656</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143329620361</t>
+    <t xml:space="preserve">8.33143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.36561393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23401927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31434440612793</t>
+    <t xml:space="preserve">8.2340202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3143424987793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40492153167725</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459831237793</t>
+    <t xml:space="preserve">8.32459735870361</t>
   </si>
   <si>
     <t xml:space="preserve">8.2323112487793</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">8.2152214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20838451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17933082580566</t>
+    <t xml:space="preserve">8.2083854675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17933177947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
@@ -3272,16 +3272,16 @@
     <t xml:space="preserve">8.07166481018066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08875370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475812911987</t>
+    <t xml:space="preserve">8.08875274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475860595703</t>
   </si>
   <si>
     <t xml:space="preserve">8.23914813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33485126495361</t>
+    <t xml:space="preserve">8.33485221862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.40150260925293</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">8.31776237487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452899932861</t>
+    <t xml:space="preserve">8.2545280456543</t>
   </si>
   <si>
     <t xml:space="preserve">8.17762279510498</t>
@@ -3299,40 +3299,40 @@
     <t xml:space="preserve">8.26478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25111103057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31605243682861</t>
+    <t xml:space="preserve">8.36048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2511100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31605339050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.21692943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16053295135498</t>
+    <t xml:space="preserve">8.1605339050293</t>
   </si>
   <si>
     <t xml:space="preserve">8.43055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32972621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45106410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44935512542725</t>
+    <t xml:space="preserve">8.32972526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45106601715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56642246246338</t>
+    <t xml:space="preserve">8.5664234161377</t>
   </si>
   <si>
     <t xml:space="preserve">8.50575351715088</t>
@@ -3341,19 +3341,19 @@
     <t xml:space="preserve">8.49891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47670078277588</t>
+    <t xml:space="preserve">8.47669982910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.02358436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08767223358154</t>
+    <t xml:space="preserve">9.08767127990723</t>
   </si>
   <si>
     <t xml:space="preserve">8.86977291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80141162872314</t>
+    <t xml:space="preserve">8.80141258239746</t>
   </si>
   <si>
     <t xml:space="preserve">8.78004932403564</t>
@@ -3362,43 +3362,43 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704639434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65614604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72023391723633</t>
+    <t xml:space="preserve">8.82704830169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65614700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72023487091064</t>
   </si>
   <si>
     <t xml:space="preserve">8.72450733184814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63905620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6091480255127</t>
+    <t xml:space="preserve">8.6390552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60914707183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.69460010528564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75441455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77150535583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88686180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88259029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92531490325928</t>
+    <t xml:space="preserve">8.75441551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77150440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88686275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88259124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92531585693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.94667911529541</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">8.98085880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92104244232178</t>
+    <t xml:space="preserve">8.92104339599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.98940467834473</t>
@@ -3419,19 +3419,19 @@
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612533569336</t>
+    <t xml:space="preserve">9.12612438201904</t>
   </si>
   <si>
     <t xml:space="preserve">9.20303058624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212928771973</t>
+    <t xml:space="preserve">9.03212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98513126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70741653442383</t>
+    <t xml:space="preserve">8.70741558074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.5877857208252</t>
@@ -3443,28 +3443,28 @@
     <t xml:space="preserve">8.26136493682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15882301330566</t>
+    <t xml:space="preserve">8.1588249206543</t>
   </si>
   <si>
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20667552947998</t>
+    <t xml:space="preserve">8.2066764831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.35706901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78454923629761</t>
+    <t xml:space="preserve">7.78455066680908</t>
   </si>
   <si>
     <t xml:space="preserve">7.81873083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8136043548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81018590927124</t>
+    <t xml:space="preserve">7.81360292434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8101863861084</t>
   </si>
   <si>
     <t xml:space="preserve">8.15540504455566</t>
@@ -3476,28 +3476,28 @@
     <t xml:space="preserve">7.8802547454834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71106290817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60168552398682</t>
+    <t xml:space="preserve">7.71106243133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60168504714966</t>
   </si>
   <si>
     <t xml:space="preserve">7.61364889144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54699611663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45129299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58459568023682</t>
+    <t xml:space="preserve">7.54699754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45129251480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58459663391113</t>
   </si>
   <si>
     <t xml:space="preserve">7.64953851699829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57434129714966</t>
+    <t xml:space="preserve">7.57434177398682</t>
   </si>
   <si>
     <t xml:space="preserve">7.58288669586182</t>
@@ -3509,88 +3509,88 @@
     <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055461883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556676864624</t>
+    <t xml:space="preserve">7.69055509567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556581497192</t>
   </si>
   <si>
     <t xml:space="preserve">7.5657958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60510396957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78625965118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56237888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72302532196045</t>
+    <t xml:space="preserve">7.60510301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78625917434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56237936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72302579879761</t>
   </si>
   <si>
     <t xml:space="preserve">7.66491937637329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77087736129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62561225891113</t>
+    <t xml:space="preserve">7.77087831497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62561273574829</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9178524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07508277893066</t>
+    <t xml:space="preserve">7.91785287857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95545148849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07508182525635</t>
   </si>
   <si>
     <t xml:space="preserve">8.14173316955566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20325756072998</t>
+    <t xml:space="preserve">8.2032585144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.2288932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50062656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39466762542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5433521270752</t>
+    <t xml:space="preserve">8.48182582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5006275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39466857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54335117340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.5578784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68178176879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68605422973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73732471466064</t>
+    <t xml:space="preserve">8.68178081512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68605327606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73732376098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93813419342041</t>
+    <t xml:space="preserve">8.97658538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93813323974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.87404537200928</t>
@@ -3605,19 +3605,19 @@
     <t xml:space="preserve">8.91677093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90395355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81422996520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61342144012451</t>
+    <t xml:space="preserve">8.90395164489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81422901153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6134204864502</t>
   </si>
   <si>
     <t xml:space="preserve">8.67323589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69887256622314</t>
+    <t xml:space="preserve">8.69887161254883</t>
   </si>
   <si>
     <t xml:space="preserve">8.70314502716064</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">8.74159622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46131896972656</t>
+    <t xml:space="preserve">8.46131992340088</t>
   </si>
   <si>
     <t xml:space="preserve">8.83131980895996</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">8.5621509552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92368698120117</t>
+    <t xml:space="preserve">8.92368793487549</t>
   </si>
   <si>
     <t xml:space="preserve">9.16629981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26775550842285</t>
+    <t xml:space="preserve">9.26775455474854</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">9.14424324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18835544586182</t>
+    <t xml:space="preserve">9.1883544921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.1927661895752</t>
@@ -3680,37 +3680,37 @@
     <t xml:space="preserve">8.23996543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25760936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21702766418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31583595275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4234676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73224449157715</t>
+    <t xml:space="preserve">8.25760841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21702671051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42346668243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79929447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73224544525146</t>
   </si>
   <si>
     <t xml:space="preserve">8.58932590484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57520961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54344940185547</t>
+    <t xml:space="preserve">8.57521057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54345035552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.77988624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71636581420898</t>
+    <t xml:space="preserve">8.71636486053467</t>
   </si>
   <si>
     <t xml:space="preserve">8.86634349822998</t>
@@ -3719,31 +3719,31 @@
     <t xml:space="preserve">8.82223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80458641052246</t>
+    <t xml:space="preserve">8.80458831787109</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91486549377441</t>
+    <t xml:space="preserve">8.91486644744873</t>
   </si>
   <si>
     <t xml:space="preserve">8.93692207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84428691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85311031341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81517505645752</t>
+    <t xml:space="preserve">8.84428787231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85310935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57168102264404</t>
+    <t xml:space="preserve">8.57168006896973</t>
   </si>
   <si>
     <t xml:space="preserve">8.78694343566895</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5575647354126</t>
+    <t xml:space="preserve">8.55756568908691</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
@@ -3773,16 +3773,16 @@
     <t xml:space="preserve">8.58756065368652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6157922744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77106380462646</t>
+    <t xml:space="preserve">8.61579132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77106475830078</t>
   </si>
   <si>
     <t xml:space="preserve">8.74459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90163230895996</t>
+    <t xml:space="preserve">8.90163326263428</t>
   </si>
   <si>
     <t xml:space="preserve">8.84869861602783</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">8.8354663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68460559844971</t>
+    <t xml:space="preserve">8.68460464477539</t>
   </si>
   <si>
     <t xml:space="preserve">8.56638813018799</t>
@@ -3800,31 +3800,31 @@
     <t xml:space="preserve">8.63167285919189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37935638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3493595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29995536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10763072967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25584506988525</t>
+    <t xml:space="preserve">8.37935543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34936046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29995632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16938781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10763168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25584411621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53639221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39700126647949</t>
+    <t xml:space="preserve">8.53639125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39700031280518</t>
   </si>
   <si>
     <t xml:space="preserve">8.32818698883057</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">8.70754337310791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45699214935303</t>
+    <t xml:space="preserve">8.45699310302734</t>
   </si>
   <si>
     <t xml:space="preserve">8.39347171783447</t>
@@ -3842,55 +3842,55 @@
     <t xml:space="preserve">8.08292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22585010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0035285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412445068359</t>
+    <t xml:space="preserve">8.22584915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00352954864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412397384644</t>
   </si>
   <si>
     <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92589426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90472030639648</t>
+    <t xml:space="preserve">7.92589378356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90472078323364</t>
   </si>
   <si>
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91354274749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94706773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15703678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04411220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78473806381226</t>
+    <t xml:space="preserve">7.9135422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94706678390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15703582763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04411125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7847375869751</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64534711837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007150650024</t>
+    <t xml:space="preserve">7.64534664154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007102966309</t>
   </si>
   <si>
     <t xml:space="preserve">7.39479494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40538167953491</t>
+    <t xml:space="preserve">7.40538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">7.51124858856201</t>
@@ -3899,37 +3899,37 @@
     <t xml:space="preserve">7.64711093902588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43890619277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52359914779663</t>
+    <t xml:space="preserve">7.4389066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52359962463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.3101019859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50948429107666</t>
+    <t xml:space="preserve">7.5094838142395</t>
   </si>
   <si>
     <t xml:space="preserve">7.73180437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73709774017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75297689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8747239112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88001871109009</t>
+    <t xml:space="preserve">7.7370982170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75297737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87472438812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88001775741577</t>
   </si>
   <si>
     <t xml:space="preserve">7.85355138778687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94353818893433</t>
+    <t xml:space="preserve">7.94353771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
@@ -3938,13 +3938,13 @@
     <t xml:space="preserve">8.08822250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14291954040527</t>
+    <t xml:space="preserve">8.14292049407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.38817882537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76047706604004</t>
+    <t xml:space="preserve">8.76047611236572</t>
   </si>
   <si>
     <t xml:space="preserve">8.69872093200684</t>
@@ -3953,43 +3953,43 @@
     <t xml:space="preserve">8.50286674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4005298614502</t>
+    <t xml:space="preserve">8.40053081512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.33524513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48698806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46934413909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4816951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40935134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28054809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53109836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47640037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46757793426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42699718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37053489685059</t>
+    <t xml:space="preserve">8.48698711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4693431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48169422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49404525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40935230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28054618835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53109931945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47640132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46757888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4269962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37053394317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.36347579956055</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">8.53286361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55580043792725</t>
+    <t xml:space="preserve">8.55580139160156</t>
   </si>
   <si>
     <t xml:space="preserve">8.4305248260498</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.2152624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26466655731201</t>
+    <t xml:space="preserve">8.26466751098633</t>
   </si>
   <si>
     <t xml:space="preserve">8.16232967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37582778930664</t>
+    <t xml:space="preserve">8.37582874298096</t>
   </si>
   <si>
     <t xml:space="preserve">8.35112476348877</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">8.29819202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41640853881836</t>
+    <t xml:space="preserve">8.41640949249268</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4075870513916</t>
+    <t xml:space="preserve">8.40758800506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">8.64402389526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67049026489258</t>
+    <t xml:space="preserve">8.67048931121826</t>
   </si>
   <si>
     <t xml:space="preserve">8.61226367950439</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">8.7887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82046890258789</t>
+    <t xml:space="preserve">8.82046794891357</t>
   </si>
   <si>
     <t xml:space="preserve">8.73400974273682</t>
@@ -4067,31 +4067,31 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456600189209</t>
+    <t xml:space="preserve">8.95456504821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91927719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8619327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8928108215332</t>
+    <t xml:space="preserve">8.91927623748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89280986785889</t>
   </si>
   <si>
     <t xml:space="preserve">9.11336612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89722156524658</t>
+    <t xml:space="preserve">8.89722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867725372314</t>
+    <t xml:space="preserve">8.99867630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4103,19 +4103,19 @@
     <t xml:space="preserve">9.26334381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2809886932373</t>
+    <t xml:space="preserve">9.28098964691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15306568145752</t>
+    <t xml:space="preserve">9.15306663513184</t>
   </si>
   <si>
     <t xml:space="preserve">9.14865493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13101100921631</t>
+    <t xml:space="preserve">9.13101005554199</t>
   </si>
   <si>
     <t xml:space="preserve">9.13983249664307</t>
@@ -4124,25 +4124,25 @@
     <t xml:space="preserve">9.08248805999756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04278755187988</t>
+    <t xml:space="preserve">9.0427885055542</t>
   </si>
   <si>
     <t xml:space="preserve">9.93383407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0485229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74415493011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1411561965942</t>
+    <t xml:space="preserve">10.0485239028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74415588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1411552429199</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720342636108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0264663696289</t>
+    <t xml:space="preserve">10.0264673233032</t>
   </si>
   <si>
     <t xml:space="preserve">9.78385543823242</t>
@@ -4151,31 +4151,31 @@
     <t xml:space="preserve">10.0705785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87207794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706630706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77944469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1191005706787</t>
+    <t xml:space="preserve">9.87207698822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706726074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77944564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190996170044</t>
   </si>
   <si>
     <t xml:space="preserve">9.99117755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5116901397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3440685272217</t>
+    <t xml:space="preserve">10.5116891860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3440675735474</t>
   </si>
   <si>
     <t xml:space="preserve">10.5778570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6131458282471</t>
+    <t xml:space="preserve">10.6131448745728</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">10.7057790756226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6925458908081</t>
+    <t xml:space="preserve">10.6925449371338</t>
   </si>
   <si>
     <t xml:space="preserve">10.7278337478638</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">10.8778123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8601684570312</t>
+    <t xml:space="preserve">10.8601675033569</t>
   </si>
   <si>
     <t xml:space="preserve">10.789589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160581588745</t>
+    <t xml:space="preserve">10.8160572052002</t>
   </si>
   <si>
     <t xml:space="preserve">10.868989944458</t>
@@ -4238,34 +4238,34 @@
     <t xml:space="preserve">11.0454359054565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1248350143433</t>
+    <t xml:space="preserve">11.1248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0983686447144</t>
+    <t xml:space="preserve">11.09836769104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8645782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6396131515503</t>
+    <t xml:space="preserve">10.6969566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660795211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.639612197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.4852237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6352014541626</t>
+    <t xml:space="preserve">10.6352005004883</t>
   </si>
   <si>
     <t xml:space="preserve">10.8274984359741</t>
@@ -5531,7 +5531,16 @@
     <t xml:space="preserve">9.41499996185303</t>
   </si>
   <si>
+    <t xml:space="preserve">9.42500019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53499984741211</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.44499969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4399995803833</t>
   </si>
 </sst>
 </file>
@@ -70974,27 +70983,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6939236111</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>1354762</v>
+        <v>1184087</v>
       </c>
       <c r="C2505" t="n">
-        <v>9.57999992370605</v>
+        <v>9.47500038146973</v>
       </c>
       <c r="D2505" t="n">
-        <v>9.32999992370605</v>
+        <v>9.38000011444092</v>
       </c>
       <c r="E2505" t="n">
-        <v>9.57999992370605</v>
+        <v>9.40999984741211</v>
       </c>
       <c r="F2505" t="n">
-        <v>9.44499969482422</v>
+        <v>9.42500019073486</v>
       </c>
       <c r="G2505" t="s">
         <v>1839</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>1135493</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>9.55000019073486</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>9.44999980926514</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>9.53499984741211</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>1354762</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>9.32999992370605</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>9.44499969482422</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6911226852</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>1088798</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>9.49499988555908</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>9.40499973297119</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>9.49499988555908</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1842</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="1843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="1844">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,163 +38,163 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4243381023407</t>
+    <t xml:space="preserve">3.42433881759644</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4560706615448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331619262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812421798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845614433289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34707689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981472969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28637146949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21324896812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03803086280823</t>
+    <t xml:space="preserve">3.46296858787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45607137680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331666946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812445640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3470766544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981496810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2863712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21324920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03803062438965</t>
   </si>
   <si>
     <t xml:space="preserve">3.13874697685242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1428861618042</t>
+    <t xml:space="preserve">3.14288568496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.10425519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16496062278748</t>
+    <t xml:space="preserve">3.1649603843689</t>
   </si>
   <si>
     <t xml:space="preserve">3.13736724853516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14564514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945216178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430674552917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27119565010071</t>
+    <t xml:space="preserve">3.1456446647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27119517326355</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222159385681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20911026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2077305316925</t>
+    <t xml:space="preserve">3.20910978317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631920814514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06700396537781</t>
+    <t xml:space="preserve">3.06700420379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.00078010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802041053772</t>
+    <t xml:space="preserve">3.00215935707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802088737488</t>
   </si>
   <si>
     <t xml:space="preserve">3.02837300300598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07114291191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322806358337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11115312576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151688575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13046884536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14150643348694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12494993209839</t>
+    <t xml:space="preserve">3.07114338874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1111536026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13046860694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14150619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12495017051697</t>
   </si>
   <si>
     <t xml:space="preserve">3.11805152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808264732361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1732382774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19531273841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18703532218933</t>
+    <t xml:space="preserve">3.23808312416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17323875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18703508377075</t>
   </si>
   <si>
     <t xml:space="preserve">3.09321761131287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18013715744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255399703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427610397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636101722717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20635032653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19807314872742</t>
+    <t xml:space="preserve">3.18013668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255375862122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427586555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636054039001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20635008811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.198073387146</t>
   </si>
   <si>
     <t xml:space="preserve">3.10563468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906797409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05458688735962</t>
+    <t xml:space="preserve">3.04906821250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05458664894104</t>
   </si>
   <si>
     <t xml:space="preserve">3.03941059112549</t>
@@ -203,43 +203,43 @@
     <t xml:space="preserve">3.00491881370544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05182790756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98422408103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05044841766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0532078742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595616340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457643508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02147436141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00629830360413</t>
+    <t xml:space="preserve">3.05182766914368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98422384262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05044794082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05320763587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595664024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457619667053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02147483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00629878044128</t>
   </si>
   <si>
     <t xml:space="preserve">3.00767850875854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0256142616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0876989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978361129761</t>
+    <t xml:space="preserve">3.02561402320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873652458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08769917488098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978432655334</t>
   </si>
   <si>
     <t xml:space="preserve">3.05596685409546</t>
@@ -248,43 +248,43 @@
     <t xml:space="preserve">3.06838345527649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01319742202759</t>
+    <t xml:space="preserve">3.01319694519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.02975296974182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01871538162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96766781806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95249152183533</t>
+    <t xml:space="preserve">3.01871562004089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9676673412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95249176025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.94421362876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93869471549988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593525886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02235889434814</t>
+    <t xml:space="preserve">2.93869495391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593573570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235865592957</t>
   </si>
   <si>
     <t xml:space="preserve">3.02659201622009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99837231636047</t>
+    <t xml:space="preserve">2.99837207794189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98426222801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99131679534912</t>
+    <t xml:space="preserve">2.99131727218628</t>
   </si>
   <si>
     <t xml:space="preserve">2.97861814498901</t>
@@ -296,55 +296,55 @@
     <t xml:space="preserve">3.06609988212585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01389312744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02094793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00683760643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01671528816223</t>
+    <t xml:space="preserve">3.01389288902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0209481716156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00683808326721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03929162025452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01671481132507</t>
   </si>
   <si>
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978303909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96450805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714959144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083203315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87702631950378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089010238647</t>
+    <t xml:space="preserve">2.99978256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9645082950592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714911460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083250999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843751907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87702608108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91088962554932</t>
   </si>
   <si>
     <t xml:space="preserve">2.7218165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61034750938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67525315284729</t>
+    <t xml:space="preserve">2.61034774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67525386810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.71899437904358</t>
@@ -356,40 +356,40 @@
     <t xml:space="preserve">2.79518842697144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85162782669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610725402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87279367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94475412368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97438526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00542712211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02518129348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04211330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07597708702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03364729881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07033324241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05481171607971</t>
+    <t xml:space="preserve">2.85162830352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83610701560974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87279295921326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94475388526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97438502311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00542759895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02518105506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04211282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07597756385803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03364706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07033276557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05481195449829</t>
   </si>
   <si>
     <t xml:space="preserve">3.03787994384766</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">3.05199027061462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17333626747131</t>
+    <t xml:space="preserve">3.17333579063416</t>
   </si>
   <si>
     <t xml:space="preserve">3.16204786300659</t>
@@ -407,34 +407,34 @@
     <t xml:space="preserve">3.15499305725098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14088296890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14793801307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10843014717102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149789810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13241696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13947200775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15076041221619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10419726371765</t>
+    <t xml:space="preserve">3.14088273048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793753623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10842967033386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149813652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13241720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13947224617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15075993537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10419702529907</t>
   </si>
   <si>
     <t xml:space="preserve">3.08444309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02800321578979</t>
+    <t xml:space="preserve">3.02800297737122</t>
   </si>
   <si>
     <t xml:space="preserve">3.0124819278717</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">3.02376985549927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07174396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604555606842</t>
+    <t xml:space="preserve">3.0717442035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045603752136</t>
   </si>
   <si>
     <t xml:space="preserve">3.03646898269653</t>
@@ -455,52 +455,52 @@
     <t xml:space="preserve">3.09008693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19732260704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21002173423767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18462419509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2128438949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707701683044</t>
+    <t xml:space="preserve">3.19732284545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21002244949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18462347984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21284365653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707677841187</t>
   </si>
   <si>
     <t xml:space="preserve">3.27774977684021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27351665496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20861101150513</t>
+    <t xml:space="preserve">3.27351689338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130990028381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20861053466797</t>
   </si>
   <si>
     <t xml:space="preserve">3.19873380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18180179595947</t>
+    <t xml:space="preserve">3.18180203437805</t>
   </si>
   <si>
     <t xml:space="preserve">3.1535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15217065811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16628074645996</t>
+    <t xml:space="preserve">3.15217137336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16628098487854</t>
   </si>
   <si>
     <t xml:space="preserve">3.12536191940308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11125206947327</t>
+    <t xml:space="preserve">3.11125135421753</t>
   </si>
   <si>
     <t xml:space="preserve">3.08726501464844</t>
@@ -509,31 +509,31 @@
     <t xml:space="preserve">3.09714198112488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0886754989624</t>
+    <t xml:space="preserve">3.11548519134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08867621421814</t>
   </si>
   <si>
     <t xml:space="preserve">3.077388048172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06186699867249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99696159362793</t>
+    <t xml:space="preserve">3.06186723709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99696111679077</t>
   </si>
   <si>
     <t xml:space="preserve">2.92923307418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95322012901306</t>
+    <t xml:space="preserve">2.95321989059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.95180916786194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93910980224609</t>
+    <t xml:space="preserve">2.93911004066467</t>
   </si>
   <si>
     <t xml:space="preserve">2.92076706886292</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">2.95886397361755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92782211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493498802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0195369720459</t>
+    <t xml:space="preserve">2.92782235145569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002886772156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622315406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01953744888306</t>
   </si>
   <si>
     <t xml:space="preserve">2.97720694541931</t>
@@ -569,121 +569,121 @@
     <t xml:space="preserve">3.01812601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96309661865234</t>
+    <t xml:space="preserve">2.96309685707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.92641091346741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98849534988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87138247489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85727190971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86856007575989</t>
+    <t xml:space="preserve">2.98849511146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87138223648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8572723865509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86856031417847</t>
   </si>
   <si>
     <t xml:space="preserve">2.92358899116516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95604228973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88690328598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89819097518921</t>
+    <t xml:space="preserve">2.95604252815247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88690304756165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89819121360779</t>
   </si>
   <si>
     <t xml:space="preserve">2.85303950309753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84034013748169</t>
+    <t xml:space="preserve">2.84034037590027</t>
   </si>
   <si>
     <t xml:space="preserve">2.82199740409851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84457325935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85021734237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78390049934387</t>
+    <t xml:space="preserve">2.84457349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85021710395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78390026092529</t>
   </si>
   <si>
     <t xml:space="preserve">2.79377770423889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82340836524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568032264709</t>
+    <t xml:space="preserve">2.82340788841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568056106567</t>
   </si>
   <si>
     <t xml:space="preserve">2.76132464408875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80929827690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89254713058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893958568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89960241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90665698051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88831400871277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91230082511902</t>
+    <t xml:space="preserve">2.80929851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8925473690033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89960217475891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86009430885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90665721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88831448554993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9123010635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.94052124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09432005882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08021020889282</t>
+    <t xml:space="preserve">3.09431982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0802104473114</t>
   </si>
   <si>
     <t xml:space="preserve">3.08303165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10560846328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585405349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523864746094</t>
+    <t xml:space="preserve">3.10560774803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585429191589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523888587952</t>
   </si>
   <si>
     <t xml:space="preserve">3.14511609077454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13806080818176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063714027405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051339149475</t>
+    <t xml:space="preserve">3.13806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051410675049</t>
   </si>
   <si>
     <t xml:space="preserve">3.20437788963318</t>
@@ -692,28 +692,28 @@
     <t xml:space="preserve">3.19591188430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12254047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573101997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290909767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06751132011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1183066368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17898035049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13665008544922</t>
+    <t xml:space="preserve">3.12254023551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06751108169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11830687522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17897987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13664984703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.07456564903259</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">3.10701870918274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529671669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2664623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25376319885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891514778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3144359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38357400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3722870349884</t>
+    <t xml:space="preserve">3.098552942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26646208763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25376296043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891490936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31443572044373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38357472419739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37228679656982</t>
   </si>
   <si>
     <t xml:space="preserve">3.37651944160461</t>
@@ -755,241 +755,241 @@
     <t xml:space="preserve">3.44565868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41461706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40756154060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40050673484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48657703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338696479797</t>
+    <t xml:space="preserve">3.41461682319641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283699989319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40756177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4005069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48657751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338648796082</t>
   </si>
   <si>
     <t xml:space="preserve">3.47105669975281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54160642623901</t>
+    <t xml:space="preserve">3.54160618782043</t>
   </si>
   <si>
     <t xml:space="preserve">3.47811150550842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48798847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185273170471</t>
+    <t xml:space="preserve">3.48798823356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185320854187</t>
   </si>
   <si>
     <t xml:space="preserve">3.50633120536804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49222111701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56277179718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5274965763092</t>
+    <t xml:space="preserve">3.49222135543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5627715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53455209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749633789062</t>
   </si>
   <si>
     <t xml:space="preserve">3.54866170883179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51056456565857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099125862122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568379402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393621444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209832191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924391746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6227388381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.650958776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.661541223526</t>
+    <t xml:space="preserve">3.51056432723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099173545837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568403244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58393597602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924439430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62273907661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65095925331116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66154050827026</t>
   </si>
   <si>
     <t xml:space="preserve">3.66506886482239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61921167373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804606437683</t>
+    <t xml:space="preserve">3.61921119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63332152366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804630279541</t>
   </si>
   <si>
     <t xml:space="preserve">3.73752284049988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68667197227478</t>
+    <t xml:space="preserve">3.68667149543762</t>
   </si>
   <si>
     <t xml:space="preserve">3.72299385070801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71936202049255</t>
+    <t xml:space="preserve">3.71936225891113</t>
   </si>
   <si>
     <t xml:space="preserve">3.7048327922821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66124677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195996284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832765579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84285616874695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85012006759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88644218444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101746559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648871421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82469534873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83922433853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451066017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097093582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455647468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98087930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92639589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082350730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91913247108459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016659736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304014205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65761399269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330151557922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62201857566833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6031322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59150862693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492442131042</t>
+    <t xml:space="preserve">3.66124653816223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832741737366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379818916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84285569190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85012030601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88644194602966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648776054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82469487190247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83922386169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451161384583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097117424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455742835999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98087954521179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92639636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91913223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016564369202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304038047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6576144695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330223083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62201929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60313177108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59150838851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492489814758</t>
   </si>
   <si>
     <t xml:space="preserve">3.67214345932007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63073635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030332565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65034937858582</t>
+    <t xml:space="preserve">3.63073682785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030356407166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218903541565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65034961700439</t>
   </si>
   <si>
     <t xml:space="preserve">3.71572971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72662615776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191367149353</t>
+    <t xml:space="preserve">3.72662591934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191438674927</t>
   </si>
   <si>
     <t xml:space="preserve">3.96635007858276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93366050720215</t>
+    <t xml:space="preserve">3.93366074562073</t>
   </si>
   <si>
     <t xml:space="preserve">3.95908641815186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96998286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05352258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04989147186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07894897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182156562805</t>
+    <t xml:space="preserve">3.96998310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05352306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04989051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894849777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267171859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182228088379</t>
   </si>
   <si>
     <t xml:space="preserve">3.91549968719482</t>
@@ -998,64 +998,64 @@
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540829658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177598953247</t>
+    <t xml:space="preserve">3.99540853500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177622795105</t>
   </si>
   <si>
     <t xml:space="preserve">4.02446556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04262638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10437345504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271872520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464977264404</t>
+    <t xml:space="preserve">4.04262590408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10437393188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464929580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.89733862876892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98814344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9554545879364</t>
+    <t xml:space="preserve">3.98814368247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545434951782</t>
   </si>
   <si>
     <t xml:space="preserve">3.93002820014954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01720094680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88281035423279</t>
+    <t xml:space="preserve">4.01720142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88280987739563</t>
   </si>
   <si>
     <t xml:space="preserve">4.07531642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06805181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14795970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04625844955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06078720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11527013778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1080060005188</t>
+    <t xml:space="preserve">4.0680513381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14796018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06078767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11527061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10800695419312</t>
   </si>
   <si>
     <t xml:space="preserve">4.12253475189209</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">4.18064975738525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1588568687439</t>
+    <t xml:space="preserve">4.15885591506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.18791437149048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1661205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17338562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09710884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14069557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24602842330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22060298919678</t>
+    <t xml:space="preserve">4.16612100601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17338514328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09710931777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14069509506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.129798412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24602890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22060394287109</t>
   </si>
   <si>
     <t xml:space="preserve">4.26055812835693</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">4.21697187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25329351425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26419019699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27508735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24239730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17701768875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08984470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30777645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687976837158</t>
+    <t xml:space="preserve">4.25329399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26419067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27508640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24239683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1770167350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08984518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.307776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29687929153442</t>
   </si>
   <si>
     <t xml:space="preserve">4.4276385307312</t>
@@ -1127,88 +1127,88 @@
     <t xml:space="preserve">4.51481103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54023599624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60198402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59835147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72184610366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56929349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56202983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62014532089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59471940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6092472076416</t>
+    <t xml:space="preserve">4.54023694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60198307037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5983510017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72184562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56929397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56202936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62014484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59471893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60924816131592</t>
   </si>
   <si>
     <t xml:space="preserve">4.4893856048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45669555664062</t>
+    <t xml:space="preserve">4.45669603347778</t>
   </si>
   <si>
     <t xml:space="preserve">4.51844358444214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33683347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52207469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575401306152</t>
+    <t xml:space="preserve">4.33683395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52207517623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575353622437</t>
   </si>
   <si>
     <t xml:space="preserve">4.49301815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50391483306885</t>
+    <t xml:space="preserve">4.50391435623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.49665021896362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46032810211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306396484375</t>
+    <t xml:space="preserve">4.46032762527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306491851807</t>
   </si>
   <si>
     <t xml:space="preserve">4.46759271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4784893989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750108718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53660345077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4385347366333</t>
+    <t xml:space="preserve">4.47848844528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750156402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53660440444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43853521347046</t>
   </si>
   <si>
     <t xml:space="preserve">4.37315607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39131689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42037391662598</t>
+    <t xml:space="preserve">4.39131736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42037439346313</t>
   </si>
   <si>
     <t xml:space="preserve">4.29324769973755</t>
@@ -1217,40 +1217,40 @@
     <t xml:space="preserve">4.40947771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51117897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42400598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31140851974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28235149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20607423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12616634368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23150062561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14432764053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94092559814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9772469997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258104324341</t>
+    <t xml:space="preserve">4.51117944717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42400646209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31140899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28235101699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20607471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12616682052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23150014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14432811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361493110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94092535972595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97724747657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258008956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.15522480010986</t>
@@ -1265,34 +1265,34 @@
     <t xml:space="preserve">4.40584516525269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41674137115479</t>
+    <t xml:space="preserve">4.4167423248291</t>
   </si>
   <si>
     <t xml:space="preserve">4.59108734130859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61288070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55113315582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57655811309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52933979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52570772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53297138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67825984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64920139312744</t>
+    <t xml:space="preserve">4.61287975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5511326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5765585899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5293402671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52570724487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53297233581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67825937271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64920234680176</t>
   </si>
   <si>
     <t xml:space="preserve">4.67099523544312</t>
@@ -1301,31 +1301,31 @@
     <t xml:space="preserve">4.64556980133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65283441543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75816822052002</t>
+    <t xml:space="preserve">4.65283489227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7581672668457</t>
   </si>
   <si>
     <t xml:space="preserve">4.75090312957764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179981231689</t>
+    <t xml:space="preserve">4.76179933547974</t>
   </si>
   <si>
     <t xml:space="preserve">4.7254786491394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68552398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911024093628</t>
+    <t xml:space="preserve">4.68552446365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911071777344</t>
   </si>
   <si>
     <t xml:space="preserve">4.65646648406982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84533977508545</t>
+    <t xml:space="preserve">4.84534072875977</t>
   </si>
   <si>
     <t xml:space="preserve">4.81265068054199</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">4.81991529464722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83807611465454</t>
+    <t xml:space="preserve">4.83807516098022</t>
   </si>
   <si>
     <t xml:space="preserve">4.88166189193726</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">4.84897232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91798400878906</t>
+    <t xml:space="preserve">4.91798448562622</t>
   </si>
   <si>
     <t xml:space="preserve">4.89255857467651</t>
@@ -1352,67 +1352,67 @@
     <t xml:space="preserve">4.95430612564087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9470419883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93977737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93251323699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99062776565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86713266372681</t>
+    <t xml:space="preserve">4.94704151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93977785110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93251276016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99062728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340991973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86713314056396</t>
   </si>
   <si>
     <t xml:space="preserve">4.7330756187439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87888145446777</t>
+    <t xml:space="preserve">4.87888193130493</t>
   </si>
   <si>
     <t xml:space="preserve">4.86018800735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82654094696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75176906585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6508264541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49380540847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62091779708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67699718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63587236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74803018569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7218599319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70690536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57979297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75924587249756</t>
+    <t xml:space="preserve">4.82654142379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75176858901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65082597732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49380493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62091732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67699670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63587188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74803066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70690584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57979345321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75924634933472</t>
   </si>
   <si>
     <t xml:space="preserve">4.83027982711792</t>
@@ -1430,100 +1430,100 @@
     <t xml:space="preserve">4.94243812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91252899169922</t>
+    <t xml:space="preserve">4.91252946853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.91626739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90505218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8826208114624</t>
+    <t xml:space="preserve">4.90505123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88262033462524</t>
   </si>
   <si>
     <t xml:space="preserve">4.93869972229004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9648699760437</t>
+    <t xml:space="preserve">4.96486902236938</t>
   </si>
   <si>
     <t xml:space="preserve">5.03216409683228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01721048355103</t>
+    <t xml:space="preserve">5.01720952987671</t>
   </si>
   <si>
     <t xml:space="preserve">5.13684558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05833387374878</t>
+    <t xml:space="preserve">5.05833435058594</t>
   </si>
   <si>
     <t xml:space="preserve">4.98356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89757442474365</t>
+    <t xml:space="preserve">4.89757490158081</t>
   </si>
   <si>
     <t xml:space="preserve">5.1293683052063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2490029335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37985515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31629848480225</t>
+    <t xml:space="preserve">5.24900341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37985467910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3162989616394</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34246873855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09945964813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0134711265564</t>
+    <t xml:space="preserve">5.34246826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09945917129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01347064971924</t>
   </si>
   <si>
     <t xml:space="preserve">5.17796993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20040130615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787858963013</t>
+    <t xml:space="preserve">5.20040082931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274229049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787906646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.21535587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22283267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11815214157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04338073730469</t>
+    <t xml:space="preserve">5.22283363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666337966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11815166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04338026046753</t>
   </si>
   <si>
     <t xml:space="preserve">4.99851703643799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11067485809326</t>
+    <t xml:space="preserve">5.11067581176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.17049264907837</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">5.04711866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11441326141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06581258773804</t>
+    <t xml:space="preserve">5.11441373825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06581163406372</t>
   </si>
   <si>
     <t xml:space="preserve">4.97982358932495</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">5.03964138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05459594726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08076620101929</t>
+    <t xml:space="preserve">5.05459642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0807671546936</t>
   </si>
   <si>
     <t xml:space="preserve">5.18544721603394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09572076797485</t>
+    <t xml:space="preserve">5.0957202911377</t>
   </si>
   <si>
     <t xml:space="preserve">5.2116174697876</t>
@@ -1568,46 +1568,46 @@
     <t xml:space="preserve">4.920006275177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77420091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76672267913818</t>
+    <t xml:space="preserve">4.77420043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76672315597534</t>
   </si>
   <si>
     <t xml:space="preserve">4.68073511123657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66951942443848</t>
+    <t xml:space="preserve">4.66951847076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67325830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68447351455688</t>
+    <t xml:space="preserve">4.67325782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
     <t xml:space="preserve">4.62839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5685772895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58727073669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56110048294067</t>
+    <t xml:space="preserve">4.56857681274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58727025985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69568920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110000610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344051361084</t>
+    <t xml:space="preserve">4.61344003677368</t>
   </si>
   <si>
     <t xml:space="preserve">4.59848594665527</t>
@@ -1619,19 +1619,19 @@
     <t xml:space="preserve">4.84523391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79289245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78167772293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7779393196106</t>
+    <t xml:space="preserve">4.792893409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915548324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78167724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77793884277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.87140417098999</t>
@@ -1640,43 +1640,43 @@
     <t xml:space="preserve">4.83775615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68821239471436</t>
+    <t xml:space="preserve">4.68821287155151</t>
   </si>
   <si>
     <t xml:space="preserve">4.71812152862549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74055242538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60222434997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54988431930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52371406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41903209686279</t>
+    <t xml:space="preserve">4.74055290222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6022253036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54988384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52371454238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48632764816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41903305053711</t>
   </si>
   <si>
     <t xml:space="preserve">4.46015739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64334917068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204214096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456581115723</t>
+    <t xml:space="preserve">4.64334964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204309463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456485748291</t>
   </si>
   <si>
     <t xml:space="preserve">4.76298427581787</t>
@@ -1688,49 +1688,49 @@
     <t xml:space="preserve">4.86392688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98730134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14806175231934</t>
+    <t xml:space="preserve">4.98730087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14806127548218</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927696228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21909427642822</t>
+    <t xml:space="preserve">5.21909475326538</t>
   </si>
   <si>
     <t xml:space="preserve">5.22657108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18918561935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15179967880249</t>
+    <t xml:space="preserve">5.18918609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15180015563965</t>
   </si>
   <si>
     <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37237787246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620761871338</t>
+    <t xml:space="preserve">5.37237739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16675424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620714187622</t>
   </si>
   <si>
     <t xml:space="preserve">6.09019041061401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87335157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79484081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76119232177734</t>
+    <t xml:space="preserve">5.87335062026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79483938217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.81353330612183</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">5.80231761932373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75745391845703</t>
+    <t xml:space="preserve">5.75745344161987</t>
   </si>
   <si>
     <t xml:space="preserve">5.82474899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87708950042725</t>
+    <t xml:space="preserve">5.87708902359009</t>
   </si>
   <si>
     <t xml:space="preserve">5.92195320129395</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">6.01167917251587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02663373947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96307754516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0079402923584</t>
+    <t xml:space="preserve">6.02663421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96307706832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00794076919556</t>
   </si>
   <si>
     <t xml:space="preserve">5.92569160461426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93316841125488</t>
+    <t xml:space="preserve">5.93316888809204</t>
   </si>
   <si>
     <t xml:space="preserve">5.90699815750122</t>
@@ -1781,58 +1781,58 @@
     <t xml:space="preserve">5.94064617156982</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07897424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93690729141235</t>
+    <t xml:space="preserve">6.0789737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9369068145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.95933866500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89952182769775</t>
+    <t xml:space="preserve">5.89952039718628</t>
   </si>
   <si>
     <t xml:space="preserve">5.89578294754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88082838058472</t>
+    <t xml:space="preserve">5.8808274269104</t>
   </si>
   <si>
     <t xml:space="preserve">5.94812297821045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95560073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97429275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114200592041</t>
+    <t xml:space="preserve">5.95560026168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97429323196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114152908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84066152572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7523398399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69474029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71778059005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68322086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66402053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66786003112793</t>
+    <t xml:space="preserve">5.840660572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75234031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69473934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71778011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68322038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66401958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66786050796509</t>
   </si>
   <si>
     <t xml:space="preserve">5.7830605506897</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">5.76002073287964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87522125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82146024703979</t>
+    <t xml:space="preserve">5.87522029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82146072387695</t>
   </si>
   <si>
     <t xml:space="preserve">5.74850034713745</t>
@@ -1856,55 +1856,55 @@
     <t xml:space="preserve">5.69858026504517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64482021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60641956329346</t>
+    <t xml:space="preserve">5.64481925964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60642004013062</t>
   </si>
   <si>
     <t xml:space="preserve">5.77538061141968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72162008285522</t>
+    <t xml:space="preserve">5.72162055969238</t>
   </si>
   <si>
     <t xml:space="preserve">5.81762027740479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78690004348755</t>
+    <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
     <t xml:space="preserve">5.95970153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05570220947266</t>
+    <t xml:space="preserve">6.0557017326355</t>
   </si>
   <si>
     <t xml:space="preserve">6.28226280212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17474126815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09026098251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12866163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22850179672241</t>
+    <t xml:space="preserve">6.17474174499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09026145935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22850227355957</t>
   </si>
   <si>
     <t xml:space="preserve">6.19394207000732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06722116470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10178136825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25154304504395</t>
+    <t xml:space="preserve">6.06722164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10178184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25154256820679</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090177536011</t>
@@ -1913,130 +1913,130 @@
     <t xml:space="preserve">6.1670618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29378175735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746284484863</t>
+    <t xml:space="preserve">6.29378223419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746236801147</t>
   </si>
   <si>
     <t xml:space="preserve">6.43586254119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4627423286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38210248947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35522222518921</t>
+    <t xml:space="preserve">6.46274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38210296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35522270202637</t>
   </si>
   <si>
     <t xml:space="preserve">6.44738340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5280237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53954362869263</t>
+    <t xml:space="preserve">6.52802324295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53954315185547</t>
   </si>
   <si>
     <t xml:space="preserve">6.57410335540771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58946371078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62018299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64322328567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62786483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66626405715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80450391769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83138418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83522367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78914403915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76610422134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98114395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98882579803467</t>
+    <t xml:space="preserve">6.58946323394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62018394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64322423934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62786340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66626358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80450439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83138465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83522415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78914356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76610469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">6.88514423370361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68930339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63554382324219</t>
+    <t xml:space="preserve">6.68930387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6355447769165</t>
   </si>
   <si>
     <t xml:space="preserve">6.61634349822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298400878906</t>
+    <t xml:space="preserve">6.54338312149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298448562622</t>
   </si>
   <si>
     <t xml:space="preserve">7.14626550674438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01570606231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026531219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00802373886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99266529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10402488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10786581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06178426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330560684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714557647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034427642822</t>
+    <t xml:space="preserve">7.01570558547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946516036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642534255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00802516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99266481399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10402536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10786485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0617847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">6.96578502655029</t>
@@ -2045,64 +2045,64 @@
     <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02722454071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274520874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04258584976196</t>
+    <t xml:space="preserve">7.02722501754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274473190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04258489608765</t>
   </si>
   <si>
     <t xml:space="preserve">7.09634494781494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7507438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506383895874</t>
+    <t xml:space="preserve">6.75074338912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93506336212158</t>
   </si>
   <si>
     <t xml:space="preserve">6.90434455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0233850479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97346496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15778541564941</t>
+    <t xml:space="preserve">7.02338457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97346448898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1577844619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.16546535491943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29602527618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16930532455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31138563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18850469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12706470489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1769847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1923451423645</t>
+    <t xml:space="preserve">7.29602670669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16930627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31138706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682590484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18850517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12706518173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17698574066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19234561920166</t>
   </si>
   <si>
     <t xml:space="preserve">7.15010547637939</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">7.26914644241333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34210634231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43426656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45730543136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978628158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658662796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2806658744812</t>
+    <t xml:space="preserve">7.34210586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43426609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4573073387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978532791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658710479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28066539764404</t>
   </si>
   <si>
     <t xml:space="preserve">7.11938571929932</t>
@@ -2135,97 +2135,97 @@
     <t xml:space="preserve">7.22306537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11554622650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06562519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08866548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98498487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77378416061401</t>
+    <t xml:space="preserve">7.11554574966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06562566757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08866453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98498439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7737832069397</t>
   </si>
   <si>
     <t xml:space="preserve">6.80066347122192</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88898420333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9273853302002</t>
+    <t xml:space="preserve">6.77762460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88898468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92738580703735</t>
   </si>
   <si>
     <t xml:space="preserve">6.90818452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91202402114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84290456771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8621039390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84674501419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08098459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0310640335083</t>
+    <t xml:space="preserve">6.91202449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84290409088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86210441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84674406051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08098554611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03106498718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.05794429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75842428207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81218338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81602478027344</t>
+    <t xml:space="preserve">6.75842380523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81218433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81602430343628</t>
   </si>
   <si>
     <t xml:space="preserve">6.87746429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74306392669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69314336776733</t>
+    <t xml:space="preserve">6.74306440353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69314432144165</t>
   </si>
   <si>
     <t xml:space="preserve">6.7200231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89282464981079</t>
+    <t xml:space="preserve">6.89282512664795</t>
   </si>
   <si>
     <t xml:space="preserve">6.79682445526123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70466423034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67778396606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7853045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234369277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538446426392</t>
+    <t xml:space="preserve">6.70466327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67778301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78530406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234321594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73538398742676</t>
   </si>
   <si>
     <t xml:space="preserve">7.20386600494385</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">7.17314577102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20002555847168</t>
+    <t xml:space="preserve">7.22690582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20002603530884</t>
   </si>
   <si>
     <t xml:space="preserve">7.11170530319214</t>
@@ -2252,67 +2252,67 @@
     <t xml:space="preserve">7.25762557983398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33826637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282657623291</t>
+    <t xml:space="preserve">7.29986619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33826732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282705307007</t>
   </si>
   <si>
     <t xml:space="preserve">7.58786678314209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56098699569702</t>
+    <t xml:space="preserve">7.56098747253418</t>
   </si>
   <si>
     <t xml:space="preserve">7.66466665267944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83362770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96418809890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00258827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17922973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86434698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49186563491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36130619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482648849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002796173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3689866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970539093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8944206237793</t>
+    <t xml:space="preserve">7.83362817764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96418857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00258922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17922782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8643479347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378562927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49186706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36130571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482744216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36898708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89442157745361</t>
   </si>
   <si>
     <t xml:space="preserve">6.27458238601685</t>
@@ -2321,46 +2321,46 @@
     <t xml:space="preserve">5.77154064178467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26690149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33602333068848</t>
+    <t xml:space="preserve">6.26690196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33602285385132</t>
   </si>
   <si>
     <t xml:space="preserve">7.15394496917725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21922588348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58018636703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59938716888428</t>
+    <t xml:space="preserve">7.21922445297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58018684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59938669204712</t>
   </si>
   <si>
     <t xml:space="preserve">7.78754806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2717809677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88021659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57023000717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364719390869</t>
+    <t xml:space="preserve">8.27178001403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88021850585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022857666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364767074585</t>
   </si>
   <si>
     <t xml:space="preserve">8.13718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35335540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72860527038574</t>
+    <t xml:space="preserve">8.35335636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72860431671143</t>
   </si>
   <si>
     <t xml:space="preserve">9.03043460845947</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">8.95701694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70413208007812</t>
+    <t xml:space="preserve">8.70413303375244</t>
   </si>
   <si>
     <t xml:space="preserve">8.75307750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99442481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83127212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969530105591</t>
+    <t xml:space="preserve">7.99442434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8312726020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969625473022</t>
   </si>
   <si>
     <t xml:space="preserve">7.81903553009033</t>
@@ -2390,55 +2390,55 @@
     <t xml:space="preserve">7.79864168167114</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87613821029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80679845809937</t>
+    <t xml:space="preserve">7.87613725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80679893493652</t>
   </si>
   <si>
     <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50904846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496912002563</t>
+    <t xml:space="preserve">7.50904703140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496959686279</t>
   </si>
   <si>
     <t xml:space="preserve">7.70482969284058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75377464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94547843933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85574388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94010877609253</t>
+    <t xml:space="preserve">7.75377416610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9454779624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8557448387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94010925292969</t>
   </si>
   <si>
     <t xml:space="preserve">7.98146200180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85739803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78709506988525</t>
+    <t xml:space="preserve">7.85739898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78709602355957</t>
   </si>
   <si>
     <t xml:space="preserve">7.75814819335938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69611597061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54310274124146</t>
+    <t xml:space="preserve">7.69611549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5431022644043</t>
   </si>
   <si>
     <t xml:space="preserve">7.600998878479</t>
@@ -2456,64 +2456,64 @@
     <t xml:space="preserve">7.65062522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55550909042358</t>
+    <t xml:space="preserve">7.55551052093506</t>
   </si>
   <si>
     <t xml:space="preserve">7.53483247756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4521222114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4934778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63408327102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40249633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663194656372</t>
+    <t xml:space="preserve">7.45212268829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49347829818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63408231735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40249729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663242340088</t>
   </si>
   <si>
     <t xml:space="preserve">7.36941289901733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58445835113525</t>
+    <t xml:space="preserve">7.58445692062378</t>
   </si>
   <si>
     <t xml:space="preserve">7.48520565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64235353469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52656078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75401258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919988632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354898452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44385242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34460067749023</t>
+    <t xml:space="preserve">7.64235305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52656126022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75401163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919940948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44385147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34460020065308</t>
   </si>
   <si>
     <t xml:space="preserve">7.39009046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37768363952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73746967315674</t>
+    <t xml:space="preserve">7.37768411636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73746919631958</t>
   </si>
   <si>
     <t xml:space="preserve">7.69198036193848</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">7.77468872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72506427764893</t>
+    <t xml:space="preserve">7.72506380081177</t>
   </si>
   <si>
     <t xml:space="preserve">7.68784475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67543792724609</t>
+    <t xml:space="preserve">7.67543745040894</t>
   </si>
   <si>
     <t xml:space="preserve">7.62167692184448</t>
@@ -2540,175 +2540,175 @@
     <t xml:space="preserve">7.71265745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581253051758</t>
+    <t xml:space="preserve">7.62581348419189</t>
   </si>
   <si>
     <t xml:space="preserve">7.52242517471313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42317485809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33632898330688</t>
+    <t xml:space="preserve">7.4231743812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3363299369812</t>
   </si>
   <si>
     <t xml:space="preserve">7.36527729034424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25775575637817</t>
+    <t xml:space="preserve">7.25775480270386</t>
   </si>
   <si>
     <t xml:space="preserve">7.08406543731689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02203321456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95586538314819</t>
+    <t xml:space="preserve">7.02203273773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95586585998535</t>
   </si>
   <si>
     <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752395629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09647226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07165908813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1709098815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03444051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98894929885864</t>
+    <t xml:space="preserve">7.06752347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09647178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07165956497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534940719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17091083526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03443956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98894882202148</t>
   </si>
   <si>
     <t xml:space="preserve">6.93932437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05511665344238</t>
+    <t xml:space="preserve">7.05511713027954</t>
   </si>
   <si>
     <t xml:space="preserve">6.91864681243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90624094009399</t>
+    <t xml:space="preserve">6.90624046325684</t>
   </si>
   <si>
     <t xml:space="preserve">6.9517297744751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89796876907349</t>
+    <t xml:space="preserve">6.8979697227478</t>
   </si>
   <si>
     <t xml:space="preserve">6.98481369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93105316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82353019714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75322723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78217506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96413660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759368896484</t>
+    <t xml:space="preserve">6.93105268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82353067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75322771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78217554092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96413707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">7.30324554443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43558025360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35700654983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.489342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59272861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80777215957642</t>
+    <t xml:space="preserve">7.43558073043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35700702667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48934125900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59272956848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80777359008789</t>
   </si>
   <si>
     <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71679258346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72092866897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84085607528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190729141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83672094345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84912776947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6671667098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67957305908203</t>
+    <t xml:space="preserve">7.71679306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72092914581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84085702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190919876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82845067977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83672285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84912824630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716718673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67957353591919</t>
   </si>
   <si>
     <t xml:space="preserve">7.61754131317139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60513401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59686470031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57205104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54723787307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55137300491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03522491455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20064258575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15515327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47772026062012</t>
+    <t xml:space="preserve">7.60513496398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59686422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57205152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54723882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55137395858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03522396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20064353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15515232086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4777193069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.14688205718994</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">8.41155242919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28748798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33711338043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6100549697876</t>
+    <t xml:space="preserve">8.28748893737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33711433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61005592346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.68449401855469</t>
@@ -2741,13 +2741,13 @@
     <t xml:space="preserve">8.55215835571289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25026893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59351253509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88299655914307</t>
+    <t xml:space="preserve">8.25026988983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59351348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.92435073852539</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">8.99051856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80028629302979</t>
+    <t xml:space="preserve">8.8002872467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.81682872772217</t>
@@ -2765,139 +2765,139 @@
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10966300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21304893493652</t>
+    <t xml:space="preserve">8.35365581512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966205596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21305084228516</t>
   </si>
   <si>
     <t xml:space="preserve">8.18823719024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13861083984375</t>
+    <t xml:space="preserve">8.13860988616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.32057285308838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24199771881104</t>
+    <t xml:space="preserve">8.24199867248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545528411865</t>
+    <t xml:space="preserve">8.22545623779297</t>
   </si>
   <si>
     <t xml:space="preserve">8.27921772003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25854015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23786163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95664930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86980581283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85326433181763</t>
+    <t xml:space="preserve">8.2585391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23786354064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95665121078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86980533599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85326290130615</t>
   </si>
   <si>
     <t xml:space="preserve">7.89875459671021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74574089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303300857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476083755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5141544342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44798707962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219289779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35287237167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46866464614868</t>
+    <t xml:space="preserve">7.74574136734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66303253173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65476036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51415491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44798612594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219385147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35287141799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46866416931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.43971633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43144464492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50588369369507</t>
+    <t xml:space="preserve">7.43144416809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50588321685791</t>
   </si>
   <si>
     <t xml:space="preserve">7.82017993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76228189468384</t>
+    <t xml:space="preserve">7.762282371521</t>
   </si>
   <si>
     <t xml:space="preserve">7.38181972503662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2039942741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06338787078857</t>
+    <t xml:space="preserve">7.20399475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06338739395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.02616834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12542057037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28670406341553</t>
+    <t xml:space="preserve">7.09233665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12542009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28670358657837</t>
   </si>
   <si>
     <t xml:space="preserve">7.12955570220947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93518829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04271030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16264057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2991099357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053575515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53896808624268</t>
+    <t xml:space="preserve">6.93518924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04271078109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16263914108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29911041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896760940552</t>
   </si>
   <si>
     <t xml:space="preserve">7.70025110244751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80281066894531</t>
+    <t xml:space="preserve">7.80281114578247</t>
   </si>
   <si>
     <t xml:space="preserve">8.03108882904053</t>
@@ -2912,34 +2912,34 @@
     <t xml:space="preserve">7.8193531036377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77138137817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79453897476196</t>
+    <t xml:space="preserve">7.77138042449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79453945159912</t>
   </si>
   <si>
     <t xml:space="preserve">7.70190525054932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86732387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81273651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79619407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6969428062439</t>
+    <t xml:space="preserve">7.86732339859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81273555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79619312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69694185256958</t>
   </si>
   <si>
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635124206543</t>
+    <t xml:space="preserve">7.97319269180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635028839111</t>
   </si>
   <si>
     <t xml:space="preserve">8.01785564422607</t>
@@ -2948,88 +2948,88 @@
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99965953826904</t>
+    <t xml:space="preserve">7.9996600151062</t>
   </si>
   <si>
     <t xml:space="preserve">8.02281761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05093955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845367431641</t>
+    <t xml:space="preserve">8.05093860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845319747925</t>
   </si>
   <si>
     <t xml:space="preserve">7.95003366470337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8805570602417</t>
+    <t xml:space="preserve">7.88055658340454</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8243145942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371513366699</t>
+    <t xml:space="preserve">7.82431554794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371656417847</t>
   </si>
   <si>
     <t xml:space="preserve">8.01289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84416532516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81604385375977</t>
+    <t xml:space="preserve">7.84416484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81604433059692</t>
   </si>
   <si>
     <t xml:space="preserve">7.63904523849487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66055059432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73498916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79480409622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72473478317261</t>
+    <t xml:space="preserve">7.66055154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73498964309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79480361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72473526000977</t>
   </si>
   <si>
     <t xml:space="preserve">7.78967714309692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80847644805908</t>
+    <t xml:space="preserve">7.80847549438477</t>
   </si>
   <si>
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82385778427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258682250977</t>
+    <t xml:space="preserve">7.8238582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258634567261</t>
   </si>
   <si>
     <t xml:space="preserve">7.71960830688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76404190063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89221715927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94007015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98963165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046268463135</t>
+    <t xml:space="preserve">7.76404237747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8922176361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94006967544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98963212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046363830566</t>
   </si>
   <si>
     <t xml:space="preserve">8.09388160705566</t>
@@ -3038,31 +3038,31 @@
     <t xml:space="preserve">8.18445873260498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2494010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28699970245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41517448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39808654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099479675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46302890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21180438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36390495300293</t>
+    <t xml:space="preserve">8.24940204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2869987487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41517543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39808559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46302700042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44252014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21180248260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36390590667725</t>
   </si>
   <si>
     <t xml:space="preserve">8.31947135925293</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">8.2442741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19129467010498</t>
+    <t xml:space="preserve">8.1912956237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.12806129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09900856018066</t>
+    <t xml:space="preserve">8.09900760650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
@@ -3086,25 +3086,25 @@
     <t xml:space="preserve">8.11951637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2271842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36903285980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24598217010498</t>
+    <t xml:space="preserve">8.22718524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36903190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2459831237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.29041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35877799987793</t>
+    <t xml:space="preserve">8.35877704620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.48011779785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45619106292725</t>
+    <t xml:space="preserve">8.45619297027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.44081020355225</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">8.46986389160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40663051605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37245178222656</t>
+    <t xml:space="preserve">8.40663146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
     <t xml:space="preserve">8.46644592285156</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">8.45960998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57496738433838</t>
+    <t xml:space="preserve">8.5749683380127</t>
   </si>
   <si>
     <t xml:space="preserve">8.28358173370361</t>
@@ -3134,22 +3134,22 @@
     <t xml:space="preserve">8.25965595245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32630634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15027904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21863842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1742057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28187274932861</t>
+    <t xml:space="preserve">8.32630729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24256610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1502799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2186393737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17420482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28187370300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.33997917175293</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">8.35365009307861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45277404785156</t>
+    <t xml:space="preserve">8.45277309417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.46473693847656</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">8.50404453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42030239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50233554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66896438598633</t>
+    <t xml:space="preserve">8.42030334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50233459472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66896343231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.64760112762451</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">8.6006031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6347827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62623882293701</t>
+    <t xml:space="preserve">8.63478374481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6262378692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.61769390106201</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">8.63051223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53822422027588</t>
+    <t xml:space="preserve">8.5382251739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42372131347656</t>
+    <t xml:space="preserve">8.42372035980225</t>
   </si>
   <si>
     <t xml:space="preserve">8.49208068847656</t>
@@ -3224,22 +3224,22 @@
     <t xml:space="preserve">8.33656120300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33143424987793</t>
+    <t xml:space="preserve">8.33143329620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.36561393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2340202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3143424987793</t>
+    <t xml:space="preserve">8.23401927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31434345245361</t>
   </si>
   <si>
     <t xml:space="preserve">8.40492153167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30579948425293</t>
+    <t xml:space="preserve">8.30579853057861</t>
   </si>
   <si>
     <t xml:space="preserve">8.49720859527588</t>
@@ -3251,49 +3251,49 @@
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459735870361</t>
+    <t xml:space="preserve">8.32459831237793</t>
   </si>
   <si>
     <t xml:space="preserve">8.2323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2152214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2083854675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17933177947998</t>
+    <t xml:space="preserve">8.21522235870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20838451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17933082580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08875274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475860595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23914813995361</t>
+    <t xml:space="preserve">8.07166385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08875370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2391471862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.33485221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40150260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2545280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17762279510498</t>
+    <t xml:space="preserve">8.40150356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31776142120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452899932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.26478290557861</t>
@@ -3308,34 +3308,34 @@
     <t xml:space="preserve">8.16565895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31605339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21692943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1605339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43055629730225</t>
+    <t xml:space="preserve">8.31605243682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2169303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16053295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43055725097656</t>
   </si>
   <si>
     <t xml:space="preserve">8.32972526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45106601715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44935607910156</t>
+    <t xml:space="preserve">8.45106506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44935512542725</t>
   </si>
   <si>
     <t xml:space="preserve">8.53480625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50575351715088</t>
+    <t xml:space="preserve">8.56642246246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50575256347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.49891757965088</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">9.02358436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08767127990723</t>
+    <t xml:space="preserve">9.08767223358154</t>
   </si>
   <si>
     <t xml:space="preserve">8.86977291107178</t>
@@ -3362,46 +3362,46 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704830169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168804168701</t>
+    <t xml:space="preserve">8.82704734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168994903564</t>
   </si>
   <si>
     <t xml:space="preserve">8.65614700317383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72023487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72450733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6390552520752</t>
+    <t xml:space="preserve">8.72023391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72450637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63905620574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.60914707183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69460010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75441551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77150440216064</t>
+    <t xml:space="preserve">8.69459915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75441455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77150535583496</t>
   </si>
   <si>
     <t xml:space="preserve">8.88686275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88259124755859</t>
+    <t xml:space="preserve">8.88259029388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.92531585693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94667911529541</t>
+    <t xml:space="preserve">8.94667816162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.95522308349609</t>
@@ -3410,22 +3410,22 @@
     <t xml:space="preserve">8.98085880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92104339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98940467834473</t>
+    <t xml:space="preserve">8.92104244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98940372467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.06630897521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12612438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20303058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212833404541</t>
+    <t xml:space="preserve">9.12612533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20302963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212928771973</t>
   </si>
   <si>
     <t xml:space="preserve">8.98513126373291</t>
@@ -3437,22 +3437,22 @@
     <t xml:space="preserve">8.5877857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28870868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26136493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1588249206543</t>
+    <t xml:space="preserve">8.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2613639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15882396697998</t>
   </si>
   <si>
     <t xml:space="preserve">8.08020973205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2066764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35706901550293</t>
+    <t xml:space="preserve">8.20667552947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35706806182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.78455066680908</t>
@@ -3461,31 +3461,31 @@
     <t xml:space="preserve">7.81873083114624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81360292434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8101863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540504455566</t>
+    <t xml:space="preserve">7.81360387802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81018543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540599822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.12635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8802547454834</t>
+    <t xml:space="preserve">7.88025426864624</t>
   </si>
   <si>
     <t xml:space="preserve">7.71106243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60168504714966</t>
+    <t xml:space="preserve">7.60168552398682</t>
   </si>
   <si>
     <t xml:space="preserve">7.61364889144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54699754714966</t>
+    <t xml:space="preserve">7.54699659347534</t>
   </si>
   <si>
     <t xml:space="preserve">7.45129251480103</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">7.64953851699829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57434177398682</t>
+    <t xml:space="preserve">7.57434129714966</t>
   </si>
   <si>
     <t xml:space="preserve">7.58288669586182</t>
@@ -3509,43 +3509,43 @@
     <t xml:space="preserve">7.41369438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69055509567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82556581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5657958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510301589966</t>
+    <t xml:space="preserve">7.69055461883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82556629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510349273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.78625917434692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56237936019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72302579879761</t>
+    <t xml:space="preserve">7.56237888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72302532196045</t>
   </si>
   <si>
     <t xml:space="preserve">7.66491937637329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77087831497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62561273574829</t>
+    <t xml:space="preserve">7.77087783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62561178207397</t>
   </si>
   <si>
     <t xml:space="preserve">8.03235626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91785287857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95545148849487</t>
+    <t xml:space="preserve">7.9178524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95545101165771</t>
   </si>
   <si>
     <t xml:space="preserve">8.07508182525635</t>
@@ -3554,22 +3554,22 @@
     <t xml:space="preserve">8.14173316955566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2032585144043</t>
+    <t xml:space="preserve">8.20325946807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.2288932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48182582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5006275177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39466857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54335117340088</t>
+    <t xml:space="preserve">8.48182678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50062656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39466762542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5433521270752</t>
   </si>
   <si>
     <t xml:space="preserve">8.5578784942627</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">8.68178081512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68605327606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73732376098633</t>
+    <t xml:space="preserve">8.68605422973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73732471466064</t>
   </si>
   <si>
     <t xml:space="preserve">8.82277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97658538818359</t>
+    <t xml:space="preserve">8.97658634185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.93813323974609</t>
@@ -3602,31 +3602,31 @@
     <t xml:space="preserve">8.95095157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91677093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90395164489746</t>
+    <t xml:space="preserve">8.91677188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90395355224609</t>
   </si>
   <si>
     <t xml:space="preserve">8.81422901153564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6134204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67323589324951</t>
+    <t xml:space="preserve">8.61342144012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67323684692383</t>
   </si>
   <si>
     <t xml:space="preserve">8.69887161254883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70314502716064</t>
+    <t xml:space="preserve">8.70314407348633</t>
   </si>
   <si>
     <t xml:space="preserve">8.74159622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46131992340088</t>
+    <t xml:space="preserve">8.46131896972656</t>
   </si>
   <si>
     <t xml:space="preserve">8.83131980895996</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">8.5621509552002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92368793487549</t>
+    <t xml:space="preserve">8.92368698120117</t>
   </si>
   <si>
     <t xml:space="preserve">9.16629981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26775455474854</t>
+    <t xml:space="preserve">9.26775550842285</t>
   </si>
   <si>
     <t xml:space="preserve">9.24128913879395</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">9.14424324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1883544921875</t>
+    <t xml:space="preserve">9.18835544586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.1927661895752</t>
@@ -3680,37 +3680,37 @@
     <t xml:space="preserve">8.23996543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25760841369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21702671051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31583499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42346668243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79929447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73224544525146</t>
+    <t xml:space="preserve">8.25760936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21702766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31583595275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4234676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73224449157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.58932590484619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57521057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54345035552979</t>
+    <t xml:space="preserve">8.57520961761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54344940185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.77988624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71636486053467</t>
+    <t xml:space="preserve">8.71636581420898</t>
   </si>
   <si>
     <t xml:space="preserve">8.86634349822998</t>
@@ -3719,31 +3719,31 @@
     <t xml:space="preserve">8.82223224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80458831787109</t>
+    <t xml:space="preserve">8.80458641052246</t>
   </si>
   <si>
     <t xml:space="preserve">8.77635669708252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91486644744873</t>
+    <t xml:space="preserve">8.91486549377441</t>
   </si>
   <si>
     <t xml:space="preserve">8.93692207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84428787231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85310935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8151741027832</t>
+    <t xml:space="preserve">8.84428691864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85311031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81517505645752</t>
   </si>
   <si>
     <t xml:space="preserve">8.70577907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57168006896973</t>
+    <t xml:space="preserve">8.57168102264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.78694343566895</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">8.85752105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55756568908691</t>
+    <t xml:space="preserve">8.5575647354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.62814235687256</t>
@@ -3773,16 +3773,16 @@
     <t xml:space="preserve">8.58756065368652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61579132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77106475830078</t>
+    <t xml:space="preserve">8.6157922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77106380462646</t>
   </si>
   <si>
     <t xml:space="preserve">8.74459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90163326263428</t>
+    <t xml:space="preserve">8.90163230895996</t>
   </si>
   <si>
     <t xml:space="preserve">8.84869861602783</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">8.8354663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68460464477539</t>
+    <t xml:space="preserve">8.68460559844971</t>
   </si>
   <si>
     <t xml:space="preserve">8.56638813018799</t>
@@ -3800,31 +3800,31 @@
     <t xml:space="preserve">8.63167285919189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37935543060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34936046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29995632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16938781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10763168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25584411621094</t>
+    <t xml:space="preserve">8.37935638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3493595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29995536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10763072967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25584506988525</t>
   </si>
   <si>
     <t xml:space="preserve">8.28407669067383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53639125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39700031280518</t>
+    <t xml:space="preserve">8.53639221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39700126647949</t>
   </si>
   <si>
     <t xml:space="preserve">8.32818698883057</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">8.70754337310791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45699310302734</t>
+    <t xml:space="preserve">8.45699214935303</t>
   </si>
   <si>
     <t xml:space="preserve">8.39347171783447</t>
@@ -3842,55 +3842,55 @@
     <t xml:space="preserve">8.08292865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22584915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00352954864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95412397384644</t>
+    <t xml:space="preserve">8.22585010528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0035285949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95412445068359</t>
   </si>
   <si>
     <t xml:space="preserve">7.90824890136719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92589378356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90472078323364</t>
+    <t xml:space="preserve">7.92589426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90472030639648</t>
   </si>
   <si>
     <t xml:space="preserve">7.80061817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9135422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94706678390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15703582763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04411125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7847375869751</t>
+    <t xml:space="preserve">7.91354274749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94706773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15703678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04411220550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78473806381226</t>
   </si>
   <si>
     <t xml:space="preserve">7.54830169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64534664154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52007102966309</t>
+    <t xml:space="preserve">7.64534711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52007150650024</t>
   </si>
   <si>
     <t xml:space="preserve">7.39479494094849</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40538215637207</t>
+    <t xml:space="preserve">7.40538167953491</t>
   </si>
   <si>
     <t xml:space="preserve">7.51124858856201</t>
@@ -3899,37 +3899,37 @@
     <t xml:space="preserve">7.64711093902588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4389066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52359962463379</t>
+    <t xml:space="preserve">7.43890619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52359914779663</t>
   </si>
   <si>
     <t xml:space="preserve">7.3101019859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5094838142395</t>
+    <t xml:space="preserve">7.50948429107666</t>
   </si>
   <si>
     <t xml:space="preserve">7.73180437088013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7370982170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75297737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87472438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88001775741577</t>
+    <t xml:space="preserve">7.73709774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75297689437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8747239112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88001871109009</t>
   </si>
   <si>
     <t xml:space="preserve">7.85355138778687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94353771209717</t>
+    <t xml:space="preserve">7.94353818893433</t>
   </si>
   <si>
     <t xml:space="preserve">8.09351539611816</t>
@@ -3938,13 +3938,13 @@
     <t xml:space="preserve">8.08822250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14292049407959</t>
+    <t xml:space="preserve">8.14291954040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.38817882537842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76047611236572</t>
+    <t xml:space="preserve">8.76047706604004</t>
   </si>
   <si>
     <t xml:space="preserve">8.69872093200684</t>
@@ -3953,43 +3953,43 @@
     <t xml:space="preserve">8.50286674499512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40053081512451</t>
+    <t xml:space="preserve">8.4005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.33524513244629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48698711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4693431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48169422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49404525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40935230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28054618835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53109931945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46757888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4269962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37053394317627</t>
+    <t xml:space="preserve">8.48698806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46934413909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4816951751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49404621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40935134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28054809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53109836578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47640037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46757793426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42699718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37053489685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.36347579956055</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">8.53286361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55580139160156</t>
+    <t xml:space="preserve">8.55580043792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.4305248260498</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.2152624130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26466751098633</t>
+    <t xml:space="preserve">8.26466655731201</t>
   </si>
   <si>
     <t xml:space="preserve">8.16232967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37582874298096</t>
+    <t xml:space="preserve">8.37582778930664</t>
   </si>
   <si>
     <t xml:space="preserve">8.35112476348877</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">8.29819202423096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41640949249268</t>
+    <t xml:space="preserve">8.41640853881836</t>
   </si>
   <si>
     <t xml:space="preserve">8.30524921417236</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">8.37406253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40758800506592</t>
+    <t xml:space="preserve">8.4075870513916</t>
   </si>
   <si>
     <t xml:space="preserve">8.49580955505371</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">8.64402389526367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67048931121826</t>
+    <t xml:space="preserve">8.67049026489258</t>
   </si>
   <si>
     <t xml:space="preserve">8.61226367950439</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">8.7887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82046794891357</t>
+    <t xml:space="preserve">8.82046890258789</t>
   </si>
   <si>
     <t xml:space="preserve">8.73400974273682</t>
@@ -4067,31 +4067,31 @@
     <t xml:space="preserve">8.88398742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95456504821777</t>
+    <t xml:space="preserve">8.95456600189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.96779918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89280986785889</t>
+    <t xml:space="preserve">8.91927719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8619327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8928108215332</t>
   </si>
   <si>
     <t xml:space="preserve">9.11336612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89722061157227</t>
+    <t xml:space="preserve">8.89722156524658</t>
   </si>
   <si>
     <t xml:space="preserve">8.97221088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99867630004883</t>
+    <t xml:space="preserve">8.99867725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.18394374847412</t>
@@ -4103,19 +4103,19 @@
     <t xml:space="preserve">9.26334381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28098964691162</t>
+    <t xml:space="preserve">9.2809886932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.22805500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15306663513184</t>
+    <t xml:space="preserve">9.15306568145752</t>
   </si>
   <si>
     <t xml:space="preserve">9.14865493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13101005554199</t>
+    <t xml:space="preserve">9.13101100921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.13983249664307</t>
@@ -4124,25 +4124,25 @@
     <t xml:space="preserve">9.08248805999756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0427885055542</t>
+    <t xml:space="preserve">9.04278755187988</t>
   </si>
   <si>
     <t xml:space="preserve">9.93383407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0485239028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74415588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1411552429199</t>
+    <t xml:space="preserve">10.0485229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74415493011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1411561965942</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720342636108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0264673233032</t>
+    <t xml:space="preserve">10.0264663696289</t>
   </si>
   <si>
     <t xml:space="preserve">9.78385543823242</t>
@@ -4151,31 +4151,31 @@
     <t xml:space="preserve">10.0705785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87207698822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94706726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77944564819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190996170044</t>
+    <t xml:space="preserve">9.87207794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94706630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77944469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1191005706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.99117755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5116891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3440675735474</t>
+    <t xml:space="preserve">10.5116901397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3440685272217</t>
   </si>
   <si>
     <t xml:space="preserve">10.5778570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6131448745728</t>
+    <t xml:space="preserve">10.6131458282471</t>
   </si>
   <si>
     <t xml:space="preserve">10.6881341934204</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">10.7057790756226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6925449371338</t>
+    <t xml:space="preserve">10.6925458908081</t>
   </si>
   <si>
     <t xml:space="preserve">10.7278337478638</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">10.8778123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8601675033569</t>
+    <t xml:space="preserve">10.8601684570312</t>
   </si>
   <si>
     <t xml:space="preserve">10.789589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160572052002</t>
+    <t xml:space="preserve">10.8160581588745</t>
   </si>
   <si>
     <t xml:space="preserve">10.868989944458</t>
@@ -4238,34 +4238,34 @@
     <t xml:space="preserve">11.0454359054565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1248340606689</t>
+    <t xml:space="preserve">11.1248350143433</t>
   </si>
   <si>
     <t xml:space="preserve">11.0586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.09836769104</t>
+    <t xml:space="preserve">11.0983686447144</t>
   </si>
   <si>
     <t xml:space="preserve">10.8645782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6969566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6528463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660795211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.639612197876</t>
+    <t xml:space="preserve">10.6969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6528453826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6396131515503</t>
   </si>
   <si>
     <t xml:space="preserve">10.4852237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6352005004883</t>
+    <t xml:space="preserve">10.6352014541626</t>
   </si>
   <si>
     <t xml:space="preserve">10.8274984359741</t>
@@ -5541,6 +5541,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.4399995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32999992370605</t>
   </si>
 </sst>
 </file>
@@ -71061,7 +71064,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6911226852</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>1088798</v>
@@ -71082,6 +71085,32 @@
         <v>1842</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6911689815</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>12533582</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>8.77000045776367</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>8.26000022888184</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>8.57999992370605</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>8.32999992370605</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INW.MI.xlsx
+++ b/data/INW.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="1844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="1845">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,79 +38,79 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433881759644</t>
+    <t xml:space="preserve">3.42433762550354</t>
   </si>
   <si>
     <t xml:space="preserve">INW.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46296858787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45607137680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46986722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47331666946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39812445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34845662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3470766544342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26981496810913</t>
+    <t xml:space="preserve">3.46296906471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4560706615448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46986746788025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47331643104553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39812469482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34845638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34707689285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26981472969055</t>
   </si>
   <si>
     <t xml:space="preserve">3.2863712310791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21324920654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03803062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13874697685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14288568496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10425519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1649603843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13736724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1456446647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30430698394775</t>
+    <t xml:space="preserve">3.21324849128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03803086280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13874650001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14288592338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10425496101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16496014595032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13736701011658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14564538002014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945216178894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30430674552917</t>
   </si>
   <si>
     <t xml:space="preserve">3.27119517326355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222159385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20910978317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20773029327393</t>
+    <t xml:space="preserve">3.24222183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20911002159119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2077305316925</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631920814514</t>
@@ -119,91 +119,91 @@
     <t xml:space="preserve">3.06700420379639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00078010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00215935707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99802088737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02837300300598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07114338874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13322830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1111536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18151664733887</t>
+    <t xml:space="preserve">3.00077962875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00215983390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99802112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02837324142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07114315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13322758674622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11115336418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18151640892029</t>
   </si>
   <si>
     <t xml:space="preserve">3.13046860694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14150619506836</t>
+    <t xml:space="preserve">3.14150643348694</t>
   </si>
   <si>
     <t xml:space="preserve">3.12495017051697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11805152893066</t>
+    <t xml:space="preserve">3.11805200576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.23808312416077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17323875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1953125</t>
+    <t xml:space="preserve">3.17323851585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19531345367432</t>
   </si>
   <si>
     <t xml:space="preserve">3.18703508377075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09321761131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18013668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19255375862122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18427586555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636054039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20635008811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.198073387146</t>
+    <t xml:space="preserve">3.09321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19255399703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18427610397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636149406433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20635032653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19807267189026</t>
   </si>
   <si>
     <t xml:space="preserve">3.10563468933105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04906821250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05458664894104</t>
+    <t xml:space="preserve">3.04906845092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0545871257782</t>
   </si>
   <si>
     <t xml:space="preserve">3.03941059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00491881370544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05182766914368</t>
+    <t xml:space="preserve">3.00491857528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05182719230652</t>
   </si>
   <si>
     <t xml:space="preserve">2.98422384262085</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">3.05044794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05320763587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01595664024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01457619667053</t>
+    <t xml:space="preserve">3.05320715904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01595640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01457643508911</t>
   </si>
   <si>
     <t xml:space="preserve">3.02147483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00629878044128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00767850875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02561402320862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09873652458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08769917488098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14978432655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05596685409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06838345527649</t>
+    <t xml:space="preserve">3.00629854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00767827033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0256142616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09873628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0876989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14978384971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0559663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06838369369507</t>
   </si>
   <si>
     <t xml:space="preserve">3.01319694519043</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">3.02975296974182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01871562004089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9676673412323</t>
+    <t xml:space="preserve">3.01871538162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96766805648804</t>
   </si>
   <si>
     <t xml:space="preserve">2.95249176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94421362876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93869495391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93593573570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02235865592957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02659201622009</t>
+    <t xml:space="preserve">2.94421410560608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93869519233704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93593549728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02235889434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02659249305725</t>
   </si>
   <si>
     <t xml:space="preserve">2.99837207794189</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">2.98426222801208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99131727218628</t>
+    <t xml:space="preserve">2.9913170337677</t>
   </si>
   <si>
     <t xml:space="preserve">2.97861814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06892204284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06609988212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01389288902283</t>
+    <t xml:space="preserve">3.0689218044281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610059738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01389265060425</t>
   </si>
   <si>
     <t xml:space="preserve">3.0209481716156</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">3.00683808326721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03929162025452</t>
+    <t xml:space="preserve">3.03929138183594</t>
   </si>
   <si>
     <t xml:space="preserve">3.01671481132507</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">3.03505802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99978256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9645082950592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86714911460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80083250999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87843751907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93205547332764</t>
+    <t xml:space="preserve">2.99978303909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96450805664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86714959144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80083203315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87843704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93205499649048</t>
   </si>
   <si>
     <t xml:space="preserve">2.87702608108521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91088962554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7218165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61034774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67525386810303</t>
+    <t xml:space="preserve">2.91089034080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72181630134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61034750938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67525362968445</t>
   </si>
   <si>
     <t xml:space="preserve">2.71899437904358</t>
@@ -353,49 +353,49 @@
     <t xml:space="preserve">2.79659938812256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79518842697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85162830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83610701560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87279295921326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94475388526917</t>
+    <t xml:space="preserve">2.79518795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85162806510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83610725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87279343605042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94475436210632</t>
   </si>
   <si>
     <t xml:space="preserve">2.97438502311707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00542759895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02518105506897</t>
+    <t xml:space="preserve">3.00542736053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02518153190613</t>
   </si>
   <si>
     <t xml:space="preserve">3.04211282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07597756385803</t>
+    <t xml:space="preserve">3.07597708702087</t>
   </si>
   <si>
     <t xml:space="preserve">3.03364706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07033276557922</t>
+    <t xml:space="preserve">3.07033324241638</t>
   </si>
   <si>
     <t xml:space="preserve">3.05481195449829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03787994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05199027061462</t>
+    <t xml:space="preserve">3.03788018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05199003219604</t>
   </si>
   <si>
     <t xml:space="preserve">3.17333579063416</t>
@@ -404,85 +404,85 @@
     <t xml:space="preserve">3.16204786300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15499305725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14088273048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14793753623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10842967033386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09149813652039</t>
+    <t xml:space="preserve">3.1549928188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14088320732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14793801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10842990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09149789810181</t>
   </si>
   <si>
     <t xml:space="preserve">3.13241720199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13947224617004</t>
+    <t xml:space="preserve">3.13947176933289</t>
   </si>
   <si>
     <t xml:space="preserve">3.15075993537903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10419702529907</t>
+    <t xml:space="preserve">3.10419774055481</t>
   </si>
   <si>
     <t xml:space="preserve">3.08444309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02800297737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0124819278717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02376985549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0717442035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06045603752136</t>
+    <t xml:space="preserve">3.02800321578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01248216629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02377009391785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07174396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06045579910278</t>
   </si>
   <si>
     <t xml:space="preserve">3.03646898269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09008693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19732284545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21002244949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18462347984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21284365653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21707677841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27774977684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27351689338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22130990028381</t>
+    <t xml:space="preserve">3.0900866985321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19732260704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21002149581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18462419509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21284413337708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21707725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27775001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27351665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22130966186523</t>
   </si>
   <si>
     <t xml:space="preserve">3.20861053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19873380661011</t>
+    <t xml:space="preserve">3.19873452186584</t>
   </si>
   <si>
     <t xml:space="preserve">3.18180203437805</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">3.1535816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15217137336731</t>
+    <t xml:space="preserve">3.15217089653015</t>
   </si>
   <si>
     <t xml:space="preserve">3.16628098487854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12536191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11125135421753</t>
+    <t xml:space="preserve">3.1253616809845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11125206947327</t>
   </si>
   <si>
     <t xml:space="preserve">3.08726501464844</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">3.09714198112488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11548519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08867621421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.077388048172</t>
+    <t xml:space="preserve">3.11548471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0886754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07738828659058</t>
   </si>
   <si>
     <t xml:space="preserve">3.06186723709106</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">2.99696111679077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92923307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95321989059448</t>
+    <t xml:space="preserve">2.92923331260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95322012901306</t>
   </si>
   <si>
     <t xml:space="preserve">2.95180916786194</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">2.95886397361755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92782235145569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98002886772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04493522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05622315406799</t>
+    <t xml:space="preserve">2.92782211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98002910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04493498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05622267723083</t>
   </si>
   <si>
     <t xml:space="preserve">3.01953744888306</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">2.99554991722107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04070210456848</t>
+    <t xml:space="preserve">3.0407018661499</t>
   </si>
   <si>
     <t xml:space="preserve">3.01812601089478</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">2.96309685707092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92641091346741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98849511146545</t>
+    <t xml:space="preserve">2.92641067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98849534988403</t>
   </si>
   <si>
     <t xml:space="preserve">2.87138223648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8572723865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86856031417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92358899116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95604252815247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88690304756165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89819121360779</t>
+    <t xml:space="preserve">2.85727214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86856055259705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92358946800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95604181289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88690328598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89819073677063</t>
   </si>
   <si>
     <t xml:space="preserve">2.85303950309753</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">2.84034037590027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82199740409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84457349777222</t>
+    <t xml:space="preserve">2.82199764251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84457302093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.85021710395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78390026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79377770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82340788841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75568056106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76132464408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80929851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8925473690033</t>
+    <t xml:space="preserve">2.78390049934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79377746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82340836524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75568032264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76132440567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80929827690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89254713058472</t>
   </si>
   <si>
     <t xml:space="preserve">2.89395809173584</t>
@@ -644,262 +644,262 @@
     <t xml:space="preserve">2.86009430885315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90665721893311</t>
+    <t xml:space="preserve">2.90665745735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.88831448554993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9123010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94052124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09431982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0802104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08303165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10560774803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08585429191589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13523888587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14511609077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13806056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16063690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17051410675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20437788963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19591188430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12254023551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10278582572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09290885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06751108169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11830687522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13664984703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07456564903259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10701870918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.098552942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24529647827148</t>
+    <t xml:space="preserve">2.91230082511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94052147865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09432029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08020997047424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08303189277649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10560846328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08585381507874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13523840904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14511632919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13806080818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16063737869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17051362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20437741279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19591212272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12253999710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09573125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10278558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09290862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06751132011414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11830711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17898011207581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13665008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07456588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10701894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09855318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24529695510864</t>
   </si>
   <si>
     <t xml:space="preserve">3.26646208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25376296043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25094079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29891490936279</t>
+    <t xml:space="preserve">3.25376272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25094056129456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29891514778137</t>
   </si>
   <si>
     <t xml:space="preserve">3.31443572044373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38357472419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37228679656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37651944160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44565868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41461682319641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44283699989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40756177902222</t>
+    <t xml:space="preserve">3.38357496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3722870349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37651968002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4456582069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41461706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40756130218506</t>
   </si>
   <si>
     <t xml:space="preserve">3.4005069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48657751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51338648796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47105669975281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54160618782043</t>
+    <t xml:space="preserve">3.48657774925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51338696479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54160666465759</t>
   </si>
   <si>
     <t xml:space="preserve">3.47811150550842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48798823356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52185320854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50633120536804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49222135543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5627715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53455209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52749633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54866170883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51056432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59099173545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568403244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58393597602844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50209903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55924439430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62273907661438</t>
+    <t xml:space="preserve">3.48798799514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52185273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5063316822052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49222183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56277179718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5345516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52749729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54866147041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51056456565857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59099149703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568379402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5839364528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50209808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55924391746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62273931503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.65095925331116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66154050827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66506886482239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61921119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63332152366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59804630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73752284049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68667149543762</t>
+    <t xml:space="preserve">3.661541223526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66506838798523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61921167373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6333212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59804677963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7375226020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68667197227478</t>
   </si>
   <si>
     <t xml:space="preserve">3.72299385070801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71936225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7048327922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66124653816223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83195972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82832741737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81379818916321</t>
+    <t xml:space="preserve">3.71936202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70483326911926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66124677658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83195996284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82832717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81379890441895</t>
   </si>
   <si>
     <t xml:space="preserve">3.84285569190979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85012030601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88644194602966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86101675033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648776054382</t>
+    <t xml:space="preserve">3.85012054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88644218444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86101698875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648847579956</t>
   </si>
   <si>
     <t xml:space="preserve">3.82469487190247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83922386169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98451161384583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90097117424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94455742835999</t>
+    <t xml:space="preserve">3.83922433853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98451137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90097165107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94455718994141</t>
   </si>
   <si>
     <t xml:space="preserve">3.98087954521179</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">3.90823554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91913223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81016564369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304038047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6576144695282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330223083496</t>
+    <t xml:space="preserve">3.91913199424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81016659736633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68303942680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65761423110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330151557922</t>
   </si>
   <si>
     <t xml:space="preserve">3.62201929092407</t>
@@ -932,64 +932,64 @@
     <t xml:space="preserve">3.60313177108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59150838851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62492489814758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67214345932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69030356407166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63218903541565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65034961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71572971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72662591934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87191438674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96635007858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93366074562073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95908641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96998310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356935501099</t>
+    <t xml:space="preserve">3.59150862693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62492442131042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67214298248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6307361125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69030404090881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63218879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65035033226013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7157289981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72662544250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87191367149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96635055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93366098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95908617973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96998286247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356983184814</t>
   </si>
   <si>
     <t xml:space="preserve">4.05352306365967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04989051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07894849777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00267171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95182228088379</t>
+    <t xml:space="preserve">4.04989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07894802093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95182156562805</t>
   </si>
   <si>
     <t xml:space="preserve">3.91549968719482</t>
@@ -998,79 +998,79 @@
     <t xml:space="preserve">4.00993680953979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99540853500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99177622795105</t>
+    <t xml:space="preserve">3.99540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99177575111389</t>
   </si>
   <si>
     <t xml:space="preserve">4.02446556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04262590408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10437393188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96271800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86464929580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89733862876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98814368247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95545434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93002820014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01720142364502</t>
+    <t xml:space="preserve">4.04262685775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10437345504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96271848678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86464905738831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8973388671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98814415931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95545482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93002867698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01720094680786</t>
   </si>
   <si>
     <t xml:space="preserve">3.88280987739563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07531642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0680513381958</t>
+    <t xml:space="preserve">4.07531690597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06805181503296</t>
   </si>
   <si>
     <t xml:space="preserve">4.14796018600464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0462589263916</t>
+    <t xml:space="preserve">4.04625797271729</t>
   </si>
   <si>
     <t xml:space="preserve">4.06078767776489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11527061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10800695419312</t>
+    <t xml:space="preserve">4.11527013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10800647735596</t>
   </si>
   <si>
     <t xml:space="preserve">4.12253475189209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18064975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15885591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18791437149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16612100601196</t>
+    <t xml:space="preserve">4.18064880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15885639190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18791389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16612148284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.17338514328003</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">4.09710931777954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14069509506226</t>
+    <t xml:space="preserve">4.14069557189941</t>
   </si>
   <si>
     <t xml:space="preserve">4.129798412323</t>
@@ -1088,40 +1088,40 @@
     <t xml:space="preserve">4.24602890014648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22060394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26055812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21697187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26419067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27508640289307</t>
+    <t xml:space="preserve">4.22060346603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26055765151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21697235107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25329351425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26419019699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27508687973022</t>
   </si>
   <si>
     <t xml:space="preserve">4.24239683151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1770167350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08984518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.307776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29687929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4276385307312</t>
+    <t xml:space="preserve">4.17701768875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08984565734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30777597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29687976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42763805389404</t>
   </si>
   <si>
     <t xml:space="preserve">4.51481103897095</t>
@@ -1130,28 +1130,28 @@
     <t xml:space="preserve">4.54023694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60198307037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5983510017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72184562683105</t>
+    <t xml:space="preserve">4.60198354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59835195541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72184610366821</t>
   </si>
   <si>
     <t xml:space="preserve">4.56929397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56202936172485</t>
+    <t xml:space="preserve">4.5620288848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.62014484405518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59471893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60924816131592</t>
+    <t xml:space="preserve">4.59471940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60924768447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.4893856048584</t>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">4.45669603347778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51844358444214</t>
+    <t xml:space="preserve">4.51844310760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.33683395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52207517623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49301815032959</t>
+    <t xml:space="preserve">4.52207565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49301719665527</t>
   </si>
   <si>
     <t xml:space="preserve">4.50391435623169</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">4.49665021896362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46032762527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45306491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46759271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47848844528198</t>
+    <t xml:space="preserve">4.46032905578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45306348800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46759223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4784893989563</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750156402588</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">4.37315607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39131736755371</t>
+    <t xml:space="preserve">4.39131641387939</t>
   </si>
   <si>
     <t xml:space="preserve">4.42037439346313</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">4.40947771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51117944717407</t>
+    <t xml:space="preserve">4.51117849349976</t>
   </si>
   <si>
     <t xml:space="preserve">4.42400646209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31140899658203</t>
+    <t xml:space="preserve">4.31140804290771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28235101699829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20607471466064</t>
+    <t xml:space="preserve">4.2060751914978</t>
   </si>
   <si>
     <t xml:space="preserve">4.12616682052612</t>
@@ -1238,94 +1238,94 @@
     <t xml:space="preserve">4.23150014877319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14432811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97361493110657</t>
+    <t xml:space="preserve">4.14432764053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97361516952515</t>
   </si>
   <si>
     <t xml:space="preserve">3.94092535972595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97724747657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08258008956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15522480010986</t>
+    <t xml:space="preserve">3.97724652290344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08258152008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15522384643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.169753074646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44579935073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40584516525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4167423248291</t>
+    <t xml:space="preserve">4.44579982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.405846118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41674184799194</t>
   </si>
   <si>
     <t xml:space="preserve">4.59108734130859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61287975311279</t>
+    <t xml:space="preserve">4.61288022994995</t>
   </si>
   <si>
     <t xml:space="preserve">4.5511326789856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5765585899353</t>
+    <t xml:space="preserve">4.57655811309814</t>
   </si>
   <si>
     <t xml:space="preserve">4.5293402671814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52570724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53297233581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67825937271118</t>
+    <t xml:space="preserve">4.52570772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53297138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67825984954834</t>
   </si>
   <si>
     <t xml:space="preserve">4.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67099523544312</t>
+    <t xml:space="preserve">4.67099475860596</t>
   </si>
   <si>
     <t xml:space="preserve">4.64556980133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65283489227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7581672668457</t>
+    <t xml:space="preserve">4.65283441543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75816774368286</t>
   </si>
   <si>
     <t xml:space="preserve">4.75090312957764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179933547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7254786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68552446365356</t>
+    <t xml:space="preserve">4.76179981231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72547817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68552350997925</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65646648406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84534072875977</t>
+    <t xml:space="preserve">4.65646696090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84533977508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.81265068054199</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">4.83807516098022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88166189193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84897232055664</t>
+    <t xml:space="preserve">4.88166236877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8489727973938</t>
   </si>
   <si>
     <t xml:space="preserve">4.91798448562622</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">4.89255857467651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95430612564087</t>
+    <t xml:space="preserve">4.95430564880371</t>
   </si>
   <si>
     <t xml:space="preserve">4.94704151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93977785110474</t>
+    <t xml:space="preserve">4.93977689743042</t>
   </si>
   <si>
     <t xml:space="preserve">4.93251276016235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99062728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94340991973877</t>
+    <t xml:space="preserve">4.99062871932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94340896606445</t>
   </si>
   <si>
     <t xml:space="preserve">4.86713314056396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7330756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87888193130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86018800735474</t>
+    <t xml:space="preserve">4.73307657241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87888145446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86018848419189</t>
   </si>
   <si>
     <t xml:space="preserve">4.82654142379761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75176858901978</t>
+    <t xml:space="preserve">4.75176906585693</t>
   </si>
   <si>
     <t xml:space="preserve">4.65082597732544</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">4.63587188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74803066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72186040878296</t>
+    <t xml:space="preserve">4.74803018569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72185945510864</t>
   </si>
   <si>
     <t xml:space="preserve">4.70690584182739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57979345321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75924634933472</t>
+    <t xml:space="preserve">4.57979297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75924587249756</t>
   </si>
   <si>
     <t xml:space="preserve">4.83027982711792</t>
@@ -1430,40 +1430,40 @@
     <t xml:space="preserve">4.94243812561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91252946853638</t>
+    <t xml:space="preserve">4.91252899169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.91626739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90505123138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88262033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93869972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96486902236938</t>
+    <t xml:space="preserve">4.90505170822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88261985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93869924545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9648699760437</t>
   </si>
   <si>
     <t xml:space="preserve">5.03216409683228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01720952987671</t>
+    <t xml:space="preserve">5.01721000671387</t>
   </si>
   <si>
     <t xml:space="preserve">5.13684558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05833435058594</t>
+    <t xml:space="preserve">5.05833387374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.98356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89757490158081</t>
+    <t xml:space="preserve">4.89757442474365</t>
   </si>
   <si>
     <t xml:space="preserve">5.1293683052063</t>
@@ -1472,46 +1472,46 @@
     <t xml:space="preserve">5.24900341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37985467910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3162989616394</t>
+    <t xml:space="preserve">5.37985515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31629848480225</t>
   </si>
   <si>
     <t xml:space="preserve">5.41350173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34246826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09945917129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01347064971924</t>
+    <t xml:space="preserve">5.34246873855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09945964813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01347160339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.17796993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20040082931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23404979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25274229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20787906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21535587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22283363342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19666337966919</t>
+    <t xml:space="preserve">5.2004017829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23404932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25274276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20787954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21535634994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22283315658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19666290283203</t>
   </si>
   <si>
     <t xml:space="preserve">5.11815166473389</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">5.04338026046753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99851703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11067581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17049264907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04711866378784</t>
+    <t xml:space="preserve">4.99851655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11067533493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17049217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04711818695068</t>
   </si>
   <si>
     <t xml:space="preserve">5.11441373825073</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">4.97982358932495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95739221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03964138031006</t>
+    <t xml:space="preserve">4.95739269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0396409034729</t>
   </si>
   <si>
     <t xml:space="preserve">5.05459642410278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0807671546936</t>
+    <t xml:space="preserve">5.08076667785645</t>
   </si>
   <si>
     <t xml:space="preserve">5.18544721603394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0957202911377</t>
+    <t xml:space="preserve">5.09572124481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.2116174697876</t>
@@ -1565,100 +1565,100 @@
     <t xml:space="preserve">4.8863582611084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.920006275177</t>
+    <t xml:space="preserve">4.92000579833984</t>
   </si>
   <si>
     <t xml:space="preserve">4.77420043945312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76672315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68073511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66951847076416</t>
+    <t xml:space="preserve">4.7667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68073606491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66951942443848</t>
   </si>
   <si>
     <t xml:space="preserve">4.71064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67325782775879</t>
+    <t xml:space="preserve">4.67325830459595</t>
   </si>
   <si>
     <t xml:space="preserve">4.68447399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62839508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56857681274414</t>
+    <t xml:space="preserve">4.62839555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56857776641846</t>
   </si>
   <si>
     <t xml:space="preserve">4.58727025985718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69568920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56110000610352</t>
+    <t xml:space="preserve">4.69568967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56110048294067</t>
   </si>
   <si>
     <t xml:space="preserve">4.40781688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61344003677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59848594665527</t>
+    <t xml:space="preserve">4.61344051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848546981812</t>
   </si>
   <si>
     <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84523391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.792893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86766624450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78915548324585</t>
+    <t xml:space="preserve">4.84523487091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79289436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86766576766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78915500640869</t>
   </si>
   <si>
     <t xml:space="preserve">4.78167724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77793884277344</t>
+    <t xml:space="preserve">4.77793836593628</t>
   </si>
   <si>
     <t xml:space="preserve">4.87140417098999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83775615692139</t>
+    <t xml:space="preserve">4.83775663375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.68821287155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71812152862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74055290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6022253036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54988384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52371454238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51997518539429</t>
+    <t xml:space="preserve">4.71812057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74055337905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60222482681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54988431930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5237135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51997470855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.48632764816284</t>
@@ -1670,22 +1670,22 @@
     <t xml:space="preserve">4.46015739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64334964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66204309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65456485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76298427581787</t>
+    <t xml:space="preserve">4.64334869384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66204166412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65456533432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76298379898071</t>
   </si>
   <si>
     <t xml:space="preserve">4.73681449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86392688751221</t>
+    <t xml:space="preserve">4.86392736434937</t>
   </si>
   <si>
     <t xml:space="preserve">4.98730087280273</t>
@@ -1700,67 +1700,67 @@
     <t xml:space="preserve">5.21909475326538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22657108306885</t>
+    <t xml:space="preserve">5.22657155990601</t>
   </si>
   <si>
     <t xml:space="preserve">5.18918609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15180015563965</t>
+    <t xml:space="preserve">5.15179967880249</t>
   </si>
   <si>
     <t xml:space="preserve">5.20414018630981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37237739562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16675424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34620714187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09019041061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87335062026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79483938217163</t>
+    <t xml:space="preserve">5.37237787246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34620761871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09018993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87335109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79484033584595</t>
   </si>
   <si>
     <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81353330612183</t>
+    <t xml:space="preserve">5.81353378295898</t>
   </si>
   <si>
     <t xml:space="preserve">5.79110145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80231761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75745344161987</t>
+    <t xml:space="preserve">5.80231666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75745439529419</t>
   </si>
   <si>
     <t xml:space="preserve">5.82474899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87708902359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92195320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98924779891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01167917251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02663421630859</t>
+    <t xml:space="preserve">5.8770899772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92195224761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98924827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01167964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02663373947144</t>
   </si>
   <si>
     <t xml:space="preserve">5.96307706832886</t>
@@ -1775,40 +1775,40 @@
     <t xml:space="preserve">5.93316888809204</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90699815750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94064617156982</t>
+    <t xml:space="preserve">5.90699863433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94064521789551</t>
   </si>
   <si>
     <t xml:space="preserve">6.0789737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9369068145752</t>
+    <t xml:space="preserve">5.93690729141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.95933866500854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89952039718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89578294754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8808274269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94812297821045</t>
+    <t xml:space="preserve">5.8995213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89578247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88082838058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94812250137329</t>
   </si>
   <si>
     <t xml:space="preserve">5.95560026168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97429323196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02114152908325</t>
+    <t xml:space="preserve">5.97429227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02114057540894</t>
   </si>
   <si>
     <t xml:space="preserve">5.9136209487915</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">5.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69473934173584</t>
+    <t xml:space="preserve">5.69474077224731</t>
   </si>
   <si>
     <t xml:space="preserve">5.71778011322021</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">5.70626020431519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76002073287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87522029876709</t>
+    <t xml:space="preserve">5.76002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87522077560425</t>
   </si>
   <si>
     <t xml:space="preserve">5.82146072387695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74850034713745</t>
+    <t xml:space="preserve">5.74850130081177</t>
   </si>
   <si>
     <t xml:space="preserve">5.69858026504517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64481925964355</t>
+    <t xml:space="preserve">5.64482021331787</t>
   </si>
   <si>
     <t xml:space="preserve">5.60642004013062</t>
@@ -1874,37 +1874,37 @@
     <t xml:space="preserve">5.78690052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95970153808594</t>
+    <t xml:space="preserve">5.95970058441162</t>
   </si>
   <si>
     <t xml:space="preserve">6.0557017326355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28226280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17474174499512</t>
+    <t xml:space="preserve">6.28226327896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17474222183228</t>
   </si>
   <si>
     <t xml:space="preserve">6.09026145935059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.128662109375</t>
+    <t xml:space="preserve">6.12866115570068</t>
   </si>
   <si>
     <t xml:space="preserve">6.22850227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19394207000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06722164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10178184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25154256820679</t>
+    <t xml:space="preserve">6.19394159317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06722211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10178136825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25154209136963</t>
   </si>
   <si>
     <t xml:space="preserve">6.17090177536011</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">6.38210296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35522270202637</t>
+    <t xml:space="preserve">6.35522222518921</t>
   </si>
   <si>
     <t xml:space="preserve">6.44738340377808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52802324295044</t>
+    <t xml:space="preserve">6.5280237197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.53954315185547</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">6.62018394470215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64322423934937</t>
+    <t xml:space="preserve">6.64322280883789</t>
   </si>
   <si>
     <t xml:space="preserve">6.62786340713501</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">6.80450439453125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83138465881348</t>
+    <t xml:space="preserve">6.83138513565063</t>
   </si>
   <si>
     <t xml:space="preserve">6.83522415161133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78914356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76610469818115</t>
+    <t xml:space="preserve">6.78914403915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76610517501831</t>
   </si>
   <si>
     <t xml:space="preserve">6.98114490509033</t>
@@ -1979,37 +1979,37 @@
     <t xml:space="preserve">6.98882484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88514423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68930387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6355447769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61634349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54338312149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79298448562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14626550674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570558547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05026626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06946516036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04642534255981</t>
+    <t xml:space="preserve">6.88514566421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6893048286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63554430007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61634302139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79298400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14626502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05026531219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06946468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04642629623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.00802516937256</t>
@@ -2018,25 +2018,25 @@
     <t xml:space="preserve">6.99266481399536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10402536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18082618713379</t>
+    <t xml:space="preserve">7.10402488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18082523345947</t>
   </si>
   <si>
     <t xml:space="preserve">7.10786485671997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0617847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07330513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00034523010254</t>
+    <t xml:space="preserve">7.06178522109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07330560684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07714462280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00034427642822</t>
   </si>
   <si>
     <t xml:space="preserve">6.96578502655029</t>
@@ -2045,28 +2045,28 @@
     <t xml:space="preserve">6.95426464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02722501754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94274473190308</t>
+    <t xml:space="preserve">7.02722454071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94274425506592</t>
   </si>
   <si>
     <t xml:space="preserve">7.04258489608765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09634494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75074338912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93506336212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90434455871582</t>
+    <t xml:space="preserve">7.0963454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75074434280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93506383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90434408187866</t>
   </si>
   <si>
     <t xml:space="preserve">7.02338457107544</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">6.97346448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1577844619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16546535491943</t>
+    <t xml:space="preserve">7.15778493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16546583175659</t>
   </si>
   <si>
     <t xml:space="preserve">7.29602670669556</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">7.16930627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31138706207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27682590484619</t>
+    <t xml:space="preserve">7.3113865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27682685852051</t>
   </si>
   <si>
     <t xml:space="preserve">7.18850517272949</t>
@@ -2102,28 +2102,28 @@
     <t xml:space="preserve">7.17698574066162</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19234561920166</t>
+    <t xml:space="preserve">7.1923451423645</t>
   </si>
   <si>
     <t xml:space="preserve">7.15010547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26914644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210586547852</t>
+    <t xml:space="preserve">7.26914501190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210729598999</t>
   </si>
   <si>
     <t xml:space="preserve">7.43426609039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4573073387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34978532791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42658710479736</t>
+    <t xml:space="preserve">7.45730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34978580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42658567428589</t>
   </si>
   <si>
     <t xml:space="preserve">7.28066539764404</t>
@@ -2132,28 +2132,28 @@
     <t xml:space="preserve">7.11938571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22306537628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11554574966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06562566757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08866453170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98498439788818</t>
+    <t xml:space="preserve">7.2230658531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11554622650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06562471389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08866500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98498487472534</t>
   </si>
   <si>
     <t xml:space="preserve">6.7737832069397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80066347122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77762460708618</t>
+    <t xml:space="preserve">6.80066442489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77762413024902</t>
   </si>
   <si>
     <t xml:space="preserve">6.88898468017578</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">6.84674406051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08098554611206</t>
+    <t xml:space="preserve">7.08098602294922</t>
   </si>
   <si>
     <t xml:space="preserve">7.03106498718262</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">6.75842380523682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81218433380127</t>
+    <t xml:space="preserve">6.81218385696411</t>
   </si>
   <si>
     <t xml:space="preserve">6.81602430343628</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">6.74306440353394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69314432144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7200231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89282512664795</t>
+    <t xml:space="preserve">6.69314384460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72002363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89282464981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.79682445526123</t>
@@ -2216,31 +2216,31 @@
     <t xml:space="preserve">6.70466327667236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67778301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78530406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71234321594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73538398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20386600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05410480499268</t>
+    <t xml:space="preserve">6.67778348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78530359268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71234369277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7353835105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20386648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05410575866699</t>
   </si>
   <si>
     <t xml:space="preserve">7.20770597457886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17314577102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22690582275391</t>
+    <t xml:space="preserve">7.17314624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22690534591675</t>
   </si>
   <si>
     <t xml:space="preserve">7.20002603530884</t>
@@ -2249,19 +2249,19 @@
     <t xml:space="preserve">7.11170530319214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25762557983398</t>
+    <t xml:space="preserve">7.2576265335083</t>
   </si>
   <si>
     <t xml:space="preserve">7.29986619949341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33826732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37282705307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58786678314209</t>
+    <t xml:space="preserve">7.33826589584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37282609939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58786630630493</t>
   </si>
   <si>
     <t xml:space="preserve">7.56098747253418</t>
@@ -2273,55 +2273,55 @@
     <t xml:space="preserve">7.83362817764282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96418857574463</t>
+    <t xml:space="preserve">7.96418809890747</t>
   </si>
   <si>
     <t xml:space="preserve">8.00258922576904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17922782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8643479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77218675613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73378562927246</t>
+    <t xml:space="preserve">8.17922878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86434888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77218723297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73378753662109</t>
   </si>
   <si>
     <t xml:space="preserve">7.49186706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36130571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56482744216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858701705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68002843856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36898708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91970491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89442157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27458238601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77154064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26690196990967</t>
+    <t xml:space="preserve">7.36130666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56482696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68002653121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3689866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91970539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8944206237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.274582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77153968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26690244674683</t>
   </si>
   <si>
     <t xml:space="preserve">6.33602285385132</t>
@@ -2330,67 +2330,67 @@
     <t xml:space="preserve">7.15394496917725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21922445297241</t>
+    <t xml:space="preserve">7.21922588348389</t>
   </si>
   <si>
     <t xml:space="preserve">7.58018684387207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59938669204712</t>
+    <t xml:space="preserve">7.59938812255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.78754806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27178001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88021850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57022857666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64364767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13718128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35335636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72860431671143</t>
+    <t xml:space="preserve">8.2717809677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8802170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57022905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64364671707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13718032836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35335731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72860527038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.03043460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95701694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70413303375244</t>
+    <t xml:space="preserve">8.95701789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70413208007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.75307750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99442434310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8312726020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74969625473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81903553009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79864168167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87613725662231</t>
+    <t xml:space="preserve">7.99442338943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83127212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74969673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81903457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79864072799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87613868713379</t>
   </si>
   <si>
     <t xml:space="preserve">7.80679893493652</t>
@@ -2399,118 +2399,118 @@
     <t xml:space="preserve">7.68035697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50904703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70482969284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75377416610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89653205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9454779624939</t>
+    <t xml:space="preserve">7.50904846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70482873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75377559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89653253555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94547843933105</t>
   </si>
   <si>
     <t xml:space="preserve">7.8557448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94010925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98146200180054</t>
+    <t xml:space="preserve">7.94010877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9814624786377</t>
   </si>
   <si>
     <t xml:space="preserve">7.85739898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78709602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75814819335938</t>
+    <t xml:space="preserve">7.78709554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75814771652222</t>
   </si>
   <si>
     <t xml:space="preserve">7.69611549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5431022644043</t>
+    <t xml:space="preserve">7.54310274124146</t>
   </si>
   <si>
     <t xml:space="preserve">7.600998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58032131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51829051971436</t>
+    <t xml:space="preserve">7.58032274246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5182900428772</t>
   </si>
   <si>
     <t xml:space="preserve">7.73333501815796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65062522888184</t>
+    <t xml:space="preserve">7.65062570571899</t>
   </si>
   <si>
     <t xml:space="preserve">7.55551052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53483247756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45212268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49347829818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63408231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40249729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40663242340088</t>
+    <t xml:space="preserve">7.53483152389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45212316513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4934778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63408279418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40249681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40663146972656</t>
   </si>
   <si>
     <t xml:space="preserve">7.36941289901733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58445692062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48520565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64235305786133</t>
+    <t xml:space="preserve">7.58445739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48520660400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64235401153564</t>
   </si>
   <si>
     <t xml:space="preserve">7.52656126022339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75401163101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72919940948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37354850769043</t>
+    <t xml:space="preserve">7.75401210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72919893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37354803085327</t>
   </si>
   <si>
     <t xml:space="preserve">7.44385147094727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34460020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39009046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37768411636353</t>
+    <t xml:space="preserve">7.34459972381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37768459320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.73746919631958</t>
@@ -2522,43 +2522,43 @@
     <t xml:space="preserve">7.77468872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72506380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68784475326538</t>
+    <t xml:space="preserve">7.72506427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68784427642822</t>
   </si>
   <si>
     <t xml:space="preserve">7.67543745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62167692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70438575744629</t>
+    <t xml:space="preserve">7.62167644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70438623428345</t>
   </si>
   <si>
     <t xml:space="preserve">7.71265745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62581348419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52242517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4231743812561</t>
+    <t xml:space="preserve">7.62581300735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52242469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42317485809326</t>
   </si>
   <si>
     <t xml:space="preserve">7.3363299369812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36527729034424</t>
+    <t xml:space="preserve">7.3652777671814</t>
   </si>
   <si>
     <t xml:space="preserve">7.25775480270386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08406543731689</t>
+    <t xml:space="preserve">7.08406448364258</t>
   </si>
   <si>
     <t xml:space="preserve">7.02203273773193</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">6.98067808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06752347946167</t>
+    <t xml:space="preserve">7.06752395629883</t>
   </si>
   <si>
     <t xml:space="preserve">7.09647178649902</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">7.17091083526611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03443956375122</t>
+    <t xml:space="preserve">7.03444004058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.98894882202148</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">6.93932437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05511713027954</t>
+    <t xml:space="preserve">7.0551176071167</t>
   </si>
   <si>
     <t xml:space="preserve">6.91864681243896</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">6.78217554092407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96413707733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30324554443359</t>
+    <t xml:space="preserve">6.96413660049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.947594165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30324506759644</t>
   </si>
   <si>
     <t xml:space="preserve">7.43558073043823</t>
@@ -2651,37 +2651,37 @@
     <t xml:space="preserve">7.60927057266235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71679306030273</t>
+    <t xml:space="preserve">7.71679210662842</t>
   </si>
   <si>
     <t xml:space="preserve">7.72092914581299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84085702896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81190919876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82845067977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83672285079956</t>
+    <t xml:space="preserve">7.84085750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81190776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82845115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8367223739624</t>
   </si>
   <si>
     <t xml:space="preserve">7.96078538894653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84912824630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66716718673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67957353591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61754131317139</t>
+    <t xml:space="preserve">7.84912729263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66716766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67957258224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61754083633423</t>
   </si>
   <si>
     <t xml:space="preserve">7.60513496398926</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">7.59686422348022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54723882675171</t>
+    <t xml:space="preserve">7.57205104827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54723787307739</t>
   </si>
   <si>
     <t xml:space="preserve">7.55137395858765</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">8.03522396087646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20064353942871</t>
+    <t xml:space="preserve">8.20064258575439</t>
   </si>
   <si>
     <t xml:space="preserve">8.15515232086182</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">8.14688205718994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31230068206787</t>
+    <t xml:space="preserve">8.31229972839355</t>
   </si>
   <si>
     <t xml:space="preserve">8.56042957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40328025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41155242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28748893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33711433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61005592346191</t>
+    <t xml:space="preserve">8.40328121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41155338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28748798370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33711338043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6100549697876</t>
   </si>
   <si>
     <t xml:space="preserve">8.68449401855469</t>
@@ -2741,43 +2741,43 @@
     <t xml:space="preserve">8.55215835571289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25026988983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59351348876953</t>
+    <t xml:space="preserve">8.25026798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59351253509521</t>
   </si>
   <si>
     <t xml:space="preserve">8.88299560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92435073852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99051856994629</t>
+    <t xml:space="preserve">8.92435169219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99051761627197</t>
   </si>
   <si>
     <t xml:space="preserve">8.8002872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81682872772217</t>
+    <t xml:space="preserve">8.81682968139648</t>
   </si>
   <si>
     <t xml:space="preserve">8.7341194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365581512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10966205596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21305084228516</t>
+    <t xml:space="preserve">8.35365676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10966300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21304988861084</t>
   </si>
   <si>
     <t xml:space="preserve">8.18823719024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13860988616943</t>
+    <t xml:space="preserve">8.13861083984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.32057285308838</t>
@@ -2789,55 +2789,55 @@
     <t xml:space="preserve">8.304030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22545623779297</t>
+    <t xml:space="preserve">8.22545528411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.27921772003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2585391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23786354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95665121078491</t>
+    <t xml:space="preserve">8.25854015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2378625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95664978027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.86980533599854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85326290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89875459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74574136734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66303253173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65476036071777</t>
+    <t xml:space="preserve">7.85326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89875411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74574184417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6630334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65475988388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.51415491104126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44798612594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33219385147095</t>
+    <t xml:space="preserve">7.44798707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33219337463379</t>
   </si>
   <si>
     <t xml:space="preserve">7.35287141799927</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46866416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43971633911133</t>
+    <t xml:space="preserve">7.46866369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43971538543701</t>
   </si>
   <si>
     <t xml:space="preserve">7.43144416809082</t>
@@ -2846,16 +2846,16 @@
     <t xml:space="preserve">7.50588321685791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82017993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38181972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20399475097656</t>
+    <t xml:space="preserve">7.82017946243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76228284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38181924819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2039942741394</t>
   </si>
   <si>
     <t xml:space="preserve">7.06338739395142</t>
@@ -2867,31 +2867,31 @@
     <t xml:space="preserve">7.09233665466309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12542009353638</t>
+    <t xml:space="preserve">7.12542057037354</t>
   </si>
   <si>
     <t xml:space="preserve">7.28670358657837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12955570220947</t>
+    <t xml:space="preserve">7.12955617904663</t>
   </si>
   <si>
     <t xml:space="preserve">6.93518924713135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04271078109741</t>
+    <t xml:space="preserve">7.04271125793457</t>
   </si>
   <si>
     <t xml:space="preserve">7.16263914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29911041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22053480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53896760940552</t>
+    <t xml:space="preserve">7.2991099357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22053527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">7.70025110244751</t>
@@ -2903,133 +2903,133 @@
     <t xml:space="preserve">8.03108882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88386535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01123905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8193531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77138042449951</t>
+    <t xml:space="preserve">7.88386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01123809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81935214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77138090133667</t>
   </si>
   <si>
     <t xml:space="preserve">7.79453945159912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70190525054932</t>
+    <t xml:space="preserve">7.70190477371216</t>
   </si>
   <si>
     <t xml:space="preserve">7.86732339859009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81273555755615</t>
+    <t xml:space="preserve">7.81273460388184</t>
   </si>
   <si>
     <t xml:space="preserve">7.79619312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69694185256958</t>
+    <t xml:space="preserve">7.6969428062439</t>
   </si>
   <si>
     <t xml:space="preserve">8.05590152740479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97319269180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99635028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01785564422607</t>
+    <t xml:space="preserve">7.97319316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99635076522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01785469055176</t>
   </si>
   <si>
     <t xml:space="preserve">8.05259323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9996600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02281761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05093860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93845319747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95003366470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88055658340454</t>
+    <t xml:space="preserve">7.99965953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02281665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05093955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93845415115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95003414154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88055753707886</t>
   </si>
   <si>
     <t xml:space="preserve">7.86897802352905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82431554794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90371656417847</t>
+    <t xml:space="preserve">7.8243145942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90371608734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.01289176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84416484832764</t>
+    <t xml:space="preserve">7.84416532516479</t>
   </si>
   <si>
     <t xml:space="preserve">7.81604433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63904523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66055154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73498964309692</t>
+    <t xml:space="preserve">7.63904619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66055011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73498868942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.79480361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72473526000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78967714309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80847549438477</t>
+    <t xml:space="preserve">7.72473478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78967761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80847597122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.85291004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8238582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77258634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71960830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76404237747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8922176361084</t>
+    <t xml:space="preserve">7.82385873794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77258682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71960783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76404285430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89221811294556</t>
   </si>
   <si>
     <t xml:space="preserve">7.94006967544556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09046363830566</t>
+    <t xml:space="preserve">7.98963117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09046459197998</t>
   </si>
   <si>
     <t xml:space="preserve">8.09388160705566</t>
@@ -3041,22 +3041,22 @@
     <t xml:space="preserve">8.24940204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2869987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41517543792725</t>
+    <t xml:space="preserve">8.28700065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41517448425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.39808559417725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38099384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46302700042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44252014160156</t>
+    <t xml:space="preserve">8.38099479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46302795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44251918792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.21180248260498</t>
@@ -3077,16 +3077,16 @@
     <t xml:space="preserve">8.12806129455566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09900760650635</t>
+    <t xml:space="preserve">8.09900856018066</t>
   </si>
   <si>
     <t xml:space="preserve">8.12293434143066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11951637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22718524932861</t>
+    <t xml:space="preserve">8.11951541900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2271842956543</t>
   </si>
   <si>
     <t xml:space="preserve">8.36903190612793</t>
@@ -3101,10 +3101,10 @@
     <t xml:space="preserve">8.35877704620361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48011779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45619297027588</t>
+    <t xml:space="preserve">8.48011875152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45619201660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.44081020355225</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">8.46986389160156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40663146972656</t>
+    <t xml:space="preserve">8.40663051605225</t>
   </si>
   <si>
     <t xml:space="preserve">8.37245082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46644592285156</t>
+    <t xml:space="preserve">8.46644687652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.45960998535156</t>
@@ -3131,19 +3131,19 @@
     <t xml:space="preserve">8.28358173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25965595245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32630729675293</t>
+    <t xml:space="preserve">8.25965690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32630634307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.24256610870361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1502799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2186393737793</t>
+    <t xml:space="preserve">8.15027904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21863842010498</t>
   </si>
   <si>
     <t xml:space="preserve">8.17420482635498</t>
@@ -3155,58 +3155,58 @@
     <t xml:space="preserve">8.33997917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35365009307861</t>
+    <t xml:space="preserve">8.35365104675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.45277309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46473693847656</t>
+    <t xml:space="preserve">8.46473789215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.50404453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42030334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50233459472656</t>
+    <t xml:space="preserve">8.42030239105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50233554840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.66896343231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64760112762451</t>
+    <t xml:space="preserve">8.6476001739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.6006031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63478374481201</t>
+    <t xml:space="preserve">8.6347827911377</t>
   </si>
   <si>
     <t xml:space="preserve">8.6262378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61769390106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54164218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62196636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69032669067383</t>
+    <t xml:space="preserve">8.6176929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5416431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6219654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69032764434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.6048755645752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63051223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5382251739502</t>
+    <t xml:space="preserve">8.63051128387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53822422027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.5536060333252</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">8.42372035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49208068847656</t>
+    <t xml:space="preserve">8.49208164215088</t>
   </si>
   <si>
     <t xml:space="preserve">8.54506015777588</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">8.40492153167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30579853057861</t>
+    <t xml:space="preserve">8.30579948425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.49720859527588</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">8.34681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32459831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2323112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21522235870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20838451385498</t>
+    <t xml:space="preserve">8.32459735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23231029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21522045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2083854675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.17933082580566</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">8.22205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07166385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08875370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99475765228271</t>
+    <t xml:space="preserve">8.07166481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08875465393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99475812911987</t>
   </si>
   <si>
     <t xml:space="preserve">8.2391471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33485221862793</t>
+    <t xml:space="preserve">8.33485126495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.40150356292725</t>
@@ -3293,37 +3293,37 @@
     <t xml:space="preserve">8.25452899932861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1776237487793</t>
+    <t xml:space="preserve">8.17762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">8.26478290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16565895080566</t>
+    <t xml:space="preserve">8.36048698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25111103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16565990447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.31605243682861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2169303894043</t>
+    <t xml:space="preserve">8.21692943572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.16053295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43055725097656</t>
+    <t xml:space="preserve">8.43055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">8.32972526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45106506347656</t>
+    <t xml:space="preserve">8.45106410980225</t>
   </si>
   <si>
     <t xml:space="preserve">8.44935512542725</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">8.50575256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49891757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47669982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02358436584473</t>
+    <t xml:space="preserve">8.4989185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47670078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02358341217041</t>
   </si>
   <si>
     <t xml:space="preserve">9.08767223358154</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">8.86977291107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80141258239746</t>
+    <t xml:space="preserve">8.80141162872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.78004932403564</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">8.66041851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82704734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71168994903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65614700317383</t>
+    <t xml:space="preserve">8.82704639434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71168899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65614604949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.72023391723633</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">8.72450637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63905620574951</t>
+    <t xml:space="preserve">8.6390552520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.60914707183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69459915161133</t>
+    <t xml:space="preserve">8.69460010528564</t>
   </si>
   <si>
     <t xml:space="preserve">8.75441455841064</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">8.88259029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92531585693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94667816162109</t>
+    <t xml:space="preserve">8.92531490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94667911529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.95522308349609</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">8.92104244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98940372467041</t>
+    <t xml:space="preserve">8.98940467834473</t>
   </si>
   <si>
     <t xml:space="preserve">9.06630897521973</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">9.20302963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212928771973</t>
+    <t xml:space="preserve">9.03212833404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.98513126373291</t>
@@ -3437,25 +3437,25 @@
     <t xml:space="preserve">8.5877857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2613639831543</t>
+    <t xml:space="preserve">8.28870868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26136493682861</t>
   </si>
   <si>
     <t xml:space="preserve">8.15882396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08020973205566</t>
+    <t xml:space="preserve">8.08021068572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.20667552947998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35706806182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78455066680908</t>
+    <t xml:space="preserve">8.35706901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78454971313477</t>
   </si>
   <si>
     <t xml:space="preserve">7.81873083114624</t>
@@ -3464,19 +3464,19 @@
     <t xml:space="preserve">7.81360387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81018543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15540599822998</t>
+    <t xml:space="preserve">7.81018590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15540504455566</t>
   </si>
   <si>
     <t xml:space="preserve">8.12635231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88025426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71106243133545</t>
+    <t xml:space="preserve">7.8802547454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71106195449829</t>
   </si>
   <si>
     <t xml:space="preserve">7.60168552398682</t>
@@ -3488,19 +3488,19 @@
     <t xml:space="preserve">7.54699659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45129251480103</t>
-  </si>
- 